--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -4439,9 +4439,9 @@
       <c r="L4" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-2. 4.5 g ile 5g arasındaki hız farkı : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
-3. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi
-4. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. 4.5 g ile 5g arasındaki : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -4467,11 +4467,11 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>• 192.168.1.1 ve 192.168.0.1 farkı; 
-  • marka bazında varsayılan kullanıcı adı ve şifre tablosu; 
-  • arayüze girilemediğinde kontrol listesi; 
-  • WiFi adı ve şifresi değiştirme; 
-  • modem sıfırlama.</t>
+          <t>1. 192.168.1.1 ve 192.168.0.1 farkı açıklanır
+2. Marka bazında varsayılan kullanıcı adı ve şifre tablosu verilir
+3. Arayüze girilemediğinde kontrol listesi verilir
+4. WiFi adı ve şifresi değiştirme adım adım anlatılır
+5. Modem sıfırlama adım adım anlatılır</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
@@ -4575,9 +4575,9 @@
       <c r="L5" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-3. turkcell 5g : https://www.turkcell.com.tr/blog/5g-ile-hayatimiza-yeni-neler-giriyor-etkilesim-cagi-ve-fwa
-4. turkcell rahat paket nedir : https://www.turkcell.com.tr/blog/turkcell-rahat-paketleri-hem-faturali-hem-faturasiz-taahhutsuz-ozgurluk</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -4620,11 +4620,11 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>• Numara gizleme kodu ve operatör ayarı; 
-  • gizli numaradan gelen aramayı engelleme; 
-  • iPhone ve Android ayrı adımlar; 
-  • operatör servisiyle kalıcı engelleme; 
-  • yasal sınırlar.</t>
+          <t>1. Numara gizleme kodu ve operatör ayarı açıklanır
+2. Gizli numaradan gelen aramayı engelleme adım adım anlatılır
+3. IPhone ve Android ayrı adımlar adım adım anlatılır
+4. Operatör servisiyle kalıcı engelleme adım adım anlatılır
+5. Yasal sınırlar açıklanır</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -4735,9 +4735,9 @@
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-3. turkcell 5g : https://www.turkcell.com.tr/blog/5g-ile-hayatimiza-yeni-neler-giriyor-etkilesim-cagi-ve-fwa
-4. turkcell rahat paket nedir : https://www.turkcell.com.tr/blog/turkcell-rahat-paketleri-hem-faturali-hem-faturasiz-taahhutsuz-ozgurluk</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -4797,11 +4797,11 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>• Kayıt ücreti ve geçerli yılın harç tutarı tablo hâlinde; 
-  • e-Devlet ve BTK üzerinden sorgulama adımları; 
-  • kayıtsız telefonun kaç gün kullanılabildiği; 
-  • IMEI numarasının telefondan öğrenilmesi; 
-  • kayıt sonrası bekleme süresi.</t>
+          <t>1. Kayıt ücreti ve geçerli yılın harç tutarı tablo hâlinde açıklanır
+2. E-Devlet ve BTK üzerinden sorgulama adımları adım adım anlatılır
+3. Kayıtsız telefonun kaç gün kullanılabildiği açıklanır
+4. IMEI numarasının telefondan öğrenilmesi adım adım anlatılır
+5. Kayıt sonrası bekleme süresi açıklanır</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="115" customHeight="1">
+    <row r="7" ht="128.5" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Google Güvenli Arama: Açma, Kapatma ve Aile Filtresi</t>
@@ -4894,9 +4894,9 @@
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>1. turkcell chatgpt : https://www.turkcell.com.tr/blog/chatgpt-yeni-google-mi-internette-arama-aliskanliklari-nasil-degisiyor
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-3. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-4. turkcell 5g : https://www.turkcell.com.tr/blog/5g-ile-hayatimiza-yeni-neler-giriyor-etkilesim-cagi-ve-fwa</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -4956,10 +4956,10 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>• Google güvenli aramanın ne yaptığı; 
-  • açma ve kapatma adımları; 
-  • kilitli olduğunda yapılabilecekler; 
-  • çocuk hesaplarında aile bağlantısı ayarı.</t>
+          <t>1. Google güvenli aramanın ne yaptığı açıklanır
+2. Açma ve kapatma adımları adım adım anlatılır
+3. Kilitli olduğunda yapılabilecekler açıklanır
+4. Çocuk hesaplarında aile bağlantısı ayarı açıklanır</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -5055,9 +5055,9 @@
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-3. turkcell 5g : https://www.turkcell.com.tr/blog/5g-ile-hayatimiza-yeni-neler-giriyor-etkilesim-cagi-ve-fwa
-4. turkcell rahat paket nedir : https://www.turkcell.com.tr/blog/turkcell-rahat-paketleri-hem-faturali-hem-faturasiz-taahhutsuz-ozgurluk</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -5083,10 +5083,10 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>• PUK kodunun nereden öğrenileceği; 
-  • PIN değiştirme ve kaldırma; 
-  • üç kez yanlış PIN girildiğinde izlenecek yol; 
-  • SIM blokesinin kaldırılması.</t>
+          <t>1. PUK kodunun nereden öğrenileceği açıklanır
+2. PIN değiştirme ve kaldırma adım adım anlatılır
+3. Üç kez yanlış PIN girildiğinde izlenecek yol açıklanır
+4. SIM blokesinin kaldırılması adım adım anlatılır</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="115" customHeight="1">
+    <row r="9" ht="128.5" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Ekran Yansıtma: Telefondan Televizyona Görüntü Aktarma</t>
@@ -5179,9 +5179,9 @@
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -5207,10 +5207,10 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>• Kablosuz yansıtma için gereken koşullar; 
-  • iPhone ve Android adımları; 
-  • kablo ile yansıtma; 
-  • televizyon bulunamadığında kontrol listesi.</t>
+          <t>1. Kablosuz yansıtma için gereken koşullar açıklanır
+2. IPhone ve Android adımları adım adım anlatılır
+3. Kablo ile yansıtma adım adım anlatılır
+4. Televizyon bulunamadığında kontrol listesi verilir</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -5301,10 +5301,10 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-2. 4.5 g ile 5g arasındaki hız farkı : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
-3. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi
-4. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu</t>
+          <t>1. mac adresi nedir : https://www.turkcell.com.tr/blog/mac-adresi-her-cihazin-kendine-ozgu-dijital-imzasi
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -5330,10 +5330,10 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>• IP adresinin ne olduğu; 
-  • kendi IP adresini öğrenme; 
-  • statik ve dinamik IP farkı; 
-  • IP adresi değiştirme yolları ve sınırları.</t>
+          <t>1. IP adresinin ne olduğu açıklanır
+2. Kendi IP adresini öğrenme adım adım anlatılır
+3. Statik ve dinamik IP farkı açıklanır
+4. IP adresi değiştirme yolları ve sınırları açıklanır</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="115" customHeight="1">
+    <row r="11" ht="128.5" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>İndirilenler Klasörü: Telefonda ve Bilgisayarda Dosya Bulma</t>
@@ -5425,10 +5425,10 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
-2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+          <t>1. wifi direct nedir : https://www.turkcell.com.tr/blog/wi-fi-direct-ile-dosya-paylasimi
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. ftp nedir : https://www.turkcell.com.tr/blog/ftp-nedir-dosya-transfer-protokolunun-temel-prensipleri
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -5454,10 +5454,10 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>• Android ve iPhone'da indirilenler klasörünün yeri; 
-  • tarayıcıya göre değişen konumlar; 
-  • indirilen dosyanın bulunamaması durumu; 
-  • depolama temizliği.</t>
+          <t>1. Android ve iPhone'da indirilenler klasörünün yeri açıklanır
+2. Tarayıcıya göre değişen konumlar açıklanır
+3. Indirilen dosyanın bulunamaması durumu açıklanır
+4. Depolama temizliği açıklanır</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="115" customHeight="1">
+    <row r="12" ht="128.5" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Instagram Hesabı: Dondurma, Giriş Sorunları ve Açılmama Nedenleri</t>
@@ -5551,9 +5551,9 @@
       <c r="L12" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -5596,11 +5596,11 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>• Hesabı geçici dondurma adımları ve kalıcı silmeden farkı; 
-  • dondurulan hesabın geri açılması; 
-  • uygulama açılmadığında kontrol listesi; 
-  • giriş yapılamadığında doğrulama adımları; 
-  • gönderilen takip isteklerinin görülmesi.</t>
+          <t>1. Hesabı geçici dondurma adımları ve kalıcı silmeden farkı açıklanır
+2. Dondurulan hesabın geri açılması adım adım anlatılır
+3. Uygulama açılmadığında kontrol listesi verilir
+4. Giriş yapılamadığında doğrulama adımları adım adım anlatılır
+5. Gönderilen takip isteklerinin görülmesi adım adım anlatılır</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="115" customHeight="1">
+    <row r="13" ht="128.5" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Spam Ne Demek? Spam Mesaj ve Aramaları Engelleme</t>
@@ -5687,10 +5687,10 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
-2. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-3. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir
-4. wlan nedir : https://www.turkcell.com.tr/blog/wlan-nedir-kablosuz-aglarin-calisma-mantigi-ve-guvenlik-rehberi</t>
+          <t>1. phishing nedir : https://www.turkcell.com.tr/blog/bu-mesaj-tuzak-olabilir-phishing-nedir-ve-nasil-anlasilir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -5716,9 +5716,9 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>• Spam tanımı; 
-  • spam mesaj ve arama engelleme adımları; 
-  • operatör tarafındaki engelleme servisleri.</t>
+          <t>1. Spam tanımı açıklanır
+2. Spam mesaj ve arama engelleme adımları adım adım anlatılır
+3. Operatör tarafındaki engelleme servisleri açıklanır</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="115" customHeight="1">
+    <row r="14" ht="128.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
@@ -5811,10 +5811,10 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>1. kotlin nedir kotlin : https://www.turkcell.com.tr/blog/kotlin-nedir-kotlin-ne-ise-yarar
-2. turkcell hosting : https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar
-3. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi
-4. iss : https://www.turkcell.com.tr/blog/iss-internet-servis-saglayicisi-nedir-ne-ise-yarar</t>
+          <t>1. kuantum bilgisayar : https://www.turkcell.com.tr/blog/kuantum-bilgisayar-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -5840,11 +5840,11 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>• SSD ile HDD farkı; 
-  • RAM'in görevi ve yeterli kapasite; 
-  • ekran kartının ne işe yaradığı; 
-  • anakartın rolü; 
-  • bilgisayar yavaşladığında hangi bileşene bakılacağı.</t>
+          <t>1. SSD ile HDD farkı açıklanır
+2. RAM'in görevi ve yeterli kapasite açıklanır
+3. Ekran kartının ne işe yaradığı açıklanır
+4. Anakartın rolü açıklanır
+5. Bilgisayar yavaşladığında hangi bileşene bakılacağı açıklanır</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="115" customHeight="1">
+    <row r="15" ht="128.5" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>E-İmza Nasıl Alınır?</t>
@@ -5931,9 +5931,9 @@
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-3. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir
-4. wlan nedir : https://www.turkcell.com.tr/blog/wlan-nedir-kablosuz-aglarin-calisma-mantigi-ve-guvenlik-rehberi</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -5959,9 +5959,9 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>• E-imza tanımı; 
-  • başvuru adımları; 
-  • mobil imza ile farkı.</t>
+          <t>1. E-imza tanımı açıklanır
+2. Başvuru adımları adım adım anlatılır
+3. Mobil imza ile farkı açıklanır</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -6050,9 +6050,9 @@
       <c r="L16" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-3. turkcell 5g : https://www.turkcell.com.tr/blog/5g-ile-hayatimiza-yeni-neler-giriyor-etkilesim-cagi-ve-fwa
-4. turkcell rahat paket nedir : https://www.turkcell.com.tr/blog/turkcell-rahat-paketleri-hem-faturali-hem-faturasiz-taahhutsuz-ozgurluk</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -6062,10 +6062,10 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>• Taahhüdün tanımı; 
-  • taahhütlü ve taahhütsüz farkı; 
-  • taahhüt süresi dolmadan çıkışta ne olduğu; 
-  • taahhüt süresinin öğrenilmesi.</t>
+          <t>1. Taahhüdün tanımı açıklanır
+2. Taahhütlü ve taahhütsüz farkı açıklanır
+3. Taahhüt süresi dolmadan çıkışta ne olduğu açıklanır
+4. Taahhüt süresinin öğrenilmesi adım adım anlatılır</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="115" customHeight="1">
+    <row r="17" ht="128.5" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Konum Paylaşma ve Numaradan Konum Bulma</t>
@@ -6158,9 +6158,9 @@
       <c r="L17" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -6186,10 +6186,10 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>• WhatsApp, Google Haritalar ve iMessage üzerinden konum paylaşma; 
-  • canlı konum paylaşımı süresi; 
-  • numaradan konum bulmanın gerçekte mümkün olup olmadığı; 
-  • konum servislerinin pil etkisi.</t>
+          <t>1. WhatsApp, Google Haritalar ve iMessage üzerinden konum paylaşma adım adım anlatılır
+2. Canlı konum paylaşımı süresi açıklanır
+3. Numaradan konum bulmanın gerçekte mümkün olup olmadığı açıklanır
+4. Konum servislerinin pil etkisi açıklanır</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -6221,7 +6221,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="115" customHeight="1">
+    <row r="18" ht="128.5" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Telefondan Telefona Veri Aktarma: Android, iPhone ve Numara Taşıma</t>
@@ -6282,9 +6282,9 @@
       <c r="L18" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -6310,11 +6310,11 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>• Android'den iPhone'a aktarma; 
-  • iPhone'dan iPhone'a hızlı başlangıç; 
-  • Android'den Android'e aktarma; 
-  • WhatsApp geçmişinin taşınması; 
-  • aktarma sırasında sık karşılaşılan durumlar.</t>
+          <t>1. Android'den iPhone'a aktarma adım adım anlatılır
+2. IPhone'dan iPhone'a hızlı başlangıç açıklanır
+3. Android'den Android'e aktarma adım adım anlatılır
+4. WhatsApp geçmişinin taşınması adım adım anlatılır
+5. Aktarma sırasında sık karşılaşılan durumlar açıklanır</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -6346,7 +6346,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="115" customHeight="1">
+    <row r="19" ht="128.5" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Chrome Eklentisi Nasıl Eklenir ve Kaldırılır?</t>
@@ -6405,9 +6405,9 @@
       <c r="L19" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -6433,10 +6433,10 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>• Eklentinin Chrome Web Mağazası üzerinden eklenmesi; 
-  • eklentinin kaldırılması ve devre dışı bırakılması; 
-  • eklenti izinlerinin görülmesi; 
-  • güvenilir eklentinin nasıl ayırt edildiği.</t>
+          <t>1. Eklentinin Chrome Web Mağazası üzerinden eklenmesi adım adım anlatılır
+2. Eklentinin kaldırılması ve devre dışı bırakılması adım adım anlatılır
+3. Eklenti izinlerinin görülmesi adım adım anlatılır
+4. Güvenilir eklentinin nasıl ayırt edildiği açıklanır</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="115" customHeight="1">
+    <row r="20" ht="142" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>E-Posta Kurulumu ve Yönetimi: Hesap Açma, Aktarma, Güvenlik</t>
@@ -6525,10 +6525,10 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
-2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+          <t>1. bulut bilişim teknolojisinin sunduğu avantajlardan : https://www.turkcell.com.tr/blog/bulut-teknolojisinin-sagladigi-guvenlik-avantajlari
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -6554,10 +6554,10 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>• E-posta adresi oluşturma adımları; 
-  • telefonda hesap kurulumu; 
-  • e-posta yazarken dikkat edilecekler; 
-  • iki adımlı doğrulama.</t>
+          <t>1. E-posta adresi oluşturma adımları adım adım anlatılır
+2. Telefonda hesap kurulumu adım adım anlatılır
+3. E-posta yazarken dikkat edilecekler açıklanır
+4. Iki adımlı doğrulama adım adım anlatılır</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="115" customHeight="1">
+    <row r="21" ht="128.5" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Telefon Güncellemesi Nasıl Yapılır?</t>
@@ -6647,9 +6647,9 @@
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -6675,10 +6675,10 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>• Android ve iOS için güncelleme adımları; 
-  • güncelleme görünmüyorsa yapılabilecekler; 
-  • güncelleme öncesi yedekleme; 
-  • depolama alanı yetmediğinde izlenecek yol.</t>
+          <t>1. Android ve iOS için güncelleme adımları adım adım anlatılır
+2. Güncelleme görünmüyorsa yapılabilecekler açıklanır
+3. Güncelleme öncesi yedekleme adım adım anlatılır
+4. Depolama alanı yetmediğinde izlenecek yol açıklanır</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="115" customHeight="1">
+    <row r="22" ht="128.5" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ekran Görüntüsü Alma: Bilgisayar, Telefon ve Kısayollar</t>
@@ -6772,9 +6772,9 @@
       <c r="L22" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
-2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. kuantum bilgisayar : https://www.turkcell.com.tr/blog/kuantum-bilgisayar-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -6817,11 +6817,11 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>• Windows'ta üç yöntem: PrtScn, Windows+Shift+S, Ekran Alıntısı Aracı; 
-  • Mac kısayolları; 
-  • telefonda ekran görüntüsü alma; 
-  • kısayol tablosu; 
-  • görüntünün kaydedildiği klasör.</t>
+          <t>1. Windows'ta üç yöntem: PrtScn, Windows+Shift+S, Ekran Alıntısı Aracı açıklanır
+2. Mac kısayolları adım adım anlatılır
+3. Telefonda ekran görüntüsü alma adım adım anlatılır
+4. Kısayol tablosu verilir
+5. Görüntünün kaydedildiği klasör açıklanır</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -6910,9 +6910,9 @@
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-3. turkcell 5g : https://www.turkcell.com.tr/blog/5g-ile-hayatimiza-yeni-neler-giriyor-etkilesim-cagi-ve-fwa
-4. turkcell rahat paket nedir : https://www.turkcell.com.tr/blog/turkcell-rahat-paketleri-hem-faturali-hem-faturasiz-taahhutsuz-ozgurluk</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -6938,10 +6938,10 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>• eSIM ile fiziksel SIM farkı; 
-  • eSIM destekleyen telefon listesi; 
-  • mevcut hattı eSIM'e taşıma adımları; 
-  • yurt dışında eSIM kullanımı.</t>
+          <t>1. ESIM ile fiziksel SIM farkı açıklanır
+2. ESIM destekleyen telefon listesi verilir
+3. Mevcut hattı eSIM'e taşıma adımları adım adım anlatılır
+4. Yurt dışında eSIM kullanımı açıklanır</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="115" customHeight="1">
+    <row r="24" ht="128.5" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Telefon Nasıl Sıfırlanır?</t>
@@ -7030,9 +7030,9 @@
       <c r="L24" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -7042,10 +7042,10 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>• Sıfırlama öncesi yedekleme; 
-  • Android'de fabrika ayarlarına dönüş adımları; 
-  • iPhone'da sıfırlama adımları; 
-  • sıfırlama sonrası hesap doğrulama.</t>
+          <t>1. Sıfırlama öncesi yedekleme adım adım anlatılır
+2. Android'de fabrika ayarlarına dönüş adımları adım adım anlatılır
+3. IPhone'da sıfırlama adımları adım adım anlatılır
+4. Sıfırlama sonrası hesap doğrulama adım adım anlatılır</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -7077,7 +7077,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="115" customHeight="1">
+    <row r="25" ht="128.5" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Deepfake Nedir ve Nasıl Anlaşılır?</t>
@@ -7132,9 +7132,9 @@
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
-3. ai agent nedir : https://www.turkcell.com.tr/blog/yapay-zeka-ajani-ai-agent-nedir-nasil-calisir
-4. yapay zeka : https://www.turkcell.com.tr/blog/yapay-zeka-cagi-nasil-calisir-hayati-nasil-donusturur</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -7160,9 +7160,9 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>• Deepfake tanımı; 
-  • sahte içeriğin anlaşılma yolları; 
-  • dolandırıcılık senaryoları.</t>
+          <t>1. Deepfake tanımı açıklanır
+2. Sahte içeriğin anlaşılma yolları adım adım anlatılır
+3. Dolandırıcılık senaryoları açıklanır</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -7194,7 +7194,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="115" customHeight="1">
+    <row r="26" ht="128.5" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Yenilenmiş Telefon: Garanti, Kalite Sınıfları ve Satın Alma</t>
@@ -7252,9 +7252,9 @@
       <c r="L26" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -7280,10 +7280,10 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>• Yenilenmiş telefon tanımı ve yasal çerçeve; 
-  • kalite sınıfları; 
-  • garanti süresi ve kapsamı; 
-  • satın almadan önce kontrol listesi.</t>
+          <t>1. Yenilenmiş telefon tanımı ve yasal çerçeve açıklanır
+2. Kalite sınıfları açıklanır
+3. Garanti süresi ve kapsamı açıklanır
+4. Satın almadan önce kontrol listesi verilir</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="115" customHeight="1">
+    <row r="27" ht="128.5" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>AirTag Nedir ve Nasıl Kullanılır?</t>
@@ -7370,10 +7370,10 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>1. kotlin nedir kotlin : https://www.turkcell.com.tr/blog/kotlin-nedir-kotlin-ne-ise-yarar
-2. turkcell hosting : https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar
-3. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi
-4. iss : https://www.turkcell.com.tr/blog/iss-internet-servis-saglayicisi-nedir-ne-ise-yarar</t>
+          <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -7399,9 +7399,9 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>• AirTag tanımı ve çalışma mantığı; 
-  • kurulum adımları; 
-  • takip edilme uyarısı ve gizlilik.</t>
+          <t>1. AirTag tanımı ve çalışma mantığı açıklanır
+2. Kurulum adımları adım adım anlatılır
+3. Takip edilme uyarısı ve gizlilik açıklanır</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -7433,7 +7433,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="115" customHeight="1">
+    <row r="28" ht="128.5" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t>OEM Ne Demek?</t>
@@ -7488,9 +7488,9 @@
       <c r="L28" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -7516,9 +7516,9 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>• OEM tanımı; 
-  • OEM ürün ile orijinal ürün farkı; 
-  • telefon ve donanımda OEM kullanımı.</t>
+          <t>1. OEM tanımı açıklanır
+2. OEM ürün ile orijinal ürün farkı açıklanır
+3. Telefon ve donanımda OEM kullanımı açıklanır</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="115" customHeight="1">
+    <row r="29" ht="128.5" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>KVKK Nedir? Kişisel Verilerin Korunması Kanunu</t>
@@ -7605,9 +7605,9 @@
       <c r="L29" s="4" t="inlineStr">
         <is>
           <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-3. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir
-4. wlan nedir : https://www.turkcell.com.tr/blog/wlan-nedir-kablosuz-aglarin-calisma-mantigi-ve-guvenlik-rehberi</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -7633,9 +7633,9 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>• KVKK tanımı; 
-  • kişisel veri türleri; 
-  • veri sahibinin hakları.</t>
+          <t>1. KVKK tanımı açıklanır
+2. Kişisel veri türleri açıklanır
+3. Veri sahibinin hakları açıklanır</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="115" customHeight="1">
+    <row r="30" ht="128.5" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Telefon Neden Isınır?</t>
@@ -7727,9 +7727,9 @@
       <c r="L30" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
-2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. turkcell b2b : https://www.turkcell.com.tr/blog/b2b-telco-sektorunde-urun-oneri-sistemleri-cok-katmanli-bir-yaklasim
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -7772,10 +7772,10 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>• Isınmanın yaygın nedenleri; 
-  • şarj sırasında ısınma; 
-  • ısınmayı azaltan ayarlar; 
-  • servise götürmeyi gerektiren durumlar.</t>
+          <t>1. Isınmanın yaygın nedenleri açıklanır
+2. Şarj sırasında ısınma adım adım anlatılır
+3. Isınmayı azaltan ayarlar açıklanır
+4. Servise götürmeyi gerektiren durumlar açıklanır</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -7862,9 +7862,9 @@
       <c r="L31" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-3. turkcell 5g : https://www.turkcell.com.tr/blog/5g-ile-hayatimiza-yeni-neler-giriyor-etkilesim-cagi-ve-fwa
-4. turkcell rahat paket nedir : https://www.turkcell.com.tr/blog/turkcell-rahat-paketleri-hem-faturali-hem-faturasiz-taahhutsuz-ozgurluk</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -7874,9 +7874,9 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>• Müşteri numarasının tanımı; 
-  • faturada ve uygulamada nereden görüldüğü; 
-  • abone numarası ile farkı.</t>
+          <t>1. Müşteri numarasının tanımı açıklanır
+2. Faturada ve uygulamada nereden görüldüğü açıklanır
+3. Abone numarası ile farkı açıklanır</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -7908,7 +7908,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="115" customHeight="1">
+    <row r="32" ht="128.5" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>OTP Ne Demek?</t>
@@ -7964,9 +7964,9 @@
       <c r="L32" s="4" t="inlineStr">
         <is>
           <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-3. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir
-4. wlan nedir : https://www.turkcell.com.tr/blog/wlan-nedir-kablosuz-aglarin-calisma-mantigi-ve-guvenlik-rehberi</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -7976,10 +7976,10 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>• OTP tanımı; 
-  • SMS ile gelen tek kullanımlık şifrenin nasıl çalıştığı; 
-  • OTP paylaşımının riskleri; 
-  • OTP gelmediğinde yapılabilecekler.</t>
+          <t>1. OTP tanımı açıklanır
+2. SMS ile gelen tek kullanımlık şifrenin nasıl çalıştığı açıklanır
+3. OTP paylaşımının riskleri açıklanır
+4. OTP gelmediğinde yapılabilecekler açıklanır</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="115" customHeight="1">
+    <row r="33" ht="128.5" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>QLED Nedir? QLED ve OLED Farkı</t>
@@ -8067,9 +8067,9 @@
       <c r="L33" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -8079,10 +8079,10 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>• QLED tanımı; 
-  • QLED ve OLED farkı tablo hâlinde; 
-  • hangi kullanım için hangisi; 
-  • parlaklık ve ömür karşılaştırması.</t>
+          <t>1. QLED tanımı açıklanır
+2. QLED ve OLED farkı tablo hâlinde açıklanır
+3. Hangi kullanım için hangisi açıklanır
+4. Parlaklık ve ömür karşılaştırması verilir</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -8114,7 +8114,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="128.5" customHeight="1">
+    <row r="34" ht="142" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Medya Okuryazarlığı Nedir?</t>
@@ -8170,9 +8170,9 @@
       <c r="L34" s="4" t="inlineStr">
         <is>
           <t>1. güneş enerjisi : https://www.turkcell.com.tr/blog/gunes-enerjisi-nedir-surdurulebilir-gelecegin-enerji-modeli-ve-uygulama-alanlari
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. sürdürülebilirlik nedir : https://www.turkcell.com.tr/blog/bugunu-yasarken-yarini-korumak-surdurulebilirlik-nedir
-3. karbon ayak izi : https://www.turkcell.com.tr/blog/dunyaya-biraktigimiz-iz-karbon-ayak-izi-nedir
-4. yeşil enerji nedir : https://www.turkcell.com.tr/blog/enerjinin-yeni-kodu-yesil-enerji-ile-gelecegi-yeniden-yazmak</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -8182,10 +8182,10 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>• Medya okuryazarlığının tanımı; 
-  • yanlış bilgiyi ayırt etme adımları; 
-  • kaynak doğrulama yöntemleri; 
-  • çocuklar için ipuçları.</t>
+          <t>1. Medya okuryazarlığının tanımı açıklanır
+2. Yanlış bilgiyi ayırt etme adımları adım adım anlatılır
+3. Kaynak doğrulama yöntemleri açıklanır
+4. Çocuklar için ipuçları açıklanır</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="115" customHeight="1">
+    <row r="35" ht="128.5" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>TAG Nedir?</t>
@@ -8269,9 +8269,9 @@
       <c r="L35" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -8281,10 +8281,10 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>• TAG teriminin anlamı; 
-  • sosyal medyada etiketleme; 
-  • NFC etiketi anlamı; 
-  • hangi bağlamda hangi anlamın kullanıldığı.</t>
+          <t>1. TAG teriminin anlamı açıklanır
+2. Sosyal medyada etiketleme adım adım anlatılır
+3. NFC etiketi anlamı açıklanır
+4. Hangi bağlamda hangi anlamın kullanıldığı açıklanır</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="115" customHeight="1">
+    <row r="36" ht="128.5" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Karekod Nasıl Okutulur?</t>
@@ -8367,9 +8367,9 @@
       <c r="L36" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -8395,9 +8395,9 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>• Kamerayla karekod okutma adımları; 
-  • kamera okutmadığında yapılabilecekler; 
-  • sahte karekodların ayırt edilmesi.</t>
+          <t>1. Kamerayla karekod okutma adımları adım adım anlatılır
+2. Kamera okutmadığında yapılabilecekler açıklanır
+3. Sahte karekodların ayırt edilmesi adım adım anlatılır</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -8429,7 +8429,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="115" customHeight="1">
+    <row r="37" ht="128.5" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Apple Arcade Nedir?</t>
@@ -8485,9 +8485,9 @@
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -8497,10 +8497,10 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>• Apple Arcade tanımı; 
-  • abonelik ücreti ve deneme süresi; 
-  • hangi cihazlarda çalıştığı; 
-  • oyunların çevrimdışı oynanabilirliği.</t>
+          <t>1. Apple Arcade tanımı açıklanır
+2. Abonelik ücreti ve deneme süresi açıklanır
+3. Hangi cihazlarda çalıştığı açıklanır
+4. Oyunların çevrimdışı oynanabilirliği açıklanır</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -8587,10 +8587,10 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-2. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-3. turkcell 5g : https://www.turkcell.com.tr/blog/5g-ile-hayatimiza-yeni-neler-giriyor-etkilesim-cagi-ve-fwa
-4. turkcell rahat paket nedir : https://www.turkcell.com.tr/blog/turkcell-rahat-paketleri-hem-faturali-hem-faturasiz-taahhutsuz-ozgurluk</t>
+          <t>1. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -8600,10 +8600,10 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>• Hat devrinin tanımı; 
-  • devir için gereken belgeler; 
-  • devir ücreti; 
-  • devir sonrası fatura ve taahhüt durumu.</t>
+          <t>1. Hat devrinin tanımı açıklanır
+2. Devir için gereken belgeler açıklanır
+3. Devir ücreti açıklanır
+4. Devir sonrası fatura ve taahhüt durumu açıklanır</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="115" customHeight="1">
+    <row r="39" ht="128.5" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>URL Nedir?</t>
@@ -8686,9 +8686,9 @@
       <c r="L39" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
 2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-3. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir
-4. bulut depolama : https://www.turkcell.com.tr/blog/dijital-hafizanin-yeni-evi-bulut-depolama</t>
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -8698,9 +8698,9 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>• URL tanımı; 
-  • URL bölümleri: protokol, alan adı, yol; 
-  • güvenli URL'nin nasıl anlaşıldığı.</t>
+          <t>1. URL tanımı açıklanır
+2. URL bölümleri: protokol, alan adı, yol açıklanır
+3. Güvenli URL'nin nasıl anlaşıldığı açıklanır</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -8732,7 +8732,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="115" customHeight="1">
+    <row r="40" ht="128.5" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>FreeDOS Nedir? İşletim Sistemi Yüklü Olmayan Bilgisayar</t>
@@ -8782,10 +8782,10 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
-2. telefon kendi kendine kapanıyor : https://www.turkcell.com.tr/blog/telefonun-kendi-kendine-acilip-kapanmasi-neden-olur
-3. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
-4. virüs temizleme : https://www.turkcell.com.tr/blog/akilli-cihazlarda-virus-nasil-temizlenir</t>
+          <t>1. kuantum bilgisayar : https://www.turkcell.com.tr/blog/kuantum-bilgisayar-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -8811,9 +8811,9 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>• FreeDOS tanımı; 
-  • işletim sistemi yüklü olmayan bilgisayarın anlamı; 
-  • sonrasında yapılabilecekler.</t>
+          <t>1. FreeDOS tanımı açıklanır
+2. Işletim sistemi yüklü olmayan bilgisayarın anlamı açıklanır
+3. Sonrasında yapılabilecekler açıklanır</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="128.5" customHeight="1">
+    <row r="4" ht="142" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/isletim-sistemi-nedir-ve-cesitleri-nelerdir</t>
@@ -9458,10 +9458,10 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>1. inovasyon örnekleri : https://www.turkcell.com.tr/blog/inovasyon-nedir-inovasyon-cesitleri-ve-ornekleri-nelerdir
-2. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
-3. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-4. cloud gaming : https://www.turkcell.com.tr/blog/oyunlar-artik-bulutta-cloud-gaming-nedir-nasil-calisir</t>
+          <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
+2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
@@ -9487,9 +9487,9 @@
       </c>
       <c r="W4" s="4" t="inlineStr">
         <is>
-          <t>• Mobil işletim sistemleri bölümü genişletilebilir; 
-  • Windows, macOS ve Linux karşılaştırması tablo hâlinde verilebilir; 
-  • FreeDOS ve işletim sistemsiz cihaz bölümü eklenebilir.</t>
+          <t>1. Mobil işletim sistemleri bölümü genişletilebilir
+2. Windows, macOS ve Linux karşılaştırması tablo hâlinde verilebilir
+3. FreeDOS ve işletim sistemsiz cihaz bölümü eklenebilir</t>
         </is>
       </c>
       <c r="X4" s="4" t="inlineStr">
@@ -9514,7 +9514,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="115" customHeight="1">
+    <row r="5" ht="128.5" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar</t>
@@ -9624,10 +9624,10 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>1. kotlin nedir kotlin : https://www.turkcell.com.tr/blog/kotlin-nedir-kotlin-ne-ise-yarar
-2. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi
-3. iss : https://www.turkcell.com.tr/blog/iss-internet-servis-saglayicisi-nedir-ne-ise-yarar
-4. turkcell hotspot : https://www.turkcell.com.tr/blog/hotspot-ile-internet-paylasimi-ne-ise-yarar-nasil-acilir</t>
+          <t>1. domain nedir : https://www.turkcell.com.tr/blog/dijital-varligin-ilk-adimi-domain-alan-adi-nedir
+   Anchor metni gövdede 8 kez geçmektedir; mevcut cümlelerden birine bağlantı verilebilir.
+2. chatgpt atlas : https://www.turkcell.com.tr/blog/ai-destekli-web-tarayici-donemi-chatgpt-atlas-nedir
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
@@ -9653,9 +9653,9 @@
       </c>
       <c r="W5" s="4" t="inlineStr">
         <is>
-          <t>• Hosting türleri karşılaştırması eklenebilir; 
-  • domain ile ilişkisi açıklanabilir; 
-  • küçük işletme için seçim kriterleri bölümü eklenebilir.</t>
+          <t>1. Hosting türleri karşılaştırması eklenebilir
+2. Domain ile ilişkisi açıklanabilir
+3. Küçük işletme için seçim kriterleri bölümü eklenebilir</t>
         </is>
       </c>
       <c r="X5" s="4" t="inlineStr">
@@ -9801,10 +9801,10 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>1. kotlin nedir kotlin : https://www.turkcell.com.tr/blog/kotlin-nedir-kotlin-ne-ise-yarar
-2. turkcell hotspot : https://www.turkcell.com.tr/blog/hotspot-ile-internet-paylasimi-ne-ise-yarar-nasil-acilir
-3. turkcell hosting : https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar
-4. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi</t>
+          <t>1. turkcell hotspot : https://www.turkcell.com.tr/blog/hotspot-ile-internet-paylasimi-ne-ise-yarar-nasil-acilir
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
+2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
@@ -9864,11 +9864,11 @@
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>• NFC özelliğinin telefonda nasıl açıldığı marka bazında eklenebilir; 
-  • iPhone ve Android ayrımı ara başlığa çıkarılabilir; 
-  • NFC destekleyen telefon listesi eklenebilir; 
-  • temassız ödeme bölümü genişletilebilir; 
-  • NFC etiketi kullanımı eklenebilir.</t>
+          <t>1. NFC özelliğinin telefonda nasıl açıldığı marka bazında eklenebilir
+2. IPhone ve Android ayrımı ara başlığa çıkarılabilir
+3. NFC destekleyen telefon listesi eklenebilir
+4. Temassız ödeme bölümü genişletilebilir
+5. NFC etiketi kullanımı eklenebilir</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
@@ -9893,7 +9893,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="209.5" customHeight="1">
+    <row r="7" ht="263.5" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
@@ -9993,9 +9993,13 @@
       <c r="U7" s="4" t="inlineStr">
         <is>
           <t>1. yapay zeka mühendisliği : https://www.turkcell.com.tr/blog/yapay-zeka-muhendisligi-nedir
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
 2. creen ai : https://www.turkcell.com.tr/blog/yesil-yapay-zeka-green-ai
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
 3. yapay zeka sanatçısı ne demek : https://www.turkcell.com.tr/blog/yapay-zeka-sanat-yapabilir-mi
-4. yapay zeka kullanirken : https://www.turkcell.com.tr/blog/yapay-zeka-kullanirken-ne-kadarini-paylasmaliyiz</t>
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
+4. ai agent nedir : https://www.turkcell.com.tr/blog/yapay-zeka-ajani-ai-agent-nedir-nasil-calisir
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -10005,11 +10009,11 @@
       </c>
       <c r="W7" s="4" t="inlineStr">
         <is>
-          <t>• Yazının hedefi çıplak marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek'; 
-  • kullanım senaryoları bölümü eklenebilir: telefonda kullanım, dosya yükleme, görsel oluşturma; 
-  • ChatGPT ile karşılaştırma tablosu eklenebilir; 
-  • ücretsiz ve ücretli sürüm farkı ayrı ara başlıkta verilebilir; 
-  • sık sorulanlar bölümü, sonuç sayfasında görünen soru bloğuyla eşleştirilebilir.</t>
+          <t>1. Yazının hedefi çıplak marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek' açıklanır
+2. Kullanım senaryoları bölümü eklenebilir: telefonda kullanım, dosya yükleme, görsel oluşturma adım adım anlatılır
+3. ChatGPT ile karşılaştırma tablosu eklenebilir
+4. Ücretsiz ve ücretli sürüm farkı ayrı ara başlıkta verilebilir
+5. Sık sorulanlar bölümü, sonuç sayfasında görünen soru bloğuyla eşleştirilebilir</t>
         </is>
       </c>
       <c r="X7" s="4" t="inlineStr">
@@ -10034,7 +10038,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="128.5" customHeight="1">
+    <row r="8" ht="142" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni</t>
@@ -10133,10 +10137,10 @@
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-2. 4.5 g ile 5g arasındaki hız farkı : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
-3. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi
-4. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu</t>
+          <t>1. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
+2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
@@ -10179,9 +10183,9 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>• Ping değerinin ne olduğu ve ideal aralık tablo hâlinde verilebilir; 
-  • ping düşürme adımları eklenebilir; 
-  • oyun senaryosu ayrı ara başlığa alınabilir.</t>
+          <t>1. Ping değerinin ne olduğu ve ideal aralık tablo hâlinde verilebilir
+2. Ping düşürme adımları eklenebilir
+3. Oyun senaryosu ayrı ara başlığa alınabilir</t>
         </is>
       </c>
       <c r="X8" s="4" t="inlineStr">
@@ -10336,10 +10340,10 @@
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>1. kotlin nedir kotlin : https://www.turkcell.com.tr/blog/kotlin-nedir-kotlin-ne-ise-yarar
-2. turkcell hosting : https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar
-3. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi
-4. iss : https://www.turkcell.com.tr/blog/iss-internet-servis-saglayicisi-nedir-ne-ise-yarar</t>
+          <t>1. tethering nedir : https://www.turkcell.com.tr/blog/tethering-nedir-usb-wi-fi-ve-bluetooth-ile-internet-paylasimi-rehberi
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
+2. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
@@ -10365,9 +10369,9 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>• Kablo ve şarj aleti seçimi bölümü eklenebilir; 
-  • USB-C standartları ve hız sınıfları tablo hâlinde verilebilir; 
-  • hangi cihazlarda bulunduğu listelenebilir.</t>
+          <t>1. Kablo ve şarj aleti seçimi bölümü eklenebilir
+2. USB-C standartları ve hız sınıfları tablo hâlinde verilebilir
+3. Hangi cihazlarda bulunduğu listelenebilir</t>
         </is>
       </c>
       <c r="X9" s="4" t="inlineStr">
@@ -10500,9 +10504,9 @@
       <c r="U10" s="4" t="inlineStr">
         <is>
           <t>1. sabit internet nedir : https://www.turkcell.com.tr/blog/sabit-internet-nedir-turleri-avantajlari-ve-kullanim-alanlari
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
 2. internet üzerinden erisim : https://www.turkcell.com.tr/blog/uzaktan-baglanti-nedir-turleri-calisma-mantigi-ve-guvenli-kullanim-rehberi
-3. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-4. 4.5 g ile 5g arasındaki hız farkı : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi</t>
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
@@ -10579,10 +10583,10 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>• Hangi bağlantının hangi kullanım için uygun olduğu tablo hâlinde verilebilir; 
-  • hız beklentisi mesafeye göre açıklanabilir; 
-  • altyapı sorgulamaya bağlantı eklenebilir; 
-  • fiber karşılaştırması genişletilebilir.</t>
+          <t>1. Hangi bağlantının hangi kullanım için uygun olduğu tablo hâlinde verilebilir
+2. Hız beklentisi mesafeye göre açıklanabilir
+3. Altyapı sorgulamaya bağlantı eklenebilir
+4. Fiber karşılaştırması genişletilebilir</t>
         </is>
       </c>
       <c r="X10" s="4" t="inlineStr">
@@ -10720,9 +10724,9 @@
       <c r="U11" s="4" t="inlineStr">
         <is>
           <t>1. ping : https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni
-2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-3. 4.5 g ile 5g arasındaki hız farkı : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
-4. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi</t>
+   Anchor metni gövdede 1 kez geçmektedir; mevcut cümlelerden birine bağlantı verilebilir.
+2. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
@@ -10748,9 +10752,9 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>• İdeal jitter değeri tablo hâlinde verilebilir; 
-  • ölçüm yöntemi eklenebilir; 
-  • paket kaybı ile ilişkisi açıklanabilir.</t>
+          <t>1. İdeal jitter değeri tablo hâlinde verilebilir
+2. Ölçüm yöntemi eklenebilir
+3. Paket kaybı ile ilişkisi açıklanabilir</t>
         </is>
       </c>
       <c r="X11" s="4" t="inlineStr">
@@ -10775,7 +10779,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="128.5" customHeight="1">
+    <row r="12" ht="142" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/wi-fi-6-nedir-wi-fi-5-ile-arasindaki-temel-farklar</t>
@@ -10881,10 +10885,10 @@
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-2. 4.5 g ile 5g arasındaki hız farkı : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
-3. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi
-4. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu</t>
+          <t>1. 4.5 g ile 5g arasındaki : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
+2. vdsl internet : https://www.turkcell.com.tr/blog/vdsl-ve-adsl-nedir-internet-baglanti-turleri-arasindaki-farklar
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
@@ -10918,9 +10922,9 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>• Wi-Fi 6 destekleyen modem listesi eklenebilir; 
-  • mesh sistemlerle ilişkisi açıklanabilir; 
-  • yükseltmenin ne zaman anlamlı olduğu bölümü eklenebilir.</t>
+          <t>1. Wi-Fi 6 destekleyen modem listesi eklenebilir
+2. Mesh sistemlerle ilişkisi açıklanabilir
+3. Yükseltmenin ne zaman anlamlı olduğu bölümü eklenebilir</t>
         </is>
       </c>
       <c r="X12" s="4" t="inlineStr">
@@ -10945,7 +10949,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="142" customHeight="1">
+    <row r="13" ht="155.5" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/mac-adresi-her-cihazin-kendine-ozgu-dijital-imzasi</t>
@@ -11056,9 +11060,9 @@
       <c r="U13" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
-2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-3. 4.5 g ile 5g arasındaki hız farkı : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
-4. vowifi nedir : https://www.turkcell.com.tr/blog/vowifi-nedir-ve-ne-ise-yarar-calisma-mantigi-ve-kullanimi</t>
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
+2. internet yavaşladı : https://www.turkcell.com.tr/blog/internet-neden-yavasladi-sorunun-kaynagini-adim-adim-bulma-rehberi
+   Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
@@ -11084,9 +11088,9 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>• MAC adresinin cihazdan öğrenilmesi işletim sistemi bazında eklenebilir; 
-  • MAC filtreleme bölümü eklenebilir; 
-  • IP adresiyle farkı açıklanabilir.</t>
+          <t>1. MAC adresinin cihazdan öğrenilmesi işletim sistemi bazında eklenebilir
+2. MAC filtreleme bölümü eklenebilir
+3. IP adresiyle farkı açıklanabilir</t>
         </is>
       </c>
       <c r="X13" s="4" t="inlineStr">

--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -649,7 +649,7 @@
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GÜNCELLEME ÖNERİSİ</t>
+          <t>GÜNCELLENEBİLECEK YAZI</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1.534.530 (satır toplamı, kümeler arası kesişim içerebilir)</t>
+          <t>1.566.780 (satır toplamı, kümeler arası kesişim içerebilir)</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1.804.250 · 247 benzersiz kelime</t>
+          <t>1.836.500 · 254 benzersiz kelime</t>
         </is>
       </c>
     </row>
@@ -690,14 +690,14 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Önerilen kelimelerin 170/187 tanesinde AI Overview görünmektedir; kısa ve alıntılanabilir bölümler bu nedenle önerilmektedir.</t>
+          <t>Önerilen kelimelerin 177/194 tanesinde AI Overview görünmektedir; kısa ve alıntılanabilir bölümler bu nedenle önerilmektedir.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>RAKİP BOŞLUĞU</t>
+          <t>CONTENT GAP</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -969,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2038,10 +2038,10 @@
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n"/>
     </row>
-    <row r="49" ht="61" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>fiber internet altyapı sorgulama</t>
+    <row r="49" ht="74.5" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>apple arcade</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Aynı hizmet sayfası kümesi.</t>
+          <t>Sonuç sayfası Apple'ın kendi hizmet adresi; yönlendirme amaçlı marka araması. Yazının hedefi 'apple arcade nedir' kelimesidir.</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2060,10 +2060,10 @@
       <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="n"/>
     </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>mesh wifi</t>
+    <row r="50" ht="61" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>fiber internet altyapı sorgulama</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Sonuç sayfası mesh cihaz satışı; ticari arama.</t>
+          <t>Aynı hizmet sayfası kümesi.</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Konu ve niyet eşleşmesi</t>
+          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
         </is>
       </c>
       <c r="E50" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>usb c kablo</t>
+          <t>mesh wifi</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Ürün araması; aynı sınıf.</t>
+          <t>Sonuç sayfası mesh cihaz satışı; ticari arama.</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2107,51 +2107,51 @@
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>puk</t>
+          <t>usb c kablo</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Çıplak kısaltma; tek başına arama niyetini taşımıyor.</t>
+          <t>Ürün araması; aynı sınıf.</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Konu eşleşmesi</t>
+          <t>Konu ve niyet eşleşmesi</t>
         </is>
       </c>
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n"/>
     </row>
-    <row r="53" ht="61" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>ttnet fiber altyapı sorgulama</t>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>puk</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Aynı hizmet sayfası kümesi; ayrıca rakip marka adı taşıyor.</t>
+          <t>Çıplak kısaltma; tek başına arama niyetini taşımıyor.</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
+          <t>Konu eşleşmesi</t>
         </is>
       </c>
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="n"/>
     </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>oem nedir</t>
+    <row r="54" ht="61" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>ttnet fiber altyapı sorgulama</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
@@ -2159,43 +2159,43 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Kendi kısa içerik önerisinde hedefleniyor.</t>
+          <t>Aynı hizmet sayfası kümesi; ayrıca rakip marka adı taşıyor.</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Başka öneriyle çakışma</t>
+          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="n"/>
     </row>
-    <row r="55" ht="47.5" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>gizli dns sunucusuna erişilemiyor</t>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>oem nedir</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>DNS hata giderme ayrı bir konu; barındırma içeriğiyle eşleşmiyor.</t>
+          <t>Kendi kısa içerik önerisinde hedefleniyor.</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Konu ve niyet eşleşmesi</t>
+          <t>Başka öneriyle çakışma</t>
         </is>
       </c>
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="n"/>
     </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>dns sunucusu yanıt vermiyor</t>
+    <row r="56" ht="47.5" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>gizli dns sunucusuna erişilemiyor</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>DNS hata giderme ayrı bir konu.</t>
+          <t>DNS hata giderme ayrı bir konu; barındırma içeriğiyle eşleşmiyor.</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2217,7 +2217,7 @@
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>adsl modem</t>
+          <t>dns sunucusu yanıt vermiyor</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Cihaz araması.</t>
+          <t>DNS hata giderme ayrı bir konu.</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2239,7 +2239,7 @@
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>vdsl internet</t>
+          <t>adsl modem</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Hizmet ve tarife araması; bilgilendirici yazı hedefi değil.</t>
+          <t>Cihaz araması.</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2261,15 +2261,15 @@
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>mesh modem</t>
+          <t>vdsl internet</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Cihaz araması.</t>
+          <t>Hizmet ve tarife araması; bilgilendirici yazı hedefi değil.</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2280,32 +2280,32 @@
       <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="n"/>
     </row>
-    <row r="60" ht="61" customHeight="1">
+    <row r="60" ht="34" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>eposta</t>
+          <t>mesh modem</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Yönlendirme amaçlı arama; 'e posta' ile aynı sonuç sayfası.</t>
+          <t>Cihaz araması.</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
+          <t>Konu ve niyet eşleşmesi</t>
         </is>
       </c>
       <c r="E60" s="2" t="n"/>
       <c r="F60" s="2" t="n"/>
     </row>
-    <row r="61" ht="47.5" customHeight="1">
+    <row r="61" ht="61" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>airtag kedi tasması</t>
+          <t>eposta</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
@@ -2313,51 +2313,51 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Ürün aksesuarı araması; AirTag tanımı sorusundan ayrı bir niyet.</t>
+          <t>Yönlendirme amaçlı arama; 'e posta' ile aynı sonuç sayfası.</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Konu eşleşmesi</t>
+          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
         </is>
       </c>
       <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="n"/>
     </row>
     <row r="62" ht="47.5" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>işletim sistemleri hakkında aşağıdakilerden hangisi doğru değildir</t>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>airtag kedi tasması</t>
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>390</v>
+        <v>880</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Sınav sorusu araması; içerikle karşılanmıyor.</t>
+          <t>Ürün aksesuarı araması; AirTag tanımı sorusundan ayrı bir niyet.</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Konu ve niyet eşleşmesi</t>
+          <t>Konu eşleşmesi</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="n"/>
     </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>mac ne</t>
+    <row r="63" ht="47.5" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>işletim sistemleri hakkında aşağıdakilerden hangisi doğru değildir</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Anlam taşımayan kelime parçası.</t>
+          <t>Sınav sorusu araması; içerikle karşılanmıyor.</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2369,17 +2369,17 @@
       <c r="F63" s="2" t="n"/>
     </row>
     <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>işletim sistemleri sadece bilgisayarlara özgü müdür</t>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>mac ne</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Sınav sorusu araması; içerikle karşılanmıyor.</t>
+          <t>Anlam taşımayan kelime parçası.</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2391,31 +2391,31 @@
       <c r="F64" s="2" t="n"/>
     </row>
     <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>wifi şifresi kırma</t>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>işletim sistemleri sadece bilgisayarlara özgü müdür</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Yetkisiz erişim araması; marka içeriğine uygun değil.</t>
+          <t>Sınav sorusu araması; içerikle karşılanmıyor.</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Konu eşleşmesi</t>
+          <t>Konu ve niyet eşleşmesi</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="n"/>
     </row>
     <row r="66" ht="34" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>instagram mavi tik nasıl alınır</t>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>wifi şifresi kırma</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Hesap doğrulama başvurusu ayrı bir konu; küme dışında.</t>
+          <t>Yetkisiz erişim araması; marka içeriğine uygun değil.</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2434,83 +2434,77 @@
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n"/>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>instagram mavi tik nasıl alınır</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Hesap doğrulama başvurusu ayrı bir konu; küme dışında.</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Konu eşleşmesi</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="20" t="inlineStr">
-        <is>
-          <t>Öneri kümelerindeki değişim</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="n"/>
     </row>
-    <row r="69" ht="36" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>Öneri kümelerindeki değişim</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+    </row>
+    <row r="70" ht="36" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Değişim</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Öneri</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Başlık</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Önceki Aylık Arama</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>Sonraki Aylık Arama</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>Gerekçe</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="34" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="n">
-        <v>454420</v>
-      </c>
-      <c r="E70" s="7" t="n">
-        <v>431020</v>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı. Havuzdan niteleyici kelime eklendi.</t>
         </is>
       </c>
     </row>
@@ -2522,191 +2516,191 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>454420</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>483870</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Niyeti eşleşmeyen kelimeler çıkarıldı. Havuzdan niteleyici kelime eklendi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="34" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>küme daraltıldı</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Konum Paylaşma ve Numaradan Konum Bulma</t>
         </is>
       </c>
-      <c r="D71" s="7" t="n">
+      <c r="D72" s="7" t="n">
         <v>415080</v>
       </c>
-      <c r="E71" s="7" t="n">
+      <c r="E72" s="7" t="n">
         <v>47080</v>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="47.5" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
+    <row r="73" ht="47.5" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>öneri kaldırıldı</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>İnternet Altyapı Sorgulama: Adrese Göre Hız ve Teknoloji Kontrolü</t>
         </is>
       </c>
-      <c r="D72" s="7" t="n">
+      <c r="D73" s="7" t="n">
         <v>256600</v>
       </c>
-      <c r="E72" s="7" t="n">
+      <c r="E73" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>Kümenin tamamı operatör hizmet sayfası aramasıdır; blog içeriğiyle karşılanmıyor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="34" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="n">
-        <v>218620</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>öneri kaldırıldı</t>
+          <t>küme daraltıldı</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Telefonda Beyaz Ekran, Siyah Ekran ve Donma Sorunları</t>
+          <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>166000</v>
+        <v>218620</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>0</v>
+        <v>26020</v>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Hacmin tamamı beyaz ekran aracı aramasından geliyordu; niteleyici kelime havuzda bulunmuyor.</t>
+          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="34" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
+          <t>öneri kaldırıldı</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Telefonda Beyaz Ekran, Siyah Ekran ve Donma Sorunları</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>166000</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Hacmin tamamı beyaz ekran aracı aramasından geliyordu; niteleyici kelime havuzda bulunmuyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
           <t>küme daraltıldı</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Gizli Numara: Arama, Kapatma ve Numara Gizleme Ayarları</t>
         </is>
       </c>
-      <c r="D75" s="7" t="n">
+      <c r="D76" s="7" t="n">
         <v>323300</v>
       </c>
-      <c r="E75" s="7" t="n">
+      <c r="E76" s="7" t="n">
         <v>327700</v>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>Niyeti eşleşmeyen kelimeler çıkarıldı. Havuzdan niteleyici kelime eklendi.</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="47.5" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="77" ht="47.5" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>küme daraltıldı</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Yurt Dışından Getirilen Telefonun IMEI Kaydı: Ücret, Süre ve Adımlar</t>
         </is>
       </c>
-      <c r="D76" s="7" t="n">
+      <c r="D77" s="7" t="n">
         <v>1264130</v>
       </c>
-      <c r="E76" s="7" t="n">
-        <v>164130</v>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="E77" s="7" t="n">
+        <v>169430</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>Niyeti eşleşmeyen kelimeler çıkarıldı. Havuzdan niteleyici kelime eklendi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="34" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>E-Posta Kurulumu ve Yönetimi: Hesap Açma, Aktarma, Güvenlik</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="n">
-        <v>165780</v>
-      </c>
-      <c r="E77" s="7" t="n">
-        <v>15100</v>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
         </is>
       </c>
     </row>
@@ -2718,19 +2712,19 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>PUK, PIN ve SIM Kilidi: Kod Öğrenme ve Kilit Açma</t>
+          <t>E-Posta Kurulumu ve Yönetimi: Hesap Açma, Aktarma, Güvenlik</t>
         </is>
       </c>
       <c r="D78" s="7" t="n">
-        <v>67200</v>
+        <v>165780</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>65300</v>
+        <v>15100</v>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
@@ -2741,56 +2735,56 @@
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>öneri bölündü</t>
+          <t>küme daraltıldı</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Tarayıcı Eklentileri ve Güncellemeleri Yönetme</t>
+          <t>PUK, PIN ve SIM Kilidi: Kod Öğrenme ve Kilit Açma</t>
         </is>
       </c>
       <c r="D79" s="7" t="n">
-        <v>125880</v>
+        <v>67200</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>33180</v>
+        <v>65300</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Küme iki ayrı soruyu bir arada taşıyordu; her soru kendi kısa içeriğine ayrıldı.</t>
+          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>öneri kaldırıldı</t>
+          <t>öneri bölündü</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>K9</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>QR Kod: Okutma, Oluşturma ve Güvenlik Riskleri</t>
+          <t>Tarayıcı Eklentileri ve Güncellemeleri Yönetme</t>
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>47400</v>
+        <v>125880</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>0</v>
+        <v>33180</v>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Küme QR okuyucu ve oluşturucu aracı aramasından oluşuyordu.</t>
+          <t>Küme iki ayrı soruyu bir arada taşıyordu; her soru kendi kısa içeriğine ayrıldı.</t>
         </is>
       </c>
     </row>
@@ -2802,23 +2796,23 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>K10</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Perplexity Nedir? Yapay Zeka Arama Motoru</t>
+          <t>QR Kod: Okutma, Oluşturma ve Güvenlik Riskleri</t>
         </is>
       </c>
       <c r="D81" s="7" t="n">
-        <v>67600</v>
+        <v>47400</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>İki kelime de marka yönlendirmesi; tanım araması havuzda yer almıyor.</t>
+          <t>Küme QR okuyucu ve oluşturucu aracı aramasından oluşuyordu.</t>
         </is>
       </c>
     </row>
@@ -2830,164 +2824,180 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Taşınabilir İnternet ve Mobil WiFi Cihazları</t>
+          <t>Perplexity Nedir? Yapay Zeka Arama Motoru</t>
         </is>
       </c>
       <c r="D82" s="7" t="n">
-        <v>32500</v>
+        <v>67600</v>
       </c>
       <c r="E82" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>İki kelime de ev interneti ürün sayfası aramasıdır.</t>
+          <t>İki kelime de marka yönlendirmesi; tanım araması havuzda yer almıyor.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
+          <t>öneri kaldırıldı</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Taşınabilir İnternet ve Mobil WiFi Cihazları</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>32500</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>İki kelime de ev interneti ürün sayfası aramasıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
           <t>küme daraltıldı</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>K5</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>AirTag Nedir ve Nasıl Kullanılır?</t>
         </is>
       </c>
-      <c r="D83" s="7" t="n">
+      <c r="D84" s="7" t="n">
         <v>21580</v>
       </c>
-      <c r="E83" s="7" t="n">
+      <c r="E84" s="7" t="n">
         <v>20700</v>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="34" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="85" ht="20.5" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>küme daraltıldı</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>K22</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Apple Arcade Nedir?</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="34" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>güncelleme kümesi daraltıldı</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
         </is>
       </c>
-      <c r="D84" s="7" t="n">
+      <c r="D86" s="7" t="n">
         <v>14045400</v>
       </c>
-      <c r="E84" s="7" t="n">
+      <c r="E86" s="7" t="n">
         <v>77400</v>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>Niyeti eşleşmeyen ya da başka öneriyle çakışan kelimeler çıkarıldı.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="2" t="n"/>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-    </row>
-    <row r="87" ht="34" customHeight="1">
-      <c r="A87" s="21" t="inlineStr">
-        <is>
-          <t>Çakışma ve cannibalization kontrolü</t>
-        </is>
-      </c>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="n"/>
       <c r="F87" s="2" t="n"/>
     </row>
-    <row r="88" ht="21" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>Kontrol</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl yapıldı</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>Sonuç</t>
-        </is>
-      </c>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="n"/>
     </row>
-    <row r="89" ht="47.5" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Öneri hedef kelimesi mevcut bir yazının arama sorgusuyla örtüşüyor mu?</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>37 önerinin hedef kelimeleri blogun 4.917 satırlık sorgu verisiyle karşılaştırıldı</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Bulgu yok</t>
-        </is>
-      </c>
+    <row r="89" ht="34" customHeight="1">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>Çakışma ve cannibalization kontrolü</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="n"/>
     </row>
-    <row r="90" ht="47.5" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>Öneri, markanın kendi hizmet ya da ürün sayfasıyla yarışıyor mu?</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Yüksek hacimli kelimelerin sonuç sayfası tek tek görüntülendi</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>11 kelime havuzdan çıkarıldı</t>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Kontrol</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Nasıl yapıldı</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Sonuç</t>
         </is>
       </c>
       <c r="D90" s="2" t="n"/>
@@ -2997,17 +3007,17 @@
     <row r="91" ht="47.5" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Yeni öneri, blogda yayında olan bir yazının konusunu tekrarlıyor mu?</t>
+          <t>Öneri hedef kelimesi mevcut bir yazının arama sorgusuyla örtüşüyor mu?</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Havuzdaki her arama 196 yayındaki yazının konusuyla karşılaştırıldı</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>4 arama yeni yazı yerine güncelleme kapsamına bırakıldı</t>
+          <t>37 önerinin hedef kelimeleri blogun 4.917 satırlık sorgu verisiyle karşılaştırıldı</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Bulgu yok</t>
         </is>
       </c>
       <c r="D91" s="2" t="n"/>
@@ -3017,37 +3027,37 @@
     <row r="92" ht="47.5" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Önerilen başlık, yayındaki bir başlığın benzeri mi?</t>
+          <t>Öneri, markanın kendi hizmet ya da ürün sayfasıyla yarışıyor mu?</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Her öneri başlığı 196 yazının başlığıyla karakter benzerliği üzerinden karşılaştırıldı (eşik 0.72)</t>
+          <t>Yüksek hacimli kelimelerin sonuç sayfası tek tek görüntülendi</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>2 bulgu</t>
+          <t>11 kelime havuzdan çıkarıldı</t>
         </is>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="n"/>
       <c r="F92" s="2" t="n"/>
     </row>
-    <row r="93" ht="34" customHeight="1">
+    <row r="93" ht="47.5" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>İki öneri aynı kelimeyi hedefliyor mu?</t>
+          <t>Yeni öneri, blogda yayında olan bir yazının konusunu tekrarlıyor mu?</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Kelime sahipliği tüm öneri kümelerinde karşılaştırıldı</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>Bulgu yok</t>
+          <t>Havuzdaki her arama 196 yayındaki yazının konusuyla karşılaştırıldı</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>4 arama yeni yazı yerine güncelleme kapsamına bırakıldı</t>
         </is>
       </c>
       <c r="D93" s="2" t="n"/>
@@ -3057,120 +3067,100 @@
     <row r="94" ht="47.5" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Bir kelime hem yeni öneride hem güncellemede hedefleniyor mu?</t>
+          <t>Önerilen başlık, yayındaki bir başlığın benzeri mi?</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Öneri ve güncelleme kümeleri karşılaştırıldı</t>
+          <t>Her öneri başlığı 196 yazının başlığıyla karakter benzerliği üzerinden karşılaştırıldı (eşik 0.72)</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Bulgu yok</t>
+          <t>2 bulgu</t>
         </is>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n"/>
       <c r="F94" s="2" t="n"/>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="n"/>
-      <c r="B95" s="2" t="n"/>
-      <c r="C95" s="2" t="n"/>
+    <row r="95" ht="34" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>İki öneri aynı kelimeyi hedefliyor mu?</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Kelime sahipliği tüm öneri kümelerinde karşılaştırıldı</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Bulgu yok</t>
+        </is>
+      </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="n"/>
       <c r="F95" s="2" t="n"/>
     </row>
-    <row r="96" ht="21" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="96" ht="47.5" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Bir kelime hem yeni öneride hem güncellemede hedefleniyor mu?</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Öneri ve güncelleme kümeleri karşılaştırıldı</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Bulgu yok</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+    </row>
+    <row r="98" ht="21" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>Bulgu Tipi</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>İlgili Öğe</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>Kelime</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Hacim</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>Karşılık</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>Karar</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20.5" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>imei sorgu</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="n">
-        <v>550000</v>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20.5" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>imei sorgula</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="n">
-        <v>550000</v>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
         </is>
       </c>
     </row>
@@ -3187,11 +3177,11 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>altyapı sorgulama</t>
+          <t>imei sorgu</t>
         </is>
       </c>
       <c r="D99" s="7" t="n">
-        <v>90500</v>
+        <v>550000</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
@@ -3217,11 +3207,11 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>alt yapı sorgulama</t>
+          <t>imei sorgula</t>
         </is>
       </c>
       <c r="D100" s="7" t="n">
-        <v>90500</v>
+        <v>550000</v>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
@@ -3247,11 +3237,11 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>internet altyapı sorgulama</t>
+          <t>altyapı sorgulama</t>
         </is>
       </c>
       <c r="D101" s="7" t="n">
-        <v>33100</v>
+        <v>90500</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
@@ -3277,11 +3267,11 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>fiber altyapı sorgulama</t>
+          <t>alt yapı sorgulama</t>
         </is>
       </c>
       <c r="D102" s="7" t="n">
-        <v>33100</v>
+        <v>90500</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
@@ -3307,11 +3297,11 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>taşınabilir internet</t>
+          <t>internet altyapı sorgulama</t>
         </is>
       </c>
       <c r="D103" s="7" t="n">
-        <v>27100</v>
+        <v>33100</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
@@ -3337,11 +3327,11 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>altyapısız internet</t>
+          <t>fiber altyapı sorgulama</t>
         </is>
       </c>
       <c r="D104" s="7" t="n">
-        <v>5400</v>
+        <v>33100</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
@@ -3367,41 +3357,41 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>taşınabilir internet fiyatları</t>
+          <t>taşınabilir internet</t>
         </is>
       </c>
       <c r="D105" s="7" t="n">
+        <v>27100</v>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Turkcell hizmet ya da ürün sayfası</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20.5" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Markanın kendi sayfası</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>öneri havuzu</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>altyapısız internet</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="n">
         <v>5400</v>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="34" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>fiber internet altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="n">
-        <v>2400</v>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
@@ -3427,11 +3417,11 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>ttnet fiber altyapı sorgulama</t>
+          <t>taşınabilir internet fiyatları</t>
         </is>
       </c>
       <c r="D107" s="7" t="n">
-        <v>1600</v>
+        <v>5400</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
@@ -3447,60 +3437,60 @@
     <row r="108" ht="34" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Mevcut yazının kapsamı</t>
+          <t>Markanın kendi sayfası</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>yeni öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>internet neden yavaş</t>
+          <t>öneri havuzu</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>fiber internet altyapı sorgulama</t>
         </is>
       </c>
       <c r="D108" s="7" t="n">
-        <v>6400</v>
-      </c>
-      <c r="E108" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/internet-neden-yavasladi-sorunun-kaynagini-adim-adim-bulma-rehberi</t>
+        <v>2400</v>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Turkcell hizmet ya da ürün sayfası</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Yeni yazı önerilmedi; kelime mevcut yazının güncelleme kapsamına bırakıldı</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="34" customHeight="1">
+          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20.5" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>Mevcut yazının kapsamı</t>
+          <t>Markanın kendi sayfası</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>yeni öneri havuzu</t>
+          <t>öneri havuzu</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>internet neden yok</t>
+          <t>ttnet fiber altyapı sorgulama</t>
         </is>
       </c>
       <c r="D109" s="7" t="n">
-        <v>7700</v>
-      </c>
-      <c r="E109" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/internet-neden-yavasladi-sorunun-kaynagini-adim-adim-bulma-rehberi</t>
+        <v>1600</v>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Turkcell hizmet ya da ürün sayfası</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Yeni yazı önerilmedi; kelime mevcut yazının güncelleme kapsamına bırakıldı</t>
+          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
         </is>
       </c>
     </row>
@@ -3517,15 +3507,15 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>vpn nasıl açılır</t>
+          <t>internet neden yavaş</t>
         </is>
       </c>
       <c r="D110" s="7" t="n">
-        <v>3800</v>
+        <v>6400</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/blog/dijital-guvenligin-temel-bileseni-vpn-nedir</t>
+          <t>https://www.turkcell.com.tr/blog/internet-neden-yavasladi-sorunun-kaynagini-adim-adim-bulma-rehberi</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -3547,15 +3537,15 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>chatgpt ücretli mi</t>
+          <t>internet neden yok</t>
         </is>
       </c>
       <c r="D111" s="7" t="n">
-        <v>3900</v>
+        <v>7700</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/blog/chatgpt-nedir-adim-adim-chatgpt-kullanma-rehberi</t>
+          <t>https://www.turkcell.com.tr/blog/internet-neden-yavasladi-sorunun-kaynagini-adim-adim-bulma-rehberi</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -3567,120 +3557,180 @@
     <row r="112" ht="34" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>Başlık benzerliği</t>
+          <t>Mevcut yazının kapsamı</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>K15 · URL Nedir?</t>
+          <t>yeni öneri havuzu</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>vpn nasıl açılır</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>3800</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/blog/crm-nedir</t>
+          <t>https://www.turkcell.com.tr/blog/dijital-guvenligin-temel-bileseni-vpn-nedir</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Yalnız 'X nedir' başlık kalıbı benzeşmektedir; konular farklı olduğu için çakışma bulunmamaktadır</t>
+          <t>Yeni yazı önerilmedi; kelime mevcut yazının güncelleme kapsamına bırakıldı</t>
         </is>
       </c>
     </row>
     <row r="113" ht="34" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
+          <t>Mevcut yazının kapsamı</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>yeni öneri havuzu</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>chatgpt ücretli mi</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/blog/chatgpt-nedir-adim-adim-chatgpt-kullanma-rehberi</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Yeni yazı önerilmedi; kelime mevcut yazının güncelleme kapsamına bırakıldı</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="34" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
           <t>Başlık benzerliği</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>K15 · URL Nedir?</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="14" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/blog/crm-nedir</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Yalnız 'X nedir' başlık kalıbı benzeşmektedir; konular farklı olduğu için çakışma bulunmamaktadır</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="34" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>Başlık benzerliği</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>K15 · URL Nedir?</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/unix-nedir</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>Yalnız 'X nedir' başlık kalıbı benzeşmektedir; konular farklı olduğu için çakışma bulunmamaktadır</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="n"/>
-      <c r="B114" s="2" t="n"/>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n"/>
-    </row>
-    <row r="115" ht="81" customHeight="1">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>YÖNTEM</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>Bir kelime öneri kümesinde ancak üç koşulu birlikte sağladığında kalmaktadır: kelimenin önerinin konusunu niteleyerek adlandırması, sonuç sayfasının bilgi amaçlı içerikle karşılanması ve kelimenin ikinci bir yaygın anlamının bulunmaması. Alışveriş listesi, giriş sayfası, sorgulama aracı ya da markanın kendi hizmet sayfasıyla karşılanan kelimeler blog kümesine alınmamıştır.</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="n"/>
-      <c r="D115" s="12" t="n"/>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="n"/>
-    </row>
-    <row r="116" ht="51" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>DAYANAK</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası kontrolü Ahrefs görüntüsüyle yapılmıştır (Eylül 2026). Doğrudan görüntülenen kelimeler 'Ahrefs sonuç sayfası görüntüsü', aynı sınıfa giren kelimeler 'Aynı sınıftaki kelimeyle örtüşen sonuç sayfası' olarak işaretlenmiştir.</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n"/>
-      <c r="D116" s="12" t="n"/>
+    <row r="116">
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" s="2" t="n"/>
       <c r="F116" s="2" t="n"/>
+    </row>
+    <row r="117" ht="81" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>YÖNTEM</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Bir kelime öneri kümesinde ancak üç koşulu birlikte sağladığında kalmaktadır: kelimenin önerinin konusunu niteleyerek adlandırması, sonuç sayfasının bilgi amaçlı içerikle karşılanması ve kelimenin ikinci bir yaygın anlamının bulunmaması. Alışveriş listesi, giriş sayfası, sorgulama aracı ya da markanın kendi hizmet sayfasıyla karşılanan kelimeler blog kümesine alınmamıştır.</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n"/>
+      <c r="D117" s="12" t="n"/>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="n"/>
+    </row>
+    <row r="118" ht="51" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>DAYANAK</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Sonuç sayfası kontrolü Ahrefs görüntüsüyle yapılmıştır (Eylül 2026). Doğrudan görüntülenen kelimeler 'Ahrefs sonuç sayfası görüntüsü', aynı sınıfa giren kelimeler 'Aynı sınıftaki kelimeyle örtüşen sonuç sayfası' olarak işaretlenmiştir.</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="n"/>
+      <c r="D118" s="12" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B115:D115"/>
-    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="B117:D117"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3791,12 +3841,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BOŞLUK TANIMI</t>
+          <t>CONTENT GAP TANIMI</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Rakibin sıraladığı ve blogun ne Ahrefs organik keyword listesinde ne de mevcut 196 yazının konu kapsamında yer aldığı kelimeler boşluk sayılmıştır. Rakip marka adı geçen kelimeler (83 kelime) elenmiştir.</t>
+          <t>Rakibin sıraladığı ve blogun ne Ahrefs organik keyword listesinde ne de mevcut 196 yazının konu kapsamında yer aldığı kelimeler content gap sayılmıştır. Rakip marka adı geçen kelimeler (83 kelime) elenmiştir.</t>
         </is>
       </c>
     </row>
@@ -4371,10 +4421,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="169" customHeight="1">
+    <row r="4" ht="250" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -4403,24 +4453,30 @@
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>192.168.0.1 (27.100)
+wifi şifre değiştirme (18.100)
 http //192.168.i.1.1 (14.800)
 modem arayüzü (9.900)
 modem şifre değiştirme (8.100)
 192.1681.1 (8.100)
+internet şifresi değiştirme (5.400)
 zte modem arayüz şifresi (4.400)
 modem arayüzü giriş (4.400)
 192.168.1.1 giriş (2.900)
 modem şifresi nasıl değiştirilir (2.900)
 modem arayüzüne nasıl girilir (2.900)
 192.168.1.1 admin (2.400)
-zte modem arayüz (1.900)</t>
+internet şifresi nasıl değiştirilir (2.400)
+wifi şifresi nasıl değiştirilir (2.400)
+zte modem arayüz (1.900)
+wifi şifresi öğrenme (880)
+modem şifresi öğrenme (170)</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>89800</v>
+        <v>119150</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>254800</v>
+        <v>284150</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -4440,7 +4496,7 @@
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
-2. 4.5 g ile 5g arasındaki : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
+2. youtube ne kadar internet yer : https://www.turkcell.com.tr/blog/youtube-izlerken-internet-kullanimi-video-kalitesine-gore-veri-tuketimi
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
@@ -4656,7 +4712,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="331" customHeight="1">
+    <row r="6" ht="358" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Yurt Dışından Getirilen Telefonun IMEI Kaydı: Ücret, Süre ve Adımlar</t>
@@ -4698,9 +4754,11 @@
 telefon imei sorgulama (5.400)
 imei öğrenme (4.400)
 yurt dışı telefon harcı (2.900)
+telefon açtırma ücreti (2.900)
 yurt dışı telefon kullanım süresi öğrenme (2.400)
 imei sorgulama numarası (2.400)
 telefon imei öğrenme (2.400)
+telefon açtırma ücreti 2026 (2.400)
 yurt dışı telefon kayıt (1.900)
 yurt dışı telefon açtırma ücreti (1.900)
 imei ücreti (1.300)
@@ -4713,10 +4771,10 @@
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>107830</v>
+        <v>113130</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>117730</v>
+        <v>123030</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -4851,7 +4909,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Abone İşlemleri &amp; Hat</t>
+          <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -4895,7 +4953,7 @@
         <is>
           <t>1. turkcell chatgpt : https://www.turkcell.com.tr/blog/chatgpt-yeni-google-mi-internette-arama-aliskanliklari-nasil-degisiyor
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
-2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+2. sosyal medya nasil : https://www.turkcell.com.tr/blog/sosyal-medya-nasil-guvenli-kullanilir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
@@ -5245,7 +5303,7 @@
     <row r="10" ht="128.5" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -5293,10 +5351,10 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>1. IP adresinin ne olduğu
-2. Kendi IP adresini öğrenme
+          <t>1. IP adresinin tanımı
+2. Kendi IP adresinin öğrenilmesi
 3. Statik ve dinamik IP farkı
-4. IP adresi değiştirme yolları ve sınırları</t>
+4. IP adresinin gizlenmesi ve değiştirilmesi</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -5330,10 +5388,10 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>1. IP adresinin ne olduğu açıklanır
-2. Kendi IP adresini öğrenme adım adım anlatılır
+          <t>1. IP adresinin tanımı açıklanır
+2. Kendi IP adresinin öğrenilmesi adım adım anlatılır
 3. Statik ve dinamik IP farkı açıklanır
-4. IP adresi değiştirme yolları ve sınırları açıklanır</t>
+4. IP adresinin gizlenmesi ve değiştirilmesi adım adım anlatılır</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -6224,7 +6282,7 @@
     <row r="18" ht="128.5" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Telefondan Telefona Veri Aktarma: Android, iPhone ve Numara Taşıma</t>
+          <t>Telefondan Telefona Veri Aktarma: Android ve iPhone</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -6319,7 +6377,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Numara taşıma ile veri aktarma farklı işlemlerdir; ikisinin ayrıldığı bir not bölümü eklenebilir.</t>
+          <t>Numara taşıma ile veri aktarma farklı işlemlerdir; ikisinin karıştırılmaması için kısa bir ayrım notu eklenebilir.</t>
         </is>
       </c>
       <c r="P18" s="8" t="n">
@@ -6349,7 +6407,7 @@
     <row r="19" ht="128.5" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Chrome Eklentisi Nasıl Eklenir ve Kaldırılır?</t>
+          <t>En İyi Chrome Eklentileri: Hangisi Ne İşe Yarar?</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -6359,7 +6417,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Chrome eklentisi nasıl eklenir?</t>
+          <t>Chrome'da en iyi eklentiler hangileri?</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -6396,10 +6454,10 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>1. Eklentinin Chrome Web Mağazası üzerinden eklenmesi
-2. Eklentinin kaldırılması ve devre dışı bırakılması
-3. Eklenti izinlerinin görülmesi
-4. Güvenilir eklentinin nasıl ayırt edildiği</t>
+          <t>1. Kullanım alanına göre eklenti seçkisi: üretkenlik, güvenlik, alışveriş
+2. Her eklenti için tek cümlelik ne işe yaradığı
+3. Eklentinin eklenmesi ve kaldırılması
+4. Eklenti izinlerinin görülmesi ve güvenilir eklentinin ayırt edilmesi</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -6412,6 +6470,14 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">Sonuç sayfasında Chrome Web Mağazası ve 'en iyi eklentiler' listeleri öne çıkmaktadır; arama, tek bir eklentiyi kurma adımından çok seçki beklemektedir. </t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -6427,21 +6493,21 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t>'un Chrome eklentileri listesi bloğunun trafik alan sayfalarından biridir; içerik liste formatındadır.</t>
+            <t>'un on iki eklentilik listesi bu formatla trafik almaktadır.</t>
           </r>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>1. Eklentinin Chrome Web Mağazası üzerinden eklenmesi adım adım anlatılır
-2. Eklentinin kaldırılması ve devre dışı bırakılması adım adım anlatılır
-3. Eklenti izinlerinin görülmesi adım adım anlatılır
-4. Güvenilir eklentinin nasıl ayırt edildiği açıklanır</t>
+          <t>1. Kullanım alanına göre eklenti seçkisi: üretkenlik, güvenlik, alışveriş açıklanır
+2. Her eklenti için tek cümlelik ne işe yaradığı açıklanır
+3. Eklentinin eklenmesi ve kaldırılması adım adım anlatılır
+4. Eklenti izinlerinin görülmesi ve güvenilir eklentinin ayırt edilmesi adım adım anlatılır</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>Yanıt ilk paragrafta üç adımda verilebilir; ayrıntı alt başlıklara bırakılabilir.</t>
+          <t>Seçki formatı sonuç sayfasıyla uyumludur; kurulum adımları listenin sonunda kısa bir bölüm olarak verilebilir.</t>
         </is>
       </c>
       <c r="P19" s="8" t="n">
@@ -6464,14 +6530,14 @@
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>Eklenti eklemek isteyen kişi iki-üç adımlık bir yanıt arıyor; soru tek ve nettir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="142" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>E-Posta Kurulumu ve Yönetimi: Hesap Açma, Aktarma, Güvenlik</t>
+          <t>Eklenti arayan kişi tek bir kurulum adımı değil, hangi eklentinin ne işe yaradığını gösteren bir seçki bekliyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="128.5" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>E-Posta Adresi Nedir, Nasıl Açılır?</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -6525,9 +6591,9 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>1. bulut bilişim teknolojisinin sunduğu avantajlardan : https://www.turkcell.com.tr/blog/bulut-teknolojisinin-sagladigi-guvenlik-avantajlari
+          <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
-2. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
@@ -6713,7 +6779,7 @@
     <row r="22" ht="128.5" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Ekran Görüntüsü Alma: Bilgisayar, Telefon ve Kısayollar</t>
+          <t>Bilgisayarda Ekran Görüntüsü Alma: Yöntemler ve Kısayollar</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -6764,16 +6830,16 @@
         <is>
           <t>1. Windows'ta üç yöntem: PrtScn, Windows+Shift+S, Ekran Alıntısı Aracı
 2. Mac kısayolları
-3. Telefonda ekran görüntüsü alma
-4. Kısayol tablosu
-5. Görüntünün kaydedildiği klasör</t>
+3. Kısayol tablosu
+4. Görüntünün kaydedildiği klasör
+5. Ekran görüntüsünün düzenlenmesi ve paylaşılması</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
+          <t>1. kuantum bilgisayar : https://www.turkcell.com.tr/blog/kuantum-bilgisayar-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
-2. kuantum bilgisayar : https://www.turkcell.com.tr/blog/kuantum-bilgisayar-nedir
+2. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
@@ -6819,9 +6885,9 @@
         <is>
           <t>1. Windows'ta üç yöntem: PrtScn, Windows+Shift+S, Ekran Alıntısı Aracı açıklanır
 2. Mac kısayolları adım adım anlatılır
-3. Telefonda ekran görüntüsü alma adım adım anlatılır
-4. Kısayol tablosu verilir
-5. Görüntünün kaydedildiği klasör açıklanır</t>
+3. Kısayol tablosu verilir
+4. Görüntünün kaydedildiği klasör açıklanır
+5. Ekran görüntüsünün düzenlenmesi ve paylaşılması adım adım anlatılır</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -6849,14 +6915,14 @@
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>Ekran görüntüsü alma sorusu Windows, Mac ve telefon için ayrı ayrı aranıyor. Üçünü tek sayfada karşılayan taraf aramanın tamamını alıyor.</t>
+          <t>Bilgisayarda ekran görüntüsü almak isteyen kişi kısayol arıyor; Windows ve Mac karşılığını tek sayfada veren içerik sonuç sayfasında sınırlı.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="128.5" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>eSIM: Nedir, Hangi Telefonlar Destekler, Nasıl Aktive Edilir?</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -7197,7 +7263,7 @@
     <row r="26" ht="128.5" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Yenilenmiş Telefon: Garanti, Kalite Sınıfları ve Satın Alma</t>
+          <t>Yenilenmiş Telefon Ne Demek? Garanti ve Kalite Sınıfları</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -7318,7 +7384,7 @@
     <row r="27" ht="128.5" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>AirTag Nedir ve Nasıl Kullanılır?</t>
+          <t>AirTag Nedir ve Nasıl Çalışır?</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -8432,49 +8498,245 @@
     <row r="37" ht="128.5" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
+          <t>Hat Devri: Ücret ve İşlem Adımları</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Kısa</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Hat devir ücreti ne kadar?</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Abone İşlemleri &amp; Hat</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>hat devir ücreti</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>hat devri nasıl yapılır (880)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>880</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>3780</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Google Keyword Planner · Eyl 2025-Ağu 2026</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>1. Hat devrinin tanımı
+2. Devir için gereken belgeler
+3. Devir ücreti
+4. Devir sonrası fatura ve taahhüt durumu</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>1. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Rakip operatörler hat devri bilgisini hizmet sayfasında veriyor; blog tarafında adım anlatan içerik bulunmamaktadır.</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>1. Hat devrinin tanımı açıklanır
+2. Devir için gereken belgeler açıklanır
+3. Devir ücreti açıklanır
+4. Devir sonrası fatura ve taahhüt durumu açıklanır</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>Ücret ve belge bilgileri değişkendir; ürün ekibiyle doğrulanmalı ve güncellenme tarihi görünür tutulmalıdır.</t>
+        </is>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q37" s="11" t="inlineStr">
+        <is>
+          <t>Öncelik 3</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Eylül</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>Hattını başkasına devretmek isteyen abone ücreti ve gereken belgeleri arıyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="128.5" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>URL Nedir?</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Kısa</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>URL nedir?</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Dijital Araç &amp; Uygulama</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>url nedir</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Google Keyword Planner · Eyl 2025-Ağu 2026</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>1. URL tanımı
+2. URL bölümleri: protokol, alan adı, yol
+3. Güvenli URL'nin nasıl anlaşıldığı</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
+2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
+   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Rakip bloglarda URL tanımı ayrı bir yazıyla karşılanmaktadır.</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>1. URL tanımı açıklanır
+2. URL bölümleri: protokol, alan adı, yol açıklanır
+3. Güvenli URL'nin nasıl anlaşıldığı açıklanır</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>Tanım sorgusudur; ilk paragrafta tek cümlelik karşılık ve ardından bölüm şeması önerilir.</t>
+        </is>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q38" s="11" t="inlineStr">
+        <is>
+          <t>Öncelik 3</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Mart</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Ocak</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>URL kelimesinin karşılığını arayan kişi kısa tanım bekliyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="128.5" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
           <t>Apple Arcade Nedir?</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Kısa</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Apple Arcade nedir?</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>apple arcade nedir</t>
         </is>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F39" s="7" t="n">
         <v>6600</v>
       </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>apple arcade (2.400)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>6600</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Google Keyword Planner · Eyl 2025-Ağu 2026</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>1. Apple Arcade tanımı
 2. Abonelik ücreti ve deneme süresi
@@ -8482,7 +8744,7 @@
 4. Oyunların çevrimdışı oynanabilirliği</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -8490,12 +8752,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>Sonuç sayfasında Apple'ın kendi sayfası ve oyun siteleri yer alıyor; Türkçe tanım içeriği sınırlıdır.</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>1. Apple Arcade tanımı açıklanır
 2. Abonelik ücreti ve deneme süresi açıklanır
@@ -8503,232 +8765,32 @@
 4. Oyunların çevrimdışı oynanabilirliği açıklanır</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Ücret bilgisi değişkendir; güncellenme tarihi görünür tutulabilir.</t>
         </is>
       </c>
-      <c r="P37" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q37" s="11" t="inlineStr">
+      <c r="P39" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q39" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>Mart</t>
-        </is>
-      </c>
-      <c r="S37" s="6" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="T37" s="4" t="inlineStr">
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
         <is>
           <t>Apple Arcade aboneliğini merak eden kişi kapsamı ve ücreti soruyor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="128.5" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Hat Devri: Ücret ve İşlem Adımları</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Kısa</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Hat devir ücreti ne kadar?</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Abone İşlemleri &amp; Hat</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>hat devir ücreti</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>2900</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>hat devri nasıl yapılır (880)</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>880</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>3780</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Google Keyword Planner · Eyl 2025-Ağu 2026</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>1. Hat devrinin tanımı
-2. Devir için gereken belgeler
-3. Devir ücreti
-4. Devir sonrası fatura ve taahhüt durumu</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>1. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
-   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
-2. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
-   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>Rakip operatörler hat devri bilgisini hizmet sayfasında veriyor; blog tarafında adım anlatan içerik bulunmamaktadır.</t>
-        </is>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>1. Hat devrinin tanımı açıklanır
-2. Devir için gereken belgeler açıklanır
-3. Devir ücreti açıklanır
-4. Devir sonrası fatura ve taahhüt durumu açıklanır</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>Ücret ve belge bilgileri değişkendir; ürün ekibiyle doğrulanmalı ve güncellenme tarihi görünür tutulmalıdır.</t>
-        </is>
-      </c>
-      <c r="P38" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q38" s="11" t="inlineStr">
-        <is>
-          <t>Öncelik 3</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>Kasım</t>
-        </is>
-      </c>
-      <c r="S38" s="6" t="inlineStr">
-        <is>
-          <t>Eylül</t>
-        </is>
-      </c>
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>Hattını başkasına devretmek isteyen abone ücreti ve gereken belgeleri arıyor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="128.5" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>URL Nedir?</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Kısa</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>URL nedir?</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Dijital Araç &amp; Uygulama</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>url nedir</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Google Keyword Planner · Eyl 2025-Ağu 2026</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>1. URL tanımı
-2. URL bölümleri: protokol, alan adı, yol
-3. Güvenli URL'nin nasıl anlaşıldığı</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
-   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
-2. superbox ping düşürme : https://www.turkcell.com.tr/blog/5g-ve-ping-5g-ile-oyunlarda-ping-dusurme-yollari-ve-cozumler
-   Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>Rakip bloglarda URL tanımı ayrı bir yazıyla karşılanmaktadır.</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>1. URL tanımı açıklanır
-2. URL bölümleri: protokol, alan adı, yol açıklanır
-3. Güvenli URL'nin nasıl anlaşıldığı açıklanır</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>Tanım sorgusudur; ilk paragrafta tek cümlelik karşılık ve ardından bölüm şeması önerilir.</t>
-        </is>
-      </c>
-      <c r="P39" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q39" s="11" t="inlineStr">
-        <is>
-          <t>Öncelik 3</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>Mart</t>
-        </is>
-      </c>
-      <c r="S39" s="6" t="inlineStr">
-        <is>
-          <t>Ocak</t>
-        </is>
-      </c>
-      <c r="T39" s="4" t="inlineStr">
-        <is>
-          <t>URL kelimesinin karşılığını arayan kişi kısa tanım bekliyor.</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -9062,21 +9124,22 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="54" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="36" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
-    <col width="52" customWidth="1" min="20" max="20"/>
-    <col width="58" customWidth="1" min="21" max="21"/>
-    <col width="52" customWidth="1" min="22" max="22"/>
-    <col width="58" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="50" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="54" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="20" max="20"/>
+    <col width="52" customWidth="1" min="21" max="21"/>
+    <col width="58" customWidth="1" min="22" max="22"/>
+    <col width="52" customWidth="1" min="23" max="23"/>
+    <col width="58" customWidth="1" min="24" max="24"/>
+    <col width="44" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="50" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -9112,6 +9175,7 @@
       <c r="Z1" s="2" t="n"/>
       <c r="AA1" s="2" t="n"/>
       <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -9142,6 +9206,7 @@
       <c r="Z2" s="2" t="n"/>
       <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="n"/>
+      <c r="AC2" s="2" t="n"/>
     </row>
     <row r="3" ht="51" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -9279,75 +9344,80 @@
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
+          <t>Rakip Karşısındaki Durum</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
           <t>Karşılaştırılan Rakip Yazı</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Gövde: Turkcell / Rakip Kelime</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>Ana Terim Geçişi: Turkcell / Rakip / Hedef</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Ana Terim Yoğunluğu: Turkcell / Rakip</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>Gövdede Geçmeyen Secondary</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>Kelime Yoğunluğu Yönergesi</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>Eklenebilecek Alt Başlıklar</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>İç Linkler (Anchor : URL)</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>Rakip Analizi</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>Güncelleme Yönergesi</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="Y3" s="5" t="inlineStr">
         <is>
           <t>Dikkat Edilecek</t>
         </is>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="Z3" s="5" t="inlineStr">
         <is>
           <t>Toplam Aylık Arama</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="AA3" s="5" t="inlineStr">
         <is>
           <t>Puan</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>Öncelik</t>
         </is>
       </c>
-      <c r="AB3" s="5" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>Ne Anlama Geliyor</t>
         </is>
@@ -9401,7 +9471,12 @@
       <c r="M4" s="8" t="n">
         <v>268</v>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Geride</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9423,32 +9498,32 @@
           </r>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>1.131 / 1.085</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>16 / 39 / 23</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>%1.41 / %3.59</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>işletim sistemleri nelerdir, bilgisayar işletim sistemleri</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>Ana terim gövdede 16 kez geçmektedir; hedef 23 geçiştir. Aradaki fark giriş paragrafı, bir ara başlık ve sonuç bölümüne dağıtılabilir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 16, rakipte 39. Gövdede hiç geçmeyen secondary keyword: işletim sistemleri nelerdir, bilgisayar işletim sistemleri. Her biri için bir alt başlık ya da bir cümle eklenebilir.</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>1. Mobil işletim sistemleri bölümü genişletilebilir
 2. Windows, macOS ve Linux karşılaştırması tablo hâlinde verilebilir
@@ -9456,7 +9531,7 @@
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: İşletim Sistemi Özellikleri Nelerdir?</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -9464,7 +9539,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9485,30 +9560,30 @@
           </r>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>1. Mobil işletim sistemleri bölümü genişletilebilir
 2. Windows, macOS ve Linux karşılaştırması tablo hâlinde verilebilir
 3. FreeDOS ve işletim sistemsiz cihaz bölümü eklenebilir</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>Sorgu eğitim amaçlı arama da içermektedir; tanım bölümü kısa ve alıntılanabilir tutulabilir.</t>
         </is>
       </c>
-      <c r="Y4" s="7" t="n">
+      <c r="Z4" s="7" t="n">
         <v>11870</v>
       </c>
-      <c r="Z4" s="8" t="n">
+      <c r="AA4" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="AA4" s="9" t="inlineStr">
+      <c r="AB4" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>Rakip aynı soruda üçüncü sırada ve yedi kat trafik alıyor. Mobil ve masaüstü ayrımı eksik.</t>
         </is>
@@ -9567,7 +9642,12 @@
       <c r="M5" s="8" t="n">
         <v>371</v>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>Geride</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9589,32 +9669,32 @@
           </r>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="P5" s="8" t="inlineStr">
         <is>
           <t>1.015 / 1.239</t>
         </is>
       </c>
-      <c r="P5" s="8" t="inlineStr">
+      <c r="Q5" s="8" t="inlineStr">
         <is>
           <t>28 / 58 / 20</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="R5" s="8" t="inlineStr">
         <is>
           <t>%2.76 / %4.68</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
           <t>Ana terim gövdede 28 kez geçmektedir; hedef 20 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 0, rakipte 8. Secondary keyword'lerin tamamı gövdede geçmektedir.</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>1. Hosting türleri karşılaştırması eklenebilir
 2. Domain ile ilişkisi açıklanabilir
@@ -9622,7 +9702,7 @@
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Hosting Nedir? Hangi Hizmetleri Sağlar? · İlginizi Çekebilir</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>1. domain nedir : https://www.turkcell.com.tr/blog/dijital-varligin-ilk-adimi-domain-alan-adi-nedir
    Anchor metni gövdede 8 kez geçmektedir; mevcut cümlelerden birine bağlantı verilebilir.
@@ -9630,7 +9710,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9651,30 +9731,30 @@
           </r>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>1. Hosting türleri karşılaştırması eklenebilir
 2. Domain ile ilişkisi açıklanabilir
 3. Küçük işletme için seçim kriterleri bölümü eklenebilir</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Sonuç sayfası ticari hizmet sayfalarından oluşmaktadır; açıklama yazısının ilk sıraya çıkması yapısal olarak sınırlıdır.</t>
         </is>
       </c>
-      <c r="Y5" s="7" t="n">
+      <c r="Z5" s="7" t="n">
         <v>8640</v>
       </c>
-      <c r="Z5" s="8" t="n">
+      <c r="AA5" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="AA5" s="9" t="inlineStr">
+      <c r="AB5" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Bu soruda hosting satan siteler önde. Yazının ilk sıraya çıkması zor; beklenti buna göre kurulmalı.</t>
         </is>
@@ -9742,7 +9822,12 @@
       <c r="M6" s="8" t="n">
         <v>1269</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Yakın</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9764,32 +9849,32 @@
           </r>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="P6" s="8" t="inlineStr">
         <is>
           <t>1.510 / 1.110</t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
+      <c r="Q6" s="8" t="inlineStr">
         <is>
           <t>53 / 60 / 30</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t>%3.51 / %5.41</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>nfc açma, iphone nfc açma, nfc özelliği olan telefonlar, nfc özelliği açma, nfc desteği nedir, nfc özelliği nasıl açılır redmi, iphone nfc nasıl açılır, apple nfc açma, nfc etiketi nedir, nfc nedir ne işe yarar, nfc kart nedir, nfc alanı neresi</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>Ana terim gövdede 53 kez geçmektedir; hedef 30 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 0, rakipte 0. Gövdede hiç geçmeyen secondary keyword: nfc açma, iphone nfc açma, nfc özelliği olan telefonlar, nfc özelliği açma, nfc desteği nedir, nfc özelliği nasıl açılır redmi, iphone nfc nasıl açılır, apple nfc açma, nfc etiketi nedir, nfc nedir ne işe yarar, nfc kart nedir, nfc alanı neresi. Her biri için bir alt başlık ya da bir cümle eklenebilir.</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
         <is>
           <t>1. NFC özelliğinin telefonda nasıl açıldığı marka bazında eklenebilir
 2. IPhone ve Android ayrımı ara başlığa çıkarılabilir
@@ -9799,7 +9884,7 @@
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: NFC Nedir, NFC ile Neler Yapılabilir? · İlginizi Çekebilir</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>1. turkcell hotspot : https://www.turkcell.com.tr/blog/hotspot-ile-internet-paylasimi-ne-ise-yarar-nasil-acilir
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -9807,7 +9892,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9862,7 +9947,7 @@
           </r>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>1. NFC özelliğinin telefonda nasıl açıldığı marka bazında eklenebilir
 2. IPhone ve Android ayrımı ara başlığa çıkarılabilir
@@ -9871,23 +9956,23 @@
 5. NFC etiketi kullanımı eklenebilir</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>Bankaların ödeme niyetli sayfaları önde olduğundan, ödeme bölümü tek başına yeterli olmayabilir; cihaz ayarları katmanı ayırt edici olmaktadır.</t>
         </is>
       </c>
-      <c r="Y6" s="7" t="n">
+      <c r="Z6" s="7" t="n">
         <v>145620</v>
       </c>
-      <c r="Z6" s="8" t="n">
+      <c r="AA6" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="AA6" s="9" t="inlineStr">
+      <c r="AB6" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr">
+      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>Sayfa tanımı veriyor ama kullanıcı NFC'yi telefonunda açmaya çalışıyor. Açma adımları eklenirse arama karşılanmış oluyor.</t>
         </is>
@@ -9949,38 +10034,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Yapısal</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>Bilim Genç · 7. sıra
 https://bilimgenc.tubitak.gov.tr/makale/google-gemini-nedir-nasil-kullanilir</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>1.589 / 486</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>50 / 27 / 32</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>%3.15 / %5.56</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>gemini yapay zeka, gemini türkçe</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>Ana terim gövdede 50 kez geçmektedir; hedef 32 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 1, rakipte 3. Gövdede hiç geçmeyen secondary keyword: gemini yapay zeka, gemini türkçe. Her biri için bir alt başlık ya da bir cümle eklenebilir.</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>1. Yazının hedefi çıplak marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek'
 2. Kullanım senaryoları bölümü eklenebilir: telefonda kullanım, dosya yükleme, görsel oluşturma
@@ -9990,7 +10080,7 @@
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Google Gemini Nedir? · Peki, Gemini’yi Kim Geliştirdi? · Gemini’ye Nasıl Ulaşılabilir? · Peki Gemini’nin GPT’den Farkı Ne?</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>1. yapay zeka mühendisliği : https://www.turkcell.com.tr/blog/yapay-zeka-muhendisligi-nedir
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -10002,12 +10092,12 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>Sonuç sayfasının ilk beş sırasını Google'ın kendi Gemini adresleri almaktadır; bilgilendirici içerik altıncı sıradan itibaren görünmektedir. Bu bandda GoIT ve TÜBİTAK Bilim Genç yazıları yer almakta, ikisi de kullanım senaryosu ve adım anlatımı içermektedir.</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>1. Yazının hedefi çıplak marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek' açıklanır
 2. Kullanım senaryoları bölümü eklenebilir: telefonda kullanım, dosya yükleme, görsel oluşturma adım adım anlatılır
@@ -10016,23 +10106,23 @@
 5. Sık sorulanlar bölümü, sonuç sayfasında görünen soru bloğuyla eşleştirilebilir</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>Yazının impression'ı çıplak marka aramasından gelmektedir ve bu aramada sonuç sayfasının üst sıraları Google'ın kendi mülkleridir; CTR'ın bu aramada yükselmesi beklenmemelidir. Kazanım uzun kuyruk sorularındadır.</t>
         </is>
       </c>
-      <c r="Y7" s="7" t="n">
+      <c r="Z7" s="7" t="n">
         <v>77400</v>
       </c>
-      <c r="Z7" s="8" t="n">
+      <c r="AA7" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="AA7" s="9" t="inlineStr">
+      <c r="AB7" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
+      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>Yazı altı ayda 16.3 milyon impression alıp 2.125 click getirmiştir. Sorun içerikte değil, çıplak marka aramasının sonuç sayfasında: üst sıralar Google'ın kendi adreslerinde. Kazanım, kullanım ve karşılaştırma sorularında.</t>
         </is>
@@ -10080,7 +10170,12 @@
       <c r="M8" s="8" t="n">
         <v>533</v>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>Geride</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10102,32 +10197,32 @@
           </r>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="P8" s="8" t="inlineStr">
         <is>
           <t>1.126 / 658</t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
+      <c r="Q8" s="8" t="inlineStr">
         <is>
           <t>23 / 27 / 23</t>
         </is>
       </c>
-      <c r="Q8" s="8" t="inlineStr">
+      <c r="R8" s="8" t="inlineStr">
         <is>
           <t>%2.04 / %4.1</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
           <t>Ana terim gövdede 23 kez geçmektedir; hedef 23 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 0, rakipte 0. Secondary keyword'lerin tamamı gövdede geçmektedir.</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>1. Ping değerinin ne olduğu ve ideal aralık tablo hâlinde verilebilir
 2. Ping düşürme adımları eklenebilir
@@ -10135,7 +10230,7 @@
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Ping Testi Nedir? Nasıl Yapılır? · İlginizi Çekebilir</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>1. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -10143,7 +10238,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10181,30 +10276,30 @@
           </r>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>1. Ping değerinin ne olduğu ve ideal aralık tablo hâlinde verilebilir
 2. Ping düşürme adımları eklenebilir
 3. Oyun senaryosu ayrı ara başlığa alınabilir</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>Rakip bir araç sayfasıyla sıralanmaktadır; yazının bir hız testi aracına bağlanması değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="Y8" s="7" t="n">
+      <c r="Z8" s="7" t="n">
         <v>4400</v>
       </c>
-      <c r="Z8" s="8" t="n">
+      <c r="AA8" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="AA8" s="10" t="inlineStr">
+      <c r="AB8" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr">
+      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>Rakip bir test aracıyla sıralanıyor. Yazıya araç bağlantısı eklenmesi aradaki farkı açıklıyor.</t>
         </is>
@@ -10259,7 +10354,12 @@
       <c r="M9" s="8" t="n">
         <v>562</v>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>Geride</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10281,32 +10381,32 @@
           </r>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="P9" s="8" t="inlineStr">
         <is>
           <t>1.002 / 928</t>
         </is>
       </c>
-      <c r="P9" s="8" t="inlineStr">
+      <c r="Q9" s="8" t="inlineStr">
         <is>
           <t>49 / 52 / 20</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="R9" s="8" t="inlineStr">
         <is>
           <t>%4.89 / %5.6</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>type c şarj aleti nedir, tip c</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>Ana terim gövdede 49 kez geçmektedir; hedef 20 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 0, rakipte 2. Gövdede hiç geçmeyen secondary keyword: type c şarj aleti nedir, tip c. Her biri için bir alt başlık ya da bir cümle eklenebilir.</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10338,7 +10438,7 @@
           </r>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>1. tethering nedir : https://www.turkcell.com.tr/blog/tethering-nedir-usb-wi-fi-ve-bluetooth-ile-internet-paylasimi-rehberi
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -10346,7 +10446,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10367,30 +10467,30 @@
           </r>
         </is>
       </c>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr">
         <is>
           <t>1. Kablo ve şarj aleti seçimi bölümü eklenebilir
 2. USB-C standartları ve hız sınıfları tablo hâlinde verilebilir
 3. Hangi cihazlarda bulunduğu listelenebilir</t>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>Sorgunun büyük bölümü ürün satın alma niyetlidir; açıklama yazısının ilk sıraya çıkması sınırlıdır, Pasaj sayfasına yönlendirme değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="Y9" s="7" t="n">
+      <c r="Z9" s="7" t="n">
         <v>3400</v>
       </c>
-      <c r="Z9" s="8" t="n">
+      <c r="AA9" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="AA9" s="10" t="inlineStr">
+      <c r="AB9" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr">
+      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>Arayan kişi çoğunlukla kablo satın alıyor. Yazı bunu karşılamıyor; ürün sayfasına köprü kurmak daha gerçekçi.</t>
         </is>
@@ -10446,7 +10546,12 @@
       <c r="M10" s="8" t="n">
         <v>724</v>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>Geride</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10468,32 +10573,32 @@
           </r>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="P10" s="8" t="inlineStr">
         <is>
           <t>1.092 / 485</t>
         </is>
       </c>
-      <c r="P10" s="8" t="inlineStr">
+      <c r="Q10" s="8" t="inlineStr">
         <is>
           <t>40 / 23 / 22</t>
         </is>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t>%3.66 / %4.74</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
           <t>Ana terim gövdede 40 kez geçmektedir; hedef 22 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 1, rakipte 1. Secondary keyword'lerin tamamı gövdede geçmektedir.</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="U10" s="4" t="inlineStr">
         <is>
           <t>1. Hangi bağlantının hangi kullanım için uygun olduğu tablo hâlinde verilebilir
 2. Hız beklentisi mesafeye göre açıklanabilir
@@ -10501,7 +10606,7 @@
 4. Fiber karşılaştırması genişletilebilir</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>1. sabit internet nedir : https://www.turkcell.com.tr/blog/sabit-internet-nedir-turleri-avantajlari-ve-kullanim-alanlari
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -10509,7 +10614,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr">
+      <c r="W10" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10581,7 +10686,7 @@
           </r>
         </is>
       </c>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="X10" s="4" t="inlineStr">
         <is>
           <t>1. Hangi bağlantının hangi kullanım için uygun olduğu tablo hâlinde verilebilir
 2. Hız beklentisi mesafeye göre açıklanabilir
@@ -10589,23 +10694,23 @@
 4. Fiber karşılaştırması genişletilebilir</t>
         </is>
       </c>
-      <c r="X10" s="4" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>Rakip sayfalar aynı formatta olduğundan fark içerik derinliğindedir; sayfa türü değişikliği gerekmemektedir.</t>
         </is>
       </c>
-      <c r="Y10" s="7" t="n">
+      <c r="Z10" s="7" t="n">
         <v>7160</v>
       </c>
-      <c r="Z10" s="8" t="n">
+      <c r="AA10" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="AA10" s="10" t="inlineStr">
+      <c r="AB10" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr">
+      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>Rakipler aynı konuyu daha ayrıntılı işliyor ve dört kat trafik alıyor. Karşılaştırma tablosu farkı kapatabilir.</t>
         </is>
@@ -10666,7 +10771,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>Geride</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10688,32 +10798,32 @@
           </r>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="P11" s="8" t="inlineStr">
         <is>
           <t>1.109 / 1.064</t>
         </is>
       </c>
-      <c r="P11" s="8" t="inlineStr">
+      <c r="Q11" s="8" t="inlineStr">
         <is>
           <t>23 / 55 / 22</t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="R11" s="8" t="inlineStr">
         <is>
           <t>%2.07 / %5.17</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>net jitter ne demek, jitter kaç olmalı, net jitter, ping ve jitter nedir</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>Ana terim gövdede 23 kez geçmektedir; hedef 22 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 23, rakipte 55. Gövdede hiç geçmeyen secondary keyword: net jitter ne demek, jitter kaç olmalı, net jitter, ping ve jitter nedir. Her biri için bir alt başlık ya da bir cümle eklenebilir.</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>1. İdeal jitter değeri tablo hâlinde verilebilir
 2. Ölçüm yöntemi eklenebilir
@@ -10721,7 +10831,7 @@
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Jitter Nedir? · Jitter Nasıl Anlaşılır?</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>1. ping : https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni
    Anchor metni gövdede 1 kez geçmektedir; mevcut cümlelerden birine bağlantı verilebilir.
@@ -10729,7 +10839,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V11" s="4" t="inlineStr">
+      <c r="W11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10750,30 +10860,30 @@
           </r>
         </is>
       </c>
-      <c r="W11" s="4" t="inlineStr">
+      <c r="X11" s="4" t="inlineStr">
         <is>
           <t>1. İdeal jitter değeri tablo hâlinde verilebilir
 2. Ölçüm yöntemi eklenebilir
 3. Paket kaybı ile ilişkisi açıklanabilir</t>
         </is>
       </c>
-      <c r="X11" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>Rakip sayfa aynı formattadır; fark ölçüm ve değer tablosundadır.</t>
         </is>
       </c>
-      <c r="Y11" s="7" t="n">
+      <c r="Z11" s="7" t="n">
         <v>5350</v>
       </c>
-      <c r="Z11" s="8" t="n">
+      <c r="AA11" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="AA11" s="11" t="inlineStr">
+      <c r="AB11" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr">
+      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>Rakip aynı formatta ama birinci sırada. Fark, ideal değer tablosu gibi somut bilgide.</t>
         </is>
@@ -10828,7 +10938,12 @@
       <c r="M12" s="8" t="n">
         <v>1662</v>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>Yakın</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10850,32 +10965,32 @@
           </r>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>1.146 / 1.639</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="Q12" s="8" t="inlineStr">
         <is>
           <t>32 / 64 / 23</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t>%2.79 / %3.9</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>wifi 6 modem nedir, wifi 5 vs wifi 6</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>Ana terim gövdede 32 kez geçmektedir; hedef 23 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 0, rakipte 2. Gövdede hiç geçmeyen secondary keyword: wifi 6 modem nedir, wifi 5 vs wifi 6. Her biri için bir alt başlık ya da bir cümle eklenebilir.</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>1. Wi-Fi 6 destekleyen modem listesi eklenebilir
 2. Mesh sistemlerle ilişkisi açıklanabilir
@@ -10883,7 +10998,7 @@
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Wi-Fi 6 Nedir? · Wi-Fi 6 Özellikleri · Wifi 6 Avantajları Nelerdir? · Wi-Fi 6 ve Wi-Fi 5 Arasındaki Farklar · Wi-Fi 6 Uyumlu Cihazlar Nelerdir?</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>1. 4.5 g ile 5g arasındaki : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -10891,7 +11006,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr">
+      <c r="W12" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10920,30 +11035,30 @@
           </r>
         </is>
       </c>
-      <c r="W12" s="4" t="inlineStr">
+      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>1. Wi-Fi 6 destekleyen modem listesi eklenebilir
 2. Mesh sistemlerle ilişkisi açıklanabilir
 3. Yükseltmenin ne zaman anlamlı olduğu bölümü eklenebilir</t>
         </is>
       </c>
-      <c r="X12" s="4" t="inlineStr">
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <t>Sorgu ticari niyet taşımaktadır; 1. sıradaki açıklama yazısının düşük trafik alması bunun göstergesidir. Cihaz sayfasına bağlantı kurulması değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="Y12" s="7" t="n">
+      <c r="Z12" s="7" t="n">
         <v>3370</v>
       </c>
-      <c r="Z12" s="8" t="n">
+      <c r="AA12" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="AA12" s="11" t="inlineStr">
+      <c r="AB12" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr">
+      <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>Birinci sırada olmasına rağmen tıklama gelmiyor, çünkü arayan kişi modem arıyor. Cihaz bağlantısı eklenmeli.</t>
         </is>
@@ -11002,7 +11117,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>Geride</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11024,32 +11144,32 @@
           </r>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>1.011 / 889</t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>43 / 46 / 20</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="R13" s="8" t="inlineStr">
         <is>
           <t>%4.25 / %5.17</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>mac adresinden cihaz bulma, telefon mac adresi nedir</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>Ana terim gövdede 43 kez geçmektedir; hedef 20 geçiştir. Mevcut kullanım hedefin üzerindedir, artırılması önerilmemektedir. Primary keyword'ün başlıkta, ilk paragrafta ve en az bir H2'de tam öbek olarak geçmesi önerilir; gövdedeki tam öbek geçişi 0, rakipte 0. Gövdede hiç geçmeyen secondary keyword: mac adresinden cihaz bulma, telefon mac adresi nedir. Her biri için bir alt başlık ya da bir cümle eklenebilir.</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>1. MAC adresinin cihazdan öğrenilmesi işletim sistemi bazında eklenebilir
 2. MAC filtreleme bölümü eklenebilir
@@ -11057,7 +11177,7 @@
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: MAC Adresi Değiştirme Nasıl Yapılır?</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -11065,7 +11185,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="W13" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11086,30 +11206,30 @@
           </r>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="X13" s="4" t="inlineStr">
         <is>
           <t>1. MAC adresinin cihazdan öğrenilmesi işletim sistemi bazında eklenebilir
 2. MAC filtreleme bölümü eklenebilir
 3. IP adresiyle farkı açıklanabilir</t>
         </is>
       </c>
-      <c r="X13" s="4" t="inlineStr">
+      <c r="Y13" s="4" t="inlineStr">
         <is>
           <t>Sorgu adım arama niyetlidir; tanım bölümü kısaltılıp adımlar öne alınabilir.</t>
         </is>
       </c>
-      <c r="Y13" s="7" t="n">
+      <c r="Z13" s="7" t="n">
         <v>2510</v>
       </c>
-      <c r="Z13" s="8" t="n">
+      <c r="AA13" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="AA13" s="11" t="inlineStr">
+      <c r="AB13" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>Kullanıcı MAC adresini bulmaya çalışıyor. Cihaz bazında adım eklenirse sayfa aramayı karşılıyor.</t>
         </is>
@@ -11144,6 +11264,7 @@
       <c r="Z14" s="2" t="n"/>
       <c r="AA14" s="2" t="n"/>
       <c r="AB14" s="2" t="n"/>
+      <c r="AC14" s="2" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -11182,6 +11303,7 @@
       <c r="Z15" s="12" t="n"/>
       <c r="AA15" s="12" t="n"/>
       <c r="AB15" s="12" t="n"/>
+      <c r="AC15" s="12" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -11220,6 +11342,7 @@
       <c r="Z16" s="12" t="n"/>
       <c r="AA16" s="12" t="n"/>
       <c r="AB16" s="12" t="n"/>
+      <c r="AC16" s="12" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -11258,6 +11381,7 @@
       <c r="Z17" s="12" t="n"/>
       <c r="AA17" s="12" t="n"/>
       <c r="AB17" s="12" t="n"/>
+      <c r="AC17" s="12" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -11296,14 +11420,55 @@
       <c r="Z18" s="12" t="n"/>
       <c r="AA18" s="12" t="n"/>
       <c r="AB18" s="12" t="n"/>
+      <c r="AC18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Rakip karşısındaki durum, sayfanın kendi sırası ile en iyi rakip sırasının karşılaştırmasından okunur: üç ve daha fazla sıra arkadaysa Geride, iki sıra içindeyse Yakın, üç ve daha fazla sıra öndeyse Önde. Rakibin sıralanmadığı başlıklarda Yapısal olarak işaretlenmiştir.</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+      <c r="P19" s="12" t="n"/>
+      <c r="Q19" s="12" t="n"/>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="12" t="n"/>
+      <c r="U19" s="12" t="n"/>
+      <c r="V19" s="12" t="n"/>
+      <c r="W19" s="12" t="n"/>
+      <c r="X19" s="12" t="n"/>
+      <c r="Y19" s="12" t="n"/>
+      <c r="Z19" s="12" t="n"/>
+      <c r="AA19" s="12" t="n"/>
+      <c r="AB19" s="12" t="n"/>
+      <c r="AC19" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B17:AB17"/>
-    <mergeCell ref="B18:AB18"/>
-    <mergeCell ref="B15:AB15"/>
-    <mergeCell ref="B16:AB16"/>
-    <mergeCell ref="A1:AB1"/>
+  <mergeCells count="6">
+    <mergeCell ref="B16:AC16"/>
+    <mergeCell ref="B15:AC15"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="B19:AC19"/>
+    <mergeCell ref="B17:AC17"/>
+    <mergeCell ref="B18:AC18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -11590,7 +11755,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ekran Görüntüsü Alma: Bilgisayar, Telefon ve Kısayollar</t>
+          <t>Bilgisayarda Ekran Görüntüsü Alma: Yöntemler ve Kısayollar</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -11724,7 +11889,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="21" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Kasım 2026</t>
@@ -11737,7 +11902,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Telefondan Telefona Veri Aktarma: Android, iPhone ve Numara Taşıma</t>
+          <t>Telefondan Telefona Veri Aktarma: Android ve iPhone</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -11830,74 +11995,74 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Güncelleme</t>
+          <t>Yeni içerik</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n">
-        <v>51</v>
-      </c>
+          <t>Apple Arcade Nedir?</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
       <c r="G12" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Öncelik 1</t>
+        <v>76</v>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Öncelik 3</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ocak</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kasım</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Aralık 2026</t>
+          <t>Kasım 2026</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Yeni içerik</t>
+          <t>Güncelleme</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>254800</v>
-      </c>
-      <c r="F13" s="7" t="n"/>
+          <t>web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n">
+        <v>51</v>
+      </c>
       <c r="G13" s="8" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -11906,7 +12071,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Ocak</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -11916,7 +12081,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Altyapı &amp; Bağlantı</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11933,7 +12098,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Spam Ne Demek? Spam Mesaj ve Aramaları Engelleme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -11942,11 +12107,11 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>27000</v>
+        <v>284150</v>
       </c>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="8" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
@@ -11955,7 +12120,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Aralık</t>
+          <t>Ocak</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -11965,7 +12130,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Güvenlik &amp; Gizlilik</t>
+          <t>Altyapı &amp; Bağlantı</t>
         </is>
       </c>
     </row>
@@ -11977,25 +12142,25 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Güncelleme</t>
+          <t>Yeni içerik</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>nfc-nedir-nfc-ile-neler-yapilabilir</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/nfc-nedir-nfc-ile-neler-yapilabilir</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n">
-        <v>189</v>
-      </c>
+          <t>Spam Ne Demek? Spam Mesaj ve Aramaları Engelleme</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F15" s="7" t="n"/>
       <c r="G15" s="8" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -12004,7 +12169,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aralık</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -12014,56 +12179,56 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Güvenlik &amp; Gizlilik</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Ocak 2027</t>
+          <t>Aralık 2026</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Yeni içerik</t>
+          <t>Güncelleme</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Apple Arcade Nedir?</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F16" s="7" t="n"/>
+          <t>nfc-nedir-nfc-ile-neler-yapilabilir</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/blog/nfc-nedir-nfc-ile-neler-yapilabilir</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n">
+        <v>189</v>
+      </c>
       <c r="G16" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>Öncelik 3</t>
+        <v>70</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Öncelik 1</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Mart</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Ocak</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Dijital Araç &amp; Uygulama</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12245,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>URL Nedir?</t>
+          <t>En İyi Chrome Eklentileri: Hangisi Ne İşe Yarar?</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -12089,128 +12254,128 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3600</v>
+        <v>18400</v>
       </c>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Öncelik 2</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>Dijital Araç &amp; Uygulama</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Ocak 2027</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Yeni içerik</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>URL Nedir?</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>Mart</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Ocak 2027</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Güncelleme</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n">
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n">
         <v>2125</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G19" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Şubat 2027</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Yeni içerik</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Google Güvenli Arama: Açma, Kapatma ve Aile Filtresi</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>113900</v>
-      </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Öncelik 1</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Nisan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Şubat</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Abone İşlemleri &amp; Hat</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12392,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Chrome Eklentisi Nasıl Eklenir ve Kaldırılır?</t>
+          <t>Google Güvenli Arama: Açma, Kapatma ve Aile Filtresi</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -12236,25 +12401,25 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>18400</v>
+        <v>113900</v>
       </c>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>Öncelik 2</t>
+        <v>90</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Öncelik 1</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>Kasım</t>
+          <t>Nisan</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Şubat</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -12271,25 +12436,25 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Güncelleme</t>
+          <t>Yeni içerik</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>ping-internette-gecikmenin-gercek-nedeni</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n">
-        <v>28</v>
-      </c>
+          <t>Müşteri Numarası Nedir, Nereden Öğrenilir?</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>6700</v>
+      </c>
+      <c r="F21" s="7" t="n"/>
       <c r="G21" s="8" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
@@ -12298,7 +12463,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mart</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
@@ -12308,46 +12473,46 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abone İşlemleri &amp; Hat</t>
         </is>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mart 2027</t>
+          <t>Şubat 2027</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Yeni içerik</t>
+          <t>Güncelleme</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>114800</v>
-      </c>
-      <c r="F22" s="7" t="n"/>
+          <t>ping-internette-gecikmenin-gercek-nedeni</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n">
+        <v>28</v>
+      </c>
       <c r="G22" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>Öncelik 1</t>
+        <v>66</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Öncelik 2</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>Ocak</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -12357,7 +12522,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Altyapı &amp; Bağlantı</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12539,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Müşteri Numarası Nedir, Nereden Öğrenilir?</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -12383,20 +12548,20 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>6700</v>
+        <v>114800</v>
       </c>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Öncelik 2</t>
+        <v>86</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Öncelik 1</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Mart</t>
+          <t>Ocak</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -12406,7 +12571,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Abone İşlemleri &amp; Hat</t>
+          <t>Altyapı &amp; Bağlantı</t>
         </is>
       </c>
     </row>
@@ -12418,34 +12583,34 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Güncelleme</t>
+          <t>Yeni içerik</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>type-c-teknolojisi-ne-ise-yarar-neden-bu-kadar-yaygin</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/type-c-teknolojisi-ne-ise-yarar-neden-bu-kadar-yaygin</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n">
-        <v>59</v>
-      </c>
+          <t>OTP Ne Demek?</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>Öncelik 2</t>
+        <v>79</v>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Öncelik 3</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mart</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
@@ -12455,37 +12620,37 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Güvenlik &amp; Gizlilik</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Nisan 2027</t>
+          <t>Mart 2027</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Yeni içerik</t>
+          <t>Güncelleme</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>AirTag Nedir ve Nasıl Kullanılır?</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>20700</v>
-      </c>
-      <c r="F25" s="7" t="n"/>
+          <t>type-c-teknolojisi-ne-ise-yarar-neden-bu-kadar-yaygin</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/blog/type-c-teknolojisi-ne-ise-yarar-neden-bu-kadar-yaygin</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n">
+        <v>59</v>
+      </c>
       <c r="G25" s="8" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
@@ -12494,17 +12659,17 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Haziran</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Nisan</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Cihaz &amp; Donanım</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12686,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>OTP Ne Demek?</t>
+          <t>AirTag Nedir ve Nasıl Çalışır?</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -12530,30 +12695,30 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>5400</v>
+        <v>20700</v>
       </c>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>Öncelik 3</t>
+        <v>81</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Öncelik 2</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>Mart</t>
+          <t>Haziran</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nisan</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Güvenlik &amp; Gizlilik</t>
+          <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12784,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Yenilenmiş Telefon: Garanti, Kalite Sınıfları ve Satın Alma</t>
+          <t>Yenilenmiş Telefon Ne Demek? Garanti ve Kalite Sınıfları</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -13069,7 +13234,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>117730</v>
+        <v>123030</v>
       </c>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="8" t="n">
@@ -13145,7 +13310,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="36" customHeight="1">
+    <row r="39" ht="21" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Temmuz 2027</t>
@@ -13158,7 +13323,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>E-Posta Kurulumu ve Yönetimi: Hesap Açma, Aktarma, Güvenlik</t>
+          <t>E-Posta Adresi Nedir, Nasıl Açılır?</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -13194,7 +13359,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="36" customHeight="1">
+    <row r="40" ht="21" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Temmuz 2027</t>
@@ -13207,7 +13372,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>eSIM: Nedir, Hangi Telefonlar Destekler, Nasıl Aktive Edilir?</t>
+          <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -13796,11 +13961,11 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId9"/>
@@ -14149,7 +14314,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -14659,7 +14824,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -14965,7 +15130,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>eSIM: Nedir, Hangi Telefonlar Destekler, Nasıl Aktive Edilir?</t>
+          <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -15832,7 +15997,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -16189,7 +16354,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -16240,7 +16405,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>AirTag Nedir ve Nasıl Kullanılır?</t>
+          <t>AirTag Nedir ve Nasıl Çalışır?</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -16393,7 +16558,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Ekran Görüntüsü Alma: Bilgisayar, Telefon ve Kısayollar</t>
+          <t>Bilgisayarda Ekran Görüntüsü Alma: Yöntemler ve Kısayollar</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -16495,7 +16660,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Yenilenmiş Telefon: Garanti, Kalite Sınıfları ve Satın Alma</t>
+          <t>Yenilenmiş Telefon Ne Demek? Garanti ve Kalite Sınıfları</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -17158,7 +17323,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -18025,7 +18190,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>eSIM: Nedir, Hangi Telefonlar Destekler, Nasıl Aktive Edilir?</t>
+          <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -18637,7 +18802,7 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -18857,7 +19022,7 @@
         </is>
       </c>
       <c r="B101" s="7" t="n">
-        <v>7600</v>
+        <v>18100</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
@@ -18892,12 +19057,12 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>Değerlendirilebilir; öneri listesine alınmamıştır</t>
+          <t>Öneri listesinde karşılığı bulunmaktadır</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19210,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -19147,7 +19312,7 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -19351,7 +19516,7 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Telefondan Telefona Veri Aktarma: Android, iPhone ve Numara Taşıma</t>
+          <t>Telefondan Telefona Veri Aktarma: Android ve iPhone</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -20575,7 +20740,7 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
@@ -21493,7 +21658,7 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
@@ -21509,7 +21674,7 @@
         </is>
       </c>
       <c r="B153" s="7" t="n">
-        <v>5300</v>
+        <v>18100</v>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
@@ -21891,7 +22056,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="20.5" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>192.168.1.1</t>
@@ -21907,7 +22072,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -22187,7 +22352,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -22346,7 +22511,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
+    <row r="19" ht="20.5" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>e sim nedir</t>
@@ -22362,7 +22527,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>eSIM: Nedir, Hangi Telefonlar Destekler, Nasıl Aktive Edilir?</t>
+          <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -22696,7 +22861,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="20.5" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>192.168.0.1</t>
@@ -22712,7 +22877,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -22887,7 +23052,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>AirTag Nedir ve Nasıl Kullanılır?</t>
+          <t>AirTag Nedir ve Nasıl Çalışır?</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -22957,7 +23122,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Ekran Görüntüsü Alma: Bilgisayar, Telefon ve Kısayollar</t>
+          <t>Bilgisayarda Ekran Görüntüsü Alma: Yöntemler ve Kısayollar</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -23027,7 +23192,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Yenilenmiş Telefon: Garanti, Kalite Sınıfları ve Satın Alma</t>
+          <t>Yenilenmiş Telefon Ne Demek? Garanti ve Kalite Sınıfları</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -23781,7 +23946,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="34" customHeight="1">
+    <row r="60" ht="20.5" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
           <t>esim nasıl alınır</t>
@@ -23797,7 +23962,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>eSIM: Nedir, Hangi Telefonlar Destekler, Nasıl Aktive Edilir?</t>
+          <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -24096,7 +24261,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="20.5" customHeight="1">
+    <row r="69" ht="34" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
           <t>modem arayüzü</t>
@@ -24112,7 +24277,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -24278,7 +24443,7 @@
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>7600</v>
+        <v>18100</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
@@ -24287,12 +24452,12 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Kısa içerik</t>
+          <t>Pillar</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -24302,7 +24467,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
+          <t>Öneri kapsamındadır</t>
         </is>
       </c>
     </row>
@@ -24392,7 +24557,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -24462,7 +24627,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -24602,7 +24767,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Telefondan Telefona Veri Aktarma: Android, iPhone ve Numara Taşıma</t>
+          <t>Telefondan Telefona Veri Aktarma: Android ve iPhone</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -25181,7 +25346,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="20.5" customHeight="1">
+    <row r="100" ht="34" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
           <t>192.168.1.1 giriş</t>
@@ -25197,7 +25362,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -25722,7 +25887,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -25748,7 +25913,7 @@
         </is>
       </c>
       <c r="B116" s="7" t="n">
-        <v>5300</v>
+        <v>18100</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
@@ -25827,7 +25992,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Ekran Görüntüsü Alma: Bilgisayar, Telefon ve Kısayollar</t>
+          <t>Bilgisayarda Ekran Görüntüsü Alma: Yöntemler ve Kısayollar</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -25958,7 +26123,7 @@
         </is>
       </c>
       <c r="B122" s="7" t="n">
-        <v>5000</v>
+        <v>880</v>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
@@ -25967,12 +26132,12 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Kısa içerik</t>
+          <t>Pillar</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -25982,7 +26147,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
+          <t>Öneri kapsamındadır</t>
         </is>
       </c>
     </row>
@@ -25993,7 +26158,7 @@
         </is>
       </c>
       <c r="B123" s="7" t="n">
-        <v>5000</v>
+        <v>2900</v>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
@@ -26002,12 +26167,12 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Yurt Dışından Getirilen Telefonun IMEI Kaydı: Ücret, Süre ve Adımlar</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>Kısa içerik</t>
+          <t>Pillar</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -26017,7 +26182,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
+          <t>Öneri kapsamındadır</t>
         </is>
       </c>
     </row>
@@ -26938,7 +27103,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Abone İşlemleri &amp; Hat</t>
+          <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
@@ -26994,7 +27159,7 @@
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>AirTag Nedir ve Nasıl Kullanılır?</t>
+          <t>AirTag Nedir ve Nasıl Çalışır?</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -27482,7 +27647,7 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Yenilenmiş Telefon: Garanti, Kalite Sınıfları ve Satın Alma</t>
+          <t>Yenilenmiş Telefon Ne Demek? Garanti ve Kalite Sınıfları</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -27674,40 +27839,40 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>150300</v>
+        <v>158600</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>84280</v>
+        <v>89780</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>90610</v>
+        <v>96010</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>111930</v>
+        <v>116530</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>115110</v>
+        <v>121110</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>82980</v>
+        <v>87480</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>85470</v>
+        <v>89790</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>111560</v>
+        <v>115960</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>157920</v>
+        <v>166060</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>119290</v>
+        <v>124010</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>116320</v>
+        <v>120920</v>
       </c>
       <c r="N17" s="17" t="n">
-        <v>137360</v>
+        <v>144660</v>
       </c>
       <c r="O17" s="8" t="inlineStr">
         <is>
@@ -27715,7 +27880,7 @@
         </is>
       </c>
       <c r="P17" s="7" t="n">
-        <v>157920</v>
+        <v>166060</v>
       </c>
       <c r="Q17" s="8" t="inlineStr">
         <is>
@@ -27784,71 +27949,71 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Apple Arcade Nedir?</t>
+          <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Dijital Araç &amp; Uygulama</t>
+          <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>10500</v>
+        <v>30080</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>7800</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>6000</v>
+        <v>22320</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>20270</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>22600</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>6000</v>
+        <v>16860</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>5700</v>
+        <v>17150</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>5700</v>
-      </c>
-      <c r="J19" s="16" t="n">
-        <v>11000</v>
+        <v>15400</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>24760</v>
       </c>
       <c r="K19" s="16" t="n">
-        <v>11000</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>9500</v>
+        <v>33800</v>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>33800</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>11000</v>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>9000</v>
+        <v>32100</v>
+      </c>
+      <c r="N19" s="16" t="n">
+        <v>34000</v>
       </c>
       <c r="O19" s="8" t="inlineStr">
         <is>
-          <t>Mart</t>
+          <t>Aralık</t>
         </is>
       </c>
       <c r="P19" s="7" t="n">
-        <v>12000</v>
+        <v>34000</v>
       </c>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>Ocak</t>
+          <t>Ekim</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
+          <t>Ekran Yansıtma: Telefondan Televizyona Görüntü Aktarma</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -27857,40 +28022,40 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>30080</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>22320</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>20270</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>22600</v>
+        <v>48000</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>39200</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>38900</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>41900</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>16860</v>
+        <v>30200</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>17150</v>
+        <v>21020</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>15400</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>24760</v>
-      </c>
-      <c r="K20" s="16" t="n">
-        <v>33800</v>
-      </c>
-      <c r="L20" s="16" t="n">
-        <v>33800</v>
-      </c>
-      <c r="M20" s="16" t="n">
-        <v>32100</v>
+        <v>21660</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>43700</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>39100</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>41900</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>47100</v>
       </c>
       <c r="N20" s="16" t="n">
-        <v>34000</v>
+        <v>51500</v>
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
@@ -27898,7 +28063,7 @@
         </is>
       </c>
       <c r="P20" s="7" t="n">
-        <v>34000</v>
+        <v>51500</v>
       </c>
       <c r="Q20" s="8" t="inlineStr">
         <is>
@@ -27906,10 +28071,10 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Ekran Yansıtma: Telefondan Televizyona Görüntü Aktarma</t>
+          <t>Telefon Nasıl Sıfırlanır?</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -27918,235 +28083,235 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>48000</v>
+        <v>13300</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>39200</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>38900</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>41900</v>
+        <v>10800</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>8300</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>30200</v>
+        <v>8600</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>21020</v>
+        <v>8900</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>21660</v>
-      </c>
-      <c r="J21" s="17" t="n">
-        <v>43700</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>39100</v>
+        <v>7220</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>14400</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>12700</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>41900</v>
+        <v>11400</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>47100</v>
-      </c>
-      <c r="N21" s="16" t="n">
-        <v>51500</v>
+        <v>12200</v>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>12900</v>
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
+          <t>Ağustos</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="n">
+        <v>14400</v>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>Haziran</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KVKK Nedir? Kişisel Verilerin Korunması Kanunu</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Güvenlik &amp; Gizlilik</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>16400</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>17200</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>16400</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>16400</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>13700</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>16400</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>13400</v>
+      </c>
+      <c r="J22" s="15" t="n">
+        <v>13100</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>13400</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>13100</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>16100</v>
+      </c>
+      <c r="N22" s="16" t="n">
+        <v>20000</v>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
           <t>Aralık</t>
         </is>
       </c>
-      <c r="P21" s="7" t="n">
-        <v>51500</v>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
+      <c r="P22" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Telefon Nasıl Sıfırlanır?</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Cihaz &amp; Donanım</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>13300</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>10800</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>8300</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>8600</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>8900</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>7220</v>
-      </c>
-      <c r="J22" s="16" t="n">
-        <v>14400</v>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v>12700</v>
-      </c>
-      <c r="L22" s="7" t="n">
-        <v>11400</v>
-      </c>
-      <c r="M22" s="17" t="n">
-        <v>12200</v>
-      </c>
-      <c r="N22" s="17" t="n">
-        <v>12900</v>
-      </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>Ağustos</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="n">
-        <v>14400</v>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>Haziran</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1">
+    <row r="23" ht="21" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>KVKK Nedir? Kişisel Verilerin Korunması Kanunu</t>
+          <t>Hat Devri: Ücret ve İşlem Adımları</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Güvenlik &amp; Gizlilik</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>16400</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>17200</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>16400</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>16400</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>13700</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>16400</v>
+          <t>Abone İşlemleri &amp; Hat</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>4480</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>2990</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>3120</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>2990</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>2380</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>2990</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>13400</v>
-      </c>
-      <c r="J23" s="15" t="n">
-        <v>13100</v>
-      </c>
-      <c r="K23" s="18" t="n">
-        <v>13400</v>
-      </c>
-      <c r="L23" s="15" t="n">
-        <v>13100</v>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>16100</v>
-      </c>
-      <c r="N23" s="16" t="n">
-        <v>20000</v>
+        <v>3120</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>3900</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>3780</v>
+      </c>
+      <c r="L23" s="16" t="n">
+        <v>4600</v>
+      </c>
+      <c r="M23" s="16" t="n">
+        <v>4600</v>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>3780</v>
       </c>
       <c r="O23" s="8" t="inlineStr">
         <is>
-          <t>Aralık</t>
+          <t>Kasım</t>
         </is>
       </c>
       <c r="P23" s="7" t="n">
-        <v>20000</v>
+        <v>4600</v>
       </c>
       <c r="Q23" s="8" t="inlineStr">
         <is>
-          <t>Ekim</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1">
+          <t>Eylül</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Hat Devri: Ücret ve İşlem Adımları</t>
+          <t>Apple Arcade Nedir?</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Abone İşlemleri &amp; Hat</t>
+          <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
       <c r="C24" s="16" t="n">
-        <v>4480</v>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>2990</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>3120</v>
+        <v>8100</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>6600</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>2990</v>
+        <v>4400</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>2380</v>
+        <v>4400</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>2990</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>3120</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>3900</v>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>3780</v>
-      </c>
-      <c r="L24" s="16" t="n">
-        <v>4600</v>
+        <v>4400</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>4400</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>8100</v>
+      </c>
+      <c r="K24" s="16" t="n">
+        <v>8100</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>6600</v>
       </c>
       <c r="M24" s="16" t="n">
-        <v>4600</v>
+        <v>8100</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>3780</v>
+        <v>6600</v>
       </c>
       <c r="O24" s="8" t="inlineStr">
         <is>
+          <t>Ocak</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
           <t>Kasım</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t>Eylül</t>
         </is>
       </c>
     </row>
@@ -28333,10 +28498,10 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>eSIM: Nedir, Hangi Telefonlar Destekler, Nasıl Aktive Edilir?</t>
+          <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -28394,10 +28559,10 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>E-Posta Kurulumu ve Yönetimi: Hesap Açma, Aktarma, Güvenlik</t>
+          <t>E-Posta Adresi Nedir, Nasıl Açılır?</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -28580,7 +28745,7 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Telefondan Telefona Veri Aktarma: Android, iPhone ve Numara Taşıma</t>
+          <t>Telefondan Telefona Veri Aktarma: Android ve iPhone</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -28641,7 +28806,7 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Ekran Görüntüsü Alma: Bilgisayar, Telefon ve Kısayollar</t>
+          <t>Bilgisayarda Ekran Görüntüsü Alma: Yöntemler ve Kısayollar</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -28824,7 +28989,7 @@
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>IP Adresi Sorgulama ve IP Adresi Değiştirme</t>
+          <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -28882,10 +29047,10 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="34" customHeight="1">
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Chrome Eklentisi Nasıl Eklenir ve Kaldırılır?</t>
+          <t>En İyi Chrome Eklentileri: Hangisi Ne İşe Yarar?</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -28946,7 +29111,7 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
+          <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -28955,40 +29120,40 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>268800</v>
+        <v>304040</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>256200</v>
+        <v>280130</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>256500</v>
+        <v>280860</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>247780</v>
+        <v>271210</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>242700</v>
+        <v>266260</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>245300</v>
+        <v>268560</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>258200</v>
+        <v>287020</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>239600</v>
+        <v>276370</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>238100</v>
+        <v>274170</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>238000</v>
-      </c>
-      <c r="M38" s="18" t="n">
-        <v>232900</v>
+        <v>268510</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>262910</v>
       </c>
       <c r="N38" s="7" t="n">
-        <v>268200</v>
+        <v>297710</v>
       </c>
       <c r="O38" s="8" t="inlineStr">
         <is>
@@ -28996,7 +29161,7 @@
         </is>
       </c>
       <c r="P38" s="7" t="n">
-        <v>268800</v>
+        <v>304040</v>
       </c>
       <c r="Q38" s="19" t="inlineStr">
         <is>

--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,11 +87,23 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0010332F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="0010332F"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="195">
     <fill>
       <patternFill/>
     </fill>
@@ -120,22 +132,947 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
+        <fgColor rgb="00EA885F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00EC8E53"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="00E88367"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
+        <fgColor rgb="00EA875F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E88269"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E98661"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E77F6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E67C73"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0057BB8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2A132"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0097BB56"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EC8D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF9645"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8BC2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E98464"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E77E6F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EA8760"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E98563"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E88466"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E88368"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EB8C57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7806D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EE934B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EE944A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E98564"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D7BC21"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EC8E54"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E77F6D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EA885E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ED914F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ED9050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EE9547"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A0BB4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0073BB74"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2A034"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8816A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E77E70"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF9843"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E98662"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EA895D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EC8E55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F19C3B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF9941"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2BC0B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF9744"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A924"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ABBC46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5AA23"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1BC0D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBBC04"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F29F36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3A42D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F09A3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B5BC3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBBB06"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAB80B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAB80A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAB909"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2A134"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EB8B59"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FABA07"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B3BC3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F09A40"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EE9646"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8816B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFBC28"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7B117"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8B313"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9B50F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1BC19"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4A827"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9B60E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F19E38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EE9449"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4A62A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EC8F51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F09B3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5AB22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8BC20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BABC39"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0076BB71"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EB8A5B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6AB21"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8B314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7806C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAB80C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8B215"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B0BC41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F19E39"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8BC06"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8BC2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDBC1D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9B510"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8B411"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009CBB52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6AC20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6AE1D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FABC05"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005BBB87"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0079BB6F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007DBB6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBBC1E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DFBC1B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BEBC36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3A330"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ABBC45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCBC1D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0086BB63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0089BB61"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F09C3C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EC8F52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EE9548"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A5BB4B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0BC1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BCBC38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8B412"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0069BB7C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4A729"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BEBC35"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0BC27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F19F37"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D2BC26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A826"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F09B3E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E67D71"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ED914E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AFBC42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBBC2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6BC2F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1BC0C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007FBB6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7AF1B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3BC0B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ED924D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EA895C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4A62B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8B216"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF9646"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A2BB4D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0069BB7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCBC2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEBC1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDBC0F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0094BB58"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6BC08"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A3BB4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9BC12"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4A52B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EB8C58"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0066BB7E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0072BB74"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008CBB5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7BC08"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7BC14"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2A133"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F09A3E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7AF1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5BC09"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDBC10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBBB05"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3BC18"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0BC34"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A1BB4D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF9842"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0080BB69"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0065BB7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3BC0A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4BC16"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005CBB86"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0071BB75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0077BB70"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F09940"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006FBB76"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E98465"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006FBB77"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4BC09"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2A035"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EB8B58"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7816B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFBC0E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BFBC35"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0085BB64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0074BB72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F19F36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4BC3E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8BC07"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0082BB67"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0063BB80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EB8D56"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,7 +1110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -217,25 +1154,580 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="39" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="41" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="42" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="43" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="44" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="45" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="46" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="47" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="48" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="49" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="50" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="51" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="52" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="53" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="54" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="55" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="56" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="57" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="58" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="59" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="60" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="61" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="62" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="63" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="64" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="65" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="66" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="67" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="68" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="69" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="70" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="71" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="72" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="73" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="74" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="75" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="76" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="77" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="78" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="79" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="80" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="81" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="82" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="83" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="84" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="85" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="86" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="87" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="88" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="89" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="90" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="91" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="92" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="93" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="94" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="95" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="96" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="97" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="98" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="99" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="100" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="101" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="102" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="103" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="104" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="105" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="106" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="107" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="108" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="109" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="110" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="111" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="112" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="113" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="114" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="115" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="116" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="117" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="118" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="119" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="120" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="121" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="122" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="123" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="124" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="125" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="126" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="127" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="128" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="129" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="130" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="131" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="132" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="133" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="134" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="135" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="136" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="137" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="138" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="139" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="140" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="141" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="142" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="143" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="144" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="145" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="146" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="147" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="148" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="149" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="150" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="151" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="152" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="153" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="154" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="155" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="156" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="157" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="158" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="159" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="160" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="161" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="162" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="163" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="164" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="165" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="166" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="167" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="168" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="169" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="170" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="171" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="172" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="173" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="174" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="175" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="176" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="177" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="178" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="179" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="180" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="181" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="182" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="183" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="184" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="185" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="186" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="187" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="188" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="189" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="190" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="191" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="192" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="193" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="194" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1499,7 +2991,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Çıplak genel ad; tek bir arama niyeti taşımıyor.</t>
+          <t>Jenerik ad; tek bir arama niyeti taşımıyor.</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1521,7 +3013,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Çıplak genel ad; tek bir arama niyeti taşımıyor.</t>
+          <t>Jenerik ad; tek bir arama niyeti taşımıyor.</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1873,7 +3365,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Çıplak kısaltma; tek başına arama niyetini taşımıyor.</t>
+          <t>Jenerik kısaltma; tek başına arama niyetini taşımıyor.</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2137,7 +3629,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Çıplak kısaltma; tek başına arama niyetini taşımıyor.</t>
+          <t>Jenerik kısaltma; tek başına arama niyetini taşımıyor.</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2465,7 +3957,7 @@
       <c r="F68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="20" t="inlineStr">
+      <c r="A69" s="205" t="inlineStr">
         <is>
           <t>Öneri kümelerindeki değişim</t>
         </is>
@@ -2973,7 +4465,7 @@
       <c r="F88" s="2" t="n"/>
     </row>
     <row r="89" ht="34" customHeight="1">
-      <c r="A89" s="21" t="inlineStr">
+      <c r="A89" s="206" t="inlineStr">
         <is>
           <t>Çakışma ve cannibalization kontrolü</t>
         </is>
@@ -10072,7 +11564,7 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>1. Yazının hedefi çıplak marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek'
+          <t>1. Yazının hedefi jenerik marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek'
 2. Kullanım senaryoları bölümü eklenebilir: telefonda kullanım, dosya yükleme, görsel oluşturma
 3. ChatGPT ile karşılaştırma tablosu eklenebilir
 4. Ücretsiz ve ücretli sürüm farkı ayrı ara başlıkta verilebilir
@@ -10099,7 +11591,7 @@
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>1. Yazının hedefi çıplak marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek' açıklanır
+          <t>1. Yazının hedefi jenerik marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek' açıklanır
 2. Kullanım senaryoları bölümü eklenebilir: telefonda kullanım, dosya yükleme, görsel oluşturma adım adım anlatılır
 3. ChatGPT ile karşılaştırma tablosu eklenebilir
 4. Ücretsiz ve ücretli sürüm farkı ayrı ara başlıkta verilebilir
@@ -10108,7 +11600,7 @@
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>Yazının impression'ı çıplak marka aramasından gelmektedir ve bu aramada sonuç sayfasının üst sıraları Google'ın kendi mülkleridir; CTR'ın bu aramada yükselmesi beklenmemelidir. Kazanım uzun kuyruk sorularındadır.</t>
+          <t>Yazının impression'ı jenerik marka aramasından gelmektedir ve bu aramada sonuç sayfasının üst sıraları Google'ın kendi mülkleridir; CTR'ın bu aramada yükselmesi beklenmemelidir. Kazanım uzun kuyruk sorularındadır.</t>
         </is>
       </c>
       <c r="Z7" s="7" t="n">
@@ -10124,7 +11616,7 @@
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>Yazı altı ayda 16.3 milyon impression alıp 2.125 click getirmiştir. Sorun içerikte değil, çıplak marka aramasının sonuç sayfasında: üst sıralar Google'ın kendi adreslerinde. Kazanım, kullanım ve karşılaştırma sorularında.</t>
+          <t>Yazı altı ayda 16.3 milyon impression alıp 2.125 click getirmiştir. Sorun içerikte değil, jenerik marka aramasının sonuç sayfasında: üst sıralar Google'ın kendi adreslerinde. Kazanım, kullanım ve karşılaştırma sorularında.</t>
         </is>
       </c>
     </row>
@@ -26883,10 +28375,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -26902,7 +28394,8 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -26927,6 +28420,7 @@
       <c r="O1" s="2" t="n"/>
       <c r="P1" s="2" t="n"/>
       <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -26946,6 +28440,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -27030,6 +28525,11 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
+          <t>Peak İndeksi</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
           <t>Önerilen Yayın Ayı</t>
         </is>
       </c>
@@ -27048,37 +28548,37 @@
       <c r="C4" s="15" t="n">
         <v>2490</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <v>3400</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="17" t="n">
         <v>1880</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="18" t="n">
         <v>2480</v>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="19" t="n">
         <v>1720</v>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" s="20" t="n">
         <v>2320</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="21" t="n">
         <v>1270</v>
       </c>
-      <c r="J4" s="15" t="n">
+      <c r="J4" s="22" t="n">
         <v>910</v>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K4" s="23" t="n">
         <v>18400</v>
       </c>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="24" t="n">
         <v>6000</v>
       </c>
-      <c r="M4" s="16" t="n">
+      <c r="M4" s="25" t="n">
         <v>15000</v>
       </c>
-      <c r="N4" s="15" t="n">
+      <c r="N4" s="26" t="n">
         <v>3280</v>
       </c>
       <c r="O4" s="8" t="inlineStr">
@@ -27089,13 +28589,16 @@
       <c r="P4" s="7" t="n">
         <v>18400</v>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="n">
+        <v>373</v>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Google Güvenli Arama: Açma, Kapatma ve Aile Filtresi</t>
@@ -27106,40 +28609,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="27" t="n">
         <v>121800</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="28" t="n">
         <v>283600</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="26" t="n">
         <v>96200</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="23" t="n">
         <v>408000</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="29" t="n">
         <v>71580</v>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" s="30" t="n">
         <v>53700</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="22" t="n">
         <v>47970</v>
       </c>
-      <c r="J5" s="15" t="n">
+      <c r="J5" s="31" t="n">
         <v>78500</v>
       </c>
-      <c r="K5" s="15" t="n">
+      <c r="K5" s="32" t="n">
         <v>73800</v>
       </c>
-      <c r="L5" s="15" t="n">
+      <c r="L5" s="33" t="n">
         <v>69400</v>
       </c>
-      <c r="M5" s="15" t="n">
+      <c r="M5" s="34" t="n">
         <v>66600</v>
       </c>
-      <c r="N5" s="15" t="n">
+      <c r="N5" s="22" t="n">
         <v>48200</v>
       </c>
       <c r="O5" s="8" t="inlineStr">
@@ -27150,7 +28653,10 @@
       <c r="P5" s="7" t="n">
         <v>408000</v>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="Q5" s="8" t="n">
+        <v>345</v>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
         <is>
           <t>Şubat</t>
         </is>
@@ -27167,40 +28673,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="35" t="n">
         <v>17100</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="36" t="n">
         <v>11900</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="37" t="n">
         <v>20100</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="38" t="n">
         <v>20400</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="39" t="n">
         <v>14100</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="23" t="n">
         <v>64400</v>
       </c>
-      <c r="I6" s="16" t="n">
+      <c r="I6" s="40" t="n">
         <v>43280</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="41" t="n">
         <v>18000</v>
       </c>
-      <c r="K6" s="15" t="n">
+      <c r="K6" s="26" t="n">
         <v>17700</v>
       </c>
-      <c r="L6" s="15" t="n">
+      <c r="L6" s="42" t="n">
         <v>11780</v>
       </c>
-      <c r="M6" s="15" t="n">
+      <c r="M6" s="22" t="n">
         <v>10400</v>
       </c>
-      <c r="N6" s="15" t="n">
+      <c r="N6" s="22" t="n">
         <v>10420</v>
       </c>
       <c r="O6" s="8" t="inlineStr">
@@ -27211,7 +28717,10 @@
       <c r="P6" s="7" t="n">
         <v>64400</v>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="8" t="n">
+        <v>298</v>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t>Nisan</t>
         </is>
@@ -27228,40 +28737,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="43" t="n">
         <v>4390</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="31" t="n">
         <v>4290</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="44" t="n">
         <v>5200</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="45" t="n">
         <v>5110</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="46" t="n">
         <v>5600</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="47" t="n">
         <v>12280</v>
       </c>
-      <c r="I7" s="16" t="n">
+      <c r="I7" s="23" t="n">
         <v>14870</v>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="48" t="n">
         <v>13900</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K7" s="49" t="n">
         <v>6570</v>
       </c>
-      <c r="L7" s="15" t="n">
+      <c r="L7" s="22" t="n">
         <v>3310</v>
       </c>
-      <c r="M7" s="15" t="n">
+      <c r="M7" s="50" t="n">
         <v>3780</v>
       </c>
-      <c r="N7" s="15" t="n">
+      <c r="N7" s="51" t="n">
         <v>3490</v>
       </c>
       <c r="O7" s="8" t="inlineStr">
@@ -27272,7 +28781,10 @@
       <c r="P7" s="7" t="n">
         <v>14870</v>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="n">
+        <v>216</v>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>Mayıs</t>
         </is>
@@ -27289,40 +28801,40 @@
           <t>Abone İşlemleri &amp; Hat</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="52" t="n">
         <v>25400</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="53" t="n">
         <v>20400</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="27" t="n">
         <v>25100</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="54" t="n">
         <v>21300</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="31" t="n">
         <v>20700</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>21000</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="22" t="n">
         <v>17700</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="55" t="n">
         <v>22600</v>
       </c>
-      <c r="K8" s="7" t="n">
+      <c r="K8" s="56" t="n">
         <v>26700</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="57" t="n">
         <v>25700</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="57" t="n">
         <v>25700</v>
       </c>
-      <c r="N8" s="16" t="n">
+      <c r="N8" s="23" t="n">
         <v>53500</v>
       </c>
       <c r="O8" s="8" t="inlineStr">
@@ -27333,7 +28845,10 @@
       <c r="P8" s="7" t="n">
         <v>53500</v>
       </c>
-      <c r="Q8" s="8" t="inlineStr">
+      <c r="Q8" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
@@ -27350,40 +28865,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="58" t="n">
         <v>12100</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="59" t="n">
         <v>8100</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="43" t="n">
         <v>6600</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="43" t="n">
         <v>6600</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="22" t="n">
         <v>5400</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="43" t="n">
         <v>6600</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="43" t="n">
         <v>6600</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="43" t="n">
         <v>6600</v>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="K9" s="60" t="n">
         <v>9900</v>
       </c>
-      <c r="L9" s="16" t="n">
+      <c r="L9" s="23" t="n">
         <v>18100</v>
       </c>
-      <c r="M9" s="16" t="n">
+      <c r="M9" s="58" t="n">
         <v>12100</v>
       </c>
-      <c r="N9" s="16" t="n">
+      <c r="N9" s="58" t="n">
         <v>12100</v>
       </c>
       <c r="O9" s="8" t="inlineStr">
@@ -27394,7 +28909,10 @@
       <c r="P9" s="7" t="n">
         <v>18100</v>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="8" t="n">
+        <v>196</v>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
@@ -27411,40 +28929,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="59" t="n">
         <v>2900</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="59" t="n">
         <v>2900</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="23" t="n">
         <v>6600</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="61" t="n">
         <v>5400</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="62" t="n">
         <v>3600</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="63" t="n">
         <v>4400</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="22" t="n">
         <v>1900</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="62" t="n">
         <v>3600</v>
       </c>
-      <c r="K10" s="15" t="n">
+      <c r="K10" s="59" t="n">
         <v>2900</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="62" t="n">
         <v>3600</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="62" t="n">
         <v>3600</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="N10" s="62" t="n">
         <v>3600</v>
       </c>
       <c r="O10" s="8" t="inlineStr">
@@ -27455,7 +28973,10 @@
       <c r="P10" s="7" t="n">
         <v>6600</v>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
+      <c r="Q10" s="8" t="n">
+        <v>176</v>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
@@ -27472,40 +28993,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="64" t="n">
         <v>109080</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="65" t="n">
         <v>88700</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="66" t="n">
         <v>92300</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="67" t="n">
         <v>85100</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="53" t="n">
         <v>70480</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="27" t="n">
         <v>82460</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="22" t="n">
         <v>63690</v>
       </c>
-      <c r="J11" s="16" t="n">
+      <c r="J11" s="68" t="n">
         <v>128600</v>
       </c>
-      <c r="K11" s="16" t="n">
+      <c r="K11" s="23" t="n">
         <v>154600</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="69" t="n">
         <v>108300</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="70" t="n">
         <v>106200</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="N11" s="71" t="n">
         <v>106600</v>
       </c>
       <c r="O11" s="8" t="inlineStr">
@@ -27516,7 +29037,10 @@
       <c r="P11" s="7" t="n">
         <v>154600</v>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="Q11" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
@@ -27533,40 +29057,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="72" t="n">
         <v>4400</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="72" t="n">
         <v>4400</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="72" t="n">
         <v>4400</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="73" t="n">
         <v>3600</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="73" t="n">
         <v>3600</v>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" s="74" t="n">
         <v>2900</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="74" t="n">
         <v>2900</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="22" t="n">
         <v>2400</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="68" t="n">
         <v>5400</v>
       </c>
-      <c r="L12" s="16" t="n">
+      <c r="L12" s="23" t="n">
         <v>6600</v>
       </c>
-      <c r="M12" s="16" t="n">
+      <c r="M12" s="68" t="n">
         <v>5400</v>
       </c>
-      <c r="N12" s="16" t="n">
+      <c r="N12" s="68" t="n">
         <v>5400</v>
       </c>
       <c r="O12" s="8" t="inlineStr">
@@ -27577,7 +29101,10 @@
       <c r="P12" s="7" t="n">
         <v>6600</v>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="8" t="n">
+        <v>154</v>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
@@ -27594,40 +29121,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="75" t="n">
         <v>3600</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="75" t="n">
         <v>3600</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="73" t="n">
         <v>2900</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="16" t="n">
         <v>2400</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="22" t="n">
         <v>1900</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="22" t="n">
         <v>1900</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="22" t="n">
         <v>1900</v>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="68" t="n">
         <v>4400</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="23" t="n">
         <v>5400</v>
       </c>
-      <c r="L13" s="16" t="n">
+      <c r="L13" s="23" t="n">
         <v>5400</v>
       </c>
-      <c r="M13" s="16" t="n">
+      <c r="M13" s="23" t="n">
         <v>5400</v>
       </c>
-      <c r="N13" s="17" t="n">
+      <c r="N13" s="68" t="n">
         <v>4400</v>
       </c>
       <c r="O13" s="8" t="inlineStr">
@@ -27638,7 +29165,10 @@
       <c r="P13" s="7" t="n">
         <v>5400</v>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="Q13" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
@@ -27655,40 +29185,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="76" t="n">
         <v>13180</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="77" t="n">
         <v>9300</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="46" t="n">
         <v>9020</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="78" t="n">
         <v>9060</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="79" t="n">
         <v>7760</v>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H14" s="37" t="n">
         <v>8880</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="22" t="n">
         <v>7460</v>
       </c>
-      <c r="J14" s="16" t="n">
+      <c r="J14" s="23" t="n">
         <v>15400</v>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="K14" s="80" t="n">
         <v>12500</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="81" t="n">
         <v>10760</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="82" t="n">
         <v>10880</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="N14" s="83" t="n">
         <v>11020</v>
       </c>
       <c r="O14" s="8" t="inlineStr">
@@ -27699,7 +29229,10 @@
       <c r="P14" s="7" t="n">
         <v>15400</v>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
@@ -27716,40 +29249,40 @@
           <t>Yapay Zeka</t>
         </is>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="23" t="n">
         <v>13700</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="41" t="n">
         <v>8200</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="84" t="n">
         <v>11000</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="85" t="n">
         <v>9500</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="84" t="n">
         <v>11000</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="86" t="n">
         <v>10200</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" s="22" t="n">
         <v>7300</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="85" t="n">
         <v>9500</v>
       </c>
-      <c r="K15" s="15" t="n">
+      <c r="K15" s="22" t="n">
         <v>7300</v>
       </c>
-      <c r="L15" s="18" t="n">
+      <c r="L15" s="87" t="n">
         <v>9000</v>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="88" t="n">
         <v>8500</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="N15" s="89" t="n">
         <v>9400</v>
       </c>
       <c r="O15" s="8" t="inlineStr">
@@ -27760,7 +29293,10 @@
       <c r="P15" s="7" t="n">
         <v>13700</v>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
@@ -27777,40 +29313,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="86" t="n">
         <v>4900</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="89" t="n">
         <v>4480</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="86" t="n">
         <v>4900</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="90" t="n">
         <v>3900</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="91" t="n">
         <v>4200</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>3700</v>
       </c>
-      <c r="I16" s="15" t="n">
+      <c r="I16" s="22" t="n">
         <v>3400</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="86" t="n">
         <v>4900</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="92" t="n">
         <v>4600</v>
       </c>
-      <c r="L16" s="17" t="n">
+      <c r="L16" s="93" t="n">
         <v>5400</v>
       </c>
-      <c r="M16" s="16" t="n">
+      <c r="M16" s="23" t="n">
         <v>6700</v>
       </c>
-      <c r="N16" s="17" t="n">
+      <c r="N16" s="94" t="n">
         <v>5700</v>
       </c>
       <c r="O16" s="8" t="inlineStr">
@@ -27821,7 +29357,10 @@
       <c r="P16" s="7" t="n">
         <v>6700</v>
       </c>
-      <c r="Q16" s="8" t="inlineStr">
+      <c r="Q16" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
@@ -27838,40 +29377,40 @@
           <t>Abone İşlemleri &amp; Hat</t>
         </is>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="95" t="n">
         <v>158600</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="36" t="n">
         <v>89780</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="96" t="n">
         <v>96010</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="97" t="n">
         <v>116530</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="98" t="n">
         <v>121110</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="22" t="n">
         <v>87480</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="99" t="n">
         <v>89790</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="62" t="n">
         <v>115960</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="23" t="n">
         <v>166060</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="100" t="n">
         <v>124010</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="101" t="n">
         <v>120920</v>
       </c>
-      <c r="N17" s="17" t="n">
+      <c r="N17" s="102" t="n">
         <v>144660</v>
       </c>
       <c r="O17" s="8" t="inlineStr">
@@ -27882,7 +29421,10 @@
       <c r="P17" s="7" t="n">
         <v>166060</v>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="Q17" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
@@ -27899,40 +29441,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="103" t="n">
         <v>40600</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="22" t="n">
         <v>32760</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="91" t="n">
         <v>40100</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="57" t="n">
         <v>39520</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="104" t="n">
         <v>47980</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="75" t="n">
         <v>47280</v>
       </c>
-      <c r="I18" s="17" t="n">
+      <c r="I18" s="105" t="n">
         <v>52400</v>
       </c>
-      <c r="J18" s="16" t="n">
+      <c r="J18" s="23" t="n">
         <v>62700</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="106" t="n">
         <v>50500</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="107" t="n">
         <v>46120</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="108" t="n">
         <v>45920</v>
       </c>
-      <c r="N18" s="18" t="n">
+      <c r="N18" s="27" t="n">
         <v>38920</v>
       </c>
       <c r="O18" s="8" t="inlineStr">
@@ -27943,13 +29485,16 @@
       <c r="P18" s="7" t="n">
         <v>62700</v>
       </c>
-      <c r="Q18" s="8" t="inlineStr">
+      <c r="Q18" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="21" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
@@ -27960,40 +29505,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="109" t="n">
         <v>30080</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="110" t="n">
         <v>22320</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="103" t="n">
         <v>20270</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="111" t="n">
         <v>22600</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="53" t="n">
         <v>16860</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="43" t="n">
         <v>17150</v>
       </c>
-      <c r="I19" s="15" t="n">
+      <c r="I19" s="22" t="n">
         <v>15400</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="112" t="n">
         <v>24760</v>
       </c>
-      <c r="K19" s="16" t="n">
+      <c r="K19" s="113" t="n">
         <v>33800</v>
       </c>
-      <c r="L19" s="16" t="n">
+      <c r="L19" s="113" t="n">
         <v>33800</v>
       </c>
-      <c r="M19" s="16" t="n">
+      <c r="M19" s="114" t="n">
         <v>32100</v>
       </c>
-      <c r="N19" s="16" t="n">
+      <c r="N19" s="23" t="n">
         <v>34000</v>
       </c>
       <c r="O19" s="8" t="inlineStr">
@@ -28004,13 +29549,16 @@
       <c r="P19" s="7" t="n">
         <v>34000</v>
       </c>
-      <c r="Q19" s="8" t="inlineStr">
+      <c r="Q19" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Ekran Yansıtma: Telefondan Televizyona Görüntü Aktarma</t>
@@ -28021,40 +29569,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="115" t="n">
         <v>48000</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="116" t="n">
         <v>39200</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="117" t="n">
         <v>38900</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="118" t="n">
         <v>41900</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="119" t="n">
         <v>30200</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="22" t="n">
         <v>21020</v>
       </c>
-      <c r="I20" s="15" t="n">
+      <c r="I20" s="21" t="n">
         <v>21660</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="120" t="n">
         <v>43700</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K20" s="121" t="n">
         <v>39100</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="118" t="n">
         <v>41900</v>
       </c>
-      <c r="M20" s="17" t="n">
+      <c r="M20" s="122" t="n">
         <v>47100</v>
       </c>
-      <c r="N20" s="16" t="n">
+      <c r="N20" s="23" t="n">
         <v>51500</v>
       </c>
       <c r="O20" s="8" t="inlineStr">
@@ -28065,7 +29613,10 @@
       <c r="P20" s="7" t="n">
         <v>51500</v>
       </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="Q20" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
@@ -28082,40 +29633,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="123" t="n">
         <v>13300</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="64" t="n">
         <v>10800</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="124" t="n">
         <v>9000</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="125" t="n">
         <v>8300</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="126" t="n">
         <v>8600</v>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H21" s="67" t="n">
         <v>8900</v>
       </c>
-      <c r="I21" s="15" t="n">
+      <c r="I21" s="22" t="n">
         <v>7220</v>
       </c>
-      <c r="J21" s="16" t="n">
+      <c r="J21" s="23" t="n">
         <v>14400</v>
       </c>
-      <c r="K21" s="17" t="n">
+      <c r="K21" s="127" t="n">
         <v>12700</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="128" t="n">
         <v>11400</v>
       </c>
-      <c r="M21" s="17" t="n">
+      <c r="M21" s="129" t="n">
         <v>12200</v>
       </c>
-      <c r="N21" s="17" t="n">
+      <c r="N21" s="109" t="n">
         <v>12900</v>
       </c>
       <c r="O21" s="8" t="inlineStr">
@@ -28126,13 +29677,16 @@
       <c r="P21" s="7" t="n">
         <v>14400</v>
       </c>
-      <c r="Q21" s="8" t="inlineStr">
+      <c r="Q21" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1">
+    <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>KVKK Nedir? Kişisel Verilerin Korunması Kanunu</t>
@@ -28143,40 +29697,40 @@
           <t>Güvenlik &amp; Gizlilik</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="72" t="n">
         <v>16400</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="121" t="n">
         <v>17200</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="72" t="n">
         <v>16400</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="72" t="n">
         <v>16400</v>
       </c>
-      <c r="G22" s="18" t="n">
+      <c r="G22" s="31" t="n">
         <v>13700</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="72" t="n">
         <v>16400</v>
       </c>
-      <c r="I22" s="18" t="n">
+      <c r="I22" s="19" t="n">
         <v>13400</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="22" t="n">
         <v>13100</v>
       </c>
-      <c r="K22" s="18" t="n">
+      <c r="K22" s="19" t="n">
         <v>13400</v>
       </c>
-      <c r="L22" s="15" t="n">
+      <c r="L22" s="22" t="n">
         <v>13100</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="130" t="n">
         <v>16100</v>
       </c>
-      <c r="N22" s="16" t="n">
+      <c r="N22" s="23" t="n">
         <v>20000</v>
       </c>
       <c r="O22" s="8" t="inlineStr">
@@ -28187,7 +29741,10 @@
       <c r="P22" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="Q22" s="8" t="inlineStr">
+      <c r="Q22" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
@@ -28204,40 +29761,40 @@
           <t>Abone İşlemleri &amp; Hat</t>
         </is>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="131" t="n">
         <v>4480</v>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="65" t="n">
         <v>2990</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="132" t="n">
         <v>3120</v>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F23" s="65" t="n">
         <v>2990</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="22" t="n">
         <v>2380</v>
       </c>
-      <c r="H23" s="15" t="n">
+      <c r="H23" s="65" t="n">
         <v>2990</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="132" t="n">
         <v>3120</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="133" t="n">
         <v>3900</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" s="134" t="n">
         <v>3780</v>
       </c>
-      <c r="L23" s="16" t="n">
+      <c r="L23" s="23" t="n">
         <v>4600</v>
       </c>
-      <c r="M23" s="16" t="n">
+      <c r="M23" s="23" t="n">
         <v>4600</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="N23" s="134" t="n">
         <v>3780</v>
       </c>
       <c r="O23" s="8" t="inlineStr">
@@ -28248,7 +29805,10 @@
       <c r="P23" s="7" t="n">
         <v>4600</v>
       </c>
-      <c r="Q23" s="8" t="inlineStr">
+      <c r="Q23" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
@@ -28265,40 +29825,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="23" t="n">
         <v>8100</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="135" t="n">
         <v>5400</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="121" t="n">
         <v>6600</v>
       </c>
-      <c r="F24" s="15" t="n">
+      <c r="F24" s="22" t="n">
         <v>4400</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="22" t="n">
         <v>4400</v>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="H24" s="22" t="n">
         <v>4400</v>
       </c>
-      <c r="I24" s="15" t="n">
+      <c r="I24" s="22" t="n">
         <v>4400</v>
       </c>
-      <c r="J24" s="16" t="n">
+      <c r="J24" s="23" t="n">
         <v>8100</v>
       </c>
-      <c r="K24" s="16" t="n">
+      <c r="K24" s="23" t="n">
         <v>8100</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="121" t="n">
         <v>6600</v>
       </c>
-      <c r="M24" s="16" t="n">
+      <c r="M24" s="23" t="n">
         <v>8100</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N24" s="121" t="n">
         <v>6600</v>
       </c>
       <c r="O24" s="8" t="inlineStr">
@@ -28309,13 +29869,16 @@
       <c r="P24" s="7" t="n">
         <v>8100</v>
       </c>
-      <c r="Q24" s="8" t="inlineStr">
+      <c r="Q24" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>PUK, PIN ve SIM Kilidi: Kod Öğrenme ve Kilit Açma</t>
@@ -28326,40 +29889,40 @@
           <t>Abone İşlemleri &amp; Hat</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="136" t="n">
         <v>64200</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="45" t="n">
         <v>51880</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="137" t="n">
         <v>56900</v>
       </c>
-      <c r="F25" s="15" t="n">
+      <c r="F25" s="22" t="n">
         <v>47800</v>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="138" t="n">
         <v>54100</v>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H25" s="139" t="n">
         <v>47980</v>
       </c>
-      <c r="I25" s="18" t="n">
+      <c r="I25" s="140" t="n">
         <v>52200</v>
       </c>
-      <c r="J25" s="16" t="n">
+      <c r="J25" s="23" t="n">
         <v>74000</v>
       </c>
-      <c r="K25" s="17" t="n">
+      <c r="K25" s="141" t="n">
         <v>67000</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" s="142" t="n">
         <v>64700</v>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="143" t="n">
         <v>65100</v>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="N25" s="144" t="n">
         <v>61700</v>
       </c>
       <c r="O25" s="8" t="inlineStr">
@@ -28370,7 +29933,10 @@
       <c r="P25" s="7" t="n">
         <v>74000</v>
       </c>
-      <c r="Q25" s="8" t="inlineStr">
+      <c r="Q25" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
@@ -28387,40 +29953,40 @@
           <t>Güvenlik &amp; Gizlilik</t>
         </is>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="145" t="n">
         <v>30700</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="86" t="n">
         <v>25800</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="146" t="n">
         <v>25100</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="146" t="n">
         <v>25100</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="22" t="n">
         <v>20500</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" s="86" t="n">
         <v>25800</v>
       </c>
-      <c r="I26" s="15" t="n">
+      <c r="I26" s="19" t="n">
         <v>21000</v>
       </c>
-      <c r="J26" s="16" t="n">
+      <c r="J26" s="23" t="n">
         <v>32100</v>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="K26" s="147" t="n">
         <v>26600</v>
       </c>
-      <c r="L26" s="18" t="n">
+      <c r="L26" s="148" t="n">
         <v>22500</v>
       </c>
-      <c r="M26" s="15" t="n">
+      <c r="M26" s="149" t="n">
         <v>21700</v>
       </c>
-      <c r="N26" s="17" t="n">
+      <c r="N26" s="145" t="n">
         <v>30700</v>
       </c>
       <c r="O26" s="8" t="inlineStr">
@@ -28431,7 +29997,10 @@
       <c r="P26" s="7" t="n">
         <v>32100</v>
       </c>
-      <c r="Q26" s="8" t="inlineStr">
+      <c r="Q26" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
@@ -28448,40 +30017,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="69" t="n">
         <v>15280</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="150" t="n">
         <v>14120</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="151" t="n">
         <v>14780</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="92" t="n">
         <v>14390</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="57" t="n">
         <v>13420</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H27" s="152" t="n">
         <v>13290</v>
       </c>
-      <c r="I27" s="15" t="n">
+      <c r="I27" s="22" t="n">
         <v>11880</v>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J27" s="153" t="n">
         <v>17200</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="128" t="n">
         <v>15900</v>
       </c>
-      <c r="L27" s="17" t="n">
+      <c r="L27" s="154" t="n">
         <v>18400</v>
       </c>
-      <c r="M27" s="17" t="n">
+      <c r="M27" s="23" t="n">
         <v>18780</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="N27" s="155" t="n">
         <v>16320</v>
       </c>
       <c r="O27" s="8" t="inlineStr">
@@ -28492,7 +30061,10 @@
       <c r="P27" s="7" t="n">
         <v>18780</v>
       </c>
-      <c r="Q27" s="8" t="inlineStr">
+      <c r="Q27" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
@@ -28509,40 +30081,40 @@
           <t>Abone İşlemleri &amp; Hat</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="156" t="n">
         <v>28200</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="22" t="n">
         <v>21900</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="22" t="n">
         <v>21900</v>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="30" t="n">
         <v>22100</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="157" t="n">
         <v>27700</v>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="H28" s="30" t="n">
         <v>22100</v>
       </c>
-      <c r="I28" s="18" t="n">
+      <c r="I28" s="41" t="n">
         <v>23400</v>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="23" t="n">
         <v>32600</v>
       </c>
-      <c r="K28" s="17" t="n">
+      <c r="K28" s="23" t="n">
         <v>32600</v>
       </c>
-      <c r="L28" s="17" t="n">
+      <c r="L28" s="158" t="n">
         <v>30600</v>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="157" t="n">
         <v>27700</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="N28" s="159" t="n">
         <v>27400</v>
       </c>
       <c r="O28" s="8" t="inlineStr">
@@ -28553,7 +30125,10 @@
       <c r="P28" s="7" t="n">
         <v>32600</v>
       </c>
-      <c r="Q28" s="8" t="inlineStr">
+      <c r="Q28" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
@@ -28570,40 +30145,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="160" t="n">
         <v>17000</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="161" t="n">
         <v>15600</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="162" t="n">
         <v>14100</v>
       </c>
-      <c r="F29" s="18" t="n">
+      <c r="F29" s="162" t="n">
         <v>14100</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="163" t="n">
         <v>12800</v>
       </c>
-      <c r="H29" s="18" t="n">
+      <c r="H29" s="60" t="n">
         <v>14300</v>
       </c>
-      <c r="I29" s="15" t="n">
+      <c r="I29" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="J29" s="18" t="n">
+      <c r="J29" s="60" t="n">
         <v>14300</v>
       </c>
-      <c r="K29" s="17" t="n">
+      <c r="K29" s="23" t="n">
         <v>18500</v>
       </c>
-      <c r="L29" s="17" t="n">
+      <c r="L29" s="123" t="n">
         <v>17500</v>
       </c>
-      <c r="M29" s="17" t="n">
+      <c r="M29" s="164" t="n">
         <v>18200</v>
       </c>
-      <c r="N29" s="17" t="n">
+      <c r="N29" s="164" t="n">
         <v>18200</v>
       </c>
       <c r="O29" s="8" t="inlineStr">
@@ -28614,7 +30189,10 @@
       <c r="P29" s="7" t="n">
         <v>18500</v>
       </c>
-      <c r="Q29" s="8" t="inlineStr">
+      <c r="Q29" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
@@ -28631,40 +30209,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="165" t="n">
         <v>9700</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="166" t="n">
         <v>9400</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="165" t="n">
         <v>9700</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="167" t="n">
         <v>8200</v>
       </c>
-      <c r="G30" s="18" t="n">
+      <c r="G30" s="82" t="n">
         <v>7900</v>
       </c>
-      <c r="H30" s="18" t="n">
+      <c r="H30" s="82" t="n">
         <v>7900</v>
       </c>
-      <c r="I30" s="18" t="n">
+      <c r="I30" s="82" t="n">
         <v>7900</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="22" t="n">
         <v>6300</v>
       </c>
-      <c r="K30" s="15" t="n">
+      <c r="K30" s="88" t="n">
         <v>7000</v>
       </c>
-      <c r="L30" s="15" t="n">
+      <c r="L30" s="88" t="n">
         <v>7000</v>
       </c>
-      <c r="M30" s="17" t="n">
+      <c r="M30" s="23" t="n">
         <v>10000</v>
       </c>
-      <c r="N30" s="17" t="n">
+      <c r="N30" s="165" t="n">
         <v>9700</v>
       </c>
       <c r="O30" s="8" t="inlineStr">
@@ -28675,7 +30253,10 @@
       <c r="P30" s="7" t="n">
         <v>10000</v>
       </c>
-      <c r="Q30" s="8" t="inlineStr">
+      <c r="Q30" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
@@ -28692,40 +30273,40 @@
           <t>Abone İşlemleri &amp; Hat</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="168" t="n">
         <v>226000</v>
       </c>
-      <c r="D31" s="18" t="n">
+      <c r="D31" s="22" t="n">
         <v>187300</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="169" t="n">
         <v>207100</v>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="F31" s="170" t="n">
         <v>203700</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="124" t="n">
         <v>204500</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="171" t="n">
         <v>214900</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="98" t="n">
         <v>216900</v>
       </c>
-      <c r="J31" s="17" t="n">
+      <c r="J31" s="23" t="n">
         <v>256400</v>
       </c>
-      <c r="K31" s="7" t="n">
+      <c r="K31" s="172" t="n">
         <v>223100</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="L31" s="173" t="n">
         <v>224900</v>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="116" t="n">
         <v>228500</v>
       </c>
-      <c r="N31" s="7" t="n">
+      <c r="N31" s="174" t="n">
         <v>221400</v>
       </c>
       <c r="O31" s="8" t="inlineStr">
@@ -28736,13 +30317,16 @@
       <c r="P31" s="7" t="n">
         <v>256400</v>
       </c>
-      <c r="Q31" s="8" t="inlineStr">
+      <c r="Q31" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1">
+    <row r="32" ht="21" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Telefondan Telefona Veri Aktarma: Android ve iPhone</t>
@@ -28753,40 +30337,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C32" s="23" t="n">
         <v>22100</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="175" t="n">
         <v>19080</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="175" t="n">
         <v>19080</v>
       </c>
-      <c r="F32" s="18" t="n">
+      <c r="F32" s="138" t="n">
         <v>16700</v>
       </c>
-      <c r="G32" s="18" t="n">
+      <c r="G32" s="56" t="n">
         <v>16800</v>
       </c>
-      <c r="H32" s="15" t="n">
+      <c r="H32" s="22" t="n">
         <v>15000</v>
       </c>
-      <c r="I32" s="15" t="n">
+      <c r="I32" s="20" t="n">
         <v>15580</v>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="J32" s="176" t="n">
         <v>19820</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="K32" s="177" t="n">
         <v>20490</v>
       </c>
-      <c r="L32" s="18" t="n">
+      <c r="L32" s="178" t="n">
         <v>16580</v>
       </c>
-      <c r="M32" s="17" t="n">
+      <c r="M32" s="179" t="n">
         <v>21220</v>
       </c>
-      <c r="N32" s="17" t="n">
+      <c r="N32" s="180" t="n">
         <v>21800</v>
       </c>
       <c r="O32" s="8" t="inlineStr">
@@ -28797,7 +30381,10 @@
       <c r="P32" s="7" t="n">
         <v>22100</v>
       </c>
-      <c r="Q32" s="8" t="inlineStr">
+      <c r="Q32" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
@@ -28814,40 +30401,40 @@
           <t>Cihaz &amp; Donanım</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="93" t="n">
         <v>31380</v>
       </c>
-      <c r="D33" s="18" t="n">
+      <c r="D33" s="119" t="n">
         <v>28090</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" s="181" t="n">
         <v>30480</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="143" t="n">
         <v>31980</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="149" t="n">
         <v>25890</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="182" t="n">
         <v>30980</v>
       </c>
-      <c r="I33" s="15" t="n">
+      <c r="I33" s="31" t="n">
         <v>25690</v>
       </c>
-      <c r="J33" s="15" t="n">
+      <c r="J33" s="22" t="n">
         <v>24780</v>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="K33" s="116" t="n">
         <v>31290</v>
       </c>
-      <c r="L33" s="17" t="n">
+      <c r="L33" s="183" t="n">
         <v>35520</v>
       </c>
-      <c r="M33" s="17" t="n">
+      <c r="M33" s="184" t="n">
         <v>34820</v>
       </c>
-      <c r="N33" s="17" t="n">
+      <c r="N33" s="23" t="n">
         <v>35680</v>
       </c>
       <c r="O33" s="8" t="inlineStr">
@@ -28858,7 +30445,10 @@
       <c r="P33" s="7" t="n">
         <v>35680</v>
       </c>
-      <c r="Q33" s="8" t="inlineStr">
+      <c r="Q33" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
@@ -28875,40 +30465,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C34" s="17" t="n">
+      <c r="C34" s="185" t="n">
         <v>133600</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="186" t="n">
         <v>112180</v>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="187" t="n">
         <v>134380</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F34" s="37" t="n">
         <v>110680</v>
       </c>
-      <c r="G34" s="18" t="n">
+      <c r="G34" s="53" t="n">
         <v>107320</v>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="H34" s="188" t="n">
         <v>106880</v>
       </c>
-      <c r="I34" s="18" t="n">
+      <c r="I34" s="22" t="n">
         <v>104920</v>
       </c>
-      <c r="J34" s="18" t="n">
+      <c r="J34" s="57" t="n">
         <v>112100</v>
       </c>
-      <c r="K34" s="7" t="n">
+      <c r="K34" s="169" t="n">
         <v>114100</v>
       </c>
-      <c r="L34" s="17" t="n">
+      <c r="L34" s="23" t="n">
         <v>136700</v>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="92" t="n">
         <v>116500</v>
       </c>
-      <c r="N34" s="17" t="n">
+      <c r="N34" s="189" t="n">
         <v>134400</v>
       </c>
       <c r="O34" s="8" t="inlineStr">
@@ -28919,7 +30509,10 @@
       <c r="P34" s="7" t="n">
         <v>136700</v>
       </c>
-      <c r="Q34" s="8" t="inlineStr">
+      <c r="Q34" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
@@ -28936,40 +30529,40 @@
           <t>Abone İşlemleri &amp; Hat</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="190" t="n">
         <v>7000</v>
       </c>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="171" t="n">
         <v>6700</v>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E35" s="23" t="n">
         <v>8200</v>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="F35" s="171" t="n">
         <v>6700</v>
       </c>
-      <c r="G35" s="18" t="n">
+      <c r="G35" s="171" t="n">
         <v>6700</v>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H35" s="22" t="n">
         <v>5700</v>
       </c>
-      <c r="I35" s="15" t="n">
+      <c r="I35" s="22" t="n">
         <v>5700</v>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="J35" s="190" t="n">
         <v>7000</v>
       </c>
-      <c r="K35" s="17" t="n">
+      <c r="K35" s="23" t="n">
         <v>8200</v>
       </c>
-      <c r="L35" s="17" t="n">
+      <c r="L35" s="23" t="n">
         <v>8200</v>
       </c>
-      <c r="M35" s="17" t="n">
+      <c r="M35" s="23" t="n">
         <v>8200</v>
       </c>
-      <c r="N35" s="17" t="n">
+      <c r="N35" s="23" t="n">
         <v>8200</v>
       </c>
       <c r="O35" s="8" t="inlineStr">
@@ -28980,7 +30573,10 @@
       <c r="P35" s="7" t="n">
         <v>8200</v>
       </c>
-      <c r="Q35" s="19" t="inlineStr">
+      <c r="Q35" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="R35" s="191" t="inlineStr">
         <is>
           <t>sezon etkisi sınırlı</t>
         </is>
@@ -28997,40 +30593,40 @@
           <t>Altyapı &amp; Bağlantı</t>
         </is>
       </c>
-      <c r="C36" s="17" t="n">
+      <c r="C36" s="23" t="n">
         <v>135900</v>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="188" t="n">
         <v>114800</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="192" t="n">
         <v>119700</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="83" t="n">
         <v>123500</v>
       </c>
-      <c r="G36" s="18" t="n">
+      <c r="G36" s="99" t="n">
         <v>114100</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H36" s="193" t="n">
         <v>116100</v>
       </c>
-      <c r="I36" s="18" t="n">
+      <c r="I36" s="22" t="n">
         <v>113400</v>
       </c>
-      <c r="J36" s="18" t="n">
+      <c r="J36" s="194" t="n">
         <v>114200</v>
       </c>
-      <c r="K36" s="7" t="n">
+      <c r="K36" s="149" t="n">
         <v>115700</v>
       </c>
-      <c r="L36" s="7" t="n">
+      <c r="L36" s="184" t="n">
         <v>134100</v>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="195" t="n">
         <v>125500</v>
       </c>
-      <c r="N36" s="7" t="n">
+      <c r="N36" s="196" t="n">
         <v>128800</v>
       </c>
       <c r="O36" s="8" t="inlineStr">
@@ -29041,13 +30637,16 @@
       <c r="P36" s="7" t="n">
         <v>135900</v>
       </c>
-      <c r="Q36" s="19" t="inlineStr">
+      <c r="Q36" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="R36" s="191" t="inlineStr">
         <is>
           <t>sezon etkisi sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>En İyi Chrome Eklentileri: Hangisi Ne İşe Yarar?</t>
@@ -29058,40 +30657,40 @@
           <t>Dijital Araç &amp; Uygulama</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="197" t="n">
         <v>18900</v>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="104" t="n">
         <v>16900</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="153" t="n">
         <v>18400</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="84" t="n">
         <v>17300</v>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="76" t="n">
         <v>18100</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="H37" s="84" t="n">
         <v>17300</v>
       </c>
-      <c r="I37" s="15" t="n">
+      <c r="I37" s="22" t="n">
         <v>14000</v>
       </c>
-      <c r="J37" s="18" t="n">
+      <c r="J37" s="130" t="n">
         <v>16500</v>
       </c>
-      <c r="K37" s="7" t="n">
+      <c r="K37" s="153" t="n">
         <v>18400</v>
       </c>
-      <c r="L37" s="7" t="n">
+      <c r="L37" s="153" t="n">
         <v>18400</v>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="23" t="n">
         <v>19700</v>
       </c>
-      <c r="N37" s="7" t="n">
+      <c r="N37" s="198" t="n">
         <v>19200</v>
       </c>
       <c r="O37" s="8" t="inlineStr">
@@ -29102,13 +30701,16 @@
       <c r="P37" s="7" t="n">
         <v>19700</v>
       </c>
-      <c r="Q37" s="19" t="inlineStr">
+      <c r="Q37" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="R37" s="191" t="inlineStr">
         <is>
           <t>sezon etkisi sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
@@ -29119,40 +30721,40 @@
           <t>Altyapı &amp; Bağlantı</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="23" t="n">
         <v>304040</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="151" t="n">
         <v>280130</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" s="130" t="n">
         <v>280860</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="78" t="n">
         <v>271210</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="20" t="n">
         <v>266260</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H38" s="55" t="n">
         <v>268560</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="I38" s="117" t="n">
         <v>287020</v>
       </c>
-      <c r="J38" s="7" t="n">
+      <c r="J38" s="89" t="n">
         <v>276370</v>
       </c>
-      <c r="K38" s="7" t="n">
+      <c r="K38" s="199" t="n">
         <v>274170</v>
       </c>
-      <c r="L38" s="7" t="n">
+      <c r="L38" s="26" t="n">
         <v>268510</v>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="22" t="n">
         <v>262910</v>
       </c>
-      <c r="N38" s="7" t="n">
+      <c r="N38" s="123" t="n">
         <v>297710</v>
       </c>
       <c r="O38" s="8" t="inlineStr">
@@ -29163,13 +30765,16 @@
       <c r="P38" s="7" t="n">
         <v>304040</v>
       </c>
-      <c r="Q38" s="19" t="inlineStr">
+      <c r="Q38" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="R38" s="191" t="inlineStr">
         <is>
           <t>sezon etkisi sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="36" customHeight="1">
+    <row r="39" ht="34" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Spam Ne Demek? Spam Mesaj ve Aramaları Engelleme</t>
@@ -29180,40 +30785,40 @@
           <t>Güvenlik &amp; Gizlilik</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="177" t="n">
         <v>27000</v>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="200" t="n">
         <v>26700</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" s="71" t="n">
         <v>25400</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="71" t="n">
         <v>25400</v>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="71" t="n">
         <v>25400</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="71" t="n">
         <v>25400</v>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="I39" s="201" t="n">
         <v>25600</v>
       </c>
-      <c r="J39" s="7" t="n">
+      <c r="J39" s="23" t="n">
         <v>28200</v>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="K39" s="202" t="n">
         <v>27500</v>
       </c>
-      <c r="L39" s="18" t="n">
+      <c r="L39" s="22" t="n">
         <v>22900</v>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="95" t="n">
         <v>27700</v>
       </c>
-      <c r="N39" s="7" t="n">
+      <c r="N39" s="203" t="n">
         <v>28000</v>
       </c>
       <c r="O39" s="8" t="inlineStr">
@@ -29224,7 +30829,10 @@
       <c r="P39" s="7" t="n">
         <v>28000</v>
       </c>
-      <c r="Q39" s="19" t="inlineStr">
+      <c r="Q39" s="8" t="n">
+        <v>107</v>
+      </c>
+      <c r="R39" s="191" t="inlineStr">
         <is>
           <t>sezon etkisi sınırlı</t>
         </is>
@@ -29241,40 +30849,40 @@
           <t>Güvenlik &amp; Gizlilik</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="23" t="n">
         <v>5400</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="23" t="n">
         <v>5400</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="23" t="n">
         <v>5400</v>
       </c>
-      <c r="F40" s="18" t="n">
+      <c r="F40" s="204" t="n">
         <v>4600</v>
       </c>
-      <c r="G40" s="18" t="n">
+      <c r="G40" s="22" t="n">
         <v>4480</v>
       </c>
-      <c r="H40" s="18" t="n">
+      <c r="H40" s="204" t="n">
         <v>4600</v>
       </c>
-      <c r="I40" s="18" t="n">
+      <c r="I40" s="22" t="n">
         <v>4480</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J40" s="23" t="n">
         <v>5400</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="K40" s="202" t="n">
         <v>5280</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="L40" s="202" t="n">
         <v>5280</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="202" t="n">
         <v>5280</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N40" s="202" t="n">
         <v>5280</v>
       </c>
       <c r="O40" s="8" t="inlineStr">
@@ -29285,7 +30893,10 @@
       <c r="P40" s="7" t="n">
         <v>5400</v>
       </c>
-      <c r="Q40" s="19" t="inlineStr">
+      <c r="Q40" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="R40" s="191" t="inlineStr">
         <is>
           <t>sezon etkisi sınırlı</t>
         </is>
@@ -29309,6 +30920,7 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -29318,7 +30930,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Hücrelerde kümedeki kelimelerin o aydaki toplam araması yazılıdır. Renk, ayın yıl ortalamasına oranını gösterir: ortalamanın %25 ve üzerinde olan aylar koyu yeşil, %12-24 üzeri açık yeşil, ortalama bandı nötr, %6-14 altı açık kırmızı, %15 ve fazlası altı kırmızıdır. Peak indeksi 115 altında kalan önerilerde sezon etkisi sınırlı sayılmış, yayın ayı puana göre belirlenmiştir.</t>
+          <t>Hücrelerde kümedeki kelimelerin o aydaki toplam araması yazılıdır. Renk satır içi konumu gösterir: satırın en düşük ayı kırmızı, orta bant sarı, en yüksek ayı yeşildir. Peak indeksi sütunu, peak ayının yıl ortalamasına oranıdır (100 = yıl ortalaması). Peak indeksi 115 altında kalan önerilerde sezon etkisi sınırlı sayılmış, yayın ayı puana göre belirlenmiştir.</t>
         </is>
       </c>
       <c r="C42" s="12" t="n"/>
@@ -29336,6 +30948,7 @@
       <c r="O42" s="12" t="n"/>
       <c r="P42" s="12" t="n"/>
       <c r="Q42" s="12" t="n"/>
+      <c r="R42" s="12" t="n"/>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -29363,12 +30976,13 @@
       <c r="O43" s="12" t="n"/>
       <c r="P43" s="12" t="n"/>
       <c r="Q43" s="12" t="n"/>
+      <c r="R43" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B43:Q43"/>
-    <mergeCell ref="B42:Q42"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B43:R43"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="B42:R42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -17,9 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Sezonsallık" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Mevcut Blog Performansı" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Planlanan İçerikler" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Kelime Denetimi" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Yöntem ve Kaynaklar" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 Terim Sözlüğü" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Yöntem ve Kaynaklar" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Terim Sözlüğü" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,12 +94,6 @@
       <b val="1"/>
       <color rgb="0010332F"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0010332F"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="195">
@@ -1110,7 +1103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1724,12 +1717,6 @@
     <xf numFmtId="3" fontId="9" fillId="194" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2461,2779 +2448,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
-    <col width="64" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Öneri kümelerinden çıkarılan kelimeler | Konu, arama niyeti ve tek anlam denetimi</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="21" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Elenen Kelime</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Aylık Arama</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Dayanak</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="61" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>13600000</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfasının ilk beş sırası Google'ın kendi Gemini adresleri; yönlendirme amaçlı marka araması.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="61" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>imei sorgu</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>'imei sorgula' ile aynı sonuç sayfası; araç ve hizmet sayfası araması.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="61" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>imei sorgula</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>550000</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası e-Devlet ve BTK sorgulama araçları ile operatörlerin hizmet sayfaları; blog içeriğinin karşılığı değil.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="61" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>konum</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>368000</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası Google Haritalar ve konum aracı; bilgi amaçlı içerik ilk sırada yer almıyor.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>google gemini</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>368000</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Aynı marka adresleri; yönlendirme amaçlı arama.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="61" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>beyaz ekran</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>165000</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>İlk altı sıra beyaz ekran aracı ve uygulaması; sorun giderme içeriği ancak yedinci sıradan itibaren görünüyor.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="61" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>e posta</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>135000</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası Gmail ve Outlook giriş adresleri; yönlendirme amaçlı arama.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="74.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>90500</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve">İlk on sıranın tamamı operatörlerin altyapı sorgulama hizmet sayfaları; Turkcell </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>Superonline</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve"> sayfası da bu sırada yer alıyor.</t>
-          </r>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-    </row>
-    <row r="12" ht="61" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>alt yapı sorgulama</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>90500</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>'altyapı sorgulama' ile aynı hizmet sayfası kümesi; yazım varyantı.</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-    </row>
-    <row r="13" ht="61" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>ekran kartı</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>60500</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası fiyat listeleri ve mağaza kategorileri; ürün arama.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-    </row>
-    <row r="14" ht="61" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>ram</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>49500</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası bilgisayar bileşeni satan mağazalar; ürün arama.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-    </row>
-    <row r="15" ht="61" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>ssd</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>49500</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Bileşen satan mağaza sayfaları; 'ram' ve 'ekran kartı' ile aynı sınıf.</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="61" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>perplexity</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>49500</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası perplexity.ai ve site bağlantıları; yönlendirme amaçlı marka araması.</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="61" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>anakart</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>33100</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Bileşen satan mağaza sayfaları; 'ram' ve 'ekran kartı' ile aynı sınıf.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-    </row>
-    <row r="18" ht="61" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>güncellemeler</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>33100</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası dağınık: uygulama mağazası yardımı, forum ve oyun videosu bir arada; tek bir arama niyeti yok.</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="61" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>internet altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>33100</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Aynı hizmet sayfası kümesi.</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="61" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>fiber altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>33100</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Aynı hizmet sayfası kümesi.</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-    </row>
-    <row r="21" ht="61" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>qr kod</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n">
-        <v>33100</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası QR okuyucu ve oluşturucu araçları; bilgi amaçlı içerik altıncı sıradan sonra.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-    </row>
-    <row r="22" ht="61" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>uzantılar</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>27100</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası Chrome Web Mağazası ve alan adı uzantısı içerikleri; iki ayrı anlam bir arada.</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-    </row>
-    <row r="23" ht="61" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>taşınabilir internet</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>27100</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>İlk iki sıra operatörlerin ev interneti ürün sayfaları; Turkcell Superbox sayfası da bu sırada.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Ahrefs sonuç sayfası görüntüsü · Eylül 2026</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>wi-fi</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>22200</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Jenerik ad; tek bir arama niyeti taşımıyor.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>wifi</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>22200</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Jenerik ad; tek bir arama niyeti taşımıyor.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>bard</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>18100</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Farklı bir ürünün marka adı; önerinin konusuyla eşleşmiyor.</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Konu eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="47.5" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>type c şarj aleti</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>18100</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfasının tamamı şarj cihazı satan mağazalar; ürün araması.</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>türkiye posta kodu</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n">
-        <v>14800</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Posta kodu sorgulaması e-posta konusuyla ilgili değil.</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Konu eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="61" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>eklentiler</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>14800</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>'uzantılar' ile aynı sınıf; mağaza yönlendirmesi.</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="61" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>eklenti</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>14800</v>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>'uzantılar' ile aynı sınıf; mağaza yönlendirmesi.</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>sistemi</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>14800</v>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Anlam taşımayan kelime parçası.</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="47.5" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>hosting</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>14800</v>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası barındırma hizmeti satan sağlayıcılar; ticari arama.</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="47.5" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>type c kablo</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>14800</v>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Kablo satan mağaza sayfaları; 'type c şarj aleti' ile aynı sınıf.</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-    </row>
-    <row r="34" ht="61" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>192168.1.1</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>9900</v>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Ana kelimenin yazım varyantı; aynı sayfaya gidiyor, toplama iki kez girmemesi için çıkarıldı.</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Yazım varyantı</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="61" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>qr kodu</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>9900</v>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>'qr kod' ile aynı araç kümesi.</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>192.168</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>8100</v>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Eksik yazılmış adres; ana kelimenin varyantı.</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Yazım varyantı</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-    </row>
-    <row r="37" ht="61" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>oem ne demek</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>6600</v>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Kendi kısa içerik önerisinde hedefleniyor; iki sayfanın aynı kelimede yarışmaması için güncelleme kümesinden çıkarıldı.</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Başka öneriyle çakışma</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-    </row>
-    <row r="38" ht="61" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>192.168.01</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>5400</v>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Ana kelimenin yazım varyantı; aynı sayfaya gidiyor, toplama iki kez girmemesi için çıkarıldı.</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Yazım varyantı</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-    </row>
-    <row r="39" ht="61" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>altyapısız internet</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>5400</v>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası operatörlerin ev interneti ürün sayfaları; blog içeriği değil.</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-    </row>
-    <row r="40" ht="61" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>taşınabilir internet fiyatları</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>5400</v>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Fiyat araması; ürün sayfası karşılığı.</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n">
-        <v>5400</v>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Jenerik kısaltma; tek başına arama niyetini taşımıyor.</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>ping testi</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="n">
-        <v>4400</v>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası hız testi araçları; bilgi amaçlı içerik değil.</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-    </row>
-    <row r="43" ht="61" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>usb type c</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="n">
-        <v>4400</v>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Ürün araması; aynı sınıf. Yazının bilgi amaçlı hedefi 'type c nedir' ve 'usb-c nedir' kelimeleridir.</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-    </row>
-    <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>freedos nedir</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Kendi kısa içerik önerisinde hedefleniyor.</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Başka öneriyle çakışma</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>type c şarj kablosu</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Ürün araması; aynı sınıf.</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>type c adaptör</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Ürün araması; aynı sınıf.</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="61" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>otomatik güncellemeler</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>'güncellemeler' ile aynı dağınık sonuç sayfası.</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="47.5" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>mac ne demek</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Mac bilgisayar ve MAC adresi anlamları bir arada; tek anlam koşulunu sağlamıyor.</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-    </row>
-    <row r="49" ht="74.5" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>apple arcade</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası Apple'ın kendi hizmet adresi; yönlendirme amaçlı marka araması. Yazının hedefi 'apple arcade nedir' kelimesidir.</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
-    </row>
-    <row r="50" ht="61" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>fiber internet altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Aynı hizmet sayfası kümesi.</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>mesh wifi</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası mesh cihaz satışı; ticari arama.</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>usb c kablo</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Ürün araması; aynı sınıf.</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>puk</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Jenerik kısaltma; tek başına arama niyetini taşımıyor.</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Konu eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="61" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>ttnet fiber altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Aynı hizmet sayfası kümesi; ayrıca rakip marka adı taşıyor.</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>oem nedir</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Kendi kısa içerik önerisinde hedefleniyor.</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Başka öneriyle çakışma</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="47.5" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>gizli dns sunucusuna erişilemiyor</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>DNS hata giderme ayrı bir konu; barındırma içeriğiyle eşleşmiyor.</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>dns sunucusu yanıt vermiyor</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>DNS hata giderme ayrı bir konu.</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-    </row>
-    <row r="58" ht="34" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>adsl modem</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Cihaz araması.</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>vdsl internet</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Hizmet ve tarife araması; bilgilendirici yazı hedefi değil.</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
-    </row>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>mesh modem</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Cihaz araması.</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="61" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>eposta</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="n">
-        <v>880</v>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Yönlendirme amaçlı arama; 'e posta' ile aynı sonuç sayfası.</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Aynı sınıftaki kelimeyle örtüşen sonuç sayfası</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-    </row>
-    <row r="62" ht="47.5" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>airtag kedi tasması</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="n">
-        <v>880</v>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Ürün aksesuarı araması; AirTag tanımı sorusundan ayrı bir niyet.</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Konu eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
-    </row>
-    <row r="63" ht="47.5" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>işletim sistemleri hakkında aşağıdakilerden hangisi doğru değildir</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="n">
-        <v>390</v>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Sınav sorusu araması; içerikle karşılanmıyor.</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-    </row>
-    <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>mac ne</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="n">
-        <v>320</v>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Anlam taşımayan kelime parçası.</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-    </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>işletim sistemleri sadece bilgisayarlara özgü müdür</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Sınav sorusu araması; içerikle karşılanmıyor.</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Konu ve niyet eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-    </row>
-    <row r="66" ht="34" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>wifi şifresi kırma</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Yetkisiz erişim araması; marka içeriğine uygun değil.</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>Konu eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-    </row>
-    <row r="67" ht="34" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>instagram mavi tik nasıl alınır</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Hesap doğrulama başvurusu ayrı bir konu; küme dışında.</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>Konu eşleşmesi</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="205" t="inlineStr">
-        <is>
-          <t>Öneri kümelerindeki değişim</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-    </row>
-    <row r="70" ht="36" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Değişim</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>Öneri</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Başlık</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Önceki Aylık Arama</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>Sonraki Aylık Arama</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="34" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Modem Arayüzüne Giriş ve Modem Şifresi Değiştirme</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="n">
-        <v>454420</v>
-      </c>
-      <c r="E71" s="7" t="n">
-        <v>483870</v>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı. Havuzdan niteleyici kelime eklendi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="34" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Konum Paylaşma ve Numaradan Konum Bulma</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>415080</v>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>47080</v>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="47.5" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>öneri kaldırıldı</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>İnternet Altyapı Sorgulama: Adrese Göre Hız ve Teknoloji Kontrolü</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="n">
-        <v>256600</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Kümenin tamamı operatör hizmet sayfası aramasıdır; blog içeriğiyle karşılanmıyor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="34" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="n">
-        <v>218620</v>
-      </c>
-      <c r="E74" s="7" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="34" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>öneri kaldırıldı</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Telefonda Beyaz Ekran, Siyah Ekran ve Donma Sorunları</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="n">
-        <v>166000</v>
-      </c>
-      <c r="E75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Hacmin tamamı beyaz ekran aracı aramasından geliyordu; niteleyici kelime havuzda bulunmuyor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="34" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>Gizli Numara: Arama, Kapatma ve Numara Gizleme Ayarları</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="n">
-        <v>323300</v>
-      </c>
-      <c r="E76" s="7" t="n">
-        <v>327700</v>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı. Havuzdan niteleyici kelime eklendi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="47.5" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>Yurt Dışından Getirilen Telefonun IMEI Kaydı: Ücret, Süre ve Adımlar</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="n">
-        <v>1264130</v>
-      </c>
-      <c r="E77" s="7" t="n">
-        <v>169430</v>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı. Havuzdan niteleyici kelime eklendi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="34" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>E-Posta Kurulumu ve Yönetimi: Hesap Açma, Aktarma, Güvenlik</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="n">
-        <v>165780</v>
-      </c>
-      <c r="E78" s="7" t="n">
-        <v>15100</v>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="34" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>PUK, PIN ve SIM Kilidi: Kod Öğrenme ve Kilit Açma</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="n">
-        <v>67200</v>
-      </c>
-      <c r="E79" s="7" t="n">
-        <v>65300</v>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="34" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>öneri bölündü</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>K9</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Tarayıcı Eklentileri ve Güncellemeleri Yönetme</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="n">
-        <v>125880</v>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>33180</v>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Küme iki ayrı soruyu bir arada taşıyordu; her soru kendi kısa içeriğine ayrıldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="34" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>öneri kaldırıldı</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>QR Kod: Okutma, Oluşturma ve Güvenlik Riskleri</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="n">
-        <v>47400</v>
-      </c>
-      <c r="E81" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>Küme QR okuyucu ve oluşturucu aracı aramasından oluşuyordu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="34" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>öneri kaldırıldı</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>K10</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Perplexity Nedir? Yapay Zeka Arama Motoru</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="n">
-        <v>67600</v>
-      </c>
-      <c r="E82" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>İki kelime de marka yönlendirmesi; tanım araması havuzda yer almıyor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="34" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>öneri kaldırıldı</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Taşınabilir İnternet ve Mobil WiFi Cihazları</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>32500</v>
-      </c>
-      <c r="E83" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>İki kelime de ev interneti ürün sayfası aramasıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="34" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>K5</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>AirTag Nedir ve Nasıl Kullanılır?</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>21580</v>
-      </c>
-      <c r="E84" s="7" t="n">
-        <v>20700</v>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20.5" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>küme daraltıldı</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>K22</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Apple Arcade Nedir?</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="E85" s="7" t="n">
-        <v>6600</v>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen kelimeler çıkarıldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="34" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>güncelleme kümesi daraltıldı</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>14045400</v>
-      </c>
-      <c r="E86" s="7" t="n">
-        <v>77400</v>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>Niyeti eşleşmeyen ya da başka öneriyle çakışan kelimeler çıkarıldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="n"/>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n"/>
-    </row>
-    <row r="89" ht="34" customHeight="1">
-      <c r="A89" s="206" t="inlineStr">
-        <is>
-          <t>Çakışma ve cannibalization kontrolü</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="n"/>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="n"/>
-    </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Kontrol</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl yapıldı</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Sonuç</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n"/>
-    </row>
-    <row r="91" ht="47.5" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Öneri hedef kelimesi mevcut bir yazının arama sorgusuyla örtüşüyor mu?</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>37 önerinin hedef kelimeleri blogun 4.917 satırlık sorgu verisiyle karşılaştırıldı</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>Bulgu yok</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="2" t="n"/>
-    </row>
-    <row r="92" ht="47.5" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>Öneri, markanın kendi hizmet ya da ürün sayfasıyla yarışıyor mu?</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Yüksek hacimli kelimelerin sonuç sayfası tek tek görüntülendi</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>11 kelime havuzdan çıkarıldı</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-    </row>
-    <row r="93" ht="47.5" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>Yeni öneri, blogda yayında olan bir yazının konusunu tekrarlıyor mu?</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Havuzdaki her arama 196 yayındaki yazının konusuyla karşılaştırıldı</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>4 arama yeni yazı yerine güncelleme kapsamına bırakıldı</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
-      <c r="F93" s="2" t="n"/>
-    </row>
-    <row r="94" ht="47.5" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>Önerilen başlık, yayındaki bir başlığın benzeri mi?</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Her öneri başlığı 196 yazının başlığıyla karakter benzerliği üzerinden karşılaştırıldı (eşik 0.72)</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>2 bulgu</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
-    </row>
-    <row r="95" ht="34" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>İki öneri aynı kelimeyi hedefliyor mu?</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Kelime sahipliği tüm öneri kümelerinde karşılaştırıldı</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Bulgu yok</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="2" t="n"/>
-    </row>
-    <row r="96" ht="47.5" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>Bir kelime hem yeni öneride hem güncellemede hedefleniyor mu?</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Öneri ve güncelleme kümeleri karşılaştırıldı</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>Bulgu yok</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="n"/>
-    </row>
-    <row r="98" ht="21" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Bulgu Tipi</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>İlgili Öğe</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Kelime</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>Hacim</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>Karşılık</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20.5" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>imei sorgu</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="n">
-        <v>550000</v>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20.5" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>imei sorgula</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="n">
-        <v>550000</v>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20.5" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="n">
-        <v>90500</v>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20.5" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>alt yapı sorgulama</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="n">
-        <v>90500</v>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20.5" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>internet altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="n">
-        <v>33100</v>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20.5" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>fiber altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="n">
-        <v>33100</v>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20.5" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>taşınabilir internet</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="n">
-        <v>27100</v>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20.5" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>altyapısız internet</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="n">
-        <v>5400</v>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20.5" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>taşınabilir internet fiyatları</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="n">
-        <v>5400</v>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="34" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>fiber internet altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20.5" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Markanın kendi sayfası</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>ttnet fiber altyapı sorgulama</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Turkcell hizmet ya da ürün sayfası</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Kelime blog kümesinden çıkarıldı; hedefi ilgili hizmet sayfasıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="34" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>Mevcut yazının kapsamı</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>yeni öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>internet neden yavaş</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="n">
-        <v>6400</v>
-      </c>
-      <c r="E110" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/internet-neden-yavasladi-sorunun-kaynagini-adim-adim-bulma-rehberi</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>Yeni yazı önerilmedi; kelime mevcut yazının güncelleme kapsamına bırakıldı</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="34" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>Mevcut yazının kapsamı</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>yeni öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>internet neden yok</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="n">
-        <v>7700</v>
-      </c>
-      <c r="E111" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/internet-neden-yavasladi-sorunun-kaynagini-adim-adim-bulma-rehberi</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>Yeni yazı önerilmedi; kelime mevcut yazının güncelleme kapsamına bırakıldı</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="34" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>Mevcut yazının kapsamı</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>yeni öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>vpn nasıl açılır</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="n">
-        <v>3800</v>
-      </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/dijital-guvenligin-temel-bileseni-vpn-nedir</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>Yeni yazı önerilmedi; kelime mevcut yazının güncelleme kapsamına bırakıldı</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="34" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>Mevcut yazının kapsamı</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>yeni öneri havuzu</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>chatgpt ücretli mi</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="n">
-        <v>3900</v>
-      </c>
-      <c r="E113" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/chatgpt-nedir-adim-adim-chatgpt-kullanma-rehberi</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>Yeni yazı önerilmedi; kelime mevcut yazının güncelleme kapsamına bırakıldı</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="34" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>Başlık benzerliği</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>K15 · URL Nedir?</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/crm-nedir</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>Yalnız 'X nedir' başlık kalıbı benzeşmektedir; konular farklı olduğu için çakışma bulunmamaktadır</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="34" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>Başlık benzerliği</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>K15 · URL Nedir?</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/blog/unix-nedir</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>Yalnız 'X nedir' başlık kalıbı benzeşmektedir; konular farklı olduğu için çakışma bulunmamaktadır</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="2" t="n"/>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n"/>
-    </row>
-    <row r="117" ht="81" customHeight="1">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>YÖNTEM</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Bir kelime öneri kümesinde ancak üç koşulu birlikte sağladığında kalmaktadır: kelimenin önerinin konusunu niteleyerek adlandırması, sonuç sayfasının bilgi amaçlı içerikle karşılanması ve kelimenin ikinci bir yaygın anlamının bulunmaması. Alışveriş listesi, giriş sayfası, sorgulama aracı ya da markanın kendi hizmet sayfasıyla karşılanan kelimeler blog kümesine alınmamıştır.</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="n"/>
-      <c r="D117" s="12" t="n"/>
-      <c r="E117" s="2" t="n"/>
-      <c r="F117" s="2" t="n"/>
-    </row>
-    <row r="118" ht="51" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>DAYANAK</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Sonuç sayfası kontrolü Ahrefs görüntüsüyle yapılmıştır (Eylül 2026). Doğrudan görüntülenen kelimeler 'Ahrefs sonuç sayfası görüntüsü', aynı sınıfa giren kelimeler 'Aynı sınıftaki kelimeyle örtüşen sonuç sayfası' olarak işaretlenmiştir.</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="n"/>
-      <c r="D118" s="12" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B118:D118"/>
-    <mergeCell ref="B117:D117"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId6"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5342,7 +2556,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="81" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>KELİME DENETİMİ</t>
@@ -5350,7 +2564,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Her kelime konu, arama niyeti ve tek anlam koşullarına göre denetlenmiştir. Sonuç sayfası alışveriş listesi, giriş sayfası, sorgulama aracı ya da markanın kendi hizmet sayfasıyla karşılanan kelimeler kümelerden çıkarılmıştır; elenen kelimeler ve gerekçeleri 11 Kelime Denetimi sekmesindedir.</t>
+          <t>Her kelime konu, arama niyeti ve tek anlam koşullarına göre denetlenmiştir. Sonuç sayfası alışveriş listesi, giriş sayfası, sorgulama aracı ya da markanın kendi hizmet sayfasıyla karşılanan kelimeler kümelerden çıkarılmıştır; Bu ölçütle elenen kelimelerin bir bölümünde hedef sayfa blog değil, markanın kendi hizmet ya da ürün sayfasıdır: imei sorgulama, altyapı sorgulama ve taşınabilir internet aramaları bu gruptadır. Önerilerin yayındaki yazılarla ve birbiriyle çakışmadığı ayrıca denetlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -5458,7 +2672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10559,7 +7773,7 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t xml:space="preserve"> bloglarının sıraladığı, blogun yer almadığı kelimelerden seçilmiştir. Her kelime konu ve arama niyeti denetiminden geçirilmiştir; elenen kelimeler 11 Kelime Denetimi sekmesinde gerekçesiyle listelenmiştir. Bir kelime tek öneriye aittir; varyantlar toplama dahil edilmemiştir.</t>
+            <t xml:space="preserve"> bloglarının sıraladığı, blogun yer almadığı kelimelerden seçilmiştir. Her kelime konu ve arama niyeti denetiminden geçirilmiştir; eleme ölçütü 11 Yöntem ve Kaynaklar sekmesinde açıklanmıştır. Bir kelime tek öneriye aittir; varyantlar toplama dahil edilmemiştir.</t>
           </r>
         </is>
       </c>

--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -8129,7 +8129,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="142" customHeight="1">
+    <row r="4" ht="291" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/isletim-sistemi-nedir-ve-cesitleri-nelerdir</t>
@@ -8231,9 +8231,9 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>1. Mobil işletim sistemleri bölümü genişletilebilir
-2. Windows, macOS ve Linux karşılaştırması tablo hâlinde verilebilir
-3. FreeDOS ve işletim sistemsiz cihaz bölümü eklenebilir
+          <t>1. Windows, macOS ve Linux Karşılaştırması
+2. İşletim Sistemi Yalnız Bilgisayarlarda mı Bulunur?
+3. Android ve iOS Arasındaki Farklar
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: İşletim Sistemi Özellikleri Nelerdir?</t>
         </is>
       </c>
@@ -8268,14 +8268,16 @@
       </c>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>1. Mobil işletim sistemleri bölümü genişletilebilir
-2. Windows, macOS ve Linux karşılaştırması tablo hâlinde verilebilir
-3. FreeDOS ve işletim sistemsiz cihaz bölümü eklenebilir</t>
+          <t>1. 'Windows nedir' sorgusu 1.059 Impression alıyor ancak sayfa 9.7 ortalama sırada kalıyor; Windows, macOS ve Linux için üç ayrı H3 açılıp her birine sürüm adı, tipik kullanıcı profili ve donanım gereksinimi yazılabilir
+2. 'işletim sistemleri sadece bilgisayarlara özgü müdür' sorgusu 646 Impression ile 3.2 sırada geliyor, yani soru soruluyor ama yanıt bölümü yok: telefon, akıllı televizyon, akıllı saat ve araç sistemlerini kapsayan 'İşletim Sistemi Yalnız Bilgisayarlarda mı Bulunur?' başlığı eklenebilir
+3. Mobil tarafta Android ve iOS tek cümlede geçiyor; ikisi ayrı H3 olarak açılıp aralarındaki uygulama mağazası, güncelleme ve donanım farkı üç maddeyle verilebilir
+4. 'bilgisayar işletim sistemleri' ve 'işletim sistemleri nelerdir' kelimeleri gövdede hiç geçmiyor; mevcut 'İşletim Sistemi Çeşitleri Nelerdir?' başlığının açılış cümlesi bu iki kalıbı da karşılayacak biçimde yazılabilir
+5. 'işletim sistemleri hakkında aşağıdakilerden hangisi doğru değildir' sorgusu 4.221 Impression alıyor ve ödev kaynaklı; bu sorguya içerik yazılması önerilmez, ölçüm okunurken hesaba katılması yeterlidir açıklanır</t>
         </is>
       </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
-          <t>Sorgu eğitim amaçlı arama da içermektedir; tanım bölümü kısa ve alıntılanabilir tutulabilir.</t>
+          <t>Sürüm adları ve donanım gereksinimleri yıl içinde değişiyor; güncellenme tarihinin görünür tutulması bu yazıda değer taşıyor.</t>
         </is>
       </c>
       <c r="Z4" s="7" t="n">
@@ -8295,7 +8297,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="128.5" customHeight="1">
+    <row r="5" ht="261" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar</t>
@@ -8402,10 +8404,10 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>1. Hosting türleri karşılaştırması eklenebilir
-2. Domain ile ilişkisi açıklanabilir
-3. Küçük işletme için seçim kriterleri bölümü eklenebilir
-Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Hosting Nedir? Hangi Hizmetleri Sağlar? · İlginizi Çekebilir</t>
+          <t>1. Hosting Türleri Karşılaştırma Tablosu
+2. Domain ve Hosting Ayrı Ayrı mı Alınır?
+3. Küçük İşletme İçin Hangi Hosting Seçilir?
+Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Hosting Nedir? Hangi Hizmetleri Sağlar?</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
@@ -8439,14 +8441,39 @@
       </c>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>1. Hosting türleri karşılaştırması eklenebilir
-2. Domain ile ilişkisi açıklanabilir
-3. Küçük işletme için seçim kriterleri bölümü eklenebilir</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">1. Sayfa 'hosting' sorgusunda 31.2 ortalama sırada; bu sorguda ilk sayfaya girebilmek için mevcut 'Hosting Türleri Nelerdir?' başlığı tabloya çevrilebilir: paylaşımlı, VPS, bulut ve adanmış sunucu satırlarında kaynak paylaşımı, tipik trafik kapasitesi ve kimin için uygun olduğu üç sütunda verilir
+2. 'domain ve hosting nedir' sorgusu 4.6 sırada 409 Impression alıyor; mevcut fark bölümü iki cümlede kalıyor, alan adı ile barındırmanın ilişkisi bir örnek üzerinden anlatılıp 'ikisi ayrı ayrı mı alınır' sorusu yanıtlanabilir
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Türk Telekom</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un aynı sorguda 3. sıradaki yazısı 1.239 kelime ve konuyu tek uzun bölümde veriyor; bizim yazımız 12 ara başlıkla daha ayrıntılı, eksik olan derinlik değil seçim kriteri: 'Küçük İşletme İçin Hangi Hosting Seçilir?' başlığı altında aylık ziyaretçi bandına göre üç senaryo eklenebilir
+4. 'turkcell host' sorgusu 399 Impression ile 5.1 sırada geliyor; markanın barındırma hizmetine tek cümlelik bir bağlantı, arama niyetini karşılar açıklanır</t>
+          </r>
         </is>
       </c>
       <c r="Y5" s="4" t="inlineStr">
         <is>
-          <t>Sonuç sayfası ticari hizmet sayfalarından oluşmaktadır; açıklama yazısının ilk sıraya çıkması yapısal olarak sınırlıdır.</t>
+          <t>Fiyat bilgisi verilmemesi, kapasite ve kullanım senaryosu üzerinden anlatılması önerilir.</t>
         </is>
       </c>
       <c r="Z5" s="7" t="n">
@@ -8466,7 +8493,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="250" customHeight="1">
+    <row r="6" ht="261" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/nfc-nedir-nfc-ile-neler-yapilabilir</t>
@@ -8582,12 +8609,37 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>1. NFC özelliğinin telefonda nasıl açıldığı marka bazında eklenebilir
-2. IPhone ve Android ayrımı ara başlığa çıkarılabilir
-3. NFC destekleyen telefon listesi eklenebilir
-4. Temassız ödeme bölümü genişletilebilir
-5. NFC etiketi kullanımı eklenebilir
-Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: NFC Nedir, NFC ile Neler Yapılabilir? · İlginizi Çekebilir</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">1. NFC Etiketi Nedir, Ne İşe Yarar?
+2. NFC Kart Nedir?
+3. iPhone'da NFC Nasıl Açılır?
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Samsung</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve"> ve Xiaomi Cihazlarda NFC Nasıl Açılır?
+5. NFC Destekleyen Telefon Modelleri
+6. Telefonda NFC Anteni Nerede Bulunur?
+Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: NFC Nedir, NFC ile Neler Yapılabilir?</t>
+          </r>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
@@ -8655,16 +8707,40 @@
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>1. NFC özelliğinin telefonda nasıl açıldığı marka bazında eklenebilir
-2. IPhone ve Android ayrımı ara başlığa çıkarılabilir
-3. NFC destekleyen telefon listesi eklenebilir
-4. Temassız ödeme bölümü genişletilebilir
-5. NFC etiketi kullanımı eklenebilir</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">1. 'nfc etiketi nedir' sorgusu 3.835 Impression alıyor ancak sayfa 8.7 sırada ve tek click getiriyor; yazıda NFC etiketi hiç geçmiyor. 'NFC Etiketi Nedir, Ne İşe Yarar?' başlığı altında etiketin ne olduğu, telefona nasıl okutulduğu ve ev otomasyonu gibi kullanım örnekleri verilebilir
+2. 'nfc kart nedir' 832 Impression alıyor; temassız kartın NFC ile ilişkisi ayrı bir H3 olarak açılabilir
+3. 'nfc açma', 'iphone nfc açma', 'apple nfc açma' ve 'nfc özelliği nasıl açılır redmi' kelimelerinin hiçbiri gövdede geçmiyor; mevcut 'NFC Nasıl Açılır ve Kullanılır?' başlığı cihaz bazında üçe ayrılabilir: iPhone, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Samsung</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve"> ve Xiaomi/Redmi. Her biri iki-üç adımla anlatılır
+4. 'nfc özelliği olan telefonlar' kelimesi gövdede yok; NFC destekleyen model ailelerini marka bazında listeleyen kısa bir tablo, bu aramayı karşılar açıklanır
+5. 'nfc alanı neresi' aramasının karşılığı da bulunmuyor; NFC anteninin telefonun neresinde olduğu ve nasıl bulunacağı tek paragrafla eklenebilir</t>
+          </r>
         </is>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>Bankaların ödeme niyetli sayfaları önde olduğundan, ödeme bölümü tek başına yeterli olmayabilir; cihaz ayarları katmanı ayırt edici olmaktadır.</t>
+          <t>Cihaz arayüzleri sürümle değişiyor; adımların model ailesi düzeyinde verilmesi ve güncellenme tarihinin görünür tutulması önerilir.</t>
         </is>
       </c>
       <c r="Z6" s="7" t="n">
@@ -8684,7 +8760,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="263.5" customHeight="1">
+    <row r="7" ht="276" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
@@ -8778,11 +8854,9 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>1. Yazının hedefi jenerik marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek'
-2. Kullanım senaryoları bölümü eklenebilir: telefonda kullanım, dosya yükleme, görsel oluşturma
-3. ChatGPT ile karşılaştırma tablosu eklenebilir
-4. Ücretsiz ve ücretli sürüm farkı ayrı ara başlıkta verilebilir
-5. Sık sorulanlar bölümü, sonuç sayfasında görünen soru bloğuyla eşleştirilebilir
+          <t>1. Gemini Türkçe Destekliyor mu?
+2. Gemini ile ChatGPT Arasındaki Fark
+3. Gemini Ücretsiz mi?
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Google Gemini Nedir? · Peki, Gemini’yi Kim Geliştirdi? · Gemini’ye Nasıl Ulaşılabilir? · Peki Gemini’nin GPT’den Farkı Ne?</t>
         </is>
       </c>
@@ -8805,16 +8879,16 @@
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>1. Yazının hedefi jenerik marka aramasından uzun kuyruğa taşınabilir: 'gemini nedir', 'gemini yapay zeka', 'gemini ne demek' açıklanır
-2. Kullanım senaryoları bölümü eklenebilir: telefonda kullanım, dosya yükleme, görsel oluşturma adım adım anlatılır
-3. ChatGPT ile karşılaştırma tablosu eklenebilir
-4. Ücretsiz ve ücretli sürüm farkı ayrı ara başlıkta verilebilir
-5. Sık sorulanlar bölümü, sonuç sayfasında görünen soru bloğuyla eşleştirilebilir</t>
+          <t>1. 'gemini yapay zeka' sorgusu 92.496 Impression ile 79 click getiriyor ve kelime gövdede hiç geçmiyor; giriş paragrafında ve bir ara başlıkta bu kalıbın kullanılması, sayfanın hâlihazırda göründüğü aramayı güçlendirir açıklanır
+2. 'gemini türkçe' kelimesi de gövdede yok; 'Gemini Türkçe Destekliyor mu?' başlığı altında dil desteği, Türkçe yanıt kalitesi ve arayüz dili üç maddeyle verilebilir
+3. Mevcut 'Gemini ile Bard Arasındaki Fark' bölümü artık geçerliliğini yitiriyor, Bard adı kullanımdan kalktı; bu bölüm 'Gemini ile ChatGPT Arasındaki Fark' karşılaştırmasına çevrilip yanıt kaynağı, görsel üretimi, dosya yükleme ve ücretsiz sürüm sınırları dört satırlık tabloya alınabilir
+4. Ücretsiz ve ücretli sürüm ayrımı yazıda geçmiyor; 'Gemini Ücretsiz mi?' başlığı, sonuç sayfasındaki soru bloğunda da görünen bir arama adım adım anlatılır
+5. Sayfanın Impression'ı jenerik marka aramasından geliyor ve o aramada sonuç sayfasının ilk beş sırası Google'ın kendi adresleri; kazanım kullanım ve karşılaştırma sorularında olduğu için yeni bölümler bu iki eksende kurgulanmalıdır</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>Yazının impression'ı jenerik marka aramasından gelmektedir ve bu aramada sonuç sayfasının üst sıraları Google'ın kendi mülkleridir; CTR'ın bu aramada yükselmesi beklenmemelidir. Kazanım uzun kuyruk sorularındadır.</t>
+          <t>Yapay zeka ürünlerinde sürüm ve fiyatlandırma sık değişiyor; tablo değerlerinin tarihiyle birlikte verilmesi önerilir.</t>
         </is>
       </c>
       <c r="Z7" s="7" t="n">
@@ -8834,7 +8908,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="142" customHeight="1">
+    <row r="8" ht="261" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni</t>
@@ -8930,10 +9004,10 @@
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>1. Ping değerinin ne olduğu ve ideal aralık tablo hâlinde verilebilir
-2. Ping düşürme adımları eklenebilir
-3. Oyun senaryosu ayrı ara başlığa alınabilir
-Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Ping Testi Nedir? Nasıl Yapılır? · İlginizi Çekebilir</t>
+          <t>1. Ping Testi Nasıl Yapılır?
+2. İdeal Ping Değerleri Tablosu
+3. Ping Nasıl Düşürülür? Dört Adım
+Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Ping Testi Nedir? Nasıl Yapılır?</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
@@ -8984,14 +9058,39 @@
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>1. Ping değerinin ne olduğu ve ideal aralık tablo hâlinde verilebilir
-2. Ping düşürme adımları eklenebilir
-3. Oyun senaryosu ayrı ara başlığa alınabilir</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Türk Telekom</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un aynı konudaki yazısının başlığı 'Ping Testi Nedir? Nasıl Yapılır?'; bizim yazımızda ölçüm bölümü var ancak test adımı yok. Komut satırından ping testi, hız testi siteleri ve oyun içi gecikme göstergesi üç adımda anlatılabilir
+2. 'ping nedir' sorgusunda sayfa 3.7 ortalama sırada ancak 3.918 Impression'dan yalnız 1 click geliyor; bu tablo sonuç sayfasının üstünde yanıtın verildiğine işaret ediyor. Giriş paragrafındaki tanımın tek cümleye indirilmesi ve ideal ping aralığının hemen altına tablo olarak konması, alıntılanma ihtimalini artırır açıklanır
+3. Ideal değer aralığı yazıda cümle içinde geçiyor; 'Rekabetçi oyun 0-30 ms, genel oyun 30-60 ms, video görüşme 60-100 ms, üzeri sorunlu' satırlarından oluşan bir tablo hem okuyucuya hem AI yanıtına daha kullanışlı geliyor açıklanır
+4. Mevcut 'Ping Nasıl Düşürülür?' bölümü genel öneriler içeriyor; kablo bağlantısı, 5 GHz bant, arka plan indirmeleri ve sunucu bölgesi seçimi gibi dört somut adıma çevrilebilir</t>
+          </r>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>Rakip bir araç sayfasıyla sıralanmaktadır; yazının bir hız testi aracına bağlanması değerlendirilebilir.</t>
+          <t>Ping değerleri bağlantı türüne göre değişiyor; verilen aralıkların hangi bağlantı için geçerli olduğu belirtilmelidir.</t>
         </is>
       </c>
       <c r="Z8" s="7" t="n">
@@ -9011,7 +9110,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="155.5" customHeight="1">
+    <row r="9" ht="223" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/type-c-teknolojisi-ne-ise-yarar-neden-bu-kadar-yaygin</t>
@@ -9120,9 +9219,10 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t xml:space="preserve">1. Kablo ve şarj aleti seçimi bölümü eklenebilir
-2. USB-C standartları ve hız sınıfları tablo hâlinde verilebilir
-3. Hangi cihazlarda bulunduğu listelenebilir
+            <t xml:space="preserve">1. Type-C Nedir, Ne Demek?
+2. USB 3.2, USB4 ve Thunderbolt Arasındaki Fark
+3. Type-C ile Hızlı Şarj Nasıl Çalışır?
+4. Kablo Kalitesi Aktarım Hızını Nasıl Etkiler?
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Type C Nedir? · Type C Girişe Sahip Olan Cihazlar Hangileridir? · USB Type-C’nin diğer USB türlerinden Farkı · USB Type-C’nin Avantajları ve USB Type-C’nin Dezavantajları · Type-C Girişli Telefonlara </t>
           </r>
           <r>
@@ -9175,14 +9275,15 @@
       </c>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>1. Kablo ve şarj aleti seçimi bölümü eklenebilir
-2. USB-C standartları ve hız sınıfları tablo hâlinde verilebilir
-3. Hangi cihazlarda bulunduğu listelenebilir</t>
+          <t>1. Sayfa 'type c' sorgusunda 91.693 Impression alıyor ancak 7.8 sırada ve 23 click getiriyor; bu aramada sonuç sayfasının üst sıraları ürün listeleyen mağazalarda olduğu için bilgi tarafında kazanım 'type c nedir' ve 'type c ne demek' kalıplarında. İkisi de gövdede birer kez geçiyor, ara başlığa taşınabilir
+2. USB-C sürümleri yazıda ayrışmıyor; USB 3.2, USB4 ve Thunderbolt 4 için veri hızı, güç aktarımı ve görüntü desteği sütunlarından oluşan bir tablo, konunun en çok karıştırılan yanını karşılar açıklanır
+3. 'Type-C ile hızlı şarj nasıl çalışır' sorusu yazıda yanıtlanmıyor; Power Delivery kademelerinin watt değerleriyle verildiği bir bölüm eklenebilir
+4. Yazıda kablo kalitesinin aktarım hızını nasıl sınırladığı geçmiyor; aynı görünen iki kablonun farklı hız vermesi somut bir okuyucu sorusu ve tek paragrafla karşılanabilir</t>
         </is>
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>Sorgunun büyük bölümü ürün satın alma niyetlidir; açıklama yazısının ilk sıraya çıkması sınırlıdır, Pasaj sayfasına yönlendirme değerlendirilebilir.</t>
+          <t>Ürün önerisi verilmemesi, teknik ayrım katmanında kalınması önerilir; şarj aleti ve kablo aramaları mağaza sayfalarına aittir.</t>
         </is>
       </c>
       <c r="Z9" s="7" t="n">
@@ -9202,7 +9303,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="155.5" customHeight="1">
+    <row r="10" ht="246" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/vdsl-ve-adsl-nedir-internet-baglanti-turleri-arasindaki-farklar</t>
@@ -9306,10 +9407,9 @@
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>1. Hangi bağlantının hangi kullanım için uygun olduğu tablo hâlinde verilebilir
-2. Hız beklentisi mesafeye göre açıklanabilir
-3. Altyapı sorgulamaya bağlantı eklenebilir
-4. Fiber karşılaştırması genişletilebilir</t>
+          <t>1. ADSL, VDSL ve Fiber Karşılaştırma Tablosu
+2. VDSL Modem Nedir, ADSL Modemden Farkı Ne?
+3. Hangi Bağlantı Kimin İçin Uygun?</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
@@ -9394,15 +9494,39 @@
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>1. Hangi bağlantının hangi kullanım için uygun olduğu tablo hâlinde verilebilir
-2. Hız beklentisi mesafeye göre açıklanabilir
-3. Altyapı sorgulamaya bağlantı eklenebilir
-4. Fiber karşılaştırması genişletilebilir</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">1. 'adsl vdsl farkı' sorgusu 3.3 ortalama sırada 3.014 Impression alıyor; bu sayfanın en güçlü olduğu alan ve mevcut karşılaştırma metin hâlinde. Hız, mesafe hassasiyeti, upload oranı ve tipik kullanım satırlarından oluşan bir tabloya çevrilmesi ilk üçe girme ihtimalini artırır açıklanır
+2. 'vdsl modem nedir' sorgusu 1.878 Impression ile 4.5 sırada; modem tarafı yazıda tek cümlede geçiyor. 'VDSL Modem Nedir, ADSL Modemden Farkı Ne?' başlığı altında uyumluluk ve değişim gerekliliği anlatılabilir
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Vodafone</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un aynı sorguda 1. sıradaki yazısı 485 kelime; bizim yazımız 1.092 kelimeyle iki katı ve daha kapsamlı. Eksik olan uzunluk değil, tablo ve karar yardımı: 'Hangi Bağlantı Kimin İçin Uygun?' bölümü, ev tipi ve kullanıcı sayısına göre üç senaryo verebilir
+4. Fiber bağlantı yazıda karşılaştırmaya girmiyor; ADSL, VDSL ve fiber üçlüsünün aynı tabloda görülmesi, okuyucunun asıl sorusunu karşılar açıklanır</t>
+          </r>
         </is>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>Rakip sayfalar aynı formatta olduğundan fark içerik derinliğindedir; sayfa türü değişikliği gerekmemektedir.</t>
+          <t>Altyapı ve hız değerleri bölgeye göre değişiyor; sorgulama işleminin ilgili hizmet sayfasından yapılabileceği belirtilebilir.</t>
         </is>
       </c>
       <c r="Z10" s="7" t="n">
@@ -9422,7 +9546,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="128.5" customHeight="1">
+    <row r="11" ht="263.5" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/internette-dalgalanma-neden-olur-jitter-degeri-nedir</t>
@@ -9531,9 +9655,10 @@
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>1. İdeal jitter değeri tablo hâlinde verilebilir
-2. Ölçüm yöntemi eklenebilir
-3. Paket kaybı ile ilişkisi açıklanabilir
+          <t>1. İdeal Jitter Değerleri Tablosu
+2. Net Jitter Ne Demek?
+3. Jitter, Ping ve Paket Kaybı Arasındaki Fark
+4. Jitter Nasıl Düşürülür?
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Jitter Nedir? · Jitter Nasıl Anlaşılır?</t>
         </is>
       </c>
@@ -9568,14 +9693,40 @@
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>1. İdeal jitter değeri tablo hâlinde verilebilir
-2. Ölçüm yöntemi eklenebilir
-3. Paket kaybı ile ilişkisi açıklanabilir</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">1. 'jitter kaç olmalı' sorgusu 866 Impression ile 7.8 sırada geliyor ve yazıda ideal aralık tablo hâlinde verilmiyor; 'Video görüşme için 30 ms altı, oyun için 20 ms altı, akış için 50 ms altı' satırlarından oluşan bir tablo bu aramayı karşılar açıklanır
+2. 'net jitter ne demek' ve 'net jitter' sorguları birlikte 1.869 Impression alıyor; terim gövdede geçmiyor. Ağ tarafındaki kullanımın ayrı bir cümleyle açıklanması yeterli açıklanır
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Vodafone</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un 1. sıradaki yazısında ana terim 55 kez geçiyor, bizim yazımızda 23; sayının artırılması değil, jitter kelimesinin ara başlıklarda ve tablo satırlarında da kullanılması öneriliyor açıklanır
+4. Jitter ile ping ve paket kaybı arasındaki fark yazıda net ayrılmıyor; üç kavramı yan yana koyan kısa bir bölüm, konunun en sık karıştırılan yanını kapatıyor açıklanır
+5. Jitter düşürme adımları yazıda genel kalıyor; kablolu bağlantı, QoS ayarı, arka plan trafiği ve modem konumu dört somut maddeye çevrilebilir</t>
+          </r>
         </is>
       </c>
       <c r="Y11" s="4" t="inlineStr">
         <is>
-          <t>Rakip sayfa aynı formattadır; fark ölçüm ve değer tablosundadır.</t>
+          <t>Değerler bağlantı türüne ve uygulamaya göre değişiyor; aralıkların hangi senaryo için geçerli olduğu yazılmalıdır.</t>
         </is>
       </c>
       <c r="Z11" s="7" t="n">
@@ -9595,7 +9746,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="142" customHeight="1">
+    <row r="12" ht="236.5" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/wi-fi-6-nedir-wi-fi-5-ile-arasindaki-temel-farklar</t>
@@ -9698,9 +9849,9 @@
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>1. Wi-Fi 6 destekleyen modem listesi eklenebilir
-2. Mesh sistemlerle ilişkisi açıklanabilir
-3. Yükseltmenin ne zaman anlamlı olduğu bölümü eklenebilir
+          <t>1. Wi-Fi 6 Modem Nedir, Hangi Modemler Destekler?
+2. OFDMA, MU-MIMO ve Target Wake Time Nedir?
+3. Wi-Fi 6E ve Wi-Fi 7 ile Arasındaki Fark
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Wi-Fi 6 Nedir? · Wi-Fi 6 Özellikleri · Wifi 6 Avantajları Nelerdir? · Wi-Fi 6 ve Wi-Fi 5 Arasındaki Farklar · Wi-Fi 6 Uyumlu Cihazlar Nelerdir?</t>
         </is>
       </c>
@@ -9743,14 +9894,39 @@
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
-          <t>1. Wi-Fi 6 destekleyen modem listesi eklenebilir
-2. Mesh sistemlerle ilişkisi açıklanabilir
-3. Yükseltmenin ne zaman anlamlı olduğu bölümü eklenebilir</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">1. 'wifi 6 modem' ve 'wifi 6 modem nedir' sorguları birlikte 4.132 Impression alıyor, sayfa 7.8 ve 4.1 sıralarda; modem tarafı yazıda tek cümlede geçiyor. 'Wi-Fi 6 Modem Nedir, Hangi Modemler Destekler?' başlığı altında uyumluluk, cihaz tarafı gereksinimi ve mevcut modemin yeterli olup olmadığı anlatılabilir
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Vodafone</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un aynı sorguda 1. sıradaki yazısı 1.639 kelime ve 14 ara başlık taşıyor; bizim yazımız 1.146 kelime ve 11 başlık. Fark, kapsam derinliğinde: OFDMA, MU-MIMO ve Target Wake Time gibi teknik kavramların her biri iki cümlelik alt bölüme çevrilebilir
+3. Wi-Fi 6E ve Wi-Fi 7 yazıda geçmiyor; okuyucu Wi-Fi 6 ile Wi-Fi 6E ayrımını sık soruyor, kısa bir bölüm bu boşluğu kapatır açıklanır
+4. 'wifi 6 nedir' sorgusunda sayfa 3.4 sırada ve 48 click alıyor; giriş paragrafındaki tanımın tek cümleye indirilmesi, ilk üçe yaklaşmak için en düşük maliyetli adım açıklanır</t>
+          </r>
         </is>
       </c>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>Sorgu ticari niyet taşımaktadır; 1. sıradaki açıklama yazısının düşük trafik alması bunun göstergesidir. Cihaz sayfasına bağlantı kurulması değerlendirilebilir.</t>
+          <t>Cihaz uyumluluğu marka ve model ailesine göre değişiyor; genel ifadeler yerine standart adları kullanılmalıdır.</t>
         </is>
       </c>
       <c r="Z12" s="7" t="n">
@@ -9770,7 +9946,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="155.5" customHeight="1">
+    <row r="13" ht="231" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/mac-adresi-her-cihazin-kendine-ozgu-dijital-imzasi</t>
@@ -9877,9 +10053,11 @@
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>1. MAC adresinin cihazdan öğrenilmesi işletim sistemi bazında eklenebilir
-2. MAC filtreleme bölümü eklenebilir
-3. IP adresiyle farkı açıklanabilir
+          <t>1. Windows ve macOS'ta MAC Adresi Nasıl Bulunur?
+2. Android ve iPhone'da MAC Adresi Nasıl Öğrenilir?
+3. Modem Arayüzünden Bağlı Cihazların MAC Adresi
+4. MAC Adresinden Cihaz Üreticisi Nasıl Bulunur?
+5. Telefonlarda MAC Adresi Neden Değişiyor?
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: MAC Adresi Değiştirme Nasıl Yapılır?</t>
         </is>
       </c>
@@ -9914,14 +10092,39 @@
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
-          <t>1. MAC adresinin cihazdan öğrenilmesi işletim sistemi bazında eklenebilir
-2. MAC filtreleme bölümü eklenebilir
-3. IP adresiyle farkı açıklanabilir</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">1. 'mac adresi sorgulama' ve 'mac adresi nasıl bulunur' sorguları birlikte 1.800 Impression alıyor, sayfa 6.7 ve 9.2 sıralarda; adım anlatımı yazıda cihaz bazında ayrışmıyor. Windows, macOS, Android, iPhone ve modem arayüzü için beş kısa adım listesi eklenebilir
+2. 'mac adresinden cihaz bulma' sorgusu 237 Impression alıyor ve yazıda karşılığı yok; MAC adresinin ilk üç baytının üretici kodunu taşıdığı ve bu bilgiyle cihaz markasının bulunabildiği tek paragrafla açıklanabilir
+3. 'telefon mac adresi nedir' sorgusu 4.3 sırada 283 Impression alıyor; telefonlarda rastgele MAC kullanımının (privacy MAC) neden devreye girdiği, okuyucunun gördüğü değerin neden değiştiğini açıklar açıklanır
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Vodafone</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un 3. sıradaki yazısında ana terim 46 kez geçiyor, bizim yazımızda 43; kelime sıklığı yeterli, eksik olan cihaz bazında adım anlatımı açıklanır</t>
+          </r>
         </is>
       </c>
       <c r="Y13" s="4" t="inlineStr">
         <is>
-          <t>Sorgu adım arama niyetlidir; tanım bölümü kısaltılıp adımlar öne alınabilir.</t>
+          <t>Rastgele MAC kullanımı işletim sistemi sürümüne göre değişiyor; adımların sürüm bilgisiyle verilmesi önerilir.</t>
         </is>
       </c>
       <c r="Z13" s="7" t="n">

--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -10033,7 +10033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -10046,16 +10046,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
-    <col width="62" customWidth="1" min="12" max="12"/>
-    <col width="52" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="52" customWidth="1" min="20" max="20"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
+    <col width="104" customWidth="1" min="12" max="12"/>
+    <col width="86" customWidth="1" min="13" max="13"/>
+    <col width="62" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="44" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="52" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -10083,6 +10085,8 @@
       <c r="R1" s="2" t="n"/>
       <c r="S1" s="2" t="n"/>
       <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -10105,6 +10109,8 @@
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -10159,56 +10165,66 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Alt Başlık Önerileri</t>
+          <t>Alt Başlık Önerileri (H2 / H3)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
+          <t>İçerik Kurgusu</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Cevaplanması Gereken Sorular (FAQ, H3)</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
           <t>İç Linkler (Anchor : URL)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Rakip Yaklaşımı</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>İçerik Yönergesi</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>Dikkat Edilecek</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Puan</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>Öncelik</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>Peak Ayı</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>Önerilen Yayın Ayı</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>Ne Anlama Geliyor</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="250" customHeight="1">
+    <row r="4" ht="344.5" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>192.168.1.1 Modem Arayüzü: Giriş ve Şifre Değiştirme</t>
@@ -10272,14 +10288,53 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>1. 192.168.1.1 ve 192.168.0.1 farkı
-2. Marka bazında varsayılan kullanıcı adı ve şifre tablosu
-3. Arayüze girilemediğinde kontrol listesi
-4. WiFi adı ve şifresi değiştirme
-5. Modem sıfırlama</t>
+          <t>H2: 192.168.1.1 Nedir, Ne İşe Yarar?
+H2: 192.168.1.1 ile 192.168.0.1 Arasındaki Fark Nedir?
+H2: Modem Arayüzüne Nasıl Girilir?
+H3: Bilgisayardan Modem Arayüzü Girişi
+H3: Telefondan Modem Arayüzü Girişi
+H2: Marka Bazında Varsayılan Kullanıcı Adı ve Şifre Tablosu
+H2: 192.168.1.1 Açılmıyorsa Ne Yapmalı?
+H2: Wi-Fi Şifresi Nasıl Değiştirilir?
+H3: Modem Arayüzünden Wi-Fi Şifre Değiştirme
+H3: Wi-Fi Şifresi Nasıl Öğrenilir?
+H2: Modem Şifresi Nasıl Değiştirilir?
+H2: Modem Nasıl Sıfırlanır?
+H2: 192.168.1.1 ve Modem Arayüzü Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>TON: Adım anlatan, jargonsuz rehber dili. Okuyucu modemin başında ve acelesi var; her bölüm doğrudan işleme başlamalı.
+H2 · 192.168.1.1 Nedir: Adresin bir web sitesi değil, modemin kendi yönetim arayüzü olduğu iki cümlede verilir. Yerel ağ adresi kavramı tek cümleyle açıklanır.
+H2 · 192.168.1.1 ile 192.168.0.1 Farkı: Hangi markanın hangisini kullandığı, doğru adresin ağ geçidi (default gateway) bilgisinden nasıl bulunacağı. Yaygın yanlış yazımlar (192.168.1.1 yerine 192.1681.1 gibi) burada bir cümleyle karşılanır.
+H2 · Modem Arayüzüne Nasıl Girilir: İki H3'te ayrı ayrı numaralı adım listesi. Bilgisayarda tarayıcı adres çubuğu, telefonda aynı Wi-Fi ağına bağlı olma koşulu vurgulanır.
+H2 · Varsayılan Kullanıcı Adı ve Şifre Tablosu: Marka / model ailesi / varsayılan adres / kullanıcı adı / şifre sütunlarından oluşan tablo. Turkcell modemleri için değerler ürün ekibiyle doğrulanır. Tablonun üstüne "etiket modemin altındadır" notu konur.
+H2 · Açılmıyorsa Ne Yapmalı: Sekiz maddelik kontrol listesi (kabloyla bağlanma, doğru ağ, tarayıcı önbelleği, https yerine http, VPN kapatma, farklı tarayıcı, ağ geçidi adresini öğrenme, mobil veriyi kapatma).
+H2 · Wi-Fi Şifresi Nasıl Değiştirilir: Arayüzdeki menü adımları numaralı liste hâlinde; şifre uzunluğu ve WPA2/WPA3 seçimi için tek cümlelik öneri. İkinci H3'te kayıtlı ağdan şifre öğrenme (Windows ve iPhone) verilir.
+H2 · Modem Şifresi Nasıl Değiştirilir: Arayüz giriş şifresi ile Wi-Fi şifresinin farklı olduğu açıkça ayrılır; bu ayrım okuyucunun en sık karıştırdığı nokta.
+H2 · Modem Nasıl Sıfırlanır: Sıfırlama düğmesinin yeri, kaç saniye basılacağı ve sıfırlama sonrası internetin yeniden kurulması gerektiği uyarısı.
+UZUNLUK: 1.800-2.300 kelime. Tablo ve numaralı listeler ağırlıkta olmalı; düz paragraf oranı düşük tutulur.
+GÖRSEL: Arayüz ekran görüntüsü yerine adım metni tercih edilir; arayüzler modele göre değişiyor.</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>H3: 192.168.1.1 Adresine Nasıl Girilir?
+Modemin Wi-Fi ağına bağlıyken tarayıcının adres çubuğuna 192.168.1.1 yazılır ve modemin altındaki etikette bulunan kullanıcı adı ile şifre girilir.
+H3: 192.168.1.1 ile 192.168.0.1 Arasındaki Fark Nedir?
+İkisi de modem arayüzünün yerel adresidir; hangisinin geçerli olduğu markaya göre değişir. Doğru adres, bilgisayarın ağ ayarlarındaki ağ geçidi satırından öğrenilebilir.
+H3: Modem Arayüzü Şifresi Nedir?
+Varsayılan kullanıcı adı ve şifre modemin altındaki etikette yazılıdır. Daha önce değiştirildiyse ve hatırlanmıyorsa modemin sıfırlanması gerekir.
+H3: Wi-Fi Şifresi Modem Arayüzünden Nasıl Değiştirilir?
+Arayüze girildikten sonra Kablosuz Ağ veya WLAN menüsündeki şifre alanı güncellenir ve kaydedilir; bağlı tüm cihazların yeniden bağlanması gerekir.
+H3: Modem Arayüzüne Girilemiyorsa Ne Yapılmalı?
+Cihazın modem ağına bağlı olduğu, adresin http ile yazıldığı ve VPN'in kapalı olduğu kontrol edilir; sorun sürerse modem kabloyla bağlanarak denenebilir.
+H3: Modem Sıfırlanınca Wi-Fi Şifresi Ne Olur?
+Sıfırlama sonrasında modem fabrika ayarlarına döner ve Wi-Fi şifresi etiketteki varsayılan değere geri gelir.</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -10287,7 +10342,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10308,7 +10363,7 @@
           </r>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>1. 192.168.1.1 ve 192.168.0.1 farkı açıklanır
 2. Marka bazında varsayılan kullanıcı adı ve şifre tablosu verilir
@@ -10317,36 +10372,36 @@
 5. Modem sıfırlama adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Turkcell modem modelleri için varsayılan bilgiler ürün ekibiyle doğrulanmalıdır.</t>
         </is>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="R4" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="S4" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="T4" s="6" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Modem şifresini değiştirmek isteyen kişi önce arayüze girmeye çalışıyor. Bu adım rakipte en çok trafik getiren sayfa.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="223" customHeight="1">
+    <row r="5" ht="304" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Gizli Numara: Arama, Kapatma ve Numara Gizleme Ayarları</t>
@@ -10408,14 +10463,51 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>1. Numara gizleme kodu ve operatör ayarı
-2. Gizli numaradan gelen aramayı engelleme
-3. IPhone ve Android ayrı adımlar
-4. Operatör servisiyle kalıcı engelleme
-5. Yasal sınırlar</t>
+          <t>H2: Gizli Numara Ne Demek?
+H2: Gizli Numaradan Nasıl Aranır?
+H3: Numara Gizleme Kodu ile Arama
+H3: Telefon Ayarlarından Numara Gizleme
+H3: iPhone'da Numara Gizleme Nasıl Yapılır?
+H2: Gizli Numara Nasıl Açılır, Gizleme Nasıl İptal Edilir?
+H2: Gizli Numara Nasıl Kapatılır, Gelen Aramalar Nasıl Engellenir?
+H3: Android'de Özel Numara Engelleme
+H3: iPhone'da Gizli Numara Kapatma
+H3: Operatör Servisiyle Kalıcı Engelleme
+H2: Gizli Numarayı Öğrenmek Mümkün mü?
+H2: Numara Gizleme ile İlgili Yasal Sınırlar
+H2: Gizli Numara Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>TON: Nötr ve açıklayıcı. Konunun iki zıt niyeti var: numarasını gizlemek isteyen ve gizli aramadan rahatsız olan okuyucu. Yazı ikisini de aynı sayfada, ayrı bölümlerde karşılamalı ve girişte bu ayrım tek cümleyle duyurulmalı.
+H2 · Gizli Numara Ne Demek: Arayanın numarasının karşı tarafta görünmemesi durumu. "Özel numara", "bilinmeyen numara" ve "gizli numara" ifadelerinin aynı şeyi anlattığı burada netleştirilir.
+H2 · Gizli Numaradan Nasıl Aranır: Üç H3. Birincisinde numaranın önüne eklenen gizleme kodu ve kodun tek aramada geçerli olduğu. İkincisinde Android arama uygulaması ayarları. Üçüncüsünde iPhone ayar yolu. Her biri numaralı adım.
+H2 · Gizli Numara Nasıl Açılır: Gizlemenin nasıl iptal edileceği; operatör tarafında sürekli gizleme tanımlıysa self servis kanaldan kapatılabileceği notu.
+H2 · Gizli Numara Nasıl Kapatılır: Yazının en çok aranan bölümü, üç H3 ile ayrılır. Android ve iPhone'da bilinmeyen arayanları sessize alma ayarı adım adım; üçüncü H3'te operatörün engelleme servisi ve nereden açılacağı.
+H2 · Gizli Numarayı Öğrenmek Mümkün mü: Dürüst yanıt verilir. Uygulama vaatlerinin çalışmadığı, yalnızca yasal süreçle mümkün olduğu yazılır. Bu bölüm yazının ayırt edici yanıdır; rakip sayfalarda net karşılığı yok.
+H2 · Yasal Sınırlar: Rahatsız edici aramada izlenebilecek yol ve şikâyet kanalı tek paragrafta.
+UZUNLUK: 1.600-2.000 kelime.
+DİKKAT: Numara gizleme kodları operatöre göre değişebiliyor; kod verilirken hangi durumda geçerli olduğu belirtilmeli.</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>H3: Gizli Numara Nasıl Yapılır?
+Aranacak numaranın başına operatörün gizleme kodu eklenir ya da telefonun arama ayarlarındaki numara gösterme seçeneği kapatılır.
+H3: Gizli Numara Nasıl Kapatılır?
+Telefon ayarlarından bilinmeyen arayanları sessize alma seçeneği açılabilir; kalıcı çözüm için operatörün gizli numara engelleme servisi kullanılır.
+H3: Özel Numara ile Gizli Numara Aynı Şey mi?
+Evet. Özel numara, bilinmeyen numara ve gizli numara ifadeleri arayanın numarasının görünmemesi durumunu anlatır.
+H3: Gizli Numaradan Arayan Kişi Öğrenilebilir mi?
+Kullanıcı tarafından öğrenilemez. Rahatsız edici aramalarda numara ancak yasal başvuru sonrasında yetkili makamlarca tespit edilebilir.
+H3: iPhone'da Numara Gizleme Nereden Yapılır?
+Ayarlar bölümündeki telefon menüsünde yer alan arayan kimliğimi göster seçeneği kapatılarak yapılır.
+H3: Gizli Numara Engellendiğinde Arayan Ne Duyar?
+Arama karşı tarafa iletilmez; arayan genellikle meşgul ya da ulaşılamıyor uyarısı alır.</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -10423,7 +10515,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10461,7 +10553,7 @@
           </r>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>1. Numara gizleme kodu ve operatör ayarı açıklanır
 2. Gizli numaradan gelen aramayı engelleme adım adım anlatılır
@@ -10470,30 +10562,30 @@
 5. Yasal sınırlar açıklanır</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Numarayı gizleme ve gizli numarayı engelleme zıt niyetlerdir; başlık ve ara başlıklar ikisini de karşılamalıdır.</t>
         </is>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="R5" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="S5" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="U5" s="6" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Kullanıcı ya numarasını gizlemek ya da gizli aramadan kurtulmak istiyor. İki ihtiyaç aynı sayfada karşılanırsa iki arama da aynı yere geliyor.</t>
         </is>
@@ -10570,14 +10662,51 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>1. Kayıt ücreti ve geçerli yılın harç tutarı tablo hâlinde
-2. E-Devlet ve BTK üzerinden sorgulama adımları
-3. Kayıtsız telefonun kaç gün kullanılabildiği
-4. IMEI numarasının telefondan öğrenilmesi
-5. Kayıt sonrası bekleme süresi</t>
+          <t>H2: Yurt Dışından Getirilen Telefonun Kaydı Neden Gerekir?
+H2: Yurt Dışı Telefon Kayıt Ücreti Ne Kadar?
+H2: IMEI Numarası Nasıl Öğrenilir?
+H3: Telefon Ekranından IMEI Sorgulama Kodu
+H3: Kutu ve Cihaz Üzerinden IMEI Öğrenme
+H2: IMEI Sorgulama Nasıl Yapılır?
+H3: e-Devlet Üzerinden IMEI Sorgulama
+H3: BTK IMEI Sorgulama Ekranı
+H2: IMEI Kaydı Nasıl Yapılır? Adım Adım
+H2: Kayıtsız Telefon Kaç Gün Kullanılabilir?
+H2: IMEI Kaydı Sonrası Telefon Ne Zaman Açılır?
+H2: Yurt Dışı Telefon Kaydı Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>TON: İşlem rehberi. Okuyucu genelde süre baskısı altında (telefonu kapanmak üzere); her bölüm doğrudan yanıtla açılmalı.
+H2 · Neden Gerekir: Yurt dışından getirilen cihazın belirli bir sürenin sonunda şebekeye kapandığı, kaydın bunu önlediği iki cümlede.
+H2 · Kayıt Ücreti Ne Kadar: Yazının en çok aranan bölümü. Geçerli yılın harç tutarı, varsa e-Devlet üzerinden ödeme farkı ve ödeme kanalları tablo hâlinde. Tablonun üstünde tutarın hangi yıl için geçerli olduğu ve güncelleme tarihi görünür yazılır.
+H2 · IMEI Nasıl Öğrenilir: İki H3. Birincisinde telefondan çevrilen sorgulama kodu, ikincisinde kutu etiketi, SIM yuvası ve ayarlar menüsü. Çift SIM cihazlarda iki IMEI bulunduğu notu eklenir.
+H2 · IMEI Sorgulama Nasıl Yapılır: İki H3'te e-Devlet ve BTK ekranları ayrı ayrı, numaralı adımlarla. Sorgu sonucunda görülen durumların (kayıtlı, kayıtsız, kullanım süresi devam ediyor) ne anlama geldiği kısa bir listeyle açıklanır.
+H2 · IMEI Kaydı Nasıl Yapılır: Adım adım numaralı liste; gereken belgeler (pasaport, giriş kaydı) ve başvuru kanalları. Kayıt hakkının kişi başına sınırlı olduğu belirtilir.
+H2 · Kayıtsız Telefon Kaç Gün Kullanılabilir: Süre net rakamla verilir ve sürenin nereden takip edileceği yazılır.
+H2 · Kayıt Sonrası Ne Zaman Açılır: Bekleme süresi ve telefonun açılmaması durumunda ne yapılacağı.
+UZUNLUK: 1.800-2.200 kelime.
+DİKKAT: Harç tutarı ve süreler yıl içinde değişiyor. Tüm rakamlar tek bir tabloda toplanmalı ki güncelleme tek yerden yapılabilsin; metin içine dağıtılmamalı.</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>H3: Yurt Dışı Telefon Kayıt Ücreti Ne Kadar?
+Kayıt ücreti her yıl yeniden belirlenen bir harç tutarıdır; güncel tutar yazıdaki ücret tablosunda güncelleme tarihiyle birlikte verilmektedir.
+H3: IMEI Numarası Nasıl Öğrenilir?
+Telefondan IMEI sorgulama kodu çevrilerek, kutu etiketinden ya da ayarlar menüsündeki telefon hakkında bölümünden öğrenilebilir.
+H3: e-Devlet'ten IMEI Sorgulama Nasıl Yapılır?
+e-Devlet'e giriş yapıldıktan sonra IMEI sorgulama hizmeti aranır, cihazın IMEI numarası girilir ve kayıt durumu görüntülenir.
+H3: Kayıtsız Telefon Kaç Gün Kullanılır?
+Yurt dışından getirilen telefon, yasal kullanım süresi boyunca şebekede çalışır; süre dolduğunda kayıt yapılmadıysa cihaz şebekeye kapatılır.
+H3: IMEI Kaydı Yapıldıktan Sonra Telefon Ne Zaman Açılır?
+Kayıt işlemi tamamlandıktan sonra cihaz genellikle kısa süre içinde şebekeye açılır; açılmazsa cihazın yeniden başlatılması denenebilir.
+H3: Bir Kişi Kaç Telefon Kaydettirebilir?
+Yurt dışından getirilen cihazların kaydı kişi başına ve belirli bir süre aralığında sınırlıdır; güncel sınır kayıt başvurusu sırasında görüntülenir.</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -10585,7 +10714,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10640,7 +10769,7 @@
           </r>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>1. Kayıt ücreti ve geçerli yılın harç tutarı tablo hâlinde açıklanır
 2. E-Devlet ve BTK üzerinden sorgulama adımları adım adım anlatılır
@@ -10649,36 +10778,36 @@
 5. Kayıt sonrası bekleme süresi açıklanır</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Ücret ve süre bilgileri yıl içinde değişmektedir; sayfanın güncellenme tarihi görünür tutulabilir.</t>
         </is>
       </c>
-      <c r="P6" s="8" t="n">
+      <c r="R6" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="Q6" s="9" t="inlineStr">
+      <c r="S6" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="S6" s="6" t="inlineStr">
+      <c r="U6" s="6" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>Yurt dışından telefon getiren kişi ücreti ve süreyi arıyor. Bu bilgiyi tek sayfada toplayan taraf aramanın tamamını karşılıyor.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="128.5" customHeight="1">
+    <row r="7" ht="263.5" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Google Güvenli Arama: Açma, Kapatma ve Aile Filtresi</t>
@@ -10730,13 +10859,44 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>1. Google güvenli aramanın ne yaptığı
-2. Açma ve kapatma adımları
-3. Kilitli olduğunda yapılabilecekler
-4. Çocuk hesaplarında aile bağlantısı ayarı</t>
+          <t>H2: Güvenli Arama Nedir, Ne İşe Yarar?
+H2: Google Güvenli Arama Nasıl Açılır?
+H2: Güvenli Arama Nasıl Kapatılır?
+H3: Bilgisayarda Güvenli Arama Filtresi Kapatma
+H3: Telefonda Google Güvenli Arama Kapatma
+H2: Güvenli Arama Kilidi Nasıl Açılır?
+H2: Çocuk Hesaplarında Güvenli Arama Ayarları
+H2: Operatörün Güvenli İnternet Hizmetiyle Farkı Nedir?
+H2: Güvenli Arama Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>TON: Ayar rehberi. Okuyucunun iki farklı niyeti var: filtreyi açmak isteyen ebeveyn ve kapatamayan kullanıcı. Girişte hangi bölümün kime olduğu tek cümleyle işaret edilir.
+H2 · Güvenli Arama Nedir: Arama sonuçlarında yetişkin içeriğin süzülmesi olduğu, tarayıcı ya da hesap düzeyinde çalıştığı iki cümlede.
+H2 · Nasıl Açılır: Google arama ayarları üzerinden numaralı adım listesi; hesaba giriş yapıldığında ayarın tüm cihazlarda geçerli olduğu notu.
+H2 · Nasıl Kapatılır: Yazının en çok aranan bölümü, iki H3. Masaüstü ve mobil adımlar ayrı verilir. Ayarın kapanmaması durumunda hangi üç nedenin olabileceği (hesap yöneticisi kilidi, ağ düzeyinde filtre, uygulama içi kısıtlama) listelenir.
+H2 · Güvenli Arama Kilidi Nasıl Açılır: Kilidin kim tarafından konabildiği ve kaldırma yetkisinin nerede olduğu. Aile bağlantısı ile yönetilen hesaplarda ebeveyn onayı gerektiği açıkça yazılır.
+H2 · Çocuk Hesaplarında Ayarlar: Aile bağlantısı üzerinden filtre yönetimi adım adım; yaş sınırı notu.
+H2 · Operatör Güvenli İnternet Farkı: İki hizmetin farkı üç satırlık tabloda: nerede çalışır, kim yönetir, neyi kapsar. Bu bölüm karışıklığı önlemek için gereklidir.
+UZUNLUK: 1.200-1.500 kelime.</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>H3: Google Güvenli Arama Nasıl Kapatılır?
+Google arama ayarlarındaki güvenli arama bölümünden filtre kapatılır; hesap bir aile yöneticisine bağlıysa ayar kilitli gelebilir.
+H3: Güvenli Arama Kilidi Neden Açılmıyor?
+Kilit çoğunlukla aile bağlantısıyla yönetilen bir hesaptan ya da ağ düzeyindeki bir filtreden kaynaklanır; bu durumda ayar hesap yöneticisi tarafından değiştirilir.
+H3: Güvenli Arama Ayarı Tüm Cihazlarda Geçerli mi?
+Google hesabına giriş yapılmışsa ayar hesaba bağlı olarak tüm cihazlarda geçerli olur; giriş yapılmadığında yalnızca o tarayıcı için çalışır.
+H3: Güvenli Arama ile Güvenli İnternet Aynı Şey mi?
+Hayır. Güvenli arama Google sonuçlarını süzer, operatörün güvenli internet hizmeti ise bağlantı düzeyinde erişimi sınırlar.
+H3: Çocuk Hesabında Güvenli Arama Nasıl Açılır?
+Aile bağlantısı uygulamasından çocuğun hesabı seçilir ve içerik kısıtlamaları bölümünden güvenli arama etkinleştirilir.</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>1. turkcell chatgpt : https://www.turkcell.com.tr/blog/chatgpt-yeni-google-mi-internette-arama-aliskanliklari-nasil-degisiyor
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -10744,7 +10904,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10799,7 +10959,7 @@
           </r>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>1. Google güvenli aramanın ne yaptığı açıklanır
 2. Açma ve kapatma adımları adım adım anlatılır
@@ -10807,36 +10967,36 @@
 4. Çocuk hesaplarında aile bağlantısı ayarı açıklanır</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Operatör tarafındaki güvenli internet hizmetiyle karıştırılmaması için ikisi ayrı ara başlıkta ele alınabilir.</t>
         </is>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="R7" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="S7" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="T7" s="6" t="inlineStr">
         <is>
           <t>Nisan</t>
         </is>
       </c>
-      <c r="S7" s="6" t="inlineStr">
+      <c r="U7" s="6" t="inlineStr">
         <is>
           <t>Şubat</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>Arama sonuçlarındaki filtreyi açmak veya kapatmak isteyen kullanıcı adım arıyor. Basit ama sürekli aranan bir konu.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="128.5" customHeight="1">
+    <row r="8" ht="317.5" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>PUK, PIN ve SIM Kilidi: Kod Öğrenme ve Kilit Açma</t>
@@ -10891,13 +11051,49 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>1. PUK kodunun nereden öğrenileceği
-2. PIN değiştirme ve kaldırma
-3. Üç kez yanlış PIN girildiğinde izlenecek yol
-4. SIM blokesinin kaldırılması</t>
+          <t>H2: PUK Kodu Nedir, Ne İşe Yarar?
+H2: PUK Kodu Nasıl Öğrenilir?
+H3: Uygulama ve Self Servis Kanallardan PUK Kodu Sorgulama
+H3: SIM Kart Ambalajından PUK Kodu Alma
+H2: PIN Kodu Nedir, PUK Kodundan Farkı Nedir?
+H2: PIN Kodu Nasıl Öğrenilir ve Değiştirilir?
+H2: PIN Kodu Üç Kez Yanlış Girilirse Ne Olur?
+H2: SIM Kart Blokesi Nasıl Kaldırılır?
+H2: SIM Kart Kilidi Nasıl Kapatılır?
+H2: PUK ve PIN Kodu Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>TON: Acil durum rehberi. Okuyucu telefonu kilitli ve panikte; giriş paragrafı doğrudan "PUK kodu şuradan öğrenilir" cümlesiyle başlamalı, tanım sonraya bırakılmamalı ama uzatılmamalı.
+H2 · PUK Kodu Nedir: SIM kartın kalıcı kilit açma kodu olduğu, sekiz haneli olduğu ve operatörden alındığı üç cümlede.
+H2 · PUK Kodu Nasıl Öğrenilir: İki H3. Birincisinde abone doğrulamasıyla self servis kanallar (uygulama, çevrimiçi işlem merkezi, çağrı merkezi) numaralı adımlarla. İkincisinde SIM kartın geldiği plastik ambalajın üzerindeki kod. Kodun üçüncü kişiyle paylaşılmaması uyarısı bölümün sonunda kutu içinde verilir.
+H2 · PIN Kodu Nedir: PIN ile PUK farkı üç satırlık tabloda: kaç hane, ne zaman sorulur, yanlış girilirse ne olur.
+H2 · PIN Nasıl Öğrenilir ve Değiştirilir: Varsayılan PIN'in operatöre göre değiştiği, telefon ayarlarından değiştirme adımları.
+H2 · Üç Kez Yanlış Girilirse: SIM'in PUK isteyeceği, PUK'un da on kez yanlış girilmesi hâlinde SIM'in kalıcı olarak kullanılamaz hâle geldiği net uyarı olarak yazılır. Bu, rakip sayfalarda çoğunlukla eksik kalan bilgi.
+H2 · SIM Blokesi Nasıl Kaldırılır: PUK ile açma adımları; PUK da tükendiyse yeni SIM talebi süreci.
+H2 · SIM Kilidi Nasıl Kapatılır: Her açılışta PIN sorulmasını kapatma adımları ve bunun güvenlik etkisi.
+UZUNLUK: 1.200-1.600 kelime.
+DİKKAT: PUK kodu abone doğrulaması gerektirir; yazıda kod paylaşımına yönlendiren hiçbir ifade bulunmamalı, yalnızca resmî kanallar gösterilmeli.</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>H3: PUK Kodu Nasıl Öğrenilir?
+PUK kodu operatörün mobil uygulaması, çevrimiçi işlem merkezi veya çağrı merkezi üzerinden abone doğrulaması yapılarak öğrenilir; SIM kartın geldiği ambalajın üzerinde de yazılıdır.
+H3: PUK Kodu Kaç Hanelidir?
+PUK kodu sekiz hanelidir ve SIM karta özeldir.
+H3: PIN Kodu ile PUK Kodu Arasındaki Fark Nedir?
+PIN dört haneli günlük kilit açma kodudur; PUK ise PIN üç kez yanlış girildiğinde SIM'i açan sekiz haneli kurtarma kodudur.
+H3: PIN Kodu Üç Kez Yanlış Girilirse Ne Olur?
+SIM kart kilitlenir ve açılması için PUK kodu istenir. PUK kodu da on kez yanlış girilirse SIM kart kalıcı olarak kullanılamaz hâle gelir.
+H3: SIM Kart Blokesi Nasıl Kaldırılır?
+Telefonun istediği ekrana PUK kodu girilir ve ardından yeni bir PIN belirlenir; PUK hakkı bittiyse yeni SIM kart talebi oluşturulur.
+H3: SIM Kart Her Açılışta PIN Soruyorsa Nasıl Kapatılır?
+Telefon ayarlarındaki SIM kart kilidi bölümünden PIN sorma seçeneği kapatılabilir; bu işlem için mevcut PIN girilir.</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -10905,7 +11101,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10926,7 +11122,7 @@
           </r>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>1. PUK kodunun nereden öğrenileceği açıklanır
 2. PIN değiştirme ve kaldırma adım adım anlatılır
@@ -10934,36 +11130,36 @@
 4. SIM blokesinin kaldırılması adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Abone doğrulaması gerektiren adımlarda self servis kanallara yönlendirme yapılabilir.</t>
         </is>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="R8" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="Q8" s="9" t="inlineStr">
+      <c r="S8" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="T8" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="S8" s="6" t="inlineStr">
+      <c r="U8" s="6" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>SIM kartı kilitlenen kişi acil çözüm arıyor. Bu anda doğru adımı veren sayfa ziyaret alıyor.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="128.5" customHeight="1">
+    <row r="9" ht="263.5" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Ekran Yansıtma: Telefondan Televizyona Görüntü Aktarma</t>
@@ -11015,13 +11211,45 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>1. Kablosuz yansıtma için gereken koşullar
-2. IPhone ve Android adımları
-3. Kablo ile yansıtma
-4. Televizyon bulunamadığında kontrol listesi</t>
+          <t>H2: Ekran Yansıtma Nedir?
+H2: Ekran Yansıtma Nasıl Yapılır?
+H3: iPhone Ekran Yansıtma Adımları
+H3: Android Telefonu Televizyona Yansıtma
+H2: Kablo ile Telefonu TV'ye Yansıtma
+H2: iPhone Ekran Yansıtma TV Bulmuyorsa Ne Yapmalı?
+H2: Yansıtma Sırasında Görüntü Donuyorsa Neye Bakılmalı?
+H2: Yansıtma Yöntemleri Karşılaştırma Tablosu
+H2: Ekran Yansıtma Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>TON: Uygulamalı rehber. Okuyucu televizyonun karşısında; her adım tek satırda ve sırayla verilmeli.
+H2 · Ekran Yansıtma Nedir: Telefon ekranının televizyonda birebir gösterilmesi; içerik aktarma (casting) ile ekran yansıtmanın farkı tek cümlede belirtilir.
+H2 · Nasıl Yapılır: İki H3. iPhone tarafında denetim merkezi üzerinden yansıtma; Android tarafında hızlı ayarlar menüsündeki yayınlama seçeneği. Her ikisinde de ön koşul aynı: telefon ve televizyon aynı Wi-Fi ağında olmalı. Bu koşul bölümün başında kutu içinde verilir.
+H2 · Kablo ile Yansıtma: HDMI adaptörü ve gereken kablo tipleri; Type-C çıkışlı telefonlarda görüntü desteğinin her modelde bulunmadığı notu.
+H2 · TV Bulmuyorsa Ne Yapmalı: Yedi maddelik kontrol listesi: aynı ağ, 2.4 GHz / 5 GHz ayrımı, televizyonun yansıtma özelliğinin açık olması, misafir ağı kısıtlaması, televizyon yazılım güncellemesi, telefonun yeniden başlatılması, router'da AP izolasyonu ayarı.
+H2 · Görüntü Donuyorsa: Ağ yoğunluğu, mesafe ve bant seçimi üç maddeyle.
+H2 · Karşılaştırma Tablosu: Kablosuz yansıtma / kablo ile bağlantı / içerik aktarma satırlarında gecikme, görüntü kalitesi, kurulum kolaylığı ve tipik kullanım sütunları.
+UZUNLUK: 1.300-1.600 kelime.
+İÇ BAĞLANTI: Ev ağı performansı bölümünde Wi-Fi ve bağlantı yazılarına doğal bağlantı kurulabilir.</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>H3: Telefon Televizyona Nasıl Yansıtılır?
+Telefon ve televizyon aynı Wi-Fi ağına bağlanır, ardından telefonun hızlı ayarlar ya da denetim merkezi menüsündeki ekran yansıtma seçeneğinden televizyon seçilir.
+H3: iPhone Ekran Yansıtma TV'yi Bulmuyorsa Ne Yapılmalı?
+İki cihazın aynı Wi-Fi ağında olduğu, televizyonun yansıtma özelliğinin açık olduğu ve misafir ağı kullanılmadığı kontrol edilir; ardından her iki cihaz yeniden başlatılır.
+H3: Ekran Yansıtma İçin İnternet Gerekli mi?
+Yansıtma aynı yerel ağ üzerinden çalışır; internet bağlantısı olmadan da aynı Wi-Fi ağına bağlı cihazlar arasında yansıtma yapılabilir.
+H3: Kablo ile Telefon TV'ye Nasıl Bağlanır?
+Telefonun bağlantı tipine uygun HDMI adaptörü kullanılır ve televizyonun HDMI girişi kaynak olarak seçilir.
+H3: Yansıtmada Görüntü Neden Takılıyor?
+Takılma çoğunlukla ağ yoğunluğundan kaynaklanır; modeme yakın olmak ve 5 GHz bandı kullanmak akıcılığı artırır.</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -11029,7 +11257,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11050,7 +11278,7 @@
           </r>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>1. Kablosuz yansıtma için gereken koşullar açıklanır
 2. IPhone ve Android adımları adım adım anlatılır
@@ -11058,36 +11286,36 @@
 4. Televizyon bulunamadığında kontrol listesi verilir</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Yansıtma kalitesi ev ağına bağlıdır; bağlantı bölümüne kısa bir not eklenebilir.</t>
         </is>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="R9" s="8" t="n">
         <v>88</v>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="S9" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="T9" s="6" t="inlineStr">
         <is>
           <t>Aralık</t>
         </is>
       </c>
-      <c r="S9" s="6" t="inlineStr">
+      <c r="U9" s="6" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>Telefondaki görüntüyü televizyona aktarmak isteyen kişi adım arıyor. Cihaz farkları netleşince arama karşılanıyor.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="128.5" customHeight="1">
+    <row r="10" ht="277" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>IP Adresi Nedir, Nasıl Sorgulanır?</t>
@@ -11138,13 +11366,48 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>1. IP adresinin tanımı
-2. Kendi IP adresinin öğrenilmesi
-3. Statik ve dinamik IP farkı
-4. IP adresinin gizlenmesi ve değiştirilmesi</t>
+          <t>H2: IP Adresi Nedir?
+H2: IP Adresim Nedir, Nasıl Öğrenilir?
+H3: Bilgisayardan IP Sorgulama
+H3: Telefondan IP Adresi Öğrenme
+H3: Modem Arayüzünden IP Sorgulama
+H2: Yerel IP ile Genel IP Arasındaki Fark Nedir?
+H2: Statik IP Nedir, Dinamik IP'den Farkı Nedir?
+H2: IPv4 ve IPv6 Arasındaki Fark Nedir?
+H2: IP Adresi Nasıl Değiştirilir?
+H2: IP Adresi Nasıl Gizlenir?
+H2: IP Adresi Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>TON: Bilgilendirici, teknik ama jargonsuz. Sonuç sayfasında IP gösteren araç siteleri önde olduğu için yazının açılışı okuyucunun sorusunu hemen karşılamalı: kendi IP adresini nereden göreceği ilk bölümde verilmeli.
+H2 · IP Adresi Nedir: İnternete bağlı her cihazın adresi olduğu, iki cümlelik tanım. Ev adresi benzetmesi tek cümleyle.
+H2 · IP Adresim Nasıl Öğrenilir: Üç H3'te bilgisayar, telefon ve modem arayüzü. Her biri üç adımı geçmeyen liste. Bölümün başında yerel IP ile genel IP'nin farklı değerler olduğu uyarısı verilir, çünkü okuyucu iki farklı sonuç görüp karışıyor.
+H2 · Yerel IP ile Genel IP Farkı: İki satırlık tablo: nerede geçerli, kim atar, dışarıdan görünür mü.
+H2 · Statik ve Dinamik IP: Fark tabloda; hangi durumda statik IP gerektiği (sunucu, kamera sistemi, uzak erişim) üç örnekle.
+H2 · IPv4 ve IPv6: Neden IPv6'ya geçildiği ve kullanıcı için pratik farkın ne olduğu iki paragrafta.
+H2 · IP Nasıl Değiştirilir: Modemin yeniden başlatılması, DHCP kirası, mobil veriye geçiş ve statik IP talebi seçenekleri.
+H2 · IP Nasıl Gizlenir: VPN ve proxy farkı; gizlemenin neyi sağlayıp neyi sağlamadığı dürüst biçimde yazılır.
+UZUNLUK: 1.500-1.800 kelime.
+DİKKAT: Yazı bir sorgulama aracına bağlanacaksa, aracın yazının en üstünde değil ilk H2'nin altında yer alması içerik bütünlüğünü korur.</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>H3: IP Adresim Nedir, Nereden Öğrenilir?
+Genel IP adresi tarayıcıdan yapılan bir IP sorgulamasıyla, yerel IP adresi ise cihazın ağ ayarları bölümünden görüntülenir.
+H3: Yerel IP ile Genel IP Arasındaki Fark Nedir?
+Yerel IP ev ağı içindeki cihazı tanımlar ve modem tarafından atanır; genel IP ise internet üzerinde bağlantıyı temsil eder ve servis sağlayıcı tarafından verilir.
+H3: Statik IP Nedir?
+Statik IP, cihaza sabit olarak atanan ve değişmeyen IP adresidir; uzaktan erişim gerektiren kullanımlarda tercih edilir.
+H3: IP Adresi Değiştirilebilir mi?
+Dinamik IP kullanan bağlantılarda modemin yeniden başlatılmasıyla adres değişebilir; sabit bir adres için servis sağlayıcıdan statik IP talep edilir.
+H3: IP Adresi Gizlenebilir mi?
+VPN kullanıldığında bağlantı VPN sunucusunun IP adresi üzerinden görünür; bu, gerçek adresin sitelerden gizlenmesini sağlar ancak tam anonimlik anlamına gelmez.</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>1. mac adresi nedir : https://www.turkcell.com.tr/blog/mac-adresi-her-cihazin-kendine-ozgu-dijital-imzasi
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -11152,7 +11415,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11173,7 +11436,7 @@
           </r>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>1. IP adresinin tanımı açıklanır
 2. Kendi IP adresinin öğrenilmesi adım adım anlatılır
@@ -11181,36 +11444,36 @@
 4. IP adresinin gizlenmesi ve değiştirilmesi adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Sonuç sayfasında IP gösteren araçlar öndedir; yazının bir sorgulama aracına bağlanması değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="R10" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="S10" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="T10" s="6" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>Kendi IP adresini öğrenmek isteyen kişi hızlı yanıt arıyor. Sonuç sayfasında araçlar önde, açıklama katmanı boş.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="128.5" customHeight="1">
+    <row r="11" ht="263.5" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>İndirilenler Klasörü: Telefonda ve Bilgisayarda Dosya Bulma</t>
@@ -11262,13 +11525,48 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>1. Android ve iPhone'da indirilenler klasörünün yeri
-2. Tarayıcıya göre değişen konumlar
-3. Indirilen dosyanın bulunamaması durumu
-4. Depolama temizliği</t>
+          <t>H2: İndirilenler Klasörü Nedir, Nerede Bulunur?
+H2: Telefonda İndirilenler Nerede?
+H3: Android'de İndirilen Dosyalar Nasıl Bulunur?
+H3: iPhone'da İndirilenler Klasörü Nerede?
+H3: Safari İndirilenler Klasörü Nasıl Açılır?
+H2: Bilgisayarda İndirilenler Klasörü Nerede?
+H2: Tarayıcıya Göre İndirilenler Nereye Kaydedilir?
+H2: İndirilen Dosya Bulunamıyorsa Ne Yapmalı?
+H2: Son İndirilenler Nasıl Görüntülenir?
+H2: İndirilenler Klasörü Nasıl Temizlenir?
+H2: İndirilenler Klasörü Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>TON: Kısa ve konum gösteren. Okuyucu dosyayı arıyor; her bölüm "şu menüye girilir" cümlesiyle başlamalı.
+H2 · İndirilenler Klasörü Nedir: Tanım tek paragraf; klasörün cihaz ve tarayıcıya göre değiştiği burada duyurulur.
+H2 · Telefonda İndirilenler Nerede: Üç H3. Android'de Dosyalar uygulaması yolu, iPhone'da Dosyalar uygulamasındaki iCloud Drive / Bu iPhone'da ayrımı, Safari'nin indirilenler menüsü. Her biri en fazla dört adım.
+H2 · Bilgisayarda İndirilenler Nerede: Windows ve macOS varsayılan yolları; hızlı erişim kısayolu.
+H2 · Tarayıcıya Göre Kayıt Yeri: Chrome, Safari, Firefox ve Edge satırlarında varsayılan klasör ve indirme geçmişi kısayolu sütunlarından oluşan tablo. Bu tablo yazının en alıntılanabilir bloğu.
+H2 · Dosya Bulunamıyorsa: Altı maddelik kontrol listesi: indirme geçmişinden konum açma, arama kutusuna dosya adı yazma, tarihe göre sıralama, uygulama içi indirme klasörü, geçici dosya uzantıları, depolama dolu uyarısı.
+H2 · Son İndirilenler: Tarayıcı indirme geçmişi kısayolları ve dosya yöneticisinde tarihe göre sıralama.
+H2 · Nasıl Temizlenir: Toplu silme adımları ve silinen dosyanın geri getirilip getirilemeyeceği notu.
+UZUNLUK: 1.200-1.500 kelime.
+DİKKAT: Menü adları sürümle değişiyor; adımlar menü adı yerine işlev adıyla verilmeli.</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>H3: İndirilenler Klasörü Telefonda Nerede?
+Android cihazlarda Dosyalar uygulamasındaki indirilenler bölümünde, iPhone'da ise Dosyalar uygulamasının bu iPhone'da sekmesinde yer alır.
+H3: Safari'de İndirilen Dosyalar Nereye Gider?
+Safari indirmeleri varsayılan olarak Dosyalar uygulamasındaki indirilenler klasörüne kaydedilir; konum Safari ayarlarından değiştirilebilir.
+H3: İndirilen Dosya Bulunamıyorsa Ne Yapılmalı?
+Tarayıcının indirme geçmişinden dosyanın konumu açılabilir; dosya adı dosya yöneticisinde aratılarak da bulunabilir.
+H3: Bilgisayarda İndirilenler Klasörü Nerede?
+Windows ve macOS'ta kullanıcı klasörünün altındaki indirilenler dizininde bulunur ve dosya yöneticisinin hızlı erişim bölümünden açılabilir.
+H3: İndirilenler Klasörü Temizlenirse Ne Olur?
+Klasördeki dosyalar silinir ve cihazda yer açılır; silinen dosyalar geri dönüşüm kutusu bulunmayan cihazlarda geri getirilemez.</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>1. wifi direct nedir : https://www.turkcell.com.tr/blog/wi-fi-direct-ile-dosya-paylasimi
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -11276,7 +11574,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11297,7 +11595,7 @@
           </r>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>1. Android ve iPhone'da indirilenler klasörünün yeri açıklanır
 2. Tarayıcıya göre değişen konumlar açıklanır
@@ -11305,36 +11603,36 @@
 4. Depolama temizliği açıklanır</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Cihaz ve sürüm farkları ekran görüntüsüyle desteklenebilir.</t>
         </is>
       </c>
-      <c r="P11" s="8" t="n">
+      <c r="R11" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q11" s="9" t="inlineStr">
+      <c r="S11" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="T11" s="6" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
+      <c r="U11" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>İndirdiği dosyayı bulamayan kişi klasörün yerini arıyor. Cihaza göre değişen bir bilgi, tek sayfada toplanabilir.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="128.5" customHeight="1">
+    <row r="12" ht="331" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Instagram Hesabı: Dondurma, Giriş Sorunları ve Açılmama Nedenleri</t>
@@ -11386,14 +11684,49 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>1. Hesabı geçici dondurma adımları ve kalıcı silmeden farkı
-2. Dondurulan hesabın geri açılması
-3. Uygulama açılmadığında kontrol listesi
-4. Giriş yapılamadığında doğrulama adımları
-5. Gönderilen takip isteklerinin görülmesi</t>
+          <t>H2: Instagram Hesabı Dondurma Nedir, Silmekten Farkı Nedir?
+H2: Instagram Hesabı Nasıl Dondurulur?
+H3: Telefondan Hesap Dondurma Adımları
+H3: Tarayıcıdan Hesap Dondurma Adımları
+H2: Dondurulan Instagram Hesabı Nasıl Açılır?
+H2: Instagram Neden Açılmıyor?
+H2: Instagram Giriş Yapamıyorum, Ne Yapmalıyım?
+H3: Şifre Sıfırlama Adımları
+H3: Doğrulama Kodu Gelmiyorsa Ne Yapılmalı?
+H2: Instagram Takip İsteği Attığım Kişiler Nasıl Görülür?
+H2: Instagram Hesap Sorunları Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>TON: Sorun çözen, sakin. Okuyucu hesabına erişemiyor ya da ara vermek istiyor; iki farklı niyet var, giriş paragrafında ikisi de işaret edilir.
+H2 · Dondurma Nedir: Geçici dondurma ile kalıcı silme farkı iki satırlık tabloda: veriler ne olur, geri dönüş mümkün mü, süre sınırı var mı.
+H2 · Nasıl Dondurulur: İki H3. Dondurma işleminin uygulamadan değil tarayıcıdan yapıldığı, bu yüzden okuyucunun uygulamada bu seçeneği bulamadığı açık uyarı olarak verilir. Bu, konunun en sık takılınan yeri.
+H2 · Dondurulan Hesap Nasıl Açılır: Yeniden giriş yapmanın yeterli olduğu; hesabın görünür olması için geçen süre.
+H2 · Instagram Neden Açılmıyor: Sekiz maddelik kontrol listesi: uygulama güncellemesi, önbellek temizliği, tarih ve saat ayarı, ağ değişimi, VPN, sunucu kaynaklı kesinti kontrolü, depolama alanı, uygulamanın yeniden kurulması.
+H2 · Giriş Yapamıyorum: İki H3'te şifre sıfırlama ve doğrulama kodu sorunları. Kod gelmiyorsa SMS filtreleri, numara doğruluğu ve e-posta seçeneği maddelenir.
+H2 · Takip İsteği Attığım Kişiler: Ayarlar içindeki hesap etkinliği yolundan adım adım; menü adının sürümle değişebildiği notu.
+UZUNLUK: 1.500-1.900 kelime.
+DİKKAT: Uygulama arayüzü sık değişiyor. Adımlar menü adıyla değil işlev sırasıyla anlatılmalı ve yazının güncellenme tarihi görünür olmalı.</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>H3: Instagram Hesabı Nasıl Dondurulur?
+Hesap dondurma işlemi uygulamadan değil tarayıcıdan yapılır: hesaba giriş yapıldıktan sonra profil düzenleme sayfasındaki hesabı geçici olarak devre dışı bırak seçeneği kullanılır.
+H3: Dondurulan Instagram Hesabı Nasıl Geri Açılır?
+Hesaba yeniden giriş yapmak yeterlidir; profil kısa süre içinde tekrar görünür hâle gelir.
+H3: Hesap Dondurmak ile Silmek Arasındaki Fark Nedir?
+Dondurmada profil geçici olarak gizlenir ve veriler korunur; silmede ise gönderiler, takipçiler ve mesajlar kalıcı olarak kaldırılır.
+H3: Instagram Neden Açılmıyor?
+Sorun çoğunlukla uygulama sürümü, önbellek ya da ağ bağlantısı kaynaklıdır; uygulamanın güncellenmesi ve farklı bir ağ denenmesi ilk adımlardır.
+H3: Instagram'a Giriş Yapamıyorum, Ne Yapmalıyım?
+Şifre sıfırlama bağlantısı istenir; doğrulama kodu gelmiyorsa e-posta seçeneği denenir ve numaranın hesapta güncel olduğu kontrol edilir.
+H3: Instagram'da Attığım Takip İstekleri Nereden Görülür?
+Ayarlar bölümündeki hesap etkinliği sayfasında yer alan takip istekleri listesinden görüntülenir.</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -11401,7 +11734,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11439,7 +11772,7 @@
           </r>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>1. Hesabı geçici dondurma adımları ve kalıcı silmeden farkı açıklanır
 2. Dondurulan hesabın geri açılması adım adım anlatılır
@@ -11448,36 +11781,36 @@
 5. Gönderilen takip isteklerinin görülmesi adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Uygulama arayüzü sık değiştiğinden adımların ekran görüntüsüyle desteklenmesi ve güncellenme tarihinin görünür tutulması önerilir.</t>
         </is>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="R12" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q12" s="9" t="inlineStr">
+      <c r="S12" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="T12" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="S12" s="6" t="inlineStr">
+      <c r="U12" s="6" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>Hesabını donduran ya da uygulamaya giremeyen kişi hızlı yanıt arıyor. Rakiplerde konu ayrı yazılara bölünmüş durumda.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="128.5" customHeight="1">
+    <row r="13" ht="209.5" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Spam Ne Demek? Spam Mesaj ve Aramaları Engelleme</t>
@@ -11525,12 +11858,38 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>1. Spam tanımı
-2. Spam mesaj ve arama engelleme adımları
-3. Operatör tarafındaki engelleme servisleri</t>
+          <t>H2: Spam Ne Demek?
+H2: Spam Arama Ne Demek?
+H2: Spam Mesajlar Nasıl Engellenir?
+H2: Spam Aramalar Nasıl Engellenir?
+H2: Operatör Tarafındaki Engelleme Servisleri
+H2: Spam Mesaj ve Aramalar Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım sorgusu. Açılış paragrafı tek cümlelik, bağlamdan bağımsız okunabilen bir tanımla başlamalı; bu cümle AI yanıtına kaynak olarak seçilme ihtimalini belirleyen yerdir.
+H2 · Spam Ne Demek: İstenmeden gönderilen toplu mesaj ve aramalar. İki cümle, üçüncüye geçilmez.
+H2 · Spam Arama Ne Demek: Tanıtım ve dolandırıcılık aramalarının ayrımı; okuyucunun ekranında gördüğü "spam" etiketinin nereden geldiği.
+H2 · Spam Mesajlar Nasıl Engellenir: Android ve iPhone adımları kısa liste hâlinde; ticari ileti izin yönetimi sisteminden izin iptali ayrı madde.
+H2 · Spam Aramalar Nasıl Engellenir: Telefon tarafındaki bilinmeyen arayan filtresi ve numara engelleme.
+H2 · Operatör Servisleri: Operatörün spam engelleme hizmetinin ne yaptığı ve nereden açıldığı iki cümlede; hizmet sayfasına iç bağlantı.
+UZUNLUK: 700-900 kelime. Yazı kısa tutulur; her bölüm en fazla iki paragraf.</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>H3: Spam Ne Demek?
+Spam, alıcının isteği dışında toplu olarak gönderilen mesaj, e-posta veya aramalara verilen addır.
+H3: Spam Arama Ne Demek?
+Spam arama, tanıtım ya da dolandırıcılık amacıyla yapılan ve kullanıcının talep etmediği telefon aramasıdır.
+H3: Spam Mesajlar Nasıl Engellenir?
+Gönderen numara engellenir, mesaj spam olarak bildirilir ve ticari ileti izinleri izin yönetim sistemi üzerinden iptal edilir.
+H3: Gelen Aramanın Spam Olduğu Nasıl Anlaşılır?
+Tanımadık numaradan gelen, kişisel bilgi ya da doğrulama kodu isteyen aramalar spam olarak değerlendirilir; kod hiçbir koşulda paylaşılmamalıdır.</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>1. phishing nedir : https://www.turkcell.com.tr/blog/bu-mesaj-tuzak-olabilir-phishing-nedir-ve-nasil-anlasilir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -11538,7 +11897,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11559,43 +11918,43 @@
           </r>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>1. Spam tanımı açıklanır
 2. Spam mesaj ve arama engelleme adımları adım adım anlatılır
 3. Operatör tarafındaki engelleme servisleri açıklanır</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Kısa ve doğrudan yanıt veren bir yapı önerilmektedir; sorgu tanım niyetlidir.</t>
         </is>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="R13" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="S13" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="T13" s="6" t="inlineStr">
         <is>
           <t>Aralık</t>
         </is>
       </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>Spam kelimesinin anlamını ve engelleme yolunu arayan kişi kısa yanıt istiyor.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="128.5" customHeight="1">
+    <row r="14" ht="317.5" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
@@ -11647,14 +12006,49 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>1. SSD ile HDD farkı
-2. RAM'in görevi ve yeterli kapasite
-3. Ekran kartının ne işe yaradığı
-4. Anakartın rolü
-5. Bilgisayar yavaşladığında hangi bileşene bakılacağı</t>
+          <t>H2: RAM Nedir, Ne İşe Yarar?
+H2: Kaç GB RAM Yeterlidir?
+H2: SSD Nedir, Ne İşe Yarar?
+H2: SSD ile HDD Arasındaki Fark Nedir?
+H2: Ekran Kartı Nedir, Ne İşe Yarar?
+H2: Anakart Nedir?
+H2: Bilgisayar Donanımı Karşılaştırma Tablosu
+H2: Bilgisayar Yavaşladığında Hangi Donanıma Bakılmalı?
+H2: Bilgisayar Donanımı Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>TON: Öğretici, ürün önerisiz. Her bileşen için aynı şablon kullanılır: bir cümlelik tanım, ne işe yaradığı, kullanıcının hangi durumda fark ettiği.
+H2 · RAM Nedir: Tanım iki cümle; "RAM ne demek" kalıbı ilk paragrafta doğal biçimde geçer.
+H2 · Kaç GB RAM Yeterlidir: Kullanım senaryosuna göre üç satırlık tablo: günlük kullanım, ofis ve tarayıcı yoğun kullanım, oyun ve içerik üretimi.
+H2 · SSD Nedir: Tanım ve ne işe yaradığı; kapasite bandı önerisi verilmez, kullanım örneği verilir.
+H2 · SSD ile HDD Farkı: Okuma hızı, dayanıklılık, gürültü, tipik kapasite ve maliyet satırlarında karşılaştırma tablosu.
+H2 · Ekran Kartı Nedir: Tümleşik ve harici ekran kartı ayrımı; hangi kullanımda hangisinin yeterli olduğu.
+H2 · Anakart Nedir: Bileşenleri birbirine bağlayan taban olduğu; yükseltme yaparken uyumluluğun neden anakarttan başladığı.
+H2 · Karşılaştırma Tablosu: RAM / SSD / ekran kartı / anakart satırlarında ne işe yarar, yavaşlığa etkisi, yükseltilebilir mi sütunları.
+H2 · Yavaşladığında Hangi Donanım: Karar akışı: açılış yavaşsa SSD, çok sekmede takılıyorsa RAM, oyun ve video işlemede takılıyorsa ekran kartı. Üç maddede net yönlendirme.
+UZUNLUK: 1.600-2.000 kelime.
+DİKKAT: Marka ve model önerisi verilmez; yazı bilgi katmanında kalır.</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>H3: RAM Ne Demek?
+RAM, bilgisayarın açık olan programları ve verileri geçici olarak tuttuğu hızlı bellektir.
+H3: Kaç GB RAM Yeterlidir?
+Günlük kullanım ve ofis işleri için orta seviye bir kapasite yeterli olurken, oyun ve video düzenleme gibi işler daha yüksek kapasite gerektirir.
+H3: SSD Ne İşe Yarar?
+SSD, işletim sistemi ve dosyaların saklandığı depolama birimidir; hareketli parça içermediği için açılış ve dosya erişimini belirgin biçimde hızlandırır.
+H3: SSD ile HDD Arasındaki Fark Nedir?
+SSD çok daha hızlı, sessiz ve darbeye dayanıklıdır; HDD ise aynı fiyata daha yüksek kapasite sunar.
+H3: Ekran Kartı Ne İşe Yarar?
+Ekran kartı görüntünün işlenmesinden sorumludur; oyun, video düzenleme ve grafik işlerinde performansı doğrudan etkiler.
+H3: Bilgisayar Yavaşladığında Önce Neye Bakılmalı?
+Açılış ve dosya erişimi yavaşsa depolama birimine, aynı anda çok uygulama açıkken takılma yaşanıyorsa RAM kapasitesine bakılır.</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>1. kuantum bilgisayar : https://www.turkcell.com.tr/blog/kuantum-bilgisayar-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -11662,7 +12056,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11683,7 +12077,7 @@
           </r>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>1. SSD ile HDD farkı açıklanır
 2. RAM'in görevi ve yeterli kapasite açıklanır
@@ -11692,36 +12086,36 @@
 5. Bilgisayar yavaşladığında hangi bileşene bakılacağı açıklanır</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Ürün önerisi verilmemeli; bilgi katmanında kalınmalıdır.</t>
         </is>
       </c>
-      <c r="P14" s="8" t="n">
+      <c r="R14" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q14" s="9" t="inlineStr">
+      <c r="S14" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="T14" s="6" t="inlineStr">
         <is>
           <t>Aralık</t>
         </is>
       </c>
-      <c r="S14" s="6" t="inlineStr">
+      <c r="U14" s="6" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>Bilgisayar alacak veya yükseltecek kişi bileşenlerin ne işe yaradığını soruyor. Tek rehber birden çok aramayı karşılıyor.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="128.5" customHeight="1">
+    <row r="15" ht="263.5" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>E-İmza Nasıl Alınır?</t>
@@ -11768,12 +12162,40 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>1. E-imza tanımı
-2. Başvuru adımları
-3. Mobil imza ile farkı</t>
+          <t>H2: E-İmza Nedir?
+H2: E-İmza Nasıl Alınır? Adım Adım
+H2: E-İmza Başvurusu İçin Gereken Belgeler
+H2: E-İmza ile Mobil İmza Arasındaki Fark Nedir?
+H2: E-İmza Nerelerde Kullanılır?
+H2: E-İmza Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>TON: İşlem rehberi. Başlıktaki soru ilk paragrafta doğrudan yanıtlanır: e-imza yetkilendirilmiş hizmet sağlayıcılarından başvuruyla alınır.
+H2 · E-İmza Nedir: Islak imzayla aynı hukuki geçerliliğe sahip elektronik imza; iki cümle.
+H2 · Nasıl Alınır: Numaralı adım listesi: sağlayıcı seçimi, çevrimiçi başvuru, kimlik doğrulama, sertifikanın teslimi, kurulum ve ilk kullanım.
+H2 · Gereken Belgeler: Bireysel ve kurumsal başvuru için iki kısa liste.
+H2 · E-İmza ile Mobil İmza Farkı: Üç satırlık tablo: nerede saklanır, hangi cihaz gerekir, nasıl kullanılır. Bu bölüm yazının ayırt edici yanıdır; Turkcell Mobil İmza hizmetine doğal iç bağlantı buradan kurulur.
+H2 · Nerelerde Kullanılır: e-Devlet işlemleri, sözleşme imzalama, kurumsal onay akışları üç madde hâlinde.
+UZUNLUK: 800-1.100 kelime.</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>H3: E-İmza Nasıl Alınır?
+Yetkilendirilmiş elektronik sertifika hizmet sağlayıcılarından çevrimiçi başvuru yapılır, kimlik doğrulaması tamamlanır ve sertifika kullanıcıya teslim edilir.
+H3: E-İmza Nedir?
+E-imza, elektronik ortamda atılan ve ıslak imzayla aynı hukuki geçerliliği taşıyan imzadır.
+H3: E-İmza ile Mobil İmza Arasındaki Fark Nedir?
+E-imza genellikle bir donanım üzerinde saklanır ve bilgisayara takılarak kullanılır; mobil imza ise SIM kart üzerinde çalışır ve telefondan onay verilerek kullanılır.
+H3: E-İmza Başvurusu İçin Hangi Belgeler Gerekir?
+Bireysel başvurularda kimlik belgesi yeterlidir; kurumsal başvurularda ayrıca yetki belgesi ve şirket bilgileri istenir.
+H3: E-İmza Nerelerde Kullanılır?
+e-Devlet işlemlerinde, resmî yazışmalarda, sözleşme onaylarında ve kurumsal imza akışlarında kullanılır.</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -11781,7 +12203,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11802,43 +12224,43 @@
           </r>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>1. E-imza tanımı açıklanır
 2. Başvuru adımları adım adım anlatılır
 3. Mobil imza ile farkı açıklanır</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Turkcell Mobil İmza hizmetiyle bağ kurulabilir; karşılaştırma bölümü ayırt edici olmaktadır.</t>
         </is>
       </c>
-      <c r="P15" s="8" t="n">
+      <c r="R15" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="S15" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="T15" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="S15" s="6" t="inlineStr">
+      <c r="U15" s="6" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>E-imza almak isteyen kişi başvuru adımını arıyor. Mobil imza karşılaştırması markaya bağlanıyor.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="128.5" customHeight="1">
+    <row r="16" ht="209.5" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Taahhüt Ne Demek?</t>
@@ -11886,13 +12308,37 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>1. Taahhüdün tanımı
-2. Taahhütlü ve taahhütsüz farkı
-3. Taahhüt süresi dolmadan çıkışta ne olduğu
-4. Taahhüt süresinin öğrenilmesi</t>
+          <t>H2: Taahhüt Ne Demek?
+H2: Taahhütlü Ne Demek, Taahhütsüzden Farkı Nedir?
+H2: Taahhüt Süresi Nasıl Öğrenilir?
+H2: Taahhüt Süresi Dolmadan Çıkılırsa Ne Olur?
+H2: Taahhüt Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım sorgusu, sade. İlk paragraf tek cümlelik karşılık verir: taahhüt, belirli bir süre hizmeti kullanma sözü karşılığında avantajlı fiyat alınmasıdır.
+H2 · Taahhüt Ne Demek: İki cümlelik tanım; telekom bağlamında hangi hizmetlerde karşımıza çıktığı.
+H2 · Taahhütlü ve Taahhütsüz Farkı: Üç satırlık tablo: fiyat avantajı, süre bağlayıcılığı, erken çıkış durumu.
+H2 · Taahhüt Süresi Nasıl Öğrenilir: Mobil uygulama ve çevrimiçi işlem merkezi üzerinden bakılabileceği; adımlar iki maddede. Ekran yolları ürün ekibiyle doğrulanır.
+H2 · Süre Dolmadan Çıkılırsa: Cayma bedeli kavramı, hesaplama mantığının süreye göre değiştiği ve tutarın sözleşmede yazdığı. Rakam verilmez; kavram açıklanır.
+UZUNLUK: 600-800 kelime. Kısa içerik formatı korunur.
+DİKKAT: Kampanya koşulları ve cayma bedeli hesabı ürün ekibiyle doğrulanmalı; yazıda tutar yerine yöntem anlatılmalı.</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>H3: Taahhüt Ne Demek?
+Taahhüt, belirli bir süre boyunca hizmeti kullanma sözü verilmesi karşılığında daha avantajlı fiyat ya da ek fayda alınmasıdır.
+H3: Taahhütlü ile Taahhütsüz Arasındaki Fark Nedir?
+Taahhütlü seçenekte fiyat daha uygundur ancak süre boyunca bağlayıcılık vardır; taahhütsüz seçenekte istenildiği zaman çıkılabilir, fiyat ise genellikle daha yüksektir.
+H3: Taahhüt Süresi Nereden Öğrenilir?
+Taahhüt süresi operatörün mobil uygulaması ya da çevrimiçi işlem merkezindeki abonelik bilgileri bölümünden görüntülenir.
+H3: Taahhüt Bitmeden Çıkılırsa Ne Olur?
+Kalan süreye bağlı olarak sözleşmede belirtilen cayma bedeli uygulanır; tutar kalan ay sayısına göre değişir.</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -11900,12 +12346,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Rakip bloglarda taahhüt tanımı abonelik sayfalarına bağlı olarak veriliyor; bağımsız tanım içeriği bulunmamaktadır.</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>1. Taahhüdün tanımı açıklanır
 2. Taahhütlü ve taahhütsüz farkı açıklanır
@@ -11913,36 +12359,36 @@
 4. Taahhüt süresinin öğrenilmesi adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>Tanım sorgusudur; ilk paragrafta tek cümlelik karşılık verilmesi önerilir. Kampanya koşulları ürün ekibiyle doğrulanmalıdır.</t>
         </is>
       </c>
-      <c r="P16" s="8" t="n">
+      <c r="R16" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q16" s="9" t="inlineStr">
+      <c r="S16" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="T16" s="6" t="inlineStr">
         <is>
           <t>Aralık</t>
         </is>
       </c>
-      <c r="S16" s="6" t="inlineStr">
+      <c r="U16" s="6" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr">
+      <c r="V16" s="4" t="inlineStr">
         <is>
           <t>Taahhüt kelimesinin ne anlama geldiğini soran kişi tek cümlelik karşılık bekliyor.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="128.5" customHeight="1">
+    <row r="17" ht="277" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Konum Paylaşma ve Numaradan Konum Bulma</t>
@@ -11994,13 +12440,48 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>1. WhatsApp, Google Haritalar ve iMessage üzerinden konum paylaşma
-2. Canlı konum paylaşımı süresi
-3. Numaradan konum bulmanın gerçekte mümkün olup olmadığı
-4. Konum servislerinin pil etkisi</t>
+          <t>H2: Konum Paylaşma Nedir?
+H2: Konum Nasıl Atılır?
+H3: WhatsApp'tan Konum Atma
+H3: Google Haritalar'dan Konum Paylaşma
+H3: iPhone'da Konum Paylaşma
+H2: Canlı Konum Nasıl Paylaşılır, Ne Kadar Sürer?
+H2: Neredeyim? Kendi Konumumu Nasıl Bulurum?
+H2: Numaradan Konum Bulma Gerçekten Mümkün mü?
+H2: Konum Paylaşımı Nasıl Durdurulur?
+H2: Konum Servisleri Pili Ne Kadar Tüketir?
+H2: Konum Paylaşma Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>TON: Uygulamalı ve dürüst. Yazının kritik bölümü numaradan konum bulma başlığı: bu arama yanıltıcı vaatlere açık ve rakip içerikler net yanıt vermiyor. Ayırt edici yan burada.
+H2 · Konum Paylaşma Nedir: Anlık konum ile canlı konum farkı iki cümlede.
+H2 · Konum Nasıl Atılır: Üç H3, her biri en fazla dört adım. Uygulama menü adları yerine işlev sırası kullanılır.
+H2 · Canlı Konum: Süre seçenekleri, paylaşımın kimlerle görüneceği ve süre dolduğunda ne olduğu.
+H2 · Neredeyim: Haritada mavi noktanın hassasiyeti, konum doğruluğunun neden değiştiği (GPS, Wi-Fi, baz istasyonu) üç maddede.
+H2 · Numaradan Konum Bulma: Dürüst yanıt. Yalnızca numarayla konum bulmanın kullanıcı tarafından mümkün olmadığı, bunu vaat eden uygulamaların çalışmadığı ve veri güvenliği riski taşıdığı; konumun ancak karşı taraf paylaştığında ya da yasal süreçle erişilebildiği yazılır.
+H2 · Paylaşım Nasıl Durdurulur: Uygulama bazında durdurma adımları ve cihaz ayarlarından konum izninin kapatılması.
+H2 · Pil Etkisi: Sürekli konum izninin pil tüketimine etkisi ve izin seviyelerinin (her zaman / uygulamayı kullanırken) farkı.
+UZUNLUK: 1.500-1.800 kelime.
+DİKKAT: Numaradan konum bulma bölümünde hiçbir üçüncü parti uygulama adı verilmemeli; yönlendirme değil uyarı yazılmalı.</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>H3: Konum Nasıl Atılır?
+Mesajlaşma uygulamasındaki ek menüsünden konum seçeneği açılır, anlık konum ya da canlı konum seçilerek gönderilir.
+H3: Canlı Konum Ne Kadar Süre Paylaşılır?
+Canlı konum, seçilen süre boyunca paylaşılır ve süre dolduğunda otomatik olarak durur; paylaşım istenildiği an elle de sonlandırılabilir.
+H3: Numaradan Konum Bulmak Mümkün mü?
+Yalnızca telefon numarasıyla bir kişinin konumunu bulmak kullanıcı tarafından mümkün değildir; konum ancak karşı taraf paylaştığında görülebilir.
+H3: Konum Paylaşımı Nasıl Durdurulur?
+Paylaşımın yapıldığı uygulamadaki konum ekranından durdurma seçeneği kullanılır ya da cihaz ayarlarından uygulamanın konum izni kapatılır.
+H3: Konum Servisleri Pili Çok mu Tüketir?
+Sürekli açık konum izni pil tüketimini artırır; iznin yalnızca uygulama kullanılırken verilmesi tüketimi azaltır.</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12008,7 +12489,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12029,7 +12510,7 @@
           </r>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>1. WhatsApp, Google Haritalar ve iMessage üzerinden konum paylaşma adım adım anlatılır
 2. Canlı konum paylaşımı süresi açıklanır
@@ -12037,36 +12518,36 @@
 4. Konum servislerinin pil etkisi açıklanır</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Numaradan konum bulma başlığı yanıltıcı vaatlere açıktır; yasal çerçeve ve gerçek sınırlar açıkça yazılmalıdır.</t>
         </is>
       </c>
-      <c r="P17" s="8" t="n">
+      <c r="R17" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="Q17" s="10" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="T17" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="S17" s="6" t="inlineStr">
+      <c r="U17" s="6" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>Konum paylaşmak isteyen çok kişi var; numaradan konum bulma ise beklentisi yanlış kurulmuş bir arama. İkisini dürüstçe ayıran sayfa güven kazanıyor.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="128.5" customHeight="1">
+    <row r="18" ht="263.5" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Telefondan Telefona Veri Aktarma: Android ve iPhone</t>
@@ -12117,14 +12598,44 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>1. Android'den iPhone'a aktarma
-2. IPhone'dan iPhone'a hızlı başlangıç
-3. Android'den Android'e aktarma
-4. WhatsApp geçmişinin taşınması
-5. Aktarma sırasında sık karşılaşılan durumlar</t>
+          <t>H2: Telefondan Telefona Veri Aktarma Nedir?
+H2: Android'den iPhone'a Aktarma Nasıl Yapılır?
+H2: iPhone'dan iPhone'a Aktarma Nasıl Yapılır?
+H2: Android'den Android'e Veri Aktarma
+H2: WhatsApp Geçmişi Yeni Telefona Nasıl Taşınır?
+H2: Aktarma Sırasında Sık Karşılaşılan Durumlar
+H2: Veri Aktarma ile Numara Taşıma Arasındaki Fark Nedir?
+H2: Veri Aktarma Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>TON: Adım rehberi. Okuyucu yeni telefonu elinde ve kurulum ekranında; her bölüm hangi ekranda ne yapılacağını sırayla vermeli.
+H2 · Veri Aktarma Nedir: Hangi verilerin taşındığı (kişiler, fotoğraflar, mesajlar, uygulamalar) ve hangilerinin taşınmadığı (bazı uygulama içi veriler, ödeme kartları) iki listede.
+H2 · Android'den iPhone'a: Kurulum sırasında uygulamalar ve veriler ekranından yapılan aktarım; kurulum tamamlandıysa sıfırlama gerektiği uyarısı. Bu uyarı çoğu rakip içerikte eksik.
+H2 · iPhone'dan iPhone'a: Hızlı başlangıç ile cihazların yan yana getirilmesi ve iCloud yedeğinden geri yükleme iki seçenek olarak.
+H2 · Android'den Android'e: Kablolu ve kablosuz aktarım; markaların kendi aktarım uygulamaları tek cümleyle.
+H2 · WhatsApp Geçmişi: Aynı platformda ve platform değiştirirken izlenecek iki farklı yol; yedeğin nereye alındığı.
+H2 · Sık Karşılaşılan Durumlar: Altı madde: aktarım yarıda kesildi, depolama yetmedi, uygulamalar geldi verileri gelmedi, fotoğraflar eksik, pil yetersiz, iki cihaz birbirini bulmuyor.
+H2 · Numara Taşıma Farkı: Veri aktarma cihazlar arasında, numara taşıma operatörler arasında yapılır. İki cümlelik ayrım; okuyucunun karıştırdığı nokta.
+UZUNLUK: 1.500-1.800 kelime.</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>H3: Android'den iPhone'a Veri Nasıl Aktarılır?
+Yeni iPhone'un kurulum ekranındaki uygulamalar ve veriler adımında Android'den aktar seçeneği kullanılır; kurulum tamamlanmışsa cihazın sıfırlanması gerekir.
+H3: iPhone'dan iPhone'a Aktarma Nasıl Yapılır?
+İki cihaz yan yana getirilerek hızlı başlangıç kullanılır ya da eski cihazın iCloud yedeği yeni cihaza geri yüklenir.
+H3: WhatsApp Sohbetleri Yeni Telefona Taşınır mı?
+Evet. Aynı işletim sistemi arasında yedekten geri yükleme, farklı işletim sistemleri arasında ise uygulamanın kendi aktarma akışı kullanılır.
+H3: Veri Aktarma ile Numara Taşıma Aynı Şey mi?
+Hayır. Veri aktarma iki telefon arasında içerik taşınmasıdır; numara taşıma ise numaranın başka bir operatöre geçirilmesidir.
+H3: Aktarma Yarıda Kesilirse Ne Olur?
+İşlem baştan başlatılabilir; aktarımın tamamlanabilmesi için iki cihazın da yeterli pil ve depolama alanına sahip olması gerekir.</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12132,7 +12643,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12153,7 +12664,7 @@
           </r>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>1. Android'den iPhone'a aktarma adım adım anlatılır
 2. IPhone'dan iPhone'a hızlı başlangıç açıklanır
@@ -12162,36 +12673,36 @@
 5. Aktarma sırasında sık karşılaşılan durumlar açıklanır</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Numara taşıma ile veri aktarma farklı işlemlerdir; ikisinin karıştırılmaması için kısa bir ayrım notu eklenebilir.</t>
         </is>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="R18" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="Q18" s="10" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="T18" s="6" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="S18" s="6" t="inlineStr">
+      <c r="U18" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr">
+      <c r="V18" s="4" t="inlineStr">
         <is>
           <t>Telefon değiştiren kişi verisini kaybetmeden taşımak istiyor. Android ve iPhone ayrımını tek sayfada veren içerik bulunmuyor.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="128.5" customHeight="1">
+    <row r="19" ht="263.5" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>En İyi Chrome Eklentileri: Hangisi Ne İşe Yarar?</t>
@@ -12241,13 +12752,43 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>1. Kullanım alanına göre eklenti seçkisi: üretkenlik, güvenlik, alışveriş
-2. Her eklenti için tek cümlelik ne işe yaradığı
-3. Eklentinin eklenmesi ve kaldırılması
-4. Eklenti izinlerinin görülmesi ve güvenilir eklentinin ayırt edilmesi</t>
+          <t>H2: Chrome Eklentileri Nedir, Ne İşe Yarar?
+H2: Üretkenlik İçin En İyi Chrome Eklentileri
+H2: Güvenlik ve Gizlilik İçin Chrome Uzantıları
+H2: Alışveriş ve Fiyat Takibi İçin Chrome Eklentileri
+H2: Chrome Eklentisi Nasıl Eklenir?
+H2: Chrome Eklentisi Nasıl Kaldırılır?
+H2: Eklenti İzinleri Nereden Görülür, Güvenilir Eklenti Nasıl Anlaşılır?
+H2: Chrome Eklentileri Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>TON: Seçki formatı. Sonuç sayfası tek eklenti kurulumu değil liste bekliyor; yazı bir seçki olarak kurgulanır ve kurulum adımları listenin sonuna alınır.
+H2 · Chrome Eklentileri Nedir: Tarayıcıya işlev ekleyen küçük yazılımlar; "uzantı" ile "eklenti" ifadelerinin aynı şeyi anlattığı burada belirtilir, çünkü iki kalıp da aranıyor.
+H2-H4 · Üç kategori: Her kategoride dört-beş eklenti. Her eklenti için sabit şablon: ad, tek cümlelik ne işe yaradığı, hangi kullanıcıya uygun olduğu. Puanlama ya da sıralama yapılmaz.
+H2 · Nasıl Eklenir: Web mağazasından kurulum üç adımda; kurulum sonrası araç çubuğuna sabitleme.
+H2 · Nasıl Kaldırılır: İki yol: araç çubuğundan sağ tık, uzantılar sayfasından kaldırma.
+H2 · İzinler ve Güvenilirlik: Eklentinin hangi verilere eriştiğinin nereden görüldüğü ve güvenilirlik için bakılacak dört işaret: geliştirici bilgisi, kullanıcı sayısı, güncelleme tarihi, istenen izinlerin işlevle uyumu. Bu bölüm yazının ayırt edici yanı.
+UZUNLUK: 1.200-1.500 kelime.
+DİKKAT: Eklenti listesi zamanla eskiyor; güncellenme tarihi görünür tutulmalı ve kaldırılan eklentiler dönemsel olarak gözden geçirilmeli.</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>H3: Chrome'da En İyi Eklentiler Hangileridir?
+İhtiyaca göre değişir: üretkenlik için not ve sekme yönetimi, gizlilik için izleyici engelleyici, alışveriş için fiyat takibi eklentileri öne çıkar.
+H3: Chrome Eklentisi Nasıl Eklenir?
+Chrome Web Mağazası'ndan eklenti sayfası açılır, Chrome'a ekle düğmesine basılır ve izinler onaylanır.
+H3: Chrome Uzantısı Nasıl Kaldırılır?
+Araç çubuğundaki simgeye sağ tıklanarak ya da uzantılar sayfasından kaldır seçeneği kullanılarak silinir.
+H3: Chrome Eklentileri Güvenli mi?
+Mağazadaki her eklenti aynı düzeyde güvenli değildir; geliştirici bilgisi, kullanıcı sayısı, son güncelleme tarihi ve istenen izinlerin işlevle uyumu kontrol edilmelidir.
+H3: Eklentinin Hangi Verilere Eriştiği Nereden Görülür?
+Uzantılar sayfasında eklentinin detay bölümü açılarak site erişimi ve izin listesi görüntülenir.</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12255,7 +12796,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12284,7 +12825,7 @@
           </r>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>1. Kullanım alanına göre eklenti seçkisi: üretkenlik, güvenlik, alışveriş açıklanır
 2. Her eklenti için tek cümlelik ne işe yaradığı açıklanır
@@ -12292,36 +12833,36 @@
 4. Eklenti izinlerinin görülmesi ve güvenilir eklentinin ayırt edilmesi adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Seçki formatı sonuç sayfasıyla uyumludur; kurulum adımları listenin sonunda kısa bir bölüm olarak verilebilir.</t>
         </is>
       </c>
-      <c r="P19" s="8" t="n">
+      <c r="R19" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="Q19" s="10" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="T19" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>Eklenti arayan kişi tek bir kurulum adımı değil, hangi eklentinin ne işe yaradığını gösteren bir seçki bekliyor.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="128.5" customHeight="1">
+    <row r="20" ht="263.5" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t>E-Posta Adresi Nedir, Nasıl Açılır?</t>
@@ -12370,13 +12911,42 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>1. E-posta adresi oluşturma adımları
-2. Telefonda hesap kurulumu
-3. E-posta yazarken dikkat edilecekler
-4. Iki adımlı doğrulama</t>
+          <t>H2: E-Posta Adresi Nedir?
+H2: E-Posta Adresi Nasıl Açılır? Adım Adım
+H2: Telefonda E-Posta Hesabı Nasıl Kurulur?
+H2: E-Posta Nasıl Yazılır?
+H3: Konu Satırı Nasıl Yazılmalı?
+H3: Resmî E-Posta Yazarken Dikkat Edilecekler
+H2: E-Posta Hesabı İçin İki Adımlı Doğrulama Nasıl Açılır?
+H2: E-Posta Adresi Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>TON: Yeni başlayana anlatan, sabırlı. Okuyucu ilk kez e-posta hesabı açıyor olabilir; adımlar atlanmadan verilir.
+H2 · E-Posta Adresi Nedir: Kullanıcı adı, @ işareti ve alan adından oluşan yapı; şema bir satırda gösterilir.
+H2 · Nasıl Açılır: Numaralı adım listesi: sağlayıcı seçimi, hesap oluşturma formu, kullanıcı adı belirleme, güçlü şifre, kurtarma bilgisi. Kullanıcı adı seçerken hangi kalıpların uygun olduğu iki maddeyle.
+H2 · Telefonda Kurulum: Android ve iPhone'da hesap ekleme adımları; iş e-postası ekleyeceklere sunucu bilgisi gerekebileceği notu.
+H2 · Nasıl Yazılır: İki H3. Konu satırı için üç kural; resmî yazışma için hitap, gövde ve kapanış şablonu. Örnek bir e-posta iskeleti verilir.
+H2 · İki Adımlı Doğrulama: Neden gerekli olduğu tek cümlede, açma adımları listede. OTP paylaşımı uyarısı tek satırlık not olarak eklenir.
+UZUNLUK: 1.100-1.400 kelime.</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>H3: E-Posta Adresi Nasıl Açılır?
+Bir e-posta sağlayıcısının hesap oluşturma sayfasından ad, kullanıcı adı ve şifre bilgileri girilir, kurtarma bilgisi eklenerek hesap tamamlanır.
+H3: E-Posta Adresi Nedir?
+E-posta adresi, kullanıcı adı ile alan adının @ işaretiyle birleşmesinden oluşan elektronik posta kimliğidir.
+H3: Telefonda E-Posta Hesabı Nasıl Eklenir?
+Cihaz ayarlarındaki hesaplar bölümünden hesap ekle seçilir, sağlayıcı belirlenir ve e-posta ile şifre girilir.
+H3: Resmî E-Posta Nasıl Yazılır?
+Açık bir konu satırı, uygun bir hitap, kısa ve tek konuya odaklı bir gövde ile kapanış cümlesi kullanılır.
+H3: E-Posta Hesabı Nasıl Korunur?
+Güçlü ve benzersiz bir şifre belirlenir, iki adımlı doğrulama açılır ve doğrulama kodları kimseyle paylaşılmaz.</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12384,7 +12954,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12405,7 +12975,7 @@
           </r>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>1. E-posta adresi oluşturma adımları adım adım anlatılır
 2. Telefonda hesap kurulumu adım adım anlatılır
@@ -12413,36 +12983,36 @@
 4. Iki adımlı doğrulama adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Sağlayıcı adımları değişmektedir; adımlar sağlayıcı bazında ayrılabilir.</t>
         </is>
       </c>
-      <c r="P20" s="8" t="n">
+      <c r="R20" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="Q20" s="10" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="T20" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="S20" s="6" t="inlineStr">
+      <c r="U20" s="6" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="T20" s="4" t="inlineStr">
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>E-posta hesabı açmak veya telefona kurmak isteyen kişi adım arıyor.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="128.5" customHeight="1">
+    <row r="21" ht="263.5" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Telefon Güncellemesi Nasıl Yapılır?</t>
@@ -12491,13 +13061,42 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>1. Android ve iOS için güncelleme adımları
-2. Güncelleme görünmüyorsa yapılabilecekler
-3. Güncelleme öncesi yedekleme
-4. Depolama alanı yetmediğinde izlenecek yol</t>
+          <t>H2: Telefon Güncellemesi Nedir, Neden Yapılmalı?
+H2: Telefon Güncellemesi Nasıl Yapılır?
+H3: Android Güncelleme Adımları
+H3: iPhone Güncelleme Adımları
+H2: Güncelleme Öncesi Yedekleme Nasıl Yapılır?
+H2: Güncelleme Görünmüyorsa Ne Yapmalı?
+H2: Depolama Alanı Yetmiyorsa Ne Yapılmalı?
+H2: Telefon Güncelleme Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>TON: Kısa adım rehberi. Yanıt açılış paragrafında verilir: güncelleme ayarlar menüsündeki yazılım güncelleme bölümünden yapılır.
+H2 · Nedir, Neden Yapılmalı: Güvenlik yamaları, hata düzeltmeleri ve yeni özellikler üç maddede.
+H2 · Nasıl Yapılır: İki H3, her biri dört adımı geçmez. Wi-Fi ve pil koşulu her ikisinin başında tek satır.
+H2 · Yedekleme: Bulut yedeği ve bilgisayara yedek iki seçenek; yedeğin tamamlandığının nereden kontrol edileceği.
+H2 · Güncelleme Görünmüyorsa: Beş madde: kademeli dağıtım, cihazın destek süresi, ağ değişimi, tarih ve saat ayarı, üretici destek sayfasından sürüm kontrolü.
+H2 · Depolama Yetmiyorsa: Geçici dosya temizliği, kullanılmayan uygulamaların kaldırılması, fotoğrafların buluta alınması üç maddede.
+UZUNLUK: 700-900 kelime.</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>H3: Telefon Güncellemesi Nasıl Yapılır?
+Ayarlar menüsündeki yazılım güncelleme bölümü açılır, güncelleme aranır ve cihaz Wi-Fi'a bağlıyken indirilip kurulur.
+H3: Güncelleme Neden Görünmüyor?
+Güncellemeler kademeli dağıtıldığı için gecikebilir; cihazın destek süresi dolmuşsa yeni sürüm hiç gelmeyebilir.
+H3: Güncelleme Öncesi Yedek Almak Gerekir mi?
+Gerekir. Nadir de olsa güncelleme sırasında veri kaybı yaşanabildiği için bulut ya da bilgisayar yedeği alınması önerilir.
+H3: Güncelleme İçin Ne Kadar Boş Alan Gerekir?
+Gereken alan sürüme göre değişir; yetersizse cihaz uyarı verir ve geçici dosyaların temizlenmesiyle alan açılabilir.
+H3: Güncelleme Sırasında Telefon Kapanırsa Ne Olur?
+Cihaz genellikle kendini kurtarma moduna alır; işlem yeniden başlatılabilir, bu nedenle güncelleme öncesi pilin yeterli olması önemlidir.</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12505,7 +13104,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12526,7 +13125,7 @@
           </r>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>1. Android ve iOS için güncelleme adımları adım adım anlatılır
 2. Güncelleme görünmüyorsa yapılabilecekler açıklanır
@@ -12534,36 +13133,36 @@
 4. Depolama alanı yetmediğinde izlenecek yol açıklanır</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Tek soruya odaklı içeriktir; yanıt açılış paragrafında verilip adımlar numaralı listeye alınabilir.</t>
         </is>
       </c>
-      <c r="P21" s="8" t="n">
+      <c r="R21" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="Q21" s="10" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="T21" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
+      <c r="U21" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="T21" s="4" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>Telefonunu güncellemek isteyen kişi adım arıyor; tek soruya odaklı kısa içerik yeterli oluyor.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="128.5" customHeight="1">
+    <row r="22" ht="236.5" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Bilgisayarda Ekran Görüntüsü Alma: Yöntemler ve Kısayollar</t>
@@ -12615,14 +13214,45 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>1. Windows'ta üç yöntem: PrtScn, Windows+Shift+S, Ekran Alıntısı Aracı
-2. Mac kısayolları
-3. Kısayol tablosu
-4. Görüntünün kaydedildiği klasör
-5. Ekran görüntüsünün düzenlenmesi ve paylaşılması</t>
+          <t>H2: Bilgisayarda Ekran Görüntüsü Alma Nedir?
+H2: Windows'ta Ekran Görüntüsü Nasıl Alınır?
+H3: PrtScn Tuşu ile Tam Ekran Görüntüsü
+H3: Windows + Shift + S ile Bölge Seçerek Alma
+H3: Ekran Alıntısı Aracı ile Alma
+H2: Mac'te Ekran Görüntüsü Nasıl Alınır?
+H2: Ekran Görüntüsü Kısayolları Tablosu
+H2: Ekran Görüntüsü Nereye Kaydedilir?
+H2: Ekran Görüntüsü Nasıl Düzenlenir ve Paylaşılır?
+H2: Ekran Görüntüsü Alma Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>TON: Kısayol rehberi. Okuyucu tek bir tuş kombinasyonu arıyor; kısayol tablosu yazının merkezinde yer almalı ve tek başına alıntılanabilir olmalı.
+H2 · Nedir: Tek paragraf; ekran görüntüsü ile ekran kaydı farkı bir cümlede.
+H2 · Windows: Üç H3, her yöntem için ne zaman tercih edileceği bir cümleyle: tam ekran, bölge seçimi, gecikmeli alma.
+H2 · Mac: Tam ekran, bölge ve pencere kısayolları üç maddede.
+H2 · Kısayollar Tablosu: İşletim sistemi / yapılacak iş / kısayol / kaydedilen yer sütunlarından oluşan tablo. Yazının en değerli bloğu; sayfanın üst yarısında yer almalı.
+H2 · Nereye Kaydedilir: Panoya kopyalanan ile dosyaya kaydedilen görüntü ayrımı; varsayılan klasör yolları.
+H2 · Düzenleme ve Paylaşma: İşaretleme, kırpma ve doğrudan paylaşma üç adımda.
+UZUNLUK: 1.200-1.500 kelime.</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>H3: Bilgisayarda Ekran Görüntüsü Nasıl Alınır?
+Windows'ta PrtScn tuşu tüm ekranı panoya kopyalar, Windows + Shift + S kombinasyonu ise seçilen bölgenin görüntüsünü alır.
+H3: Ekran Görüntüsü Nereye Kaydedilir?
+Kısayolla alınan görüntüler panoya kopyalanır; ekran alıntısı aracıyla kaydedilenler ise resimler klasöründeki ekran görüntüleri dizinine gider.
+H3: Klavyeden Ekran Görüntüsü Nasıl Alınır?
+PrtScn tuşu tam ekranı, Alt + PrtScn kombinasyonu ise yalnızca etkin pencereyi kopyalar.
+H3: Mac'te Ekran Görüntüsü Kısayolu Nedir?
+Command + Shift + 3 tüm ekranı, Command + Shift + 4 ise seçilen alanı kaydeder.
+H3: Ekran Görüntüsü Nasıl Düzenlenir?
+Alınan görüntü ekran alıntısı aracında ya da varsayılan görsel düzenleyicide açılarak kırpılabilir ve üzerine işaretleme yapılabilir.</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>1. kuantum bilgisayar : https://www.turkcell.com.tr/blog/kuantum-bilgisayar-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12630,7 +13260,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12668,7 +13298,7 @@
           </r>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>1. Windows'ta üç yöntem: PrtScn, Windows+Shift+S, Ekran Alıntısı Aracı açıklanır
 2. Mac kısayolları adım adım anlatılır
@@ -12677,36 +13307,36 @@
 5. Ekran görüntüsünün düzenlenmesi ve paylaşılması adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Kısayol tablosu alıntılanabilir bir blok olarak kurgulanabilir.</t>
         </is>
       </c>
-      <c r="P22" s="8" t="n">
+      <c r="R22" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="Q22" s="10" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="T22" s="6" t="inlineStr">
         <is>
           <t>Aralık</t>
         </is>
       </c>
-      <c r="S22" s="6" t="inlineStr">
+      <c r="U22" s="6" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr">
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>Bilgisayarda ekran görüntüsü almak isteyen kişi kısayol arıyor; Windows ve Mac karşılığını tek sayfada veren içerik sonuç sayfasında sınırlı.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="128.5" customHeight="1">
+    <row r="23" ht="317.5" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
@@ -12754,13 +13384,49 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>1. ESIM ile fiziksel SIM farkı
-2. ESIM destekleyen telefon listesi
-3. Mevcut hattı eSIM'e taşıma adımları
-4. Yurt dışında eSIM kullanımı</t>
+          <t>H2: eSIM Nedir?
+H2: eSIM ile Fiziksel SIM Arasındaki Fark Nedir?
+H2: eSIM Nasıl Alınır?
+H2: eSIM Nasıl Aktive Edilir?
+H3: iPhone'da eSIM Kurulumu
+H3: Android Cihazlarda eSIM Kurulumu
+H2: eSIM Destekleyen Telefonlar Hangileri?
+H2: Mevcut Hat eSIM'e Nasıl Taşınır?
+H2: eSIM Yurt Dışında Nasıl Kullanılır?
+H2: eSIM Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım ve kurulum bir arada. Bu başlık Telco AI Overview takip listesindeki eSIM kümesiyle örtüşüyor; taramada eSIM sorgularının beşinde de AI Overview çıkıyor ve cihaz üreticisi dokümantasyonu ile video kaynakları öne çıkıyor. Yazı bu iki formatın karşılığını metin tarafında vermeli: cihaz bazında adım ve alıntılanabilir tanım.
+H2 · eSIM Nedir: İki cümlelik, bağlamdan bağımsız okunabilen tanım. AI yanıtına kaynak olarak seçilme ihtimalini belirleyen bölüm burasıdır; uzatılmaz.
+H2 · eSIM ile Fiziksel SIM Farkı: Dört satırlık tablo: fiziksel kart gerekir mi, cihaz değişiminde ne olur, aynı anda kaç hat, yurt dışı kullanımı.
+H2 · eSIM Nasıl Alınır: Başvuru kanalları ve gereken koşullar; QR kodun nasıl geldiği.
+H2 · Nasıl Aktive Edilir: İki H3'te iPhone ve Android adımları ayrı ayrı, numaralı liste hâlinde. QR kod okutma ve elle bilgi girme iki seçenek olarak verilir. Bu bölüm cihaz üreticisi dokümantasyonunun karşılığıdır.
+H2 · Destekleyen Telefonlar: Marka ve model ailesi düzeyinde tablo. Model listesi hızla değiştiği için tabloya güncelleme tarihi konur ve tek tek model yerine aile adı kullanılır.
+H2 · Mevcut Hattı Taşıma: Fiziksel SIM'den eSIM'e geçiş adımları ve geçiş sırasında hattın ne kadar süre kapalı kalabileceği.
+H2 · Yurt Dışında Kullanım: İkinci hat olarak yerel eSIM kullanımı ve ana hattın açık kalması.
+UZUNLUK: 1.400-1.700 kelime.
+DİKKAT: Cihaz listesi ve başvuru akışı ürün ekibiyle doğrulanmalı; güncellenme tarihi görünür tutulmalıdır.</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>H3: eSIM Nedir?
+eSIM, telefonun içine gömülü olarak gelen ve fiziksel SIM kart takmaya gerek bırakmayan dijital SIM teknolojisidir.
+H3: eSIM Nasıl Alınır?
+Operatörün mobil uygulaması, çevrimiçi işlem merkezi ya da mağazaları üzerinden başvuru yapılır ve kurulum için bir QR kod iletilir.
+H3: eSIM Nasıl Aktif Edilir?
+Cihaz ayarlarındaki hücresel bağlantı bölümünden eSIM ekle seçilir, operatörden gelen QR kod okutulur ve hat birkaç dakika içinde etkinleşir.
+H3: eSIM Hangi Telefonlarda Var?
+Son yılların üst ve orta segment modellerinin büyük bölümü eSIM destekler; desteğin olup olmadığı cihaz ayarlarındaki hücresel bağlantı menüsünden kontrol edilebilir.
+H3: Mevcut Hat eSIM'e Taşınabilir mi?
+Evet. Numara değişmeden fiziksel SIM eSIM'e dönüştürülebilir; işlem sırasında hat kısa süre kapalı kalabilir.
+H3: eSIM Yurt Dışında Kullanılabilir mi?
+Kullanılabilir. eSIM destekleyen cihazlarda ana hat açık kalırken ikinci hat olarak yerel bir eSIM paketi de tanımlanabilir.</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12768,7 +13434,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12789,7 +13455,7 @@
           </r>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>1. ESIM ile fiziksel SIM farkı açıklanır
 2. ESIM destekleyen telefon listesi verilir
@@ -12797,36 +13463,36 @@
 4. Yurt dışında eSIM kullanımı açıklanır</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Destekleyen cihaz listesi hızla değişmektedir; güncellenebilir tablo olarak kurgulanabilir.</t>
         </is>
       </c>
-      <c r="P23" s="8" t="n">
+      <c r="R23" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="Q23" s="9" t="inlineStr">
+      <c r="S23" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="T23" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="S23" s="6" t="inlineStr">
+      <c r="U23" s="6" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr">
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>eSIM'e geçmek isteyen kişi önce telefonunun desteklediğini doğrulamak istiyor. Cihaz listesi sayfayı vazgeçilmez kılıyor. Telco AI Overview takip listesi: bu başlık Telco AI Overview takibindeki eSIM kümesiyle örtüşmektedir ve Öncelik 2 bandından yükseltilmiştir; ayrıntısı 06B sekmesindedir.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="128.5" customHeight="1">
+    <row r="24" ht="263.5" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Telefon Nasıl Sıfırlanır?</t>
@@ -12874,13 +13540,41 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>1. Sıfırlama öncesi yedekleme
-2. Android'de fabrika ayarlarına dönüş adımları
-3. IPhone'da sıfırlama adımları
-4. Sıfırlama sonrası hesap doğrulama</t>
+          <t>H2: Telefon Sıfırlama Nedir, Verilere Ne Olur?
+H2: Sıfırlama Öncesi Yedekleme Nasıl Yapılır?
+H2: Android Telefon Nasıl Sıfırlanır?
+H2: iPhone Nasıl Sıfırlanır?
+H2: Fabrika Ayarlarına Sıfırlama Sonrası Hesap Doğrulaması
+H2: Telefon Sıfırlama Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>TON: Uyarı önce, adım sonra. Açılış paragrafı veri kaybı uyarısıyla başlar; bu, okuyucunun geri dönemeyeceği bir işlem.
+H2 · Nedir, Verilere Ne Olur: Fabrika ayarlarına dönüşün cihazdaki tüm veriyi sildiği net cümleyle; hangi verilerin bulutta kaldığı ayrı cümlede.
+H2 · Yedekleme: Bulut yedeği, fotoğraf yedeği ve WhatsApp yedeği üç ayrı madde; yedeğin tamamlandığının kontrolü.
+H2 · Android Sıfırlama: Ayarlar üzerinden adımlar ve cihaz açılmıyorsa kurtarma modu yolu.
+H2 · iPhone Sıfırlama: Ayarlar üzerinden adımlar ve bilgisayar üzerinden geri yükleme seçeneği.
+H2 · Hesap Doğrulaması: Sıfırlama sonrası cihazın önceki hesabın şifresini isteyeceği (etkinleştirme kilidi); bu yüzden sıfırlamadan önce hesabın cihazdan çıkarılması gerektiği. Bu uyarı rakip içeriklerde çoğunlukla eksik ve ikinci el cihazlarda en sık yaşanan sorun.
+UZUNLUK: 800-1.000 kelime.
+DİKKAT: Menü adları sürüme göre değişiyor; güncellenme tarihi görünür tutulmalı.</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>H3: Telefon Nasıl Sıfırlanır?
+Ayarlar menüsündeki sistem ya da genel bölümünden fabrika ayarlarına sıfırlama seçeneği açılır ve ekrandaki onaylar tamamlanır.
+H3: Telefon Sıfırlanınca Veriler Silinir mi?
+Evet. Cihazdaki fotoğraflar, uygulamalar ve ayarlar tamamen silinir; yalnızca buluta yedeklenmiş veriler geri getirilebilir.
+H3: Sıfırlama Öncesi Ne Yapılmalı?
+Bulut yedeği alınmalı ve cihazdan hesap çıkışı yapılmalıdır; aksi hâlde sıfırlama sonrası etkinleştirme kilidi devreye girer.
+H3: Telefon Açılmıyorsa Nasıl Sıfırlanır?
+Cihaz kurtarma moduna alınarak sıfırlama yapılabilir; tuş kombinasyonu markaya göre değişir.
+H3: Sıfırlama Sonrası Hesap Şifresi Neden İsteniyor?
+Cihaz güvenliği için etkinleştirme kilidi devrededir; kilidin kalkması için cihaza en son giriş yapılan hesabın şifresi gerekir.</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12888,12 +13582,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Rakip bloglarda sıfırlama adımları Android ve iPhone için ayrı yazılara bölünmüştür; tek sayfada veren rakip bulunmamaktadır.</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>1. Sıfırlama öncesi yedekleme adım adım anlatılır
 2. Android'de fabrika ayarlarına dönüş adımları adım adım anlatılır
@@ -12901,36 +13595,36 @@
 4. Sıfırlama sonrası hesap doğrulama adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>Veri kaybı uyarısının açılışta verilmesi önerilir; adımlar cihaz sürümüne göre değiştiğinden güncellenme tarihi görünür tutulabilir.</t>
         </is>
       </c>
-      <c r="P24" s="8" t="n">
+      <c r="R24" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="Q24" s="10" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="T24" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="S24" s="6" t="inlineStr">
+      <c r="U24" s="6" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr">
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>Telefonunu satmadan ya da sorun gidermek için sıfırlamak isteyen kişi adım arıyor.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="128.5" customHeight="1">
+    <row r="25" ht="263.5" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Deepfake Nedir ve Nasıl Anlaşılır?</t>
@@ -12977,12 +13671,41 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>1. Deepfake tanımı
-2. Sahte içeriğin anlaşılma yolları
-3. Dolandırıcılık senaryoları</t>
+          <t>H2: Deepfake Nedir?
+H2: Deepfake Nasıl Yapılır, Nasıl Çalışır?
+H2: Deepfake Nasıl Anlaşılır?
+H2: Deepfake ile Yapılan Dolandırıcılık Senaryoları
+H2: Deepfake İçerikle Karşılaşınca Ne Yapılmalı?
+H2: Deepfake Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>TON: Bilgilendirici ve korumacı. Yazının amacı tanım vermek ve okuyucuyu dolandırıcılığa karşı hazırlamak; teknik üretim ayrıntısına girilmez.
+H2 · Deepfake Nedir: Yapay zekayla üretilmiş sahte görüntü, ses ve video; iki cümlelik tanım.
+H2 · Nasıl Çalışır: Yöntem üst düzeyde anlatılır, uygulama adı ya da üretim adımı verilmez.
+H2 · Nasıl Anlaşılır: Sekiz maddelik kontrol listesi: göz kırpma ve yüz kenarları, ışık tutarsızlığı, ses ile dudak uyumu, ton geçişleri, arka plan bozulmaları, kaynak hesabın geçmişi, aynı içeriğin başka kaynakta bulunup bulunmadığı, tersine görsel arama.
+H2 · Dolandırıcılık Senaryoları: Ses klonlamayla akraba araması, yatırım vaadi içeren sahte ünlü videosu, kurumsal yönetici taklidi üç senaryo hâlinde; her senaryoda dur ve doğrula yönergesi.
+H2 · Karşılaşınca Ne Yapılmalı: İçeriğin bildirilmesi, paylaşılmaması ve mağduriyet hâlinde başvuru kanalı.
+UZUNLUK: 900-1.200 kelime.
+İÇ BAĞLANTI: Blogun yapay zeka ve dijital güvenlik yazılarına bağlanır.</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>H3: Deepfake Nedir?
+Deepfake, yapay zeka kullanılarak bir kişinin yüzünün ya da sesinin gerçekmiş gibi taklit edildiği sahte görüntü ve ses içerikleridir.
+H3: Deepfake Nasıl Anlaşılır?
+Yüz kenarlarındaki bozulmalar, ışık ve gölge tutarsızlıkları, ses ile dudak hareketinin uyumsuzluğu ve içeriğin başka güvenilir kaynakta bulunmaması temel işaretlerdir.
+H3: Deepfake Yasal mı?
+İçeriğin kendisi teknoloji olarak yasaktır denemez; ancak kişilik haklarını ihlal eden, dolandırıcılık ya da iftira amacı taşıyan kullanımlar suç teşkil eder.
+H3: Deepfake ile Nasıl Dolandırılırım?
+En yaygın senaryo, tanıdık bir sesin taklit edilerek acil para talebinde bulunulmasıdır; bu tür aramalarda kişi başka bir kanaldan doğrulanmalıdır.
+H3: Deepfake İçerik Görürsem Ne Yapmalıyım?
+İçerik paylaşılmadan platforma bildirilmeli; kişisel bir mağduriyet varsa yasal başvuru yapılmalıdır.</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -12990,7 +13713,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13011,43 +13734,43 @@
           </r>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>1. Deepfake tanımı açıklanır
 2. Sahte içeriğin anlaşılma yolları adım adım anlatılır
 3. Dolandırıcılık senaryoları açıklanır</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>Blogun mevcut yapay zeka içerikleriyle iç bağlantı kurulabilir.</t>
         </is>
       </c>
-      <c r="P25" s="8" t="n">
+      <c r="R25" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="Q25" s="10" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="T25" s="6" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="S25" s="6" t="inlineStr">
+      <c r="U25" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr">
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>Sahte video ve ses içeriklerinin nasıl anlaşıldığını merak eden kişi tanım arıyor.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="128.5" customHeight="1">
+    <row r="26" ht="263.5" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Yenilenmiş Telefon Ne Demek? Garanti ve Kalite Sınıfları</t>
@@ -13096,13 +13819,43 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>1. Yenilenmiş telefon tanımı ve yasal çerçeve
-2. Kalite sınıfları
-3. Garanti süresi ve kapsamı
-4. Satın almadan önce kontrol listesi</t>
+          <t>H2: Yenilenmiş Telefon Ne Demek?
+H2: Yenilenmiş Telefon ile İkinci El Arasındaki Fark Nedir?
+H2: Yenilenmiş Telefon Kalite Sınıfları Nelerdir?
+H2: Yenilenmiş Telefonda Garanti Süresi Ne Kadar?
+H2: Yenilenmiş iPhone Alınır mı?
+H2: Satın Almadan Önce Kontrol Listesi
+H2: Yenilenmiş Telefon Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>TON: Karar yardımı. Okuyucu satın alma öncesinde ve tereddütte; yazı satış yapmaz, karar verdirir.
+H2 · Ne Demek: Yetkili yenileme merkezinde kontrol edilip yenilenen ve garantiyle satılan cihaz; iki cümlelik tanım.
+H2 · İkinci El Farkı: Dört satırlık tablo: kim satar, garanti var mı, parça değişimi yapıldı mı, fatura düzenlenir mi.
+H2 · Kalite Sınıfları: Sınıfların ne anlama geldiği tablo hâlinde: dış görünüm, çizik durumu, pil sağlığı beklentisi. Sınıf adlandırmasının satıcıya göre değişebildiği notu eklenir.
+H2 · Garanti Süresi: Yasal asgari garanti süresi ve kapsamı; garanti dışında kalan durumlar.
+H2 · Yenilenmiş iPhone Alınır mı: Okuyucunun asıl sorusu. Avantaj ve dikkat edilecekler yan yana iki listede; karar okuyucuya bırakılır.
+H2 · Kontrol Listesi: Sekiz madde: IMEI sorgulama, pil sağlığı, ekran ve kasa kontrolü, garanti belgesi, fatura, yenileme yetki belgesi, iade koşulu, orijinal parça bilgisi.
+UZUNLUK: 1.200-1.500 kelime.
+DİKKAT: Yenilenmiş cihaz satışına ilişkin güncel mevzuat doğrulanmalı; süre ve kapsam bilgileri tarih notuyla verilmelidir.</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>H3: Yenilenmiş Telefon Ne Demek?
+Yenilenmiş telefon, yetkili yenileme merkezinde teknik kontrolden geçirilmiş, gerekli parçaları değiştirilmiş ve garantiyle yeniden satışa sunulmuş cihazdır.
+H3: Yenilenmiş Telefon ile İkinci El Arasındaki Fark Nedir?
+Yenilenmiş cihaz yetkili bir merkez tarafından kontrol edilir, faturalı ve garantili satılır; ikinci el cihazda böyle bir güvence bulunmaz.
+H3: Yenilenmiş Telefonda Garanti Var mı?
+Vardır. Yenilenmiş cihazlar yasal olarak belirlenmiş bir süre boyunca garanti kapsamında satılır.
+H3: Yenilenmiş iPhone Alınır mı?
+Garanti belgesi, IMEI kaydı ve pil sağlığı kontrol edildiğinde uygun bir seçenek olabilir; bu üç başlık satın alma öncesinde sorgulanmalıdır.
+H3: Yenilenmiş Telefonun Kalite Sınıfı Ne Anlama Gelir?
+Kalite sınıfı cihazın dış görünümündeki kullanım izlerini tanımlar; işlevsel performans tüm sınıflarda kontrol edilmiş olur.</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -13110,7 +13863,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13131,7 +13884,7 @@
           </r>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>1. Yenilenmiş telefon tanımı ve yasal çerçeve açıklanır
 2. Kalite sınıfları açıklanır
@@ -13139,36 +13892,36 @@
 4. Satın almadan önce kontrol listesi verilir</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>Yenilenmiş cihaz satışıyla ilgili güncel mevzuat doğrulanmalıdır.</t>
         </is>
       </c>
-      <c r="P26" s="8" t="n">
+      <c r="R26" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="Q26" s="10" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="T26" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="S26" s="6" t="inlineStr">
+      <c r="U26" s="6" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="T26" s="4" t="inlineStr">
+      <c r="V26" s="4" t="inlineStr">
         <is>
           <t>Yenilenmiş telefon almayı düşünen kişi garanti ve kalite soruyor. Satın alma kararına yakın bir arama.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="128.5" customHeight="1">
+    <row r="27" ht="263.5" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>AirTag Nedir ve Nasıl Çalışır?</t>
@@ -13216,12 +13969,42 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>1. AirTag tanımı ve çalışma mantığı
-2. Kurulum adımları
-3. Takip edilme uyarısı ve gizlilik</t>
+          <t>H2: AirTag Nedir?
+H2: AirTag Nasıl Çalışır?
+H2: AirTag Ne İşe Yarar?
+H2: AirTag Nasıl Kurulur?
+H2: Kaybolan Eşya AirTag ile Nasıl Bulunur?
+H2: AirTag ile Takip Edilme Uyarısı ve Gizlilik
+H2: AirTag Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım ve kullanım. Ayırt edici bölüm gizlilik başlığı; rakip sayfalarda karşılığı zayıf.
+H2 · AirTag Nedir: Eşyaya takılan konum takip cihazı; iki cümlelik tanım.
+H2 · Nasıl Çalışır: Cihazın kendi GPS'i olmadığı, çevredeki Apple cihazlarının ağı üzerinden konum bildirdiği açıkça yazılır. Bu, okuyucunun en çok yanlış bildiği nokta.
+H2 · Ne İşe Yarar: Anahtar, çanta, bavul, bisiklet dört kullanım örneği.
+H2 · Nasıl Kurulur: Dört adım: cihaza yaklaştırma, isim verme, hesaba ekleme, konum izni.
+H2 · Kaybolan Eşya Nasıl Bulunur: Yakındaysa ses ve hassas bulma, uzaktaysa harita üzerinde son konum ve kayıp modu.
+H2 · Takip Edilme Uyarısı ve Gizlilik: Tanımadık bir AirTag ile seyahat edildiğinde telefonun uyarı verdiği, uyarıyı alan kişinin ne yapması gerektiği ve Android tarafında tarama seçeneği. Yazının en değerli bölümü.
+UZUNLUK: 900-1.200 kelime.</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>H3: AirTag Nedir?
+AirTag, eşyalara takılarak konumlarının takip edilmesini sağlayan küçük bir takip cihazıdır.
+H3: AirTag Nasıl Çalışır?
+AirTag'in kendi GPS'i yoktur; konumunu çevredeki uyumlu cihazların oluşturduğu ağ üzerinden şifreli olarak bildirir.
+H3: AirTag Ne İşe Yarar?
+Anahtar, cüzdan, çanta ve bavul gibi sık kaybolan eşyaların yerinin bulunmasında kullanılır.
+H3: Yanımda Bilinmeyen Bir AirTag Varsa Ne Olur?
+Telefon bir süre sonra bilinmeyen bir takip cihazının sizinle hareket ettiği uyarısını verir; cihaz bulunup devre dışı bırakılabilir.
+H3: AirTag Android Telefonlarda Çalışır mı?
+AirTag kurulumu ve takibi Apple cihazlarla yapılır; Android kullanıcıları ise bilinmeyen takip cihazlarını tarama uygulamasıyla tespit edebilir.</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -13229,7 +14012,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13250,43 +14033,43 @@
           </r>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>1. AirTag tanımı ve çalışma mantığı açıklanır
 2. Kurulum adımları adım adım anlatılır
 3. Takip edilme uyarısı ve gizlilik açıklanır</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>Gizlilik uyarısı bölümü rakip sayfalarda eksiktir.</t>
         </is>
       </c>
-      <c r="P27" s="8" t="n">
+      <c r="R27" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="Q27" s="10" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="T27" s="6" t="inlineStr">
         <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="S27" s="6" t="inlineStr">
+      <c r="U27" s="6" t="inlineStr">
         <is>
           <t>Nisan</t>
         </is>
       </c>
-      <c r="T27" s="4" t="inlineStr">
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>Eşya takip cihazı alan veya takip edildiğinden şüphelenen kişi bilgi arıyor.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="128.5" customHeight="1">
+    <row r="28" ht="209.5" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t>OEM Ne Demek?</t>
@@ -13333,12 +14116,36 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>1. OEM tanımı
-2. OEM ürün ile orijinal ürün farkı
-3. Telefon ve donanımda OEM kullanımı</t>
+          <t>H2: OEM Ne Demek?
+H2: OEM Ürün ile Orijinal Ürün Arasındaki Fark Nedir?
+H2: Telefon ve Bilgisayar Donanımında OEM Ne Anlama Gelir?
+H2: OEM Ürün Alınır mı?
+H2: OEM Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım sorgusu. İlk paragraf açılım ve tek cümlelik karşılık verir; bu cümle bağlamdan bağımsız okunabilir olmalı.
+H2 · OEM Ne Demek: Açılımı ve Türkçe karşılığı; bir ürünü başka bir markanın adıyla satılmak üzere üreten firma olduğu.
+H2 · OEM ile Orijinal Farkı: Üç satırlık tablo: kim üretir, hangi kutuda gelir, garanti kim tarafından verilir. Okuyucunun "OEM sahte mi" sorusu burada net biçimde yanıtlanır: sahte değildir, ambalaj ve garanti kanalı farklıdır.
+H2 · Donanımda OEM: Yazılım lisansı, şarj adaptörü ve yedek parça üç örnekle.
+H2 · Alınır mı: Garanti kaynağı ve satıcı güvenilirliği iki maddede; karar okuyucuya bırakılır.
+UZUNLUK: 600-800 kelime.</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>H3: OEM Ne Demek?
+OEM, bir ürünü kendi markasıyla değil, başka bir markanın adı altında satılmak üzere üreten firmayı tanımlar.
+H3: OEM Ürün Sahte mi?
+Hayır. OEM ürün aynı üretim hattından çıkabilir; fark genellikle ambalaj, aksesuar içeriği ve garantinin hangi kanaldan verildiğidir.
+H3: OEM ile Orijinal Ürün Arasındaki Fark Nedir?
+Orijinal ürün marka ambalajıyla ve marka garantisiyle satılır; OEM ürün sade ambalajla gelir ve garanti çoğunlukla satıcı tarafından verilir.
+H3: OEM Yazılım Ne Demek?
+Cihazla birlikte önceden kurulu gelen ve o cihaza bağlı olan yazılım lisansıdır; başka bir cihaza aktarılamaz.</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -13346,7 +14153,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13367,43 +14174,43 @@
           </r>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>1. OEM tanımı açıklanır
 2. OEM ürün ile orijinal ürün farkı açıklanır
 3. Telefon ve donanımda OEM kullanımı açıklanır</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>Tanım sorgusudur; kısa ve alıntılanabilir bir açılış paragrafı önerilmektedir.</t>
         </is>
       </c>
-      <c r="P28" s="8" t="n">
+      <c r="R28" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="Q28" s="10" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="T28" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="S28" s="6" t="inlineStr">
+      <c r="U28" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="T28" s="4" t="inlineStr">
+      <c r="V28" s="4" t="inlineStr">
         <is>
           <t>Ürün açıklamalarında gördüğü OEM ifadesinin anlamını arayan kişi tek cümlelik yanıt istiyor.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="128.5" customHeight="1">
+    <row r="29" ht="263.5" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>KVKK Nedir? Kişisel Verilerin Korunması Kanunu</t>
@@ -13450,12 +14257,41 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>1. KVKK tanımı
-2. Kişisel veri türleri
-3. Veri sahibinin hakları</t>
+          <t>H2: KVKK Nedir?
+H2: Kişisel Veri Nedir, Hangi Bilgiler Kişisel Veri Sayılır?
+H2: Özel Nitelikli Kişisel Veri Ne Demek?
+H2: KVKK Kapsamında Veri Sahibinin Hakları Nelerdir?
+H2: Kişisel Verilerin Korunması İçin Ne Yapılabilir?
+H2: KVKK Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>TON: Bilgilendirici, hukuki danışmanlık niteliği taşımayan. Yazı kanunu tanıtır, yorumlamaz.
+H2 · KVKK Nedir: Açılımı ve amacı iki cümlede; ne zaman yürürlüğe girdiği tek cümle.
+H2 · Kişisel Veri Nedir: Kimliği belirli ya da belirlenebilir kişiye ait her bilgi; ad, telefon, e-posta, konum, IP gibi örnekler madde hâlinde.
+H2 · Özel Nitelikli Veri: Sağlık, biyometrik veri, din ve benzeri kategorilerin neden ayrı korunduğu.
+H2 · Veri Sahibinin Hakları: Altı madde: bilgi talep etme, düzeltme, silme, aktarım bilgisi, itiraz, zararın giderilmesi. Her hak tek cümleyle.
+H2 · Ne Yapılabilir: Kullanıcı tarafında pratik öneriler: izin metinlerinin okunması, uygulama izinlerinin gözden geçirilmesi, gereksiz paylaşımdan kaçınma.
+UZUNLUK: 900-1.100 kelime.
+DİKKAT: Hukuki metin niteliği taşımamalı; yorum ve tavsiye yerine tanım ve haklar listesiyle sınırlı kalınmalıdır.</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>H3: KVKK Nedir?
+KVKK, Kişisel Verilerin Korunması Kanunu'nun kısaltmasıdır ve kişisel verilerin işlenmesine ilişkin usul ve esasları düzenler.
+H3: KVKK Ne Demek?
+Kişisel verilerin hukuka uygun biçimde işlenmesini ve kişilerin mahremiyetinin korunmasını amaçlayan kanunu ifade eder.
+H3: Hangi Bilgiler Kişisel Veri Sayılır?
+Ad, soyad, telefon numarası, e-posta adresi, konum bilgisi ve IP adresi gibi kişiyi belirli ya da belirlenebilir kılan her türlü bilgi kişisel veridir.
+H3: KVKK Kapsamında Hangi Haklara Sahibim?
+Verilerinizin işlenip işlenmediğini öğrenme, düzeltilmesini veya silinmesini isteme, aktarıldığı tarafları öğrenme ve işleme faaliyetine itiraz etme haklarınız bulunur.
+H3: Kişisel Verilerimin Silinmesini Nasıl İsterim?
+Verinin işlendiği kuruma başvurularak silme talebi iletilir; kurum yasal süre içinde talebi sonuçlandırmakla yükümlüdür.</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -13463,7 +14299,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13484,43 +14320,43 @@
           </r>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>1. KVKK tanımı açıklanır
 2. Kişisel veri türleri açıklanır
 3. Veri sahibinin hakları açıklanır</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>Hukuki metin niteliği taşımamalıdır; bilgilendirme sınırında kalınmalıdır.</t>
         </is>
       </c>
-      <c r="P29" s="8" t="n">
+      <c r="R29" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="Q29" s="10" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="T29" s="6" t="inlineStr">
         <is>
           <t>Aralık</t>
         </is>
       </c>
-      <c r="S29" s="6" t="inlineStr">
+      <c r="U29" s="6" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="T29" s="4" t="inlineStr">
+      <c r="V29" s="4" t="inlineStr">
         <is>
           <t>Kişisel verilerle ilgili hakkını merak eden kişi kısa açıklama arıyor.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="128.5" customHeight="1">
+    <row r="30" ht="263.5" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Telefon Neden Isınır?</t>
@@ -13571,13 +14407,40 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>1. Isınmanın yaygın nedenleri
-2. Şarj sırasında ısınma
-3. Isınmayı azaltan ayarlar
-4. Servise götürmeyi gerektiren durumlar</t>
+          <t>H2: Telefon Neden Isınır?
+H2: Telefon Isınmasının En Sık Nedenleri
+H2: Şarj Sırasında Telefon Neden Isınır?
+H2: Telefon Isınması Nasıl Azaltılır?
+H2: Telefon Isınması Ne Zaman Servis Gerektirir?
+H2: Telefon Isınması Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>TON: Neden-çözüm sırası. Açılış paragrafı ısınmanın üç ana nedenini tek cümlede özetler: yoğun işlem, şarj ve ortam sıcaklığı.
+H2 · Neden Isınır: Isınmanın normal olduğu durum ile sorun işareti olan durumun ayrımı.
+H2 · En Sık Nedenler: Altı madde: oyun ve video, arka plan uygulamaları, zayıf şebeke sinyali, doğrudan güneş, güncelleme sonrası indeksleme, kılıf.
+H2 · Şarjda Isınma: Hızlı şarjın neden ısı ürettiği ve hangi düzeydeki ısınmanın normal olduğu.
+H2 · Nasıl Azaltılır: Altı somut adım: kılıfı çıkarma, arka plan yenilemesini kapatma, parlaklığı düşürme, şarj sırasında kullanmamak, güncellemeleri tamamlatmak, ortam sıcaklığından uzak tutmak.
+H2 · Servis Gerektiren Durumlar: Dört işaret: dokunulamayacak kadar ısınma, kullanılmazken ısınma, şişen pil, kapanma. Şişen pil için cihazın kullanılmaması uyarısı ayrı satırda.
+UZUNLUK: 800-1.000 kelime.</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>H3: Telefon Neden Isınır?
+Yoğun işlem gerektiren uygulamalar, şarj işlemi, zayıf şebeke sinyali ve yüksek ortam sıcaklığı telefonun ısınmasının en yaygın nedenleridir.
+H3: Şarj Sırasında Telefonun Isınması Normal mi?
+Hafif ısınma normaldir; özellikle hızlı şarj sırasında sıcaklık artar. Ancak cihaz elde tutulamayacak kadar ısınıyorsa şarj durdurulmalıdır.
+H3: Telefon Isınması Nasıl Önlenir?
+Kılıf çıkarılabilir, arka plan uygulamaları kapatılabilir, ekran parlaklığı düşürülebilir ve cihaz şarjdayken kullanılmayabilir.
+H3: Telefon Isınması Pile Zarar Verir mi?
+Sürekli yüksek sıcaklık pil ömrünü kısaltır; bu nedenle cihazın uzun süre sıcak kalmasından kaçınılmalıdır.
+H3: Telefon Kullanılmazken Isınıyorsa Ne Yapmalı?
+Arka planda çalışan uygulamalar kontrol edilmeli; sorun sürüyorsa ve pilde şişme varsa cihaz kullanılmadan yetkili servise başvurulmalıdır.</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -13585,7 +14448,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13623,7 +14486,7 @@
           </r>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>1. Isınmanın yaygın nedenleri açıklanır
 2. Şarj sırasında ısınma adım adım anlatılır
@@ -13631,36 +14494,36 @@
 4. Servise götürmeyi gerektiren durumlar açıklanır</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Tek soruya odaklı içeriktir; yanıt açılış paragrafında üç nedenle özetlenebilir.</t>
         </is>
       </c>
-      <c r="P30" s="8" t="n">
+      <c r="R30" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="Q30" s="10" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="T30" s="6" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="S30" s="6" t="inlineStr">
+      <c r="U30" s="6" t="inlineStr">
         <is>
           <t>Mayıs</t>
         </is>
       </c>
-      <c r="T30" s="4" t="inlineStr">
+      <c r="V30" s="4" t="inlineStr">
         <is>
           <t>Telefonu ısınan kişi nedenini ve ne yapacağını soruyor; yanıt kısa ve doğrudan verilebilir.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="128.5" customHeight="1">
+    <row r="31" ht="209.5" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Müşteri Numarası Nedir, Nereden Öğrenilir?</t>
@@ -13707,12 +14570,38 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>1. Müşteri numarasının tanımı
-2. Faturada ve uygulamada nereden görüldüğü
-3. Abone numarası ile farkı</t>
+          <t>H2: Müşteri Numarası Nedir?
+H2: Müşteri Numarası Nereden Öğrenilir?
+H3: Faturada Müşteri Numarası Nerede Yazar?
+H3: Mobil Uygulamadan Müşteri Numarası Öğrenme
+H2: Müşteri Numarası ile Abone Numarası Arasındaki Fark Nedir?
+H2: Müşteri Numarası Hangi İşlemlerde Kullanılır?
+H2: Müşteri Numarası Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım ve konum gösterme. Okuyucu bir işlem sırasında numarayı arıyor; ilk paragraf tanımı verir, ikinci bölüm doğrudan nereden bulunacağını söyler.
+H2 · Müşteri Numarası Nedir: Aboneye özel, hattan bağımsız kimlik numarası olduğu iki cümlede.
+H2 · Nereden Öğrenilir: İki H3. Faturada hangi bölümde yer aldığı ve uygulamada hangi ekranda göründüğü. Ekran yolları ürün ekibiyle doğrulanır.
+H2 · Abone Numarası Farkı: İki satırlık tablo: neyi tanımlar, kaç tane olur. Bir müşterinin birden çok hattı olabileceği ama tek müşteri numarası bulunduğu net yazılır.
+H2 · Hangi İşlemlerde Kullanılır: Fatura ödeme, başvuru takibi, çağrı merkezi doğrulaması üç madde.
+UZUNLUK: 500-700 kelime.</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>H3: Müşteri Numarası Nedir?
+Müşteri numarası, operatörün her aboneye verdiği ve hat sayısından bağımsız olarak kişiyi tanımlayan kimlik numarasıdır.
+H3: Müşteri Numarası Nereden Öğrenilir?
+Fatura üzerindeki abone bilgileri bölümünde ve operatörün mobil uygulamasındaki hesap bilgileri ekranında yer alır.
+H3: Müşteri Numarası ile Abone Numarası Aynı mı?
+Değildir. Abone numarası hatta özeldir; müşteri numarası ise kişiye özeldir ve birden çok hat aynı müşteri numarasına bağlı olabilir.
+H3: Müşteri Numarası Nerelerde Kullanılır?
+Fatura ödemelerinde, başvuru takibinde ve çağrı merkezi görüşmelerinde kimlik doğrulaması amacıyla kullanılır.</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>1. hotspot nedir : https://www.turkcell.com.tr/blog/hotspot-internet-paketi-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -13720,48 +14609,48 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>Rakip operatörler müşteri numarasını hizmet sayfasında açıklıyor; blog tarafında tanım içeriği bulunmamaktadır.</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>1. Müşteri numarasının tanımı açıklanır
 2. Faturada ve uygulamada nereden görüldüğü açıklanır
 3. Abone numarası ile farkı açıklanır</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Tanım sorgusudur; hesap ekranına yönlendirme ürün ekibiyle doğrulanmalıdır.</t>
         </is>
       </c>
-      <c r="P31" s="8" t="n">
+      <c r="R31" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="Q31" s="10" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="T31" s="6" t="inlineStr">
         <is>
           <t>Mart</t>
         </is>
       </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T31" s="4" t="inlineStr">
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
         <is>
           <t>Müşteri numarasını nereden bulacağını arayan abone kısa ve net yanıt bekliyor.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="128.5" customHeight="1">
+    <row r="32" ht="250" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>OTP Ne Demek?</t>
@@ -13808,13 +14697,41 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>1. OTP tanımı
-2. SMS ile gelen tek kullanımlık şifrenin nasıl çalıştığı
-3. OTP paylaşımının riskleri
-4. OTP gelmediğinde yapılabilecekler</t>
+          <t>H2: OTP Ne Demek?
+H2: OTP Nasıl Çalışır?
+H2: OTP Kodu Nerelerde Kullanılır?
+H2: OTP Kodu Neden Kimseyle Paylaşılmamalı?
+H2: OTP Kodu Gelmiyorsa Ne Yapılmalı?
+H2: OTP Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım ve güvenlik uyarısı. Açılış paragrafı açılımı ve tek cümlelik tanımı verir.
+H2 · OTP Ne Demek: One Time Password açılımı ve tek kullanımlık şifre karşılığı; geçerlilik süresinin sınırlı olduğu.
+H2 · Nasıl Çalışır: SMS, uygulama ve e-posta üç kanal; kodun neden her seferinde değiştiği tek cümlede.
+H2 · Nerelerde Kullanılır: Bankacılık, e-ticaret ödemesi, hesap girişi, işlem onayı dört madde.
+H2 · Neden Paylaşılmamalı: Yazının en değerli bölümü. Kurum çalışanı gibi arayıp kod isteyen dolandırıcılık senaryosu somut anlatılır; hiçbir kurumun telefonda OTP istemediği kalın harflerle verilir. Kod paylaşıldığında ne olabileceği tek cümlede.
+H2 · Kod Gelmiyorsa: Beş madde: şebeke sinyali, numaranın güncelliği, SMS engelleme filtresi, saat ayarı (doğrulama uygulamalarında), yeniden gönderme süresi.
+UZUNLUK: 600-800 kelime.
+İÇ BAĞLANTI: Spam ve dolandırıcılık yazılarına bağlanır.</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>H3: OTP Ne Demek?
+OTP, tek kullanımlık şifre anlamına gelir ve yalnızca bir işlem için geçerli olan, kısa süre sonra geçersiz hâle gelen doğrulama kodudur.
+H3: OTP Kodu Nerede Kullanılır?
+Bankacılık işlemlerinde, çevrimiçi ödemelerde ve hesap girişlerinde kimlik doğrulaması amacıyla kullanılır.
+H3: OTP Kodu Paylaşılırsa Ne Olur?
+Kodu ele geçiren kişi hesabınıza giriş yapabilir veya adınıza işlem gerçekleştirebilir; bu nedenle kod hiçbir koşulda paylaşılmamalıdır.
+H3: Bankalar Telefonda OTP Kodu İster mi?
+İstemez. Kod talep eden aramalar dolandırıcılık girişimidir ve derhal sonlandırılmalıdır.
+H3: OTP Kodu Gelmiyorsa Ne Yapmalıyım?
+Şebeke bağlantısı, kayıtlı telefon numarasının güncelliği ve mesaj engelleme filtreleri kontrol edilir, ardından kod yeniden istenir.</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>1. claude ai : https://www.turkcell.com.tr/blog/claude-ai-anthropicin-guvenlik-merkezli-yapay-zeka-modeli
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -13822,12 +14739,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>Sonuç sayfasında bankaların bilgilendirme sayfaları öne çıkmaktadır; telekom tarafında tanım içeriği sınırlıdır.</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>1. OTP tanımı açıklanır
 2. SMS ile gelen tek kullanımlık şifrenin nasıl çalıştığı açıklanır
@@ -13835,36 +14752,36 @@
 4. OTP gelmediğinde yapılabilecekler açıklanır</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>Dolandırıcılık uyarısı bölümü marka güvenliği açısından değerli olabilir.</t>
         </is>
       </c>
-      <c r="P32" s="8" t="n">
+      <c r="R32" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="Q32" s="11" t="inlineStr">
+      <c r="S32" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="T32" s="6" t="inlineStr">
         <is>
           <t>Mart</t>
         </is>
       </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T32" s="4" t="inlineStr">
+      <c r="U32" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
         <is>
           <t>Bankadan ya da uygulamadan gelen OTP ifadesinin ne olduğunu soran kişi kısa yanıt bekliyor.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="128.5" customHeight="1">
+    <row r="33" ht="263.5" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>QLED Nedir? QLED ve OLED Farkı</t>
@@ -13911,13 +14828,43 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>1. QLED tanımı
-2. QLED ve OLED farkı tablo hâlinde
-3. Hangi kullanım için hangisi
-4. Parlaklık ve ömür karşılaştırması</t>
+          <t>H2: QLED Nedir?
+H2: OLED Nedir?
+H2: QLED ve OLED Farkı Nedir?
+H2: Parlaklık ve Kontrast Karşılaştırması
+H2: Panel Ömrü ve Görüntü Kalıcılığı
+H2: Hangi Kullanım İçin Hangisi Daha Uygun?
+H2: QLED ve OLED Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>TON: Karşılaştırma. Ürün önerisi verilmez; okuyucu iki teknoloji arasında karar veriyor.
+H2 · QLED Nedir: Arkadan aydınlatmalı LCD panelin kuantum nokta katmanıyla geliştirilmiş hâli; iki cümle.
+H2 · OLED Nedir: Her pikselin kendi ışığını ürettiği panel; iki cümle.
+H2 · QLED ve OLED Farkı: Yazının merkezindeki tablo. Satırlar: aydınlatma yöntemi, siyah derinliği, tepe parlaklığı, görüş açısı, görüntü kalıcılığı riski, tipik kullanım ömrü.
+H2 · Parlaklık ve Kontrast: Aydınlık odada ve karanlık odada hangisinin öne çıktığı iki paragrafta.
+H2 · Panel Ömrü: Görüntü kalıcılığının ne olduğu ve hangi kullanımda risk oluşturduğu.
+H2 · Hangi Kullanım İçin Hangisi: Üç senaryo: aydınlık salon, ev sineması, oyun konsolu. Her senaryoda tek cümlelik yönlendirme.
+UZUNLUK: 900-1.100 kelime.
+DİKKAT: Marka ve model önerisi verilmez; teknoloji karşılaştırması katmanında kalınır.</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>H3: QLED Nedir?
+QLED, arkadan aydınlatmalı LCD panelin kuantum nokta katmanıyla daha geniş renk aralığı ve yüksek parlaklık sunacak biçimde geliştirilmiş hâlidir.
+H3: QLED ile OLED Arasındaki Fark Nedir?
+OLED'de her piksel kendi ışığını üretir ve tam siyah elde edilir; QLED ise arkadan aydınlatma kullanır ve genellikle daha yüksek tepe parlaklığı sağlar.
+H3: Aydınlık Odada Hangisi Daha İyi?
+Yüksek tepe parlaklığı nedeniyle QLED paneller aydınlık ortamlarda daha okunaklı bir görüntü sunar.
+H3: OLED'de Görüntü Kalıcılığı Sorun mu?
+Uzun süre sabit kalan görüntülerde risk vardır; güncel panellerde bu riski azaltan koruma özellikleri bulunur.
+H3: Oyun İçin QLED mi OLED mi?
+Tepki süresi ve siyah derinliği nedeniyle OLED öne çıkar; ancak sabit arayüz öğeleri uzun süre ekranda kalıyorsa QLED daha güvenli bir tercih olabilir.</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -13925,12 +14872,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>Rakip bloglarda QLED tanımı televizyon satış sayfalarına bağlı veriliyor; bağımsız karşılaştırma içeriği sınırlıdır.</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>1. QLED tanımı açıklanır
 2. QLED ve OLED farkı tablo hâlinde açıklanır
@@ -13938,36 +14885,36 @@
 4. Parlaklık ve ömür karşılaştırması verilir</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Ürün önerisi verilmemesi, bilgi katmanında kalınması önerilir.</t>
         </is>
       </c>
-      <c r="P33" s="8" t="n">
+      <c r="R33" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="Q33" s="11" t="inlineStr">
+      <c r="S33" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="T33" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="S33" s="6" t="inlineStr">
+      <c r="U33" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="T33" s="4" t="inlineStr">
+      <c r="V33" s="4" t="inlineStr">
         <is>
           <t>Televizyon alacak kişi QLED ile OLED arasındaki farkı soruyor.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="142" customHeight="1">
+    <row r="34" ht="263.5" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Medya Okuryazarlığı Nedir?</t>
@@ -14014,13 +14961,41 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>1. Medya okuryazarlığının tanımı
-2. Yanlış bilgiyi ayırt etme adımları
-3. Kaynak doğrulama yöntemleri
-4. Çocuklar için ipuçları</t>
+          <t>H2: Medya Okuryazarlığı Nedir?
+H2: Medya Okuryazarlığı Neden Önemli?
+H2: Yanlış Bilgi Nasıl Ayırt Edilir?
+H2: Kaynak Doğrulama Yöntemleri
+H2: Çocuklar İçin Medya Okuryazarlığı İpuçları
+H2: Medya Okuryazarlığı Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>TON: Eğitici ve uygulanabilir. Tanımdan sonra hemen yönteme geçilir; yazı bir beceri kazandırma amacı taşır.
+H2 · Nedir: Medya içeriğini çözümleme, değerlendirme ve üretme becerisi; iki cümlelik tanım.
+H2 · Neden Önemli: Yapay zeka üretimi içeriğin yaygınlaşmasıyla doğrulama becerisinin değerinin arttığı; iki paragraf.
+H2 · Yanlış Bilgi Nasıl Ayırt Edilir: Yedi maddelik kontrol listesi: kaynak var mı, tarih güncel mi, başlık ile gövde uyumlu mu, duygu yükü aşırı mı, görsel bağlamından koparılmış mı, başka kaynak doğruluyor mu, yazar kim.
+H2 · Kaynak Doğrulama: Tersine görsel arama, resmî kaynak kontrolü, doğrulama platformları üç yöntem.
+H2 · Çocuklar İçin: Yaşa uygun beş öneri: birlikte izleme, soru sorma alışkanlığı, reklam ile içerik ayrımı, paylaşmadan önce düşünme, ekran süresi.
+UZUNLUK: 900-1.100 kelime.
+İÇ BAĞLANTI: Deepfake ve dijital güvenlik yazılarına bağlanır; bu bağ konuyu markanın çizgisine oturtur.</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>H3: Medya Okuryazarlığı Nedir?
+Medya okuryazarlığı, karşılaşılan haber, görsel ve video içeriklerini sorgulama, kaynağını değerlendirme ve doğruluğunu ayırt etme becerisidir.
+H3: Medya Okuryazarlığı Neden Önemlidir?
+Yapay zekayla üretilen içeriklerin yaygınlaşmasıyla birlikte doğru bilgiyi ayırt etme becerisi günlük kararlar için belirleyici hâle gelmiştir.
+H3: Yanlış Bilgi Nasıl Anlaşılır?
+İçeriğin kaynağı, tarihi ve yazarı kontrol edilir; başlığın gövdeyle uyumu ve aynı bilginin güvenilir başka kaynaklarda yer alıp almadığı sorgulanır.
+H3: Görselin Gerçek Olup Olmadığı Nasıl Anlaşılır?
+Tersine görsel arama yapılarak görselin daha önce nerede kullanıldığı ve hangi bağlama ait olduğu tespit edilebilir.
+H3: Çocuklara Medya Okuryazarlığı Nasıl Kazandırılır?
+İçerik birlikte izlenip sorular sorulabilir, reklam ile içerik ayrımı anlatılabilir ve paylaşmadan önce düşünme alışkanlığı kazandırılabilir.</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>1. güneş enerjisi : https://www.turkcell.com.tr/blog/gunes-enerjisi-nedir-surdurulebilir-gelecegin-enerji-modeli-ve-uygulama-alanlari
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -14028,12 +15003,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Konuyu eğitim kaynakları ve kurumsal sayfalar karşılıyor; marka blogu tarafında sade bir tanım içeriği bulunmamaktadır.</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>1. Medya okuryazarlığının tanımı açıklanır
 2. Yanlış bilgiyi ayırt etme adımları adım adım anlatılır
@@ -14041,36 +15016,36 @@
 4. Çocuklar için ipuçları açıklanır</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Blogun dijital güvenlik yazılarıyla bağlantılandırılması konuyu markanın çizgisine oturtabilir.</t>
         </is>
       </c>
-      <c r="P34" s="8" t="n">
+      <c r="R34" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="Q34" s="11" t="inlineStr">
+      <c r="S34" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="T34" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="S34" s="6" t="inlineStr">
+      <c r="U34" s="6" t="inlineStr">
         <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="T34" s="4" t="inlineStr">
+      <c r="V34" s="4" t="inlineStr">
         <is>
           <t>Doğru bilgiyi ayırt etmeyi öğrenmek isteyen kişi tanım ve yöntem arıyor.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="128.5" customHeight="1">
+    <row r="35" ht="209.5" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>TAG Nedir?</t>
@@ -14113,13 +15088,38 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>1. TAG teriminin anlamı
-2. Sosyal medyada etiketleme
-3. NFC etiketi anlamı
-4. Hangi bağlamda hangi anlamın kullanıldığı</t>
+          <t>H2: TAG Nedir?
+H2: Sosyal Medyada Etiketleme Ne Anlama Gelir?
+H2: NFC Etiketi (Tag) Nedir?
+H2: Web ve Ölçümlemede Tag Ne Demek?
+H2: Hangi Bağlamda Hangi Anlam Kullanılır?
+H2: TAG Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>TON: Çok anlamlı terim açıklaması. Açılış paragrafı kelimenin birden çok anlamı olduğunu duyurur ve yazıda hangi üç anlamın ele alındığını sayar; okuyucu doğru bölüme hemen gidebilmeli.
+H2 · TAG Nedir: Genel anlamıyla etiket; içeriği sınıflandıran işaret.
+H2 · Sosyal Medyada Etiketleme: Kişi etiketleme ve konu etiketi (hashtag) ayrımı; ikisi karıştırılıyor.
+H2 · NFC Etiketi: Küçük bir çipin okutulmasıyla işlem başlatılması; ev otomasyonu ve kartvizit iki örnekle.
+H2 · Web ve Ölçümlemede Tag: Sayfaya eklenen ölçümleme kodu anlamı ve HTML etiketi anlamı iki cümlede ayrı ayrı.
+H2 · Hangi Bağlamda Hangi Anlam: Üç satırlık tablo: bağlam, anlamı, tipik cümle örneği. Bu tablo yazının en kullanışlı bloğu.
+UZUNLUK: 700-900 kelime.</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>H3: TAG Nedir?
+TAG, Türkçede etiket anlamına gelir ve bağlama göre sosyal medyada kişi etiketlemeyi, NFC çipini ya da web sayfasına eklenen ölçümleme kodunu ifade eder.
+H3: Sosyal Medyada Tag Ne Demek?
+Bir gönderide kişinin hesabının bağlanmasıdır; konu etiketi anlamındaki hashtag ise içeriğin konusunu sınıflandırır.
+H3: NFC Tag Ne İşe Yarar?
+Telefonun yaklaştırılmasıyla önceden tanımlanmış bir işlemi başlatan küçük bir çiptir; ev otomasyonu ve dijital kartvizit gibi kullanımları vardır.
+H3: HTML'de Tag Ne Anlama Gelir?
+Sayfanın yapısını tanımlayan işaretleme öğesidir; başlık, paragraf ve bağlantı gibi öğeler tag'lerle belirtilir.</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -14127,12 +15127,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>Tanım araması; sonuç sayfası karışık kaynaklardan oluşuyor, marka blogu bulunmamaktadır.</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>1. TAG teriminin anlamı açıklanır
 2. Sosyal medyada etiketleme adım adım anlatılır
@@ -14140,36 +15140,36 @@
 4. Hangi bağlamda hangi anlamın kullanıldığı açıklanır</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>Kelimenin birden çok anlamı bulunmaktadır; açılışta hangi anlamların ele alındığı belirtilmelidir.</t>
         </is>
       </c>
-      <c r="P35" s="8" t="n">
+      <c r="R35" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="Q35" s="11" t="inlineStr">
+      <c r="S35" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="T35" s="6" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="S35" s="6" t="inlineStr">
+      <c r="U35" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="T35" s="4" t="inlineStr">
+      <c r="V35" s="4" t="inlineStr">
         <is>
           <t>TAG kelimesinin karşılığını arayan kişi kısa tanım bekliyor.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="128.5" customHeight="1">
+    <row r="36" ht="250" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Karekod Nasıl Okutulur?</t>
@@ -14212,12 +15212,42 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>1. Kamerayla karekod okutma adımları
-2. Kamera okutmadığında yapılabilecekler
-3. Sahte karekodların ayırt edilmesi</t>
+          <t>H2: Karekod Nedir?
+H2: Karekod Nasıl Okutulur?
+H3: iPhone ile Karekod Okutma
+H3: Android ile Karekod Okutma
+H2: Kamera Karekodu Okutmuyorsa Ne Yapmalı?
+H2: Ekrandaki Karekod Nasıl Okutulur?
+H2: Sahte Karekodlar Nasıl Ayırt Edilir?
+H2: Karekod Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tek soruya odaklı, kısa. Yanıt açılış paragrafında: kamera uygulaması karekoda tutulur ve çıkan bağlantıya dokunulur.
+H2 · Karekod Nedir: İki boyutlu barkod; QR kod ile aynı şey olduğu tek cümlede.
+H2 · Nasıl Okutulur: İki H3, her biri üç adım. Kamera uygulamasının karekod okuma ayarının açık olması gerektiği notu.
+H2 · Kamera Okutmuyorsa: Altı madde: ayarın kapalı olması, mesafe, ışık, lens kirliliği, kodun hasarlı olması, üçüncü parti okuyucu.
+H2 · Ekrandaki Karekod: Aynı cihazın ekranındaki kodun okutulamadığı durumda ekran görüntüsü alıp galeriden okutma yöntemi. Pratikte en sık sorulan durum.
+H2 · Sahte Karekodlar: Yapıştırılmış kod, kısaltılmış bağlantı ve ödeme isteyen sayfa üç işaret; bağlantı adresi açılmadan önce kontrol edilmeli.
+UZUNLUK: 700-900 kelime.</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>H3: Karekod Nasıl Okutulur?
+Telefonun kamera uygulaması açılır, karekoda yaklaşık on santimetre mesafeden tutulur ve ekranda beliren bağlantıya dokunulur.
+H3: Kamera Karekodu Okumuyorsa Ne Yapılmalı?
+Kamera ayarlarındaki karekod tarama seçeneğinin açık olduğu kontrol edilir; ışık, mesafe ve lens temizliği de sonucu etkiler.
+H3: Ekrandaki Karekod Aynı Telefonla Okutulabilir mi?
+Doğrudan okutulamaz; kodun ekran görüntüsü alınıp galeriden okutularak bağlantıya ulaşılabilir.
+H3: Karekod Güvenli mi?
+Kodun kendisi bir bağlantıdan ibarettir; açılan adres kontrol edilmeden kişisel bilgi veya ödeme bilgisi girilmemelidir.
+H3: Karekod ile QR Kod Aynı Şey mi?
+Evet. Karekod, QR kodun Türkçe karşılığıdır.</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -14225,7 +15255,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14246,43 +15276,43 @@
           </r>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>1. Kamerayla karekod okutma adımları adım adım anlatılır
 2. Kamera okutmadığında yapılabilecekler açıklanır
 3. Sahte karekodların ayırt edilmesi adım adım anlatılır</t>
         </is>
       </c>
-      <c r="O36" s="4" t="inlineStr">
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>Tek soruya odaklı içeriktir; adımlar numaralı listeye alınabilir.</t>
         </is>
       </c>
-      <c r="P36" s="8" t="n">
+      <c r="R36" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="Q36" s="11" t="inlineStr">
+      <c r="S36" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="T36" s="6" t="inlineStr">
         <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="S36" s="6" t="inlineStr">
+      <c r="U36" s="6" t="inlineStr">
         <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="T36" s="4" t="inlineStr">
+      <c r="V36" s="4" t="inlineStr">
         <is>
           <t>Karekod okutmayı bilmeyen kişi adım arıyor; soru tek ve nettir.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="128.5" customHeight="1">
+    <row r="37" ht="263.5" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Hat Devri: Ücret ve İşlem Adımları</t>
@@ -14329,13 +15359,41 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>1. Hat devrinin tanımı
-2. Devir için gereken belgeler
-3. Devir ücreti
-4. Devir sonrası fatura ve taahhüt durumu</t>
+          <t>H2: Hat Devri Nedir?
+H2: Hat Devri Nasıl Yapılır? Adım Adım
+H2: Hat Devri İçin Gereken Belgeler
+H2: Hat Devir Ücreti Ne Kadar?
+H2: Devir Sonrası Fatura ve Taahhüt Ne Olur?
+H2: Hat Devri Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>TON: İşlem rehberi. Okuyucu bir işlemi tamamlamak üzere; her bölüm doğrudan koşul ve adım verir.
+H2 · Hat Devri Nedir: Numaranın aynı operatörde kalarak başka bir kişinin adına geçirilmesi; numara taşımadan farklı olduğu tek cümlede belirtilir çünkü ikisi karıştırılıyor.
+H2 · Nasıl Yapılır: Numaralı adım listesi: iki tarafın da bulunması, başvuru kanalı, kimlik doğrulama, onay, aktivasyon.
+H2 · Gereken Belgeler: Devreden ve devralan için ayrı kısa listeler; kurumsal hatlarda ek belge notu.
+H2 · Devir Ücreti: Ücretin nasıl belirlendiği ve nereden öğrenileceği. Tutar yazılmaz; güncel tutarın işlem sırasında görüntülendiği belirtilir.
+H2 · Fatura ve Taahhüt: Devir öncesi borcun kapatılması gerektiği, taahhüdün devredilip devredilemeyeceği ve devreden tarafın sorumluluğunun ne zaman bittiği üç maddede.
+UZUNLUK: 600-800 kelime.
+DİKKAT: Ücret, belge ve taahhüt koşulları ürün ekibiyle doğrulanmalı; güncellenme tarihi görünür tutulmalıdır.</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>H3: Hat Devri Nasıl Yapılır?
+Devreden ve devralan kişilerin başvuru kanalında birlikte bulunması, kimlik doğrulaması yapılması ve devir onayının verilmesiyle tamamlanır.
+H3: Hat Devir Ücreti Ne Kadar?
+Devir işleminde alınan ücret güncel tarifeye göre belirlenir ve işlem sırasında görüntülenir.
+H3: Hat Devri ile Numara Taşıma Aynı Şey mi?
+Hayır. Hat devrinde numara aynı operatörde kalır ve sahibi değişir; numara taşımada ise numara başka bir operatöre geçer.
+H3: Hat Devri İçin Hangi Belgeler Gerekir?
+Devreden ve devralan tarafın kimlik belgesi gereklidir; kurumsal hatlarda ayrıca yetki belgesi istenir.
+H3: Devirden Sonra Eski Faturalardan Kim Sorumlu?
+Devir tarihine kadar oluşan borçlardan devreden taraf sorumludur; devir öncesinde hesabın kapatılmış olması gerekir.</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>1. hat resetleme nedir : https://www.turkcell.com.tr/blog/hat-resetleme-nedir-ne-zaman-ve-nasil-yapilir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -14343,12 +15401,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Rakip operatörler hat devri bilgisini hizmet sayfasında veriyor; blog tarafında adım anlatan içerik bulunmamaktadır.</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>1. Hat devrinin tanımı açıklanır
 2. Devir için gereken belgeler açıklanır
@@ -14356,36 +15414,36 @@
 4. Devir sonrası fatura ve taahhüt durumu açıklanır</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>Ücret ve belge bilgileri değişkendir; ürün ekibiyle doğrulanmalı ve güncellenme tarihi görünür tutulmalıdır.</t>
         </is>
       </c>
-      <c r="P37" s="8" t="n">
+      <c r="R37" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="Q37" s="11" t="inlineStr">
+      <c r="S37" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="T37" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="S37" s="6" t="inlineStr">
+      <c r="U37" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="T37" s="4" t="inlineStr">
+      <c r="V37" s="4" t="inlineStr">
         <is>
           <t>Hattını başkasına devretmek isteyen abone ücreti ve gereken belgeleri arıyor.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="128.5" customHeight="1">
+    <row r="38" ht="209.5" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t>URL Nedir?</t>
@@ -14428,12 +15486,40 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>1. URL tanımı
-2. URL bölümleri: protokol, alan adı, yol
-3. Güvenli URL'nin nasıl anlaşıldığı</t>
+          <t>H2: URL Nedir?
+H2: URL Bölümleri Nelerdir?
+H3: Protokol Ne Anlama Gelir?
+H3: Alan Adı ve Alt Alan Adı
+H3: Yol ve Sorgu Parametreleri
+H2: Güvenli URL Nasıl Anlaşılır?
+H2: Kısaltılmış Bağlantılar Neden Riskli Olabilir?
+H2: URL Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım sorgusu. İlk paragraf tek cümlelik karşılık verir ve hemen ardından örnek bir adres şema hâlinde parçalarına ayrılır.
+H2 · URL Nedir: İnternetteki bir kaynağın adresi; açılımı parantez içinde.
+H2 · URL Bölümleri: Üç H3. Örnek bir adres üzerinden protokol, alan adı, yol ve sorgu parametreleri renkli olmayan sade bir şemayla gösterilir. Bu şema yazının en öğretici bloğu.
+H2 · Güvenli URL Nasıl Anlaşılır: Beş madde: https, alan adının doğru yazımı, benzer harf oyunları, kilit simgesinin ne anlama geldiği ve neyi garanti etmediği, sertifika uyarısı.
+H2 · Kısaltılmış Bağlantılar: Hedefin görünmediği, önizleme yöntemleri ve şüpheli durumda tıklanmaması.
+UZUNLUK: 700-900 kelime.
+İÇ BAĞLANTI: Karekod ve dijital güvenlik yazılarına bağlanır.</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>H3: URL Nedir?
+URL, internetteki bir sayfanın veya dosyanın tam adresidir ve tarayıcının hangi kaynağa ulaşacağını belirtir.
+H3: URL Hangi Bölümlerden Oluşur?
+Protokol, alan adı, yol ve gerektiğinde sorgu parametrelerinden oluşur.
+H3: Güvenli URL Nasıl Anlaşılır?
+Adresin https ile başlaması ve alan adının doğru yazıldığının kontrol edilmesi ilk adımdır; kilit simgesi bağlantının şifreli olduğunu gösterir, sitenin güvenilirliğini kanıtlamaz.
+H3: Kısaltılmış Bağlantılar Güvenli mi?
+Kısaltılmış bağlantıda hedef adres görünmez; kaynağı bilinmeyen kısa bağlantılara tıklanmaması önerilir.</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -14441,48 +15527,48 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Rakip bloglarda URL tanımı ayrı bir yazıyla karşılanmaktadır.</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>1. URL tanımı açıklanır
 2. URL bölümleri: protokol, alan adı, yol açıklanır
 3. Güvenli URL'nin nasıl anlaşıldığı açıklanır</t>
         </is>
       </c>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>Tanım sorgusudur; ilk paragrafta tek cümlelik karşılık ve ardından bölüm şeması önerilir.</t>
         </is>
       </c>
-      <c r="P38" s="8" t="n">
+      <c r="R38" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="Q38" s="11" t="inlineStr">
+      <c r="S38" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="T38" s="6" t="inlineStr">
         <is>
           <t>Mart</t>
         </is>
       </c>
-      <c r="S38" s="6" t="inlineStr">
+      <c r="U38" s="6" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="T38" s="4" t="inlineStr">
+      <c r="V38" s="4" t="inlineStr">
         <is>
           <t>URL kelimesinin karşılığını arayan kişi kısa tanım bekliyor.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="128.5" customHeight="1">
+    <row r="39" ht="250" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Apple Arcade Nedir?</t>
@@ -14525,13 +15611,41 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>1. Apple Arcade tanımı
-2. Abonelik ücreti ve deneme süresi
-3. Hangi cihazlarda çalıştığı
-4. Oyunların çevrimdışı oynanabilirliği</t>
+          <t>H2: Apple Arcade Nedir?
+H2: Apple Arcade Abonelik Ücreti Ne Kadar?
+H2: Apple Arcade Hangi Cihazlarda Çalışır?
+H2: Apple Arcade Oyunları Çevrimdışı Oynanır mı?
+H2: Apple Arcade Nasıl Abone Olunur ve İptal Edilir?
+H2: Apple Arcade Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>TON: Tanım ve abonelik bilgisi. Türkçe tanım içeriği sınırlı olduğu için yazının açılışı doğrudan tanımı vermeli.
+H2 · Nedir: Reklamsız ve uygulama içi satın alma içermeyen oyun aboneliği; iki cümle.
+H2 · Ücret: Aylık ücret ve deneme süresi; paket aboneliklerin içinde yer aldığı notu. Tutar tarih notuyla verilir.
+H2 · Hangi Cihazlarda: iPhone, iPad, Mac, Apple TV listesi ve aynı abonelikle aile paylaşımı.
+H2 · Çevrimdışı Oynanır mı: İndirildikten sonra çevrimdışı oynanabildiği; aboneliğin doğrulanması için ara ara bağlantı gerektiği.
+H2 · Abonelik ve İptal: Üç adımlık abone olma ve iptal yolu; iptal sonrası oyunlara erişimin ne zaman kesildiği.
+UZUNLUK: 600-800 kelime.
+DİKKAT: Ücret ve deneme süresi değişkendir; güncellenme tarihi görünür tutulmalıdır.</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>H3: Apple Arcade Nedir?
+Apple Arcade, tek bir aylık abonelikle reklamsız ve uygulama içi satın alma içermeyen oyunlara erişim sunan oyun servisidir.
+H3: Apple Arcade Ücreti Ne Kadar?
+Servis aylık abonelik ücretiyle sunulur ve bazı paket aboneliklerin içinde de yer alır; güncel tutar servis sayfasından görüntülenir.
+H3: Apple Arcade Hangi Cihazlarda Çalışır?
+iPhone, iPad, Mac ve Apple TV cihazlarında aynı abonelikle kullanılabilir.
+H3: Apple Arcade Oyunları İnternetsiz Oynanır mı?
+Oyunlar indirildikten sonra çevrimdışı oynanabilir; aboneliğin doğrulanması için zaman zaman bağlantı gerekir.
+H3: Apple Arcade Aboneliği Nasıl İptal Edilir?
+Cihaz ayarlarındaki abonelikler bölümünden servis seçilerek iptal edilir; erişim dönem sonuna kadar sürer.</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -14539,12 +15653,12 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Sonuç sayfasında Apple'ın kendi sayfası ve oyun siteleri yer alıyor; Türkçe tanım içeriği sınırlıdır.</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>1. Apple Arcade tanımı açıklanır
 2. Abonelik ücreti ve deneme süresi açıklanır
@@ -14552,36 +15666,36 @@
 4. Oyunların çevrimdışı oynanabilirliği açıklanır</t>
         </is>
       </c>
-      <c r="O39" s="4" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>Ücret bilgisi değişkendir; güncellenme tarihi görünür tutulabilir.</t>
         </is>
       </c>
-      <c r="P39" s="8" t="n">
+      <c r="R39" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="Q39" s="11" t="inlineStr">
+      <c r="S39" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="T39" s="6" t="inlineStr">
         <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="S39" s="6" t="inlineStr">
+      <c r="U39" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="T39" s="4" t="inlineStr">
+      <c r="V39" s="4" t="inlineStr">
         <is>
           <t>Apple Arcade aboneliğini merak eden kişi kapsamı ve ücreti soruyor.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="128.5" customHeight="1">
+    <row r="40" ht="209.5" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>FreeDOS Nedir? İşletim Sistemi Yüklü Olmayan Bilgisayar</t>
@@ -14624,12 +15738,39 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>1. FreeDOS tanımı
-2. Işletim sistemi yüklü olmayan bilgisayarın anlamı
-3. Sonrasında yapılabilecekler</t>
+          <t>H2: FreeDOS Nedir?
+H2: İşletim Sistemi Yüklü Olmayan Bilgisayar Ne Demek?
+H2: FreeDOS Bilgisayar Neden Daha Uygun Fiyatlı?
+H2: FreeDOS Bilgisayara İşletim Sistemi Nasıl Kurulur?
+H2: FreeDOS Bilgisayar Alınır mı?
+H2: FreeDOS Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>TON: Karar yardımı. Okuyucu mağazada ya da ürün sayfasında "FreeDOS" ibaresini görmüş ve ne anlama geldiğini soruyor.
+H2 · FreeDOS Nedir: Açık kaynaklı, DOS uyumlu ve ücretsiz bir işletim sistemi; iki cümle.
+H2 · İşletim Sistemi Yüklü Olmayan Bilgisayar: Cihazın boş gelmediği, üzerinde FreeDOS bulunduğu ama günlük kullanıma uygun olmadığı net biçimde.
+H2 · Neden Daha Uygun Fiyatlı: Lisans maliyeti farkı tek paragraf.
+H2 · İşletim Sistemi Nasıl Kurulur: Kurulum medyası hazırlama, önyükleme sırası ve kurulum adımları üst düzeyde; lisans satın alınması gerektiği notu.
+H2 · Alınır mı: Lisans maliyeti, kurulum bilgisi gereksinimi ve garanti etkisi üç maddede; karar okuyucuya bırakılır.
+UZUNLUK: 600-800 kelime.
+İÇ BAĞLANTI: Blogun işletim sistemi yazısına bağlanır.</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>H3: FreeDOS Nedir?
+FreeDOS, açık kaynaklı ve ücretsiz bir DOS uyumlu işletim sistemidir; genellikle yeni bilgisayarlara lisans maliyetini düşürmek için kurulu gelir.
+H3: FreeDOS Bilgisayar Ne Anlama Gelir?
+Cihazın Windows veya macOS gibi bir işletim sistemiyle değil, temel bir sistemle geldiğini gösterir; günlük kullanım için ayrıca işletim sistemi kurulması gerekir.
+H3: FreeDOS Bilgisayara Windows Kurulabilir mi?
+Kurulabilir. Lisans satın alındıktan sonra kurulum medyası hazırlanarak sistem yüklenebilir.
+H3: FreeDOS Bilgisayar Neden Daha Ucuz?
+Fiyat farkı büyük ölçüde işletim sistemi lisans bedelinin cihaza dahil olmamasından kaynaklanır.</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>1. kuantum bilgisayar : https://www.turkcell.com.tr/blog/kuantum-bilgisayar-nedir
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.
@@ -14637,7 +15778,7 @@
    Yazı planında karşılığı bulunmamaktadır; konuya değinen bir cümle eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14658,37 +15799,37 @@
           </r>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>1. FreeDOS tanımı açıklanır
 2. Işletim sistemi yüklü olmayan bilgisayarın anlamı açıklanır
 3. Sonrasında yapılabilecekler açıklanır</t>
         </is>
       </c>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>Blogun işletim sistemi yazısıyla iç bağlantı kurulabilir.</t>
         </is>
       </c>
-      <c r="P40" s="8" t="n">
+      <c r="R40" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="Q40" s="11" t="inlineStr">
+      <c r="S40" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="T40" s="6" t="inlineStr">
         <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="S40" s="6" t="inlineStr">
+      <c r="U40" s="6" t="inlineStr">
         <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="T40" s="4" t="inlineStr">
+      <c r="V40" s="4" t="inlineStr">
         <is>
           <t>İşletim sistemi yüklü olmayan bilgisayar alan kişi ne yapacağını arıyor.</t>
         </is>
@@ -14715,6 +15856,8 @@
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="n"/>
+      <c r="U41" s="2" t="n"/>
+      <c r="V41" s="2" t="n"/>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -14745,6 +15888,8 @@
       <c r="R42" s="12" t="n"/>
       <c r="S42" s="12" t="n"/>
       <c r="T42" s="12" t="n"/>
+      <c r="U42" s="12" t="n"/>
+      <c r="V42" s="12" t="n"/>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -14775,6 +15920,8 @@
       <c r="R43" s="12" t="n"/>
       <c r="S43" s="12" t="n"/>
       <c r="T43" s="12" t="n"/>
+      <c r="U43" s="12" t="n"/>
+      <c r="V43" s="12" t="n"/>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
@@ -14805,6 +15952,8 @@
       <c r="R44" s="12" t="n"/>
       <c r="S44" s="12" t="n"/>
       <c r="T44" s="12" t="n"/>
+      <c r="U44" s="12" t="n"/>
+      <c r="V44" s="12" t="n"/>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -14876,14 +16025,16 @@
       <c r="R45" s="12" t="n"/>
       <c r="S45" s="12" t="n"/>
       <c r="T45" s="12" t="n"/>
+      <c r="U45" s="12" t="n"/>
+      <c r="V45" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="B42:T42"/>
-    <mergeCell ref="B45:T45"/>
-    <mergeCell ref="B44:T44"/>
-    <mergeCell ref="B43:T43"/>
+    <mergeCell ref="B43:V43"/>
+    <mergeCell ref="B44:V44"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="B45:V45"/>
+    <mergeCell ref="B42:V42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14895,7 +16046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -14918,15 +16069,17 @@
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="36" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="52" customWidth="1" min="21" max="21"/>
-    <col width="58" customWidth="1" min="22" max="22"/>
-    <col width="52" customWidth="1" min="23" max="23"/>
+    <col width="58" customWidth="1" min="21" max="21"/>
+    <col width="104" customWidth="1" min="22" max="22"/>
+    <col width="86" customWidth="1" min="23" max="23"/>
     <col width="58" customWidth="1" min="24" max="24"/>
-    <col width="44" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="50" customWidth="1" min="29" max="29"/>
+    <col width="52" customWidth="1" min="25" max="25"/>
+    <col width="58" customWidth="1" min="26" max="26"/>
+    <col width="44" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="50" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -14963,6 +16116,8 @@
       <c r="AA1" s="2" t="n"/>
       <c r="AB1" s="2" t="n"/>
       <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -14994,6 +16149,8 @@
       <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="n"/>
       <c r="AC2" s="2" t="n"/>
+      <c r="AD2" s="2" t="n"/>
+      <c r="AE2" s="2" t="n"/>
     </row>
     <row r="3" ht="51" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -15166,45 +16323,55 @@
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>Eklenebilecek Alt Başlıklar</t>
+          <t>Eklenebilecek Alt Başlıklar (H2 / H3)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
+          <t>İçerik Kurgusu</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>Cevaplanması Gereken Sorular (FAQ, H3)</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
           <t>İç Linkler (Anchor : URL)</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="Y3" s="5" t="inlineStr">
         <is>
           <t>Rakip Analizi</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="Z3" s="5" t="inlineStr">
         <is>
           <t>Güncelleme Yönergesi</t>
         </is>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="AA3" s="5" t="inlineStr">
         <is>
           <t>Dikkat Edilecek</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>Toplam Aylık Arama</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>Puan</t>
         </is>
       </c>
-      <c r="AB3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>Öncelik</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>Ne Anlama Geliyor</t>
         </is>
@@ -15312,13 +16479,41 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>1. Windows, macOS ve Linux Karşılaştırması
-2. İşletim Sistemi Yalnız Bilgisayarlarda mı Bulunur?
-3. Android ve iOS Arasındaki Farklar
+          <t>H2: Windows, macOS ve Linux Arasındaki Farklar Nelerdir?
+H3: Windows Nedir, Kimler İçin Uygundur?
+H3: macOS Nedir, Hangi Cihazlarda Çalışır?
+H3: Linux Nedir, Neden Tercih Edilir?
+H2: İşletim Sistemi Yalnız Bilgisayarlarda mı Bulunur?
+H2: Android ve iOS Arasındaki Farklar Nelerdir?
+H2: İşletim Sistemleri Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: İşletim Sistemi Özellikleri Nelerdir?</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>EKLENECEK BÖLÜMLERİN YERİ: Üç H3'lü karşılaştırma bölümü mevcut "İşletim Sistemi Çeşitleri Nelerdir?" başlığının hemen altına; mobil ve cihaz bölümleri onun ardına; FAQ yazının sonuna.
+H2 · Windows, macOS ve Linux Farkları: Üç H3'ün her birinde aynı şablon kullanılır: güncel sürüm adı, tipik kullanıcı profili, donanım gereksinimi, güçlü olduğu kullanım. "Windows nedir" sorgusu 1.059 Impression alıyor ve sayfa 9.7 ortalama sırada; bu kalıbın H3 başlığında ve açılış cümlesinde geçmesi sıralamayı destekler. Bölümün sonunda üç sistemi yan yana koyan dört satırlık tablo yer alır: lisans, donanım, uygulama ekosistemi, güncelleme yönetimi.
+H2 · Yalnız Bilgisayarlarda mı: "işletim sistemleri sadece bilgisayarlara özgü müdür" sorgusu 646 Impression ile 3.2 sırada geliyor, yani soru soruluyor ama yazıda yanıt bölümü yok. Telefon, akıllı televizyon, akıllı saat, araç bilgi eğlence sistemi ve modem yazılımı beş örnekle verilir; her biri tek cümle.
+H2 · Android ve iOS Farkları: Şu an ikisi tek cümlede geçiyor. Uygulama mağazası, güncelleme dağıtımı, donanım çeşitliliği ve özelleştirme dört satırlık tabloya alınır.
+GÖVDE DÜZENLEMESİ: "bilgisayar işletim sistemleri" ve "işletim sistemleri nelerdir" kalıpları gövdede hiç geçmiyor; mevcut çeşitler bölümünün açılış cümlesi bu iki kalıbı da doğal biçimde karşılayacak şekilde yeniden yazılır.
+ÖLÇÜM NOTU: "işletim sistemleri hakkında aşağıdakilerden hangisi doğru değildir" sorgusu 4.221 Impression alıyor ancak ödev kaynaklı; bu sorguya bölüm yazılması önerilmez, yalnızca ölçüm okunurken hesaba katılır.</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>H3: İşletim Sistemi Nedir?
+İşletim sistemi, donanım ile uygulamalar arasında köprü kuran ve cihazın temel işlevlerini yöneten yazılımdır.
+H3: Bilgisayar İşletim Sistemleri Nelerdir?
+En yaygın bilgisayar işletim sistemleri Windows, macOS ve Linux dağıtımlarıdır.
+H3: Windows Nedir?
+Windows, kişisel bilgisayarlarda en yaygın kullanılan, geniş donanım ve uygulama desteği sunan işletim sistemidir.
+H3: İşletim Sistemi Yalnızca Bilgisayarlarda mı Bulunur?
+Hayır. Telefonlar, akıllı televizyonlar, akıllı saatler ve araç bilgi sistemleri de kendi işletim sistemleriyle çalışır.
+H3: Android ile iOS Arasındaki Fark Nedir?
+Android çok sayıda üreticinin cihazında çalışır ve daha geniş özelleştirme sunar; iOS yalnızca Apple cihazlarında çalışır ve güncellemeleri tüm cihazlara aynı anda ulaşır.</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>1. gemini : https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -15326,7 +16521,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15347,7 +16542,7 @@
           </r>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>1. 'Windows nedir' sorgusu 1.059 Impression alıyor ancak sayfa 9.7 ortalama sırada kalıyor; Windows, macOS ve Linux için üç ayrı H3 açılıp her birine sürüm adı, tipik kullanıcı profili ve donanım gereksinimi yazılabilir
 2. 'işletim sistemleri sadece bilgisayarlara özgü müdür' sorgusu 646 Impression ile 3.2 sırada geliyor, yani soru soruluyor ama yanıt bölümü yok: telefon, akıllı televizyon, akıllı saat ve araç sistemlerini kapsayan 'İşletim Sistemi Yalnız Bilgisayarlarda mı Bulunur?' başlığı eklenebilir
@@ -15356,29 +16551,29 @@
 5. 'işletim sistemleri hakkında aşağıdakilerden hangisi doğru değildir' sorgusu 4.221 Impression alıyor ve ödev kaynaklı; bu sorguya içerik yazılması önerilmez, ölçüm okunurken hesaba katılması yeterlidir açıklanır</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>Sürüm adları ve donanım gereksinimleri yıl içinde değişiyor; güncellenme tarihinin görünür tutulması bu yazıda değer taşıyor.</t>
         </is>
       </c>
-      <c r="Z4" s="7" t="n">
+      <c r="AB4" s="7" t="n">
         <v>11870</v>
       </c>
-      <c r="AA4" s="8" t="n">
+      <c r="AC4" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="AB4" s="9" t="inlineStr">
+      <c r="AD4" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>Rakip aynı soruda üçüncü sırada ve yedi kat trafik alıyor. Mobil ve masaüstü ayrımı eksik.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="261" customHeight="1">
+    <row r="5" ht="263.5" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar</t>
@@ -15485,13 +16680,62 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>1. Hosting Türleri Karşılaştırma Tablosu
-2. Domain ve Hosting Ayrı Ayrı mı Alınır?
-3. Küçük İşletme İçin Hangi Hosting Seçilir?
+          <t>H2: Hosting Türleri Karşılaştırma Tablosu
+H2: Domain ve Hosting Ayrı Ayrı mı Alınır?
+H2: Küçük İşletme İçin Hangi Hosting Seçilir?
+H2: Hosting Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Hosting Nedir? Hangi Hizmetleri Sağlar?</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">EKLENECEK BÖLÜMLERİN YERİ: Karşılaştırma tablosu mevcut "Hosting Türleri Nelerdir?" başlığının içine; domain bölümü mevcut fark bölümünün yerine; seçim bölümü yazının sonuna, FAQ en sona.
+H2 · Hosting Türleri Karşılaştırma Tablosu: Sayfa "hosting" sorgusunda 31.2 ortalama sırada. Mevcut türler bölümü metin hâlinde; paylaşımlı, VPS, bulut ve adanmış sunucu satırlarında kaynak paylaşımı, tipik trafik kapasitesi ve kimin için uygun olduğu sütunlarından oluşan tabloya çevrilir. Tablo bölümün başında yer alır, açıklamalar altında kalır.
+H2 · Domain ve Hosting Ayrı Ayrı mı Alınır: "domain ve hosting nedir" sorgusu 4.6 sırada 409 Impression alıyor; mevcut fark bölümü iki cümlede kalıyor. Alan adı ile barındırmanın ilişkisi tek bir örnek üzerinden anlatılır (alan adı tabela, hosting dükkân), ardından "ikisi ayrı ayrı mı alınır" sorusu doğrudan yanıtlanır: ayrı alınabilir de, aynı sağlayıcıdan birlikte de alınabilir.
+H2 · Küçük İşletme İçin Hangi Hosting: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Türk Telekom</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un 3. sıradaki yazısı 1.239 kelime ve tek uzun bölüm; bizim yazımız 12 ara başlıkla zaten daha ayrıntılı. Eksik olan derinlik değil karar yardımı. Aylık ziyaretçi bandına göre üç senaryo verilir: tanıtım sitesi, blog, e-ticaret. Her senaryoda önerilen tür ve gerekçesi tek cümlede.
+GÖVDE DÜZENLEMESİ: "turkcell host" sorgusu 399 Impression ile 5.1 sırada geliyor; markanın barındırma hizmetine tek cümlelik bir iç bağlantı arama niyetini karşılar.
+DİKKAT: Fiyat bilgisi verilmez; kapasite ve kullanım senaryosu üzerinden anlatılır.</t>
+          </r>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>H3: Hosting Nedir?
+Hosting, bir web sitesinin dosyalarının internette sürekli erişilebilir olacak şekilde sunucuda barındırılması hizmetidir.
+H3: Host Ne Demek?
+Host, siteyi barındıran sunucuyu ya da bu barındırma hizmetini veren sağlayıcıyı ifade eder.
+H3: Domain ve Hosting Nedir, Farkı Nedir?
+Domain sitenin adresidir; hosting ise sitenin dosyalarının durduğu alandır. İkisi birlikte çalışır ancak ayrı hizmetlerdir.
+H3: Domain ve Hosting Ayrı Ayrı mı Alınır?
+Ayrı sağlayıcılardan alınabileceği gibi aynı sağlayıcıdan birlikte de alınabilir; birlikte alındığında yönlendirme ayarları hazır gelir.
+H3: Küçük Bir Site İçin Hangi Hosting Yeterli?
+Düşük ziyaretçili tanıtım siteleri ve bloglar için paylaşımlı hosting genellikle yeterlidir; trafik arttığında VPS veya bulut çözümlere geçilebilir.</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>1. domain nedir : https://www.turkcell.com.tr/blog/dijital-varligin-ilk-adimi-domain-alan-adi-nedir
    Anchor metni gövdede 8 kez geçmektedir; mevcut cümlelerden birine bağlantı verilebilir.
@@ -15499,7 +16743,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15520,7 +16764,7 @@
           </r>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15552,29 +16796,29 @@
           </r>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Fiyat bilgisi verilmemesi, kapasite ve kullanım senaryosu üzerinden anlatılması önerilir.</t>
         </is>
       </c>
-      <c r="Z5" s="7" t="n">
+      <c r="AB5" s="7" t="n">
         <v>8640</v>
       </c>
-      <c r="AA5" s="8" t="n">
+      <c r="AC5" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="AB5" s="9" t="inlineStr">
+      <c r="AD5" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>Bu soruda hosting satan siteler önde. Yazının ilk sıraya çıkması zor; beklenti buna göre kurulmalı.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="261" customHeight="1">
+    <row r="6" ht="317.5" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/nfc-nedir-nfc-ile-neler-yapilabilir</t>
@@ -15696,10 +16940,11 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t xml:space="preserve">1. NFC Etiketi Nedir, Ne İşe Yarar?
-2. NFC Kart Nedir?
-3. iPhone'da NFC Nasıl Açılır?
-4. </t>
+            <t xml:space="preserve">H2: NFC Etiketi Nedir, Ne İşe Yarar?
+H2: NFC Kart Nedir?
+H2: NFC Nasıl Açılır?
+H3: iPhone'da NFC Nasıl Açılır?
+H3: </t>
           </r>
           <r>
             <rPr>
@@ -15716,14 +16961,43 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t xml:space="preserve"> ve Xiaomi Cihazlarda NFC Nasıl Açılır?
-5. NFC Destekleyen Telefon Modelleri
-6. Telefonda NFC Anteni Nerede Bulunur?
+            <t xml:space="preserve"> Cihazlarda NFC Özelliği Nasıl Açılır?
+H3: Xiaomi ve Redmi Cihazlarda NFC Nasıl Açılır?
+H2: NFC Özelliği Olan Telefonlar Hangileri?
+H2: Telefonda NFC Alanı Neresi?
+H2: NFC Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: NFC Nedir, NFC ile Neler Yapılabilir?</t>
           </r>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>EKLENECEK BÖLÜMLERİN YERİ: Etiket ve kart bölümleri mevcut kullanım alanları bölümünün ardına; cihaz bazlı açma bölümleri mevcut "NFC Nasıl Açılır ve Kullanılır?" başlığının yerine; model listesi ve anten bölümü onun ardına.
+H2 · NFC Etiketi Nedir: "nfc etiketi nedir" sorgusu 3.835 Impression alıyor, sayfa 8.7 sırada ve tek click getiriyor; terim yazıda hiç geçmiyor. Bölümde etiketin ne olduğu, telefona nasıl okutulduğu ve üç kullanım örneği (ev otomasyonu, dijital kartvizit, Wi-Fi paylaşımı) verilir.
+H2 · NFC Kart Nedir: "nfc kart nedir" 832 Impression alıyor. Temassız banka kartı ve ulaşım kartının NFC ile ilişkisi tek paragrafta; kartın telefona okutulmasıyla ödeme yapılmasının farkı ayrı cümlede.
+H2 · NFC Nasıl Açılır: Üç H3. "nfc açma", "iphone nfc açma", "apple nfc açma" ve "nfc özelliği nasıl açılır redmi" kelimelerinin hiçbiri gövdede geçmiyor. Her H3'te iki-üç adımlık liste; iPhone tarafında NFC'nin arka planda sürekli açık olduğu ve ayrı bir düğme bulunmadığı bilgisi verilir, çünkü okuyucu bu ayarı arıyor ve bulamıyor.
+H2 · NFC Özelliği Olan Telefonlar: "nfc özelliği olan telefonlar" gövdede yok. Marka bazında model ailesi düzeyinde kısa tablo; tek tek model yerine aile adı kullanılır ve tabloya güncelleme tarihi konur.
+H2 · Telefonda NFC Alanı Neresi: "nfc alanı neresi" aramasının karşılığı yok. Antenin genellikle cihazın arka üst bölümünde bulunduğu ve okutma sırasında telefonun hangi noktasının temas etmesi gerektiği tek paragrafta.
+DİKKAT: Cihaz arayüzleri sürümle değişiyor; adımlar model ailesi düzeyinde verilir ve güncellenme tarihi görünür tutulur.</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>H3: NFC Ne Demek?
+NFC, cihazların birbirine birkaç santimetre yaklaştırıldığında kablosuz veri alışverişi yapmasını sağlayan yakın alan iletişim teknolojisidir.
+H3: NFC Nasıl Açılır?
+Android cihazlarda ayarlar menüsündeki bağlantılar bölümünden NFC seçeneği etkinleştirilir; iPhone modellerinde NFC arka planda sürekli açıktır ve ayrı bir ayar bulunmaz.
+H3: NFC Etiketi Nedir?
+NFC etiketi, telefon yaklaştırıldığında önceden tanımlanmış bir işlemi başlatan küçük bir çiptir.
+H3: NFC Kart Nedir?
+Temassız ödeme ve geçiş kartlarında bulunan, okuyucuya yaklaştırıldığında veri aktaran NFC çipli karttır.
+H3: Telefonumda NFC Var mı, Nasıl Anlarım?
+Cihaz ayarlarında bağlantılar bölümünde NFC seçeneğinin bulunması desteklendiğini gösterir; seçenek yoksa cihaz NFC desteklemiyor demektir.
+H3: Telefonda NFC Alanı Nerede?
+NFC anteni çoğu modelde cihazın arka yüzünün üst bölümünde yer alır; okutma sırasında bu bölgenin okuyucuya temas etmesi gerekir.</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>1. turkcell hotspot : https://www.turkcell.com.tr/blog/hotspot-ile-internet-paylasimi-ne-ise-yarar-nasil-acilir
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -15731,7 +17005,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15786,7 +17060,7 @@
           </r>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15819,23 +17093,23 @@
           </r>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>Cihaz arayüzleri sürümle değişiyor; adımların model ailesi düzeyinde verilmesi ve güncellenme tarihinin görünür tutulması önerilir.</t>
         </is>
       </c>
-      <c r="Z6" s="7" t="n">
+      <c r="AB6" s="7" t="n">
         <v>145620</v>
       </c>
-      <c r="AA6" s="8" t="n">
+      <c r="AC6" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="AB6" s="9" t="inlineStr">
+      <c r="AD6" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>Sayfa tanımı veriyor ama kullanıcı NFC'yi telefonunda açmaya çalışıyor. Açma adımları eklenirse arama karşılanmış oluyor.</t>
         </is>
@@ -15935,13 +17209,40 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>1. Gemini Türkçe Destekliyor mu?
-2. Gemini ile ChatGPT Arasındaki Fark
-3. Gemini Ücretsiz mi?
+          <t>H2: Gemini Yapay Zeka Ne İşe Yarar?
+H2: Gemini Türkçe Destekliyor mu?
+H2: Gemini ile ChatGPT Arasındaki Fark Nedir?
+H2: Gemini Ücretsiz mi?
+H2: Gemini Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Google Gemini Nedir? · Peki, Gemini’yi Kim Geliştirdi? · Gemini’ye Nasıl Ulaşılabilir? · Peki Gemini’nin GPT’den Farkı Ne?</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>EKLENECEK BÖLÜMLERİN YERİ: Kullanım bölümü mevcut tanıtım bölümünün ardına; Türkçe ve karşılaştırma bölümleri mevcut "Gemini ile Bard Arasındaki Fark" bölümünün yerine; ücret bölümü onun ardına.
+H2 · Gemini Yapay Zeka Ne İşe Yarar: "gemini yapay zeka" sorgusu 92.496 Impression ile 79 click getiriyor ve bu kalıp gövdede hiç geçmiyor. Bölümde dört kullanım senaryosu verilir: metin yazma ve özetleme, görsel yorumlama, kod yardımı, Google uygulamalarıyla entegre kullanım. Kalıbın giriş paragrafında ve bu H2'de doğal biçimde geçmesi sağlanır.
+H2 · Gemini Türkçe Destekliyor mu: "gemini türkçe" kelimesi gövdede yok. Dil desteği, Türkçe yanıt kalitesi ve arayüz dilinin nasıl değiştirileceği üç maddede.
+H2 · Gemini ile ChatGPT Farkı: Mevcut Bard karşılaştırması geçerliliğini yitirdi, Bard adı kullanımdan kalktı. Bölüm ChatGPT karşılaştırmasına çevrilir ve dört satırlık tabloya alınır: yanıt kaynağı ve güncel bilgiye erişim, görsel üretimi, dosya yükleme, ücretsiz sürüm sınırları. Tabloya gözlem tarihi eklenir.
+H2 · Gemini Ücretsiz mi: Ücretsiz ve ücretli sürüm ayrımı yazıda geçmiyor; sonuç sayfasındaki soru bloğunda da görünen bir arama. Ücretsiz sürümde neyin bulunduğu ve ücretli sürümün ne eklediği iki maddede.
+STRATEJİ NOTU: Sayfanın Impression'ı jenerik marka aramasından geliyor ve o aramada sonuç sayfasının ilk beş sırası Google'ın kendi adresleri. Kazanım kullanım ve karşılaştırma sorularında; yeni bölümler bu iki eksende kurgulanır.
+DİKKAT: Yapay zeka ürünlerinde sürüm ve fiyatlandırma sık değişiyor; tablo değerleri tarihiyle birlikte verilir.</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>H3: Gemini Nedir?
+Gemini, Google'ın metin, görsel ve kod gibi farklı içerik türlerini anlayıp yanıt üretebilen yapay zeka modeli ve uygulamasıdır.
+H3: Gemini Yapay Zeka Ne İşe Yarar?
+Metin yazma ve özetleme, görsel yorumlama, kod yardımı ve Google uygulamalarıyla birlikte çalışma gibi işlerde kullanılır.
+H3: Gemini Türkçe Destekliyor mu?
+Destekliyor. Türkçe soru sorulabilir, Türkçe yanıt alınabilir ve arayüz dili Türkçe olarak ayarlanabilir.
+H3: Gemini Ücretsiz mi?
+Temel sürüm ücretsiz kullanılabilir; gelişmiş modeller ve ek özellikler ücretli abonelikle sunulur.
+H3: Gemini ile ChatGPT Arasındaki Fark Nedir?
+İki servis de yapay zeka sohbet asistanıdır; farklar güncel bilgiye erişim biçimi, entegre oldukları uygulama ekosistemi ve ücretsiz sürüm sınırlarında ortaya çıkar.</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>1. yapay zeka mühendisliği : https://www.turkcell.com.tr/blog/yapay-zeka-muhendisligi-nedir
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -15953,12 +17254,12 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>Sonuç sayfasının ilk beş sırasını Google'ın kendi Gemini adresleri almaktadır; bilgilendirici içerik altıncı sıradan itibaren görünmektedir. Bu bandda GoIT ve TÜBİTAK Bilim Genç yazıları yer almakta, ikisi de kullanım senaryosu ve adım anlatımı içermektedir.</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>1. 'gemini yapay zeka' sorgusu 92.496 Impression ile 79 click getiriyor ve kelime gövdede hiç geçmiyor; giriş paragrafında ve bir ara başlıkta bu kalıbın kullanılması, sayfanın hâlihazırda göründüğü aramayı güçlendirir açıklanır
 2. 'gemini türkçe' kelimesi de gövdede yok; 'Gemini Türkçe Destekliyor mu?' başlığı altında dil desteği, Türkçe yanıt kalitesi ve arayüz dili üç maddeyle verilebilir
@@ -15967,29 +17268,29 @@
 5. Sayfanın Impression'ı jenerik marka aramasından geliyor ve o aramada sonuç sayfasının ilk beş sırası Google'ın kendi adresleri; kazanım kullanım ve karşılaştırma sorularında olduğu için yeni bölümler bu iki eksende kurgulanmalıdır</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Yapay zeka ürünlerinde sürüm ve fiyatlandırma sık değişiyor; tablo değerlerinin tarihiyle birlikte verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="Z7" s="7" t="n">
+      <c r="AB7" s="7" t="n">
         <v>77400</v>
       </c>
-      <c r="AA7" s="8" t="n">
+      <c r="AC7" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="AB7" s="9" t="inlineStr">
+      <c r="AD7" s="9" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>Yazı altı ayda 16.3 milyon impression alıp 2.125 click getirmiştir. Sorun içerikte değil, jenerik marka aramasının sonuç sayfasında: üst sıralar Google'ın kendi adreslerinde. Kazanım, kullanım ve karşılaştırma sorularında.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="261" customHeight="1">
+    <row r="8" ht="263.5" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni</t>
@@ -16085,13 +17386,63 @@
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>1. Ping Testi Nasıl Yapılır?
-2. İdeal Ping Değerleri Tablosu
-3. Ping Nasıl Düşürülür? Dört Adım
+          <t>H2: Ping Testi Nasıl Yapılır?
+H3: Komut Satırından Ping Testi
+H3: Hız Testi Siteleriyle Ping Ölçümü
+H2: İdeal Ping Değerleri Tablosu
+H2: Ping Nasıl Düşürülür? Dört Adım
+H2: Ping Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Ping Testi Nedir? Nasıl Yapılır?</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">EKLENECEK BÖLÜMLERİN YERİ: Test bölümü mevcut ölçüm bölümünün yerine; değer tablosu tanımın hemen ardına, sayfanın üst yarısına; düşürme bölümü mevcut "Ping Nasıl Düşürülür?" başlığının yerine.
+H2 · Ping Testi Nasıl Yapılır: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Türk Telekom</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un aynı konudaki yazısının başlığı "Ping Testi Nedir? Nasıl Yapılır?" ve sıralamayı bir test aracıyla alıyor. Bizim yazımızda ölçüm bölümü var ancak test adımı yok. İki H3'te komut satırı ve hız testi siteleri anlatılır; üçüncü yöntem olarak oyun içi gecikme göstergesi tek paragrafta verilir.
+H2 · İdeal Ping Değerleri Tablosu: "ping nedir" sorgusunda sayfa 3.7 ortalama sırada ancak 3.918 Impression'dan yalnız 1 click geliyor; bu tablo, yanıtın sonuç sayfasının üstünde verildiğine işaret ediyor. Giriş paragrafındaki tanım tek cümleye indirilir ve hemen altına değer tablosu konur: rekabetçi oyun 0-30 ms, genel oyun 30-60 ms, video görüşme 60-100 ms, 100 ms üzeri sorunlu. Her satırda hangi bağlantı türü için geçerli olduğu belirtilir.
+H2 · Ping Nasıl Düşürülür: Mevcut bölüm genel öneriler içeriyor. Dört somut adıma çevrilir: kablolu bağlantıya geçmek, 5 GHz bandı kullanmak, arka plan indirmelerini durdurmak, oyunda sunucu bölgesini yakın seçmek. Her adımın beklenen etkisi tek cümlede.
+DİKKAT: Ping değerleri bağlantı türüne göre değişiyor; verilen aralıkların hangi bağlantı için geçerli olduğu tabloda yazılmalıdır.</t>
+          </r>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>H3: Ping Nedir?
+Ping, gönderilen bir veri paketinin hedefe ulaşıp geri dönmesi için geçen süredir ve milisaniye cinsinden ölçülür.
+H3: İyi Bir Ping Değeri Kaç Olmalı?
+Çevrimiçi oyunlarda 30 ms altı çok iyi, 60 ms altı yeterli kabul edilir; 100 ms üzerindeki değerler gecikme olarak hissedilir.
+H3: Ping Testi Nasıl Yapılır?
+Komut satırından ping komutu çalıştırılarak ya da bir hız testi sitesi üzerinden ölçüm yapılarak test edilir.
+H3: Ping Nasıl Düşürülür?
+Kablolu bağlantıya geçilmesi, 5 GHz bandın kullanılması, arka plan indirmelerinin durdurulması ve yakın sunucu bölgesinin seçilmesi gecikmeyi azaltır.
+H3: Yüksek Ping Neden Olur?
+Ağ yoğunluğu, kablosuz bağlantı kalitesi, uzak sunucu konumu ve arka planda çalışan indirmeler yüksek pingin başlıca nedenleridir.</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>1. proxy : https://www.turkcell.com.tr/blog/proxy-nedir-internette-gizlilik-erisim-ve-guvenlik-uzerindeki-rolu
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -16099,7 +17450,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16137,7 +17488,7 @@
           </r>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16169,29 +17520,29 @@
           </r>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>Ping değerleri bağlantı türüne göre değişiyor; verilen aralıkların hangi bağlantı için geçerli olduğu belirtilmelidir.</t>
         </is>
       </c>
-      <c r="Z8" s="7" t="n">
+      <c r="AB8" s="7" t="n">
         <v>4400</v>
       </c>
-      <c r="AA8" s="8" t="n">
+      <c r="AC8" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="AB8" s="10" t="inlineStr">
+      <c r="AD8" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AC8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>Rakip bir test aracıyla sıralanıyor. Yazıya araç bağlantısı eklenmesi aradaki farkı açıklıyor.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="223" customHeight="1">
+    <row r="9" ht="236.5" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/type-c-teknolojisi-ne-ise-yarar-neden-bu-kadar-yaygin</t>
@@ -16300,10 +17651,11 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t xml:space="preserve">1. Type-C Nedir, Ne Demek?
-2. USB 3.2, USB4 ve Thunderbolt Arasındaki Fark
-3. Type-C ile Hızlı Şarj Nasıl Çalışır?
-4. Kablo Kalitesi Aktarım Hızını Nasıl Etkiler?
+            <t xml:space="preserve">H2: Type-C Nedir, Ne Demek?
+H2: USB 3.2, USB4 ve Thunderbolt Arasındaki Fark Nedir?
+H2: Type-C ile Hızlı Şarj Nasıl Çalışır?
+H2: Kablo Kalitesi Aktarım Hızını Nasıl Etkiler?
+H2: Type-C Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Type C Nedir? · Type C Girişe Sahip Olan Cihazlar Hangileridir? · USB Type-C’nin diğer USB türlerinden Farkı · USB Type-C’nin Avantajları ve USB Type-C’nin Dezavantajları · Type-C Girişli Telefonlara </t>
           </r>
           <r>
@@ -16327,13 +17679,37 @@
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
+          <t>EKLENECEK BÖLÜMLERİN YERİ: Tanım bölümü yazının başına, giriş paragrafından hemen sonra; sürüm tablosu mevcut avantajlar bölümünün ardına; şarj ve kablo bölümleri onun ardına.
+H2 · Type-C Nedir, Ne Demek: Sayfa "type c" sorgusunda 91.693 Impression alıyor ancak 7.8 sırada ve 23 click getiriyor; bu aramada üst sıralar ürün listeleyen mağazalarda. Bilgi tarafındaki kazanım "type c nedir" ve "type c ne demek" kalıplarında ve ikisi de gövdede birer kez geçiyor. Kalıplar ara başlığa taşınır ve bölüm iki cümlelik, bağlamdan bağımsız okunabilen bir tanımla açılır.
+H2 · USB 3.2, USB4 ve Thunderbolt Farkı: Sürümler yazıda ayrışmıyor; konunun en çok karıştırılan yanı bu. Dört sütunlu tablo: standart adı, veri hızı, güç aktarımı, görüntü desteği. Konnektör şekli ile standart arasındaki farkın aynı olmadığı tablonun altında tek cümleyle belirtilir.
+H2 · Type-C ile Hızlı Şarj: "Type-C ile hızlı şarj nasıl çalışır" sorusu yazıda yanıtlanmıyor. Power Delivery kademelerinin watt değerleriyle verildiği bir bölüm eklenir; cihazın da desteklemesi gerektiği notu ayrı cümlede.
+H2 · Kablo Kalitesi: Aynı görünen iki kablonun neden farklı hız verdiği somut bir okuyucu sorusu ve yazıda karşılığı yok. Kablo içindeki hat sayısı ve sertifikasyonun aktarım hızını nasıl sınırladığı tek paragrafta.
+DİKKAT: Ürün önerisi verilmez, teknik ayrım katmanında kalınır; şarj aleti ve kablo satın alma aramaları mağaza sayfalarına aittir.</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>H3: Type-C Nedir?
+Type-C, her iki yönde de takılabilen, veri aktarımı, şarj ve görüntü çıkışını tek kablo üzerinden destekleyen evrensel bağlantı standardıdır.
+H3: Type-C ile USB-C Aynı Şey mi?
+Evet. USB-C ve Type-C aynı konnektör tipini ifade eder.
+H3: Her Type-C Kablo Aynı Hızda mı?
+Değildir. Konnektör aynı olsa da desteklenen USB standardı ve kablo sertifikasyonu aktarım hızını belirler.
+H3: Type-C ile Hızlı Şarj Nasıl Çalışır?
+Power Delivery protokolü sayesinde şarj cihazı ile telefon anlaşır ve cihazın desteklediği en yüksek güç kademesinde şarj yapılır.
+H3: Type-C Girişten Görüntü Aktarılır mı?
+Cihaz ve kablo destekliyorsa aktarılır; her Type-C girişte görüntü çıkışı bulunmaz.</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
           <t>1. tethering nedir : https://www.turkcell.com.tr/blog/tethering-nedir-usb-wi-fi-ve-bluetooth-ile-internet-paylasimi-rehberi
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
 2. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16354,7 +17730,7 @@
           </r>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr">
         <is>
           <t>1. Sayfa 'type c' sorgusunda 91.693 Impression alıyor ancak 7.8 sırada ve 23 click getiriyor; bu aramada sonuç sayfasının üst sıraları ürün listeleyen mağazalarda olduğu için bilgi tarafında kazanım 'type c nedir' ve 'type c ne demek' kalıplarında. İkisi de gövdede birer kez geçiyor, ara başlığa taşınabilir
 2. USB-C sürümleri yazıda ayrışmıyor; USB 3.2, USB4 ve Thunderbolt 4 için veri hızı, güç aktarımı ve görüntü desteği sütunlarından oluşan bir tablo, konunun en çok karıştırılan yanını karşılar açıklanır
@@ -16362,29 +17738,29 @@
 4. Yazıda kablo kalitesinin aktarım hızını nasıl sınırladığı geçmiyor; aynı görünen iki kablonun farklı hız vermesi somut bir okuyucu sorusu ve tek paragrafla karşılanabilir</t>
         </is>
       </c>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>Ürün önerisi verilmemesi, teknik ayrım katmanında kalınması önerilir; şarj aleti ve kablo aramaları mağaza sayfalarına aittir.</t>
         </is>
       </c>
-      <c r="Z9" s="7" t="n">
+      <c r="AB9" s="7" t="n">
         <v>3400</v>
       </c>
-      <c r="AA9" s="8" t="n">
+      <c r="AC9" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="AB9" s="10" t="inlineStr">
+      <c r="AD9" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>Arayan kişi çoğunlukla kablo satın alıyor. Yazı bunu karşılamıyor; ürün sayfasına köprü kurmak daha gerçekçi.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="246" customHeight="1">
+    <row r="10" ht="263.5" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/vdsl-ve-adsl-nedir-internet-baglanti-turleri-arasindaki-farklar</t>
@@ -16488,12 +17864,60 @@
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>1. ADSL, VDSL ve Fiber Karşılaştırma Tablosu
-2. VDSL Modem Nedir, ADSL Modemden Farkı Ne?
-3. Hangi Bağlantı Kimin İçin Uygun?</t>
+          <t>H2: ADSL, VDSL ve Fiber Karşılaştırma Tablosu
+H2: VDSL Modem Nedir, ADSL Modemden Farkı Nedir?
+H2: Hangi Bağlantı Kimin İçin Uygun?
+H2: ADSL ve VDSL Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">EKLENECEK BÖLÜMLERİN YERİ: Karşılaştırma tablosu mevcut fark bölümünün yerine; modem bölümü onun ardına; seçim bölümü yazının sonuna.
+H2 · ADSL, VDSL ve Fiber Karşılaştırma Tablosu: "adsl vdsl farkı" sorgusu 3.3 ortalama sırada 3.014 Impression alıyor; sayfanın en güçlü olduğu alan ve mevcut karşılaştırma metin hâlinde. Tabloya çevrilir: indirme hızı bandı, yükleme hızı oranı, santrale mesafe hassasiyeti, tipik kullanım. Fiber sütunu eklenir, çünkü okuyucunun asıl sorusu üçlü karşılaştırma ve yazıda fiber karşılaştırmaya girmiyor.
+H2 · VDSL Modem Nedir: "vdsl modem nedir" sorgusu 1.878 Impression ile 4.5 sırada; modem tarafı yazıda tek cümlede geçiyor. Bölümde ADSL modemin VDSL bağlantıda çalışıp çalışmadığı, modem değişiminin ne zaman gerektiği ve uyumluluğun nereden kontrol edileceği üç maddede.
+H2 · Hangi Bağlantı Kimin İçin Uygun: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Vodafone</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un 1. sıradaki yazısı 485 kelime, bizim yazımız 1.092 kelimeyle iki katı ve daha kapsamlı. Eksik olan uzunluk değil karar yardımı. Ev tipi ve eş zamanlı kullanıcı sayısına göre üç senaryo verilir: tek kişilik kullanım, aile kullanımı, evden çalışma. Her senaryoda önerilen bağlantı ve gerekçesi tek cümlede.
+DİKKAT: Altyapı ve hız değerleri bölgeye göre değişiyor; altyapı sorgulamasının ilgili hizmet sayfasından yapılabileceği belirtilir.</t>
+          </r>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>H3: ADSL Nedir?
+ADSL, mevcut telefon hattı üzerinden internet bağlantısı sağlayan ve indirme hızı yükleme hızından yüksek olan bağlantı türüdür.
+H3: VDSL Nedir?
+VDSL, ADSL ile aynı bakır altyapıyı kullanan ancak daha yüksek hız sunabilen ve santrale yakınlıktan daha çok etkilenen bağlantı türüdür.
+H3: ADSL ile VDSL Arasındaki Fark Nedir?
+VDSL daha yüksek indirme ve yükleme hızı sunar; ancak santrale uzaklık arttıkça hız kaybı ADSL'e göre daha belirgin olur.
+H3: VDSL Modem Nedir, ADSL Modem Kullanılabilir mi?
+VDSL modem VDSL standardını destekleyen cihazdır; ADSL modemler VDSL bağlantıda çalışmaz ve modem değişimi gerekir.
+H3: Fiber ile VDSL Arasındaki Fark Nedir?
+Fiber bağlantı optik kablo kullanır ve mesafeden neredeyse etkilenmez; VDSL ise bakır hat üzerinden çalışır ve hız mesafeye göre düşer.</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="inlineStr">
         <is>
           <t>1. sabit internet nedir : https://www.turkcell.com.tr/blog/sabit-internet-nedir-turleri-avantajlari-ve-kullanim-alanlari
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -16501,7 +17925,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16573,7 +17997,7 @@
           </r>
         </is>
       </c>
-      <c r="X10" s="4" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16605,23 +18029,23 @@
           </r>
         </is>
       </c>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="AA10" s="4" t="inlineStr">
         <is>
           <t>Altyapı ve hız değerleri bölgeye göre değişiyor; sorgulama işleminin ilgili hizmet sayfasından yapılabileceği belirtilebilir.</t>
         </is>
       </c>
-      <c r="Z10" s="7" t="n">
+      <c r="AB10" s="7" t="n">
         <v>7160</v>
       </c>
-      <c r="AA10" s="8" t="n">
+      <c r="AC10" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="AB10" s="10" t="inlineStr">
+      <c r="AD10" s="10" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="inlineStr">
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>Rakipler aynı konuyu daha ayrıntılı işliyor ve dört kat trafik alıyor. Karşılaştırma tablosu farkı kapatabilir.</t>
         </is>
@@ -16736,14 +18160,64 @@
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>1. İdeal Jitter Değerleri Tablosu
-2. Net Jitter Ne Demek?
-3. Jitter, Ping ve Paket Kaybı Arasındaki Fark
-4. Jitter Nasıl Düşürülür?
+          <t>H2: İdeal Jitter Değerleri Tablosu
+H2: Net Jitter Ne Demek?
+H2: Jitter, Ping ve Paket Kaybı Arasındaki Fark Nedir?
+H2: Jitter Nasıl Düşürülür?
+H2: Jitter Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Jitter Nedir? · Jitter Nasıl Anlaşılır?</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">EKLENECEK BÖLÜMLERİN YERİ: Değer tablosu tanım bölümünün hemen ardına; net jitter ve karşılaştırma bölümleri onun ardına; düşürme bölümü mevcut çözüm bölümünün yerine.
+H2 · İdeal Jitter Değerleri Tablosu: "jitter kaç olmalı" sorgusu 866 Impression ile 7.8 sırada geliyor ve yazıda ideal aralık tablo hâlinde verilmiyor. Tablo satırları: video görüşme 30 ms altı, çevrimiçi oyun 20 ms altı, video akışı 50 ms altı, üzeri fark edilir bozulma. Her satırda hangi senaryo için geçerli olduğu yazılır.
+H2 · Net Jitter Ne Demek: "net jitter ne demek" ve "net jitter" sorguları birlikte 1.869 Impression alıyor ve terim gövdede geçmiyor. Ağ tarafındaki kullanımın ne anlama geldiği ve hız testi sonuçlarında bu adla görülmesi tek paragrafta.
+H2 · Jitter, Ping ve Paket Kaybı Farkı: Üç kavram yazıda net ayrılmıyor; konunun en sık karıştırılan yanı. Üç satırlık tablo: neyi ölçer, birimi, yüksek olduğunda ne hissedilir.
+H2 · Jitter Nasıl Düşürülür: Mevcut adımlar genel kalıyor. Dört somut maddeye çevrilir: kablolu bağlantı, modemde QoS ayarı, arka plan trafiğinin durdurulması, modem konumunun değiştirilmesi. Her maddenin hangi durumda işe yaradığı tek cümlede.
+GÖVDE DÜZENLEMESİ: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Vodafone</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un 1. sıradaki yazısında ana terim 55 kez, bizim yazımızda 23 kez geçiyor. Sayının artırılması değil, jitter kelimesinin ara başlıklarda ve tablo satırlarında da kullanılması öneriliyor.
+DİKKAT: Değerler bağlantı türüne ve uygulamaya göre değişiyor; aralıkların hangi senaryo için geçerli olduğu yazılmalıdır.</t>
+          </r>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>H3: Jitter Ne Demek?
+Jitter, ardışık veri paketlerinin varış süreleri arasındaki dalgalanmadır ve milisaniye cinsinden ölçülür.
+H3: Jitter Kaç Olmalı?
+Video görüşmeler için 30 ms, çevrimiçi oyunlar için 20 ms altındaki değerler iyi kabul edilir.
+H3: Net Jitter Ne Demek?
+Ağ üzerindeki gecikme dalgalanmasını ifade eder ve hız testi sonuçlarında bu adla görüntülenir.
+H3: Jitter ile Ping Arasındaki Fark Nedir?
+Ping gecikmenin kendisini ölçer; jitter ise bu gecikmenin ne kadar dalgalandığını gösterir.
+H3: Jitter Nasıl Düşürülür?
+Kablolu bağlantıya geçilmesi, modemde QoS ayarının kullanılması, arka plan trafiğinin durdurulması ve modem konumunun iyileştirilmesi dalgalanmayı azaltır.</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
         <is>
           <t>1. ping : https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni
    Anchor metni gövdede 1 kez geçmektedir; mevcut cümlelerden birine bağlantı verilebilir.
@@ -16751,7 +18225,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W11" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16772,7 +18246,7 @@
           </r>
         </is>
       </c>
-      <c r="X11" s="4" t="inlineStr">
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16805,29 +18279,29 @@
           </r>
         </is>
       </c>
-      <c r="Y11" s="4" t="inlineStr">
+      <c r="AA11" s="4" t="inlineStr">
         <is>
           <t>Değerler bağlantı türüne ve uygulamaya göre değişiyor; aralıkların hangi senaryo için geçerli olduğu yazılmalıdır.</t>
         </is>
       </c>
-      <c r="Z11" s="7" t="n">
+      <c r="AB11" s="7" t="n">
         <v>5350</v>
       </c>
-      <c r="AA11" s="8" t="n">
+      <c r="AC11" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="AB11" s="11" t="inlineStr">
+      <c r="AD11" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AC11" s="4" t="inlineStr">
+      <c r="AE11" s="4" t="inlineStr">
         <is>
           <t>Rakip aynı formatta ama birinci sırada. Fark, ideal değer tablosu gibi somut bilgide.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="236.5" customHeight="1">
+    <row r="12" ht="263.5" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/wi-fi-6-nedir-wi-fi-5-ile-arasindaki-temel-farklar</t>
@@ -16930,13 +18404,67 @@
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>1. Wi-Fi 6 Modem Nedir, Hangi Modemler Destekler?
-2. OFDMA, MU-MIMO ve Target Wake Time Nedir?
-3. Wi-Fi 6E ve Wi-Fi 7 ile Arasındaki Fark
+          <t>H2: Wi-Fi 6 Modem Nedir, Hangi Modemler Destekler?
+H2: OFDMA, MU-MIMO ve Target Wake Time Nedir?
+H3: OFDMA Ne İşe Yarar?
+H3: MU-MIMO Ne İşe Yarar?
+H3: Target Wake Time Ne İşe Yarar?
+H2: Wi-Fi 6 ile Wi-Fi 6E Arasındaki Fark Nedir?
+H2: Wi-Fi 7 Nedir, Beklemeye Değer mi?
+H2: Wi-Fi 6 Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Wi-Fi 6 Nedir? · Wi-Fi 6 Özellikleri · Wifi 6 Avantajları Nelerdir? · Wi-Fi 6 ve Wi-Fi 5 Arasındaki Farklar · Wi-Fi 6 Uyumlu Cihazlar Nelerdir?</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">EKLENECEK BÖLÜMLERİN YERİ: Modem bölümü mevcut karşılaştırma bölümünün ardına; teknik kavramlar bölümü onun ardına; 6E ve Wi-Fi 7 bölümleri yazının sonuna.
+H2 · Wi-Fi 6 Modem Nedir: "wifi 6 modem" ve "wifi 6 modem nedir" sorguları birlikte 4.132 Impression alıyor, sayfa 7.8 ve 4.1 sıralarda; modem tarafı yazıda tek cümlede geçiyor. Bölümde üç soru yanıtlanır: modemin Wi-Fi 6 desteklediği nereden anlaşılır, mevcut modem yeterli mi, cihaz tarafında da destek gerekiyor mu.
+H2 · OFDMA, MU-MIMO ve Target Wake Time: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Vodafone</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un 1. sıradaki yazısı 1.639 kelime ve 14 ara başlık taşıyor; bizim yazımız 1.146 kelime ve 11 başlık. Fark kapsam derinliğinde. Üç kavram üç H3'e ayrılır; her biri iki cümle: ne yapar, kullanıcı bunu nerede hisseder.
+H2 · Wi-Fi 6 ile Wi-Fi 6E Farkı: Okuyucu bu ayrımı sık soruyor ve yazıda geçmiyor. 6 GHz bandının eklenmesi ve bunun kalabalık ortamda ne değiştirdiği iki paragrafta.
+H2 · Wi-Fi 7: Standart adı ve getirdikleri kısaca; yeni modem alacak okuyucuya karar cümlesi verilir.
+GÖVDE DÜZENLEMESİ: "wifi 6 nedir" sorgusunda sayfa 3.4 sırada ve 48 click alıyor; giriş paragrafındaki tanımın tek cümleye indirilmesi ilk üçe yaklaşmak için en düşük maliyetli adım.
+DİKKAT: Cihaz uyumluluğu marka ve model ailesine göre değişiyor; genel ifadeler yerine standart adları kullanılır.</t>
+          </r>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>H3: Wi-Fi 6 Nedir?
+Wi-Fi 6, kalabalık ağlarda daha yüksek verim ve daha düşük gecikme sağlayan kablosuz ağ standardıdır.
+H3: Wi-Fi 6 Modem Nedir?
+Wi-Fi 6 standardını destekleyen ve bu standardın sunduğu verimi sağlayabilen modemdir; kutu ya da ürün sayfasındaki standart bilgisinden anlaşılır.
+H3: Wi-Fi 5 ile Wi-Fi 6 Arasındaki Fark Nedir?
+Wi-Fi 6 aynı anda bağlı çok sayıda cihazda daha kararlı hız sunar, gecikmeyi düşürür ve cihazların pil tüketimini azaltır.
+H3: Wi-Fi 6 İçin Telefonun da Desteklemesi Gerekir mi?
+Gerekir. Verimden yararlanabilmek için hem modemin hem de bağlanan cihazın Wi-Fi 6 desteklemesi gerekir.
+H3: Wi-Fi 6 ile Wi-Fi 6E Arasındaki Fark Nedir?
+Wi-Fi 6E, Wi-Fi 6'nın 6 GHz bandını da kullanabilen sürümüdür; bu band kalabalık ortamlarda daha az girişim sunar.</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>1. 4.5 g ile 5g arasındaki : https://www.turkcell.com.tr/blog/5g-ve-4g-arasindaki-farklar-sadece-hiz-mi-yoksa-yeni-bir-donem-mi
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -16944,7 +18472,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W12" s="4" t="inlineStr">
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16973,7 +18501,7 @@
           </r>
         </is>
       </c>
-      <c r="X12" s="4" t="inlineStr">
+      <c r="Z12" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17005,29 +18533,29 @@
           </r>
         </is>
       </c>
-      <c r="Y12" s="4" t="inlineStr">
+      <c r="AA12" s="4" t="inlineStr">
         <is>
           <t>Cihaz uyumluluğu marka ve model ailesine göre değişiyor; genel ifadeler yerine standart adları kullanılmalıdır.</t>
         </is>
       </c>
-      <c r="Z12" s="7" t="n">
+      <c r="AB12" s="7" t="n">
         <v>3370</v>
       </c>
-      <c r="AA12" s="8" t="n">
+      <c r="AC12" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="AB12" s="11" t="inlineStr">
+      <c r="AD12" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>Birinci sırada olmasına rağmen tıklama gelmiyor, çünkü arayan kişi modem arıyor. Cihaz bağlantısı eklenmeli.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="231" customHeight="1">
+    <row r="13" ht="263.5" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/mac-adresi-her-cihazin-kendine-ozgu-dijital-imzasi</t>
@@ -17134,15 +18662,65 @@
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>1. Windows ve macOS'ta MAC Adresi Nasıl Bulunur?
-2. Android ve iPhone'da MAC Adresi Nasıl Öğrenilir?
-3. Modem Arayüzünden Bağlı Cihazların MAC Adresi
-4. MAC Adresinden Cihaz Üreticisi Nasıl Bulunur?
-5. Telefonlarda MAC Adresi Neden Değişiyor?
+          <t>H2: MAC Adresi Nasıl Bulunur?
+H3: Windows ve macOS'ta MAC Adresi Sorgulama
+H3: Android ve iPhone'da MAC Adresi Nasıl Öğrenilir?
+H3: Modem Arayüzünden Bağlı Cihazların MAC Adresi
+H2: MAC Adresinden Cihaz Üreticisi Nasıl Bulunur?
+H2: Telefon MAC Adresi Nedir, Neden Değişiyor?
+H2: MAC Adresi Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: MAC Adresi Değiştirme Nasıl Yapılır?</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">EKLENECEK BÖLÜMLERİN YERİ: Adım bölümü mevcut tanım bölümünün hemen ardına; üretici ve rastgele MAC bölümleri onun ardına.
+H2 · MAC Adresi Nasıl Bulunur: "mac adresi sorgulama" ve "mac adresi nasıl bulunur" sorguları birlikte 1.800 Impression alıyor, sayfa 6.7 ve 9.2 sıralarda; adım anlatımı yazıda cihaz bazında ayrışmıyor. Üç H3'te beş platform için kısa adım listeleri verilir. Her liste üç adımı geçmez.
+H2 · MAC Adresinden Cihaz Üreticisi: "mac adresinden cihaz bulma" sorgusu 237 Impression alıyor ve yazıda karşılığı yok. Adresin ilk üç baytının üretici kodunu taşıdığı ve bu bilgiyle cihaz markasının belirlenebildiği tek paragrafta; tam cihaz kimliğinin bu yolla bulunamayacağı da aynı bölümde belirtilir.
+H2 · Telefon MAC Adresi Neden Değişiyor: "telefon mac adresi nedir" sorgusu 4.3 sırada 283 Impression alıyor. Telefonlarda gizlilik amacıyla rastgele MAC kullanıldığı, bu yüzden aynı cihazın farklı ağlarda farklı adres gösterdiği ve ayarın nereden kapatılabileceği anlatılır. Okuyucunun gördüğü değerin neden değiştiğini açıklayan tek bölüm bu.
+GÖVDE DÜZENLEMESİ: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Vodafone</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>'un 3. sıradaki yazısında ana terim 46, bizim yazımızda 43 kez geçiyor; kelime sıklığı yeterli, eksik olan cihaz bazında adım anlatımı.
+DİKKAT: Rastgele MAC kullanımı işletim sistemi sürümüne göre değişiyor; adımlar sürüm bilgisiyle verilir.</t>
+          </r>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>H3: MAC Adresi Nedir?
+MAC adresi, ağa bağlanan her cihazın ağ donanımına üretim aşamasında atanan benzersiz kimlik numarasıdır.
+H3: MAC Adresi Nasıl Bulunur?
+Windows'ta ağ ayrıntıları ekranından, telefonlarda ise Wi-Fi ağ bilgileri bölümünden görüntülenir.
+H3: Telefon MAC Adresi Nedir?
+Telefonun kablosuz ağ donanımına ait kimlik numarasıdır; gizlilik için çoğu cihazda ağ bazında rastgele üretilir.
+H3: MAC Adresi Neden Değişiyor?
+Modern işletim sistemleri gizlilik amacıyla her ağ için farklı bir rastgele MAC adresi kullanır; bu ayar cihazdan kapatılabilir.
+H3: MAC Adresinden Cihaz Bulunur mu?
+Adresin ilk bölümü üretici bilgisini taşır ve cihaz markası belirlenebilir; ancak bu yolla cihazın kimin olduğu tespit edilemez.</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
         <is>
           <t>1. kaybolan telefon nasıl bulunur : https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.
@@ -17150,7 +18728,7 @@
    Anchor metni gövdede geçmemektedir; konuya değinen bir cümle ya da alt başlık eklenirse bağlantı verilebilir.</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="Y13" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17171,7 +18749,7 @@
           </r>
         </is>
       </c>
-      <c r="X13" s="4" t="inlineStr">
+      <c r="Z13" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17203,23 +18781,23 @@
           </r>
         </is>
       </c>
-      <c r="Y13" s="4" t="inlineStr">
+      <c r="AA13" s="4" t="inlineStr">
         <is>
           <t>Rastgele MAC kullanımı işletim sistemi sürümüne göre değişiyor; adımların sürüm bilgisiyle verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="Z13" s="7" t="n">
+      <c r="AB13" s="7" t="n">
         <v>2510</v>
       </c>
-      <c r="AA13" s="8" t="n">
+      <c r="AC13" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="AB13" s="11" t="inlineStr">
+      <c r="AD13" s="11" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>Kullanıcı MAC adresini bulmaya çalışıyor. Cihaz bazında adım eklenirse sayfa aramayı karşılıyor.</t>
         </is>
@@ -17255,6 +18833,8 @@
       <c r="AA14" s="2" t="n"/>
       <c r="AB14" s="2" t="n"/>
       <c r="AC14" s="2" t="n"/>
+      <c r="AD14" s="2" t="n"/>
+      <c r="AE14" s="2" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -17294,6 +18874,8 @@
       <c r="AA15" s="12" t="n"/>
       <c r="AB15" s="12" t="n"/>
       <c r="AC15" s="12" t="n"/>
+      <c r="AD15" s="12" t="n"/>
+      <c r="AE15" s="12" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -17333,6 +18915,8 @@
       <c r="AA16" s="12" t="n"/>
       <c r="AB16" s="12" t="n"/>
       <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="12" t="n"/>
+      <c r="AE16" s="12" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -17372,6 +18956,8 @@
       <c r="AA17" s="12" t="n"/>
       <c r="AB17" s="12" t="n"/>
       <c r="AC17" s="12" t="n"/>
+      <c r="AD17" s="12" t="n"/>
+      <c r="AE17" s="12" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -17411,6 +18997,8 @@
       <c r="AA18" s="12" t="n"/>
       <c r="AB18" s="12" t="n"/>
       <c r="AC18" s="12" t="n"/>
+      <c r="AD18" s="12" t="n"/>
+      <c r="AE18" s="12" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -17450,15 +19038,17 @@
       <c r="AA19" s="12" t="n"/>
       <c r="AB19" s="12" t="n"/>
       <c r="AC19" s="12" t="n"/>
+      <c r="AD19" s="12" t="n"/>
+      <c r="AE19" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B16:AC16"/>
-    <mergeCell ref="B15:AC15"/>
-    <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="B19:AC19"/>
-    <mergeCell ref="B17:AC17"/>
-    <mergeCell ref="B18:AC18"/>
+    <mergeCell ref="B18:AE18"/>
+    <mergeCell ref="B16:AE16"/>
+    <mergeCell ref="B15:AE15"/>
+    <mergeCell ref="A1:AE1"/>
+    <mergeCell ref="B19:AE19"/>
+    <mergeCell ref="B17:AE17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>

--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -10401,7 +10401,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="304" customHeight="1">
+    <row r="5" ht="409" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Gizli Numara: Arama, Kapatma ve Numara Gizleme Ayarları</t>
@@ -10474,6 +10474,7 @@
 H3: iPhone'da Gizli Numara Kapatma
 H3: Operatör Servisiyle Kalıcı Engelleme
 H2: Gizli Numarayı Öğrenmek Mümkün mü?
+H2: Gizli Numaradan Gelen Aramalar Tehlikeli mi?
 H2: Numara Gizleme ile İlgili Yasal Sınırlar
 H2: Gizli Numara Hakkında Sıkça Sorulan Sorular</t>
         </is>
@@ -10503,6 +10504,10 @@
 Kullanıcı tarafından öğrenilemez. Rahatsız edici aramalarda numara ancak yasal başvuru sonrasında yetkili makamlarca tespit edilebilir.
 H3: iPhone'da Numara Gizleme Nereden Yapılır?
 Ayarlar bölümündeki telefon menüsünde yer alan arayan kimliğimi göster seçeneği kapatılarak yapılır.
+H3: Gizli Numaradan Gelen Aramalar Tehlikeli mi?
+Her gizli arama zararlı değildir; ancak kişisel bilgi, doğrulama kodu ya da ödeme talep eden aramalar dolandırıcılık girişimi olarak değerlendirilmelidir.
+H3: Gizli Numara Engelleme Kalıcı mı?
+Telefon ayarından yapılan engelleme cihaz sıfırlandığında kalkar; operatör tarafında tanımlanan engelleme ise talep edilene kadar sürer.
 H3: Gizli Numara Engellendiğinde Arayan Ne Duyar?
 Arama karşı tarafa iletilmez; arayan genellikle meşgul ya da ulaşılamıyor uyarısı alır.</t>
         </is>
@@ -10591,7 +10596,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="358" customHeight="1">
+    <row r="6" ht="409" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Yurt Dışından Getirilen Telefonun IMEI Kaydı: Ücret, Süre ve Adımlar</t>
@@ -10670,6 +10675,7 @@
 H2: IMEI Sorgulama Nasıl Yapılır?
 H3: e-Devlet Üzerinden IMEI Sorgulama
 H3: BTK IMEI Sorgulama Ekranı
+H2: IMEI Sorgulama Neden Önemlidir?
 H2: IMEI Kaydı Nasıl Yapılır? Adım Adım
 H2: Kayıtsız Telefon Kaç Gün Kullanılabilir?
 H2: IMEI Kaydı Sonrası Telefon Ne Zaman Açılır?
@@ -10702,6 +10708,10 @@
 Yurt dışından getirilen telefon, yasal kullanım süresi boyunca şebekede çalışır; süre dolduğunda kayıt yapılmadıysa cihaz şebekeye kapatılır.
 H3: IMEI Kaydı Yapıldıktan Sonra Telefon Ne Zaman Açılır?
 Kayıt işlemi tamamlandıktan sonra cihaz genellikle kısa süre içinde şebekeye açılır; açılmazsa cihazın yeniden başlatılması denenebilir.
+H3: IMEI Sorgulama Neden Önemlidir?
+Sorgulama, cihazın kayıtlı olup olmadığını ve şebekeye kapatılma riskini önceden gösterir; ikinci el alımda da ilk kontrol adımıdır.
+H3: Yurt Dışı Telefon Kayıt Ücreti Taksitle Ödenir mi?
+Harç ödemesi tek seferde yapılır; taksit imkânı ödeme yapılan kanalın kart koşullarına bağlıdır.
 H3: Bir Kişi Kaç Telefon Kaydettirebilir?
 Yurt dışından getirilen cihazların kaydı kişi başına ve belirli bir süre aralığında sınırlıdır; güncel sınır kayıt başvurusu sırasında görüntülenir.</t>
         </is>
@@ -10807,7 +10817,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="263.5" customHeight="1">
+    <row r="7" ht="371.5" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Google Güvenli Arama: Açma, Kapatma ve Aile Filtresi</t>
@@ -10864,6 +10874,8 @@
 H2: Güvenli Arama Nasıl Kapatılır?
 H3: Bilgisayarda Güvenli Arama Filtresi Kapatma
 H3: Telefonda Google Güvenli Arama Kapatma
+H2: iPhone'da Güvenli Arama Nasıl Kapatılır?
+H2: Operatör Ayarlarından Güvenli Arama Nasıl Kapatılır?
 H2: Güvenli Arama Kilidi Nasıl Açılır?
 H2: Çocuk Hesaplarında Güvenli Arama Ayarları
 H2: Operatörün Güvenli İnternet Hizmetiyle Farkı Nedir?
@@ -10893,7 +10905,11 @@
 H3: Güvenli Arama ile Güvenli İnternet Aynı Şey mi?
 Hayır. Güvenli arama Google sonuçlarını süzer, operatörün güvenli internet hizmeti ise bağlantı düzeyinde erişimi sınırlar.
 H3: Çocuk Hesabında Güvenli Arama Nasıl Açılır?
-Aile bağlantısı uygulamasından çocuğun hesabı seçilir ve içerik kısıtlamaları bölümünden güvenli arama etkinleştirilir.</t>
+Aile bağlantısı uygulamasından çocuğun hesabı seçilir ve içerik kısıtlamaları bölümünden güvenli arama etkinleştirilir.
+H3: iPhone'da Güvenli Arama Nasıl Kapatılır?
+Safari ya da Chrome üzerinden Google arama ayarları açılır ve güvenli arama seçeneği kapatılır; ekran süresi kısıtlaması varsa önce o kaldırılır.
+H3: Operatörün Güvenli İnternet Hizmeti Nasıl Kapatılır?
+Operatörün mobil uygulaması ya da çevrimiçi işlem merkezindeki güvenli internet bölümünden profil kapatılır; işlem abone doğrulaması gerektirir.</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -11159,7 +11175,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="263.5" customHeight="1">
+    <row r="9" ht="409" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Ekran Yansıtma: Telefondan Televizyona Görüntü Aktarma</t>
@@ -11211,15 +11227,43 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>H2: Ekran Yansıtma Nedir?
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">H2: Ekran Yansıtma Nedir?
 H2: Ekran Yansıtma Nasıl Yapılır?
 H3: iPhone Ekran Yansıtma Adımları
 H3: Android Telefonu Televizyona Yansıtma
 H2: Kablo ile Telefonu TV'ye Yansıtma
+H2: Televizyonda Ekran Yansıtma Özelliği Nasıl Açılır?
+H3: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Samsung</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve"> ve LG Televizyonlarda Yansıtma
+H3: Vestel, Arçelik ve Beko Televizyonlarda Yansıtma
+H2: Bilgisayardan Televizyona Ekran Yansıtma
 H2: iPhone Ekran Yansıtma TV Bulmuyorsa Ne Yapmalı?
 H2: Yansıtma Sırasında Görüntü Donuyorsa Neye Bakılmalı?
 H2: Yansıtma Yöntemleri Karşılaştırma Tablosu
 H2: Ekran Yansıtma Hakkında Sıkça Sorulan Sorular</t>
+          </r>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -11246,7 +11290,13 @@
 H3: Kablo ile Telefon TV'ye Nasıl Bağlanır?
 Telefonun bağlantı tipine uygun HDMI adaptörü kullanılır ve televizyonun HDMI girişi kaynak olarak seçilir.
 H3: Yansıtmada Görüntü Neden Takılıyor?
-Takılma çoğunlukla ağ yoğunluğundan kaynaklanır; modeme yakın olmak ve 5 GHz bandı kullanmak akıcılığı artırır.</t>
+Takılma çoğunlukla ağ yoğunluğundan kaynaklanır; modeme yakın olmak ve 5 GHz bandı kullanmak akıcılığı artırır.
+H3: Televizyonda Ekran Yansıtma Özelliği Nasıl Açılır?
+Televizyonun kaynak ya da ayarlar menüsünden ekran yansıtma özelliği etkinleştirilir; menü adı markaya göre Screen Mirroring, Smart View veya Miracast olarak geçer.
+H3: Eski Televizyonlarda Ekran Yansıtma Mümkün mü?
+Akıllı olmayan televizyonlarda kablosuz yansıtma çalışmaz; HDMI adaptörü ya da harici bir yayın cihazı kullanılarak görüntü aktarılabilir.
+H3: Bilgisayardan Televizyona Ekran Yansıtma Nasıl Yapılır?
+Windows'ta bağlan menüsünden televizyon seçilir; kablosuz bağlantı desteklenmiyorsa HDMI kablosu kullanılır.</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -11473,7 +11523,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="263.5" customHeight="1">
+    <row r="11" ht="371.5" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>İndirilenler Klasörü: Telefonda ve Bilgisayarda Dosya Bulma</t>
@@ -11532,6 +11582,7 @@
 H3: Safari İndirilenler Klasörü Nasıl Açılır?
 H2: Bilgisayarda İndirilenler Klasörü Nerede?
 H2: Tarayıcıya Göre İndirilenler Nereye Kaydedilir?
+H2: Uygulama İçi İndirilenler Nerede? Telegram, YouTube ve WhatsApp
 H2: İndirilen Dosya Bulunamıyorsa Ne Yapmalı?
 H2: Son İndirilenler Nasıl Görüntülenir?
 H2: İndirilenler Klasörü Nasıl Temizlenir?
@@ -11562,6 +11613,10 @@
 Tarayıcının indirme geçmişinden dosyanın konumu açılabilir; dosya adı dosya yöneticisinde aratılarak da bulunabilir.
 H3: Bilgisayarda İndirilenler Klasörü Nerede?
 Windows ve macOS'ta kullanıcı klasörünün altındaki indirilenler dizininde bulunur ve dosya yöneticisinin hızlı erişim bölümünden açılabilir.
+H3: Telegram'da İndirilenler Nerede?
+Telegram indirdiği dosyaları kendi klasörüne kaydeder; uygulamanın ayarlarından cihazın galerisine kaydetme seçeneği açılabilir.
+H3: YouTube'da İndirilenler Nerede?
+YouTube üzerinden indirilen videolar uygulama içinde saklanır ve yalnızca uygulamadan izlenebilir; cihazın dosya yöneticisinde görünmez.
 H3: İndirilenler Klasörü Temizlenirse Ne Olur?
 Klasördeki dosyalar silinir ve cihazda yer açılır; silinen dosyalar geri dönüşüm kutusu bulunmayan cihazlarda geri getirilemez.</t>
         </is>
@@ -11810,7 +11865,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="209.5" customHeight="1">
+    <row r="13" ht="409" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Spam Ne Demek? Spam Mesaj ve Aramaları Engelleme</t>
@@ -11860,6 +11915,8 @@
         <is>
           <t>H2: Spam Ne Demek?
 H2: Spam Arama Ne Demek?
+H2: Spam Numara Ne Demek?
+H2: Spam Bildir ve Spam Şüphesi Ne Anlama Gelir?
 H2: Spam Mesajlar Nasıl Engellenir?
 H2: Spam Aramalar Nasıl Engellenir?
 H2: Operatör Tarafındaki Engelleme Servisleri
@@ -11886,7 +11943,15 @@
 H3: Spam Mesajlar Nasıl Engellenir?
 Gönderen numara engellenir, mesaj spam olarak bildirilir ve ticari ileti izinleri izin yönetim sistemi üzerinden iptal edilir.
 H3: Gelen Aramanın Spam Olduğu Nasıl Anlaşılır?
-Tanımadık numaradan gelen, kişisel bilgi ya da doğrulama kodu isteyen aramalar spam olarak değerlendirilir; kod hiçbir koşulda paylaşılmamalıdır.</t>
+Tanımadık numaradan gelen, kişisel bilgi ya da doğrulama kodu isteyen aramalar spam olarak değerlendirilir; kod hiçbir koşulda paylaşılmamalıdır.
+H3: Spam Numara Ne Demek?
+Çok sayıda kullanıcı tarafından istenmeyen olarak bildirilen ve bu nedenle telefon uygulamasında uyarı etiketiyle gösterilen numaradır.
+H3: Spam Şüphesi Ne Demek?
+Telefonun arayan numarayı bilinen istenmeyen arama listeleriyle eşleştirdiğini ve bu aramanın büyük olasılıkla tanıtım ya da dolandırıcılık amaçlı olduğunu gösterir.
+H3: Spam Bildir Ne İşe Yarar?
+Bildirim, o numaranın istenmeyen olarak işaretlenmesini sağlar ve benzer aramaların hem kendinizde hem diğer kullanıcılarda uyarı almasına katkıda bulunur.
+H3: Spam Atmak Ne Demek?
+Aynı içeriğin çok sayıda kişiye ya da aynı kişiye tekrar tekrar gönderilmesini ifade eder.</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -11954,7 +12019,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="317.5" customHeight="1">
+    <row r="14" ht="409" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SSD, RAM ve Ekran Kartı: Bilgisayar Donanımı Rehberi</t>
@@ -12008,9 +12073,14 @@
         <is>
           <t>H2: RAM Nedir, Ne İşe Yarar?
 H2: Kaç GB RAM Yeterlidir?
+H2: RAM Plus ve Sanal RAM Nedir?
 H2: SSD Nedir, Ne İşe Yarar?
+H2: SSD Çeşitleri: SATA, NVMe ve M.2
 H2: SSD ile HDD Arasındaki Fark Nedir?
+H2: RAM Raporu Nedir, Nereden Bakılır?
 H2: Ekran Kartı Nedir, Ne İşe Yarar?
+H3: Dahili ve Harici Ekran Kartı Arasındaki Fark
+H3: Paylaşımlı ve Onboard Ekran Kartı Ne Demek?
 H2: Anakart Nedir?
 H2: Bilgisayar Donanımı Karşılaştırma Tablosu
 H2: Bilgisayar Yavaşladığında Hangi Donanıma Bakılmalı?
@@ -12044,6 +12114,18 @@
 SSD çok daha hızlı, sessiz ve darbeye dayanıklıdır; HDD ise aynı fiyata daha yüksek kapasite sunar.
 H3: Ekran Kartı Ne İşe Yarar?
 Ekran kartı görüntünün işlenmesinden sorumludur; oyun, video düzenleme ve grafik işlerinde performansı doğrudan etkiler.
+H3: RAM Raporu Nedir?
+RAM raporu, telefonun bellek kullanımını ve hangi uygulamaların ne kadar bellek tükettiğini gösteren tanılama ekranıdır.
+H3: Dahili ve Harici Ekran Kartı Arasındaki Fark Nedir?
+Dahili ekran kartı işlemciyle bütünleşik çalışır ve sistem belleğini kullanır; harici ekran kartı ayrı bir bileşendir ve kendi belleğine sahiptir.
+H3: Paylaşımlı Ekran Kartı Ne Demek?
+Ekran kartının ayrı bir belleği olmadığını, sistem RAM'inin bir bölümünü görüntü işleme için kullandığını ifade eder.
+H3: RAM Plus Nedir?
+RAM Plus, telefonun depolama alanının bir bölümünü geçici olarak bellek gibi kullanmasını sağlayan sanal RAM özelliğidir.
+H3: Sanal RAM Gerçek RAM'in Yerini Tutar mı?
+Tutmaz. Depolama birimi bellekten yavaştır; sanal RAM yalnızca yoğun anlarda ek nefes alanı sağlar.
+H3: NVMe ile SATA SSD Arasındaki Fark Nedir?
+NVMe diskler SATA'ya göre çok daha yüksek okuma ve yazma hızı sunar; M.2 ise diskin fiziksel bağlantı biçimini tanımlar.
 H3: Bilgisayar Yavaşladığında Önce Neye Bakılmalı?
 Açılış ve dosya erişimi yavaşsa depolama birimine, aynı anda çok uygulama açıkken takılma yaşanıyorsa RAM kapasitesine bakılır.</t>
         </is>
@@ -12088,7 +12170,8 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Ürün önerisi verilmemeli; bilgi katmanında kalınmalıdır.</t>
+          <t>Ürün önerisi verilmemeli; bilgi katmanında kalınmalıdır.
+NİYET NOTU: 'ram krizi' (500) bellek fiyatlarına ilişkin haber niyetlidir ve bu yazının kapsamı dışındadır.</t>
         </is>
       </c>
       <c r="R14" s="8" t="n">
@@ -12115,7 +12198,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="263.5" customHeight="1">
+    <row r="15" ht="371.5" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>E-İmza Nasıl Alınır?</t>
@@ -12166,6 +12249,8 @@
 H2: E-İmza Nasıl Alınır? Adım Adım
 H2: E-İmza Başvurusu İçin Gereken Belgeler
 H2: E-İmza ile Mobil İmza Arasındaki Fark Nedir?
+H2: Mobil İmza e-Devlet Üzerinden Nasıl Alınır?
+H2: E-İmza Ücreti Ne Kadar, Ücretsiz Alınabilir mi?
 H2: E-İmza Nerelerde Kullanılır?
 H2: E-İmza Hakkında Sıkça Sorulan Sorular</t>
         </is>
@@ -12192,7 +12277,11 @@
 H3: E-İmza Başvurusu İçin Hangi Belgeler Gerekir?
 Bireysel başvurularda kimlik belgesi yeterlidir; kurumsal başvurularda ayrıca yetki belgesi ve şirket bilgileri istenir.
 H3: E-İmza Nerelerde Kullanılır?
-e-Devlet işlemlerinde, resmî yazışmalarda, sözleşme onaylarında ve kurumsal imza akışlarında kullanılır.</t>
+e-Devlet işlemlerinde, resmî yazışmalarda, sözleşme onaylarında ve kurumsal imza akışlarında kullanılır.
+H3: Mobil İmza e-Devlet'ten Nasıl Alınır?
+Mobil imza başvurusu operatör üzerinden yapılır; hat sahibi doğrulandıktan sonra imza e-Devlet girişlerinde kullanılabilir hâle gelir.
+H3: E-İmza Ücretsiz Alınabilir mi?
+Sertifika hizmeti ücretlidir; bazı kurumlar çalışanlarına ya da üyelerine kurumsal anlaşma kapsamında sağlayabilir.</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -12260,7 +12349,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="209.5" customHeight="1">
+    <row r="16" ht="371.5" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Taahhüt Ne Demek?</t>
@@ -12310,8 +12399,10 @@
         <is>
           <t>H2: Taahhüt Ne Demek?
 H2: Taahhütlü Ne Demek, Taahhütsüzden Farkı Nedir?
-H2: Taahhüt Süresi Nasıl Öğrenilir?
+H2: Taahhüt Etmek Ne Demek?
+H2: Taahhüt Süresi ve Taahhüt Tarihi Nasıl Öğrenilir?
 H2: Taahhüt Süresi Dolmadan Çıkılırsa Ne Olur?
+H2: Taahhüt Bittiğinde Ne Olur?
 H2: Taahhüt Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
@@ -12335,7 +12426,13 @@
 H3: Taahhüt Süresi Nereden Öğrenilir?
 Taahhüt süresi operatörün mobil uygulaması ya da çevrimiçi işlem merkezindeki abonelik bilgileri bölümünden görüntülenir.
 H3: Taahhüt Bitmeden Çıkılırsa Ne Olur?
-Kalan süreye bağlı olarak sözleşmede belirtilen cayma bedeli uygulanır; tutar kalan ay sayısına göre değişir.</t>
+Kalan süreye bağlı olarak sözleşmede belirtilen cayma bedeli uygulanır; tutar kalan ay sayısına göre değişir.
+H3: Taahhüt Etmek Ne Demek?
+Bir hizmeti belirli bir süre boyunca kullanacağını sözleşmeyle beyan etmek anlamına gelir.
+H3: Taahhüt Tarihi Ne Demek?
+Taahhüdün başladığı ve biteceği tarihleri ifade eder; abonelik bilgileri ekranında görüntülenir.
+H3: Taahhüt Bittiğinde Ne Olur?
+Süre dolduğunda bağlayıcılık sona erer; tarife çoğunlukla taahhütsüz koşullarla devam eder ve dilendiğinde değiştirilebilir.</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -12388,7 +12485,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="277" customHeight="1">
+    <row r="17" ht="371.5" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Konum Paylaşma ve Numaradan Konum Bulma</t>
@@ -12448,6 +12545,7 @@
 H2: Canlı Konum Nasıl Paylaşılır, Ne Kadar Sürer?
 H2: Neredeyim? Kendi Konumumu Nasıl Bulurum?
 H2: Numaradan Konum Bulma Gerçekten Mümkün mü?
+H2: Operatörler Numaradan Konum Bulma Hizmeti Veriyor mu?
 H2: Konum Paylaşımı Nasıl Durdurulur?
 H2: Konum Servisleri Pili Ne Kadar Tüketir?
 H2: Konum Paylaşma Hakkında Sıkça Sorulan Sorular</t>
@@ -12477,6 +12575,10 @@
 Yalnızca telefon numarasıyla bir kişinin konumunu bulmak kullanıcı tarafından mümkün değildir; konum ancak karşı taraf paylaştığında görülebilir.
 H3: Konum Paylaşımı Nasıl Durdurulur?
 Paylaşımın yapıldığı uygulamadaki konum ekranından durdurma seçeneği kullanılır ya da cihaz ayarlarından uygulamanın konum izni kapatılır.
+H3: Operatörler Numaradan Konum Bulma Hizmeti Veriyor mu?
+Bireysel kullanıcıya açık böyle bir hizmet bulunmamaktadır; konum bilgisi yalnızca yasal talep üzerine yetkili makamlarla paylaşılır.
+H3: Telefondan Konum Nasıl Atılır?
+Mesajlaşma uygulamasının ek menüsünden konum seçilir, harita üzerinde nokta onaylanır ve gönderilir.
 H3: Konum Servisleri Pili Çok mu Tüketir?
 Sürekli açık konum izni pil tüketimini artırır; iznin yalnızca uygulama kullanılırken verilmesi tüketimi azaltır.</t>
         </is>
@@ -13336,7 +13438,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="317.5" customHeight="1">
+    <row r="23" ht="371.5" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>eSIM Nedir, Nasıl Aktive Edilir?</t>
@@ -13422,6 +13524,8 @@
 Son yılların üst ve orta segment modellerinin büyük bölümü eSIM destekler; desteğin olup olmadığı cihaz ayarlarındaki hücresel bağlantı menüsünden kontrol edilebilir.
 H3: Mevcut Hat eSIM'e Taşınabilir mi?
 Evet. Numara değişmeden fiziksel SIM eSIM'e dönüştürülebilir; işlem sırasında hat kısa süre kapalı kalabilir.
+H3: eSIM Kart Nedir?
+eSIM kart, fiziksel bir kart yerine cihaza gömülü çip üzerinde tanımlanan dijital SIM kartı ifade eder.
 H3: eSIM Yurt Dışında Kullanılabilir mi?
 Kullanılabilir. eSIM destekleyen cihazlarda ana hat açık kalırken ikinci hat olarak yerel bir eSIM paketi de tanımlanabilir.</t>
         </is>
@@ -13492,7 +13596,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="263.5" customHeight="1">
+    <row r="24" ht="371.5" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Telefon Nasıl Sıfırlanır?</t>
@@ -13544,6 +13648,7 @@
 H2: Sıfırlama Öncesi Yedekleme Nasıl Yapılır?
 H2: Android Telefon Nasıl Sıfırlanır?
 H2: iPhone Nasıl Sıfırlanır?
+H2: Şifresi Unutulan Telefon Nasıl Sıfırlanır?
 H2: Fabrika Ayarlarına Sıfırlama Sonrası Hesap Doğrulaması
 H2: Telefon Sıfırlama Hakkında Sıkça Sorulan Sorular</t>
         </is>
@@ -13562,7 +13667,13 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>H3: Telefon Nasıl Sıfırlanır?
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">H3: Telefon Nasıl Sıfırlanır?
 Ayarlar menüsündeki sistem ya da genel bölümünden fabrika ayarlarına sıfırlama seçeneği açılır ve ekrandaki onaylar tamamlanır.
 H3: Telefon Sıfırlanınca Veriler Silinir mi?
 Evet. Cihazdaki fotoğraflar, uygulamalar ve ayarlar tamamen silinir; yalnızca buluta yedeklenmiş veriler geri getirilebilir.
@@ -13570,8 +13681,30 @@
 Bulut yedeği alınmalı ve cihazdan hesap çıkışı yapılmalıdır; aksi hâlde sıfırlama sonrası etkinleştirme kilidi devreye girer.
 H3: Telefon Açılmıyorsa Nasıl Sıfırlanır?
 Cihaz kurtarma moduna alınarak sıfırlama yapılabilir; tuş kombinasyonu markaya göre değişir.
+H3: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Samsung</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve"> Telefon Nasıl Sıfırlanır?
+Ayarlar bölümündeki genel yönetim menüsünden sıfırla seçeneği açılır ve fabrika ayarlarına sıfırla adımı tamamlanır.
+H3: Şifresi Unutulan Telefon Nasıl Sıfırlanır?
+Cihaz kurtarma moduna alınarak sıfırlanabilir; sıfırlama sonrasında cihaza en son giriş yapılan hesabın şifresi istenir.
 H3: Sıfırlama Sonrası Hesap Şifresi Neden İsteniyor?
 Cihaz güvenliği için etkinleştirme kilidi devrededir; kilidin kalkması için cihaza en son giriş yapılan hesabın şifresi gerekir.</t>
+          </r>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -13770,7 +13903,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="263.5" customHeight="1">
+    <row r="26" ht="409" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Yenilenmiş Telefon Ne Demek? Garanti ve Kalite Sınıfları</t>
@@ -13824,6 +13957,7 @@
 H2: Yenilenmiş Telefon Kalite Sınıfları Nelerdir?
 H2: Yenilenmiş Telefonda Garanti Süresi Ne Kadar?
 H2: Yenilenmiş iPhone Alınır mı?
+H2: Yenilenmiş Telefon Nereden Alınır?
 H2: Satın Almadan Önce Kontrol Listesi
 H2: Yenilenmiş Telefon Hakkında Sıkça Sorulan Sorular</t>
         </is>
@@ -13852,7 +13986,13 @@
 H3: Yenilenmiş iPhone Alınır mı?
 Garanti belgesi, IMEI kaydı ve pil sağlığı kontrol edildiğinde uygun bir seçenek olabilir; bu üç başlık satın alma öncesinde sorgulanmalıdır.
 H3: Yenilenmiş Telefonun Kalite Sınıfı Ne Anlama Gelir?
-Kalite sınıfı cihazın dış görünümündeki kullanım izlerini tanımlar; işlevsel performans tüm sınıflarda kontrol edilmiş olur.</t>
+Kalite sınıfı cihazın dış görünümündeki kullanım izlerini tanımlar; işlevsel performans tüm sınıflarda kontrol edilmiş olur.
+H3: A Kalite Yenilenmiş Telefon Ne Demek?
+Dış yüzeyinde belirgin kullanım izi bulunmayan, yeniye en yakın görünümdeki cihazları tanımlar.
+H3: B ve C Kalite Yenilenmiş Telefon Ne Demek?
+B sınıfında hafif, C sınıfında daha belirgin kullanım izleri bulunur; iki sınıfta da cihazın işlevleri kontrol edilmiştir.
+H3: Yenilenmiş Telefon Nereden Alınır?
+Yetkili yenileme merkezleri ve bu merkezlerle çalışan satış kanalları üzerinden alınır; faturanın ve garanti belgesinin verildiği doğrulanmalıdır.</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -13921,7 +14061,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="263.5" customHeight="1">
+    <row r="27" ht="371.5" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>AirTag Nedir ve Nasıl Çalışır?</t>
@@ -14000,6 +14140,10 @@
 Anahtar, cüzdan, çanta ve bavul gibi sık kaybolan eşyaların yerinin bulunmasında kullanılır.
 H3: Yanımda Bilinmeyen Bir AirTag Varsa Ne Olur?
 Telefon bir süre sonra bilinmeyen bir takip cihazının sizinle hareket ettiği uyarısını verir; cihaz bulunup devre dışı bırakılabilir.
+H3: AirTag Ne İşe Yarar, Nasıl Faydası Olur?
+Eşyanın son görüldüğü konumu haritada gösterir, yakındayken ses çıkararak bulunmasını sağlar ve kaybolduğunda kayıp moduna alınabilir.
+H3: AirTag 2. Nesil Nedir?
+İlk sürümün yerini alan, konum hassasiyeti ve menzili geliştirilmiş modeli tanımlar; kurulum ve kullanım mantığı aynıdır.
 H3: AirTag Android Telefonlarda Çalışır mı?
 AirTag kurulumu ve takibi Apple cihazlarla yapılır; Android kullanıcıları ise bilinmeyen takip cihazlarını tarama uygulamasıyla tespit edebilir.</t>
         </is>
@@ -14069,7 +14213,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="209.5" customHeight="1">
+    <row r="28" ht="263.5" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t>OEM Ne Demek?</t>
@@ -14142,7 +14286,9 @@
 H3: OEM ile Orijinal Ürün Arasındaki Fark Nedir?
 Orijinal ürün marka ambalajıyla ve marka garantisiyle satılır; OEM ürün sade ambalajla gelir ve garanti çoğunlukla satıcı tarafından verilir.
 H3: OEM Yazılım Ne Demek?
-Cihazla birlikte önceden kurulu gelen ve o cihaza bağlı olan yazılım lisansıdır; başka bir cihaza aktarılamaz.</t>
+Cihazla birlikte önceden kurulu gelen ve o cihaza bağlı olan yazılım lisansıdır; başka bir cihaza aktarılamaz.
+H3: OEM Paket Ne Demek?
+Ürünün perakende kutusu ve aksesuarları olmadan, sade ambalajda satılan hâlidir; içerik aynı, sunum farklıdır.</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -14210,7 +14356,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="263.5" customHeight="1">
+    <row r="29" ht="371.5" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>KVKK Nedir? Kişisel Verilerin Korunması Kanunu</t>
@@ -14261,6 +14407,8 @@
 H2: Kişisel Veri Nedir, Hangi Bilgiler Kişisel Veri Sayılır?
 H2: Özel Nitelikli Kişisel Veri Ne Demek?
 H2: KVKK Kapsamında Veri Sahibinin Hakları Nelerdir?
+H2: KVKK İzni ve Aydınlatma Metni Nedir?
+H2: KVKK Onayı Geri Alınabilir mi?
 H2: Kişisel Verilerin Korunması İçin Ne Yapılabilir?
 H2: KVKK Hakkında Sıkça Sorulan Sorular</t>
         </is>
@@ -14287,6 +14435,10 @@
 Ad, soyad, telefon numarası, e-posta adresi, konum bilgisi ve IP adresi gibi kişiyi belirli ya da belirlenebilir kılan her türlü bilgi kişisel veridir.
 H3: KVKK Kapsamında Hangi Haklara Sahibim?
 Verilerinizin işlenip işlenmediğini öğrenme, düzeltilmesini veya silinmesini isteme, aktarıldığı tarafları öğrenme ve işleme faaliyetine itiraz etme haklarınız bulunur.
+H3: KVKK İzni Nedir?
+Kişisel verilerin belirli bir amaçla işlenebilmesi için kişiden alınan açık rızadır; hangi verinin ne amaçla işleneceği aydınlatma metninde belirtilir.
+H3: KVKK Onayı Geri Alınabilir mi?
+Alınabilir. Açık rıza istenildiği zaman geri çekilebilir ve bu durumda ilgili veri işleme faaliyeti durdurulur.
 H3: Kişisel Verilerimin Silinmesini Nasıl İsterim?
 Verinin işlendiği kuruma başvurularak silme talebi iletilir; kurum yasal süre içinde talebi sonuçlandırmakla yükümlüdür.</t>
         </is>
@@ -14356,7 +14508,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="263.5" customHeight="1">
+    <row r="30" ht="371.5" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Telefon Neden Isınır?</t>
@@ -14436,6 +14588,10 @@
 Kılıf çıkarılabilir, arka plan uygulamaları kapatılabilir, ekran parlaklığı düşürülebilir ve cihaz şarjdayken kullanılmayabilir.
 H3: Telefon Isınması Pile Zarar Verir mi?
 Sürekli yüksek sıcaklık pil ömrünü kısaltır; bu nedenle cihazın uzun süre sıcak kalmasından kaçınılmalıdır.
+H3: Telefon Neden Çok Isınır?
+Aynı anda çalışan yoğun uygulamalar, uzun süreli video ve oyun kullanımı, zayıf şebeke sinyali ve yüksek ortam sıcaklığı bir araya geldiğinde ısınma belirginleşir.
+H3: Telefon Şarj Olurken Neden Isınır?
+Şarj sırasında pile aktarılan enerjinin bir bölümü ısıya dönüşür; hızlı şarjda bu ısı daha yüksek olur ve belirli bir düzeye kadar normaldir.
 H3: Telefon Kullanılmazken Isınıyorsa Ne Yapmalı?
 Arka planda çalışan uygulamalar kontrol edilmeli; sorun sürüyorsa ve pilde şişme varsa cihaz kullanılmadan yetkili servise başvurulmalıdır.</t>
         </is>
@@ -14523,7 +14679,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="209.5" customHeight="1">
+    <row r="31" ht="317.5" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Müşteri Numarası Nedir, Nereden Öğrenilir?</t>
@@ -14574,6 +14730,8 @@
 H2: Müşteri Numarası Nereden Öğrenilir?
 H3: Faturada Müşteri Numarası Nerede Yazar?
 H3: Mobil Uygulamadan Müşteri Numarası Öğrenme
+H2: Bankacılıkta Müşteri Numarası Nedir?
+H2: Telekom Hizmetlerinde Müşteri Numarası Nedir?
 H2: Müşteri Numarası ile Abone Numarası Arasındaki Fark Nedir?
 H2: Müşteri Numarası Hangi İşlemlerde Kullanılır?
 H2: Müşteri Numarası Hakkında Sıkça Sorulan Sorular</t>
@@ -14582,7 +14740,10 @@
       <c r="L31" s="4" t="inlineStr">
         <is>
           <t>TON: Tanım ve konum gösterme. Okuyucu bir işlem sırasında numarayı arıyor; ilk paragraf tanımı verir, ikinci bölüm doğrudan nereden bulunacağını söyler.
-H2 · Müşteri Numarası Nedir: Aboneye özel, hattan bağımsız kimlik numarası olduğu iki cümlede.
+NİYET NOTU: Soru kelimesi taramasında bu terimin aramalarının büyük bölümü bankacılık kaynaklıdır (yapı kredi 2.400, kurumsal 700, bireysel 700, banka 600, firma 500, halkbank 450). Telekom niyeti azınlıktadır. Aynı ayrımı rakip blog da yapmakta ve konuyu bankacılık ile telekom başlıkları altında ikiye bölmektedir. Yazı bu nedenle terimi önce genel olarak tanımlar, sonra iki alanı ayrı bölümlerde ele alır; jenerik hacmin tamamının bu yazıyla karşılanamayacağı hesaba katılmalıdır.
+H2 · Müşteri Numarası Nedir: Kuruma kayıtlı kişiyi tanımlayan, ürün ve hat sayısından bağımsız kimlik numarası olduğu iki cümlede.
+H2 · Bankacılıkta Müşteri Numarası: Bankaların internet ve mobil şubeye girişte istediği numara; kartın arkasında, sözleşmede ve mobil uygulamada nerede göründüğü. Bireysel, kurumsal ve firma müşteri numarası ayrımı tek paragrafta.
+H2 · Telekom Hizmetlerinde Müşteri Numarası: Operatör tarafındaki karşılığı ve hangi işlemlerde istendiği.
 H2 · Nereden Öğrenilir: İki H3. Faturada hangi bölümde yer aldığı ve uygulamada hangi ekranda göründüğü. Ekran yolları ürün ekibiyle doğrulanır.
 H2 · Abone Numarası Farkı: İki satırlık tablo: neyi tanımlar, kaç tane olur. Bir müşterinin birden çok hattı olabileceği ama tek müşteri numarası bulunduğu net yazılır.
 H2 · Hangi İşlemlerde Kullanılır: Fatura ödeme, başvuru takibi, çağrı merkezi doğrulaması üç madde.
@@ -14598,7 +14759,11 @@
 H3: Müşteri Numarası ile Abone Numarası Aynı mı?
 Değildir. Abone numarası hatta özeldir; müşteri numarası ise kişiye özeldir ve birden çok hat aynı müşteri numarasına bağlı olabilir.
 H3: Müşteri Numarası Nerelerde Kullanılır?
-Fatura ödemelerinde, başvuru takibinde ve çağrı merkezi görüşmelerinde kimlik doğrulaması amacıyla kullanılır.</t>
+Fatura ödemelerinde, başvuru takibinde ve çağrı merkezi görüşmelerinde kimlik doğrulaması amacıyla kullanılır.
+H3: Bankacılıkta Müşteri Numarası Nedir?
+Bankanın her müşterisine verdiği ve internet ile mobil şube girişlerinde kullanılan numaradır; kart arkasında, sözleşmede ve mobil uygulamada görüntülenir.
+H3: Bireysel ve Kurumsal Müşteri Numarası Farkı Nedir?
+Bireysel numara kişiye, kurumsal numara ise firmaya tanımlanır; kurumsal işlemlerde ayrıca yetkili kullanıcı bilgisi istenir.</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -14623,7 +14788,8 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>Tanım sorgusudur; hesap ekranına yönlendirme ürün ekibiyle doğrulanmalıdır.</t>
+          <t>Tanım sorgusudur; hesap ekranına yönlendirme ürün ekibiyle doğrulanmalıdır.
+NİYET NOTU: Jenerik 'müşteri numarası' hacminin büyük bölümü bankacılık aramalarından gelmektedir (yapı kredi 2.400, banka 600, firma 500, halkbank 450, ziraat ve akbank 250'şer). Banka markası içeren aramalar bu yazıyla karşılanamaz. Yazı bankacılık ve telekom kullanımını ayrı bölümlerde ele almakta, aynı ayrımı rakip blog da yapmaktadır.</t>
         </is>
       </c>
       <c r="R31" s="8" t="n">
@@ -14650,7 +14816,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="250" customHeight="1">
+    <row r="32" ht="304" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>OTP Ne Demek?</t>
@@ -14702,6 +14868,7 @@
 H2: OTP Kodu Nerelerde Kullanılır?
 H2: OTP Kodu Neden Kimseyle Paylaşılmamalı?
 H2: OTP Kodu Gelmiyorsa Ne Yapılmalı?
+H2: OTP Hatalı Uyarısı Ne Anlama Gelir?
 H2: OTP Hakkında Sıkça Sorulan Sorular</t>
         </is>
       </c>
@@ -14728,7 +14895,9 @@
 H3: Bankalar Telefonda OTP Kodu İster mi?
 İstemez. Kod talep eden aramalar dolandırıcılık girişimidir ve derhal sonlandırılmalıdır.
 H3: OTP Kodu Gelmiyorsa Ne Yapmalıyım?
-Şebeke bağlantısı, kayıtlı telefon numarasının güncelliği ve mesaj engelleme filtreleri kontrol edilir, ardından kod yeniden istenir.</t>
+Şebeke bağlantısı, kayıtlı telefon numarasının güncelliği ve mesaj engelleme filtreleri kontrol edilir, ardından kod yeniden istenir.
+H3: OTP Hatalı Ne Demek?
+Girilen kodun süresi dolmuş ya da yanlış girilmiş demektir; yeni kod istenip süresi içinde girilmelidir.</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -14781,7 +14950,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="263.5" customHeight="1">
+    <row r="33" ht="317.5" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t>QLED Nedir? QLED ve OLED Farkı</t>
@@ -14831,6 +15000,7 @@
           <t>H2: QLED Nedir?
 H2: OLED Nedir?
 H2: QLED ve OLED Farkı Nedir?
+H2: Neo QLED Nedir, QLED'den Farkı Nedir?
 H2: Parlaklık ve Kontrast Karşılaştırması
 H2: Panel Ömrü ve Görüntü Kalıcılığı
 H2: Hangi Kullanım İçin Hangisi Daha Uygun?
@@ -14860,6 +15030,8 @@
 Yüksek tepe parlaklığı nedeniyle QLED paneller aydınlık ortamlarda daha okunaklı bir görüntü sunar.
 H3: OLED'de Görüntü Kalıcılığı Sorun mu?
 Uzun süre sabit kalan görüntülerde risk vardır; güncel panellerde bu riski azaltan koruma özellikleri bulunur.
+H3: Neo QLED Nedir?
+Neo QLED, arkadan aydınlatmada mini LED kullanan ve bu sayede daha hassas parlaklık kontrolü ile daha derin siyah sunabilen QLED sürümüdür.
 H3: Oyun İçin QLED mi OLED mi?
 Tepki süresi ve siyah derinliği nedeniyle OLED öne çıkar; ancak sabit arayüz öğeleri uzun süre ekranda kalıyorsa QLED daha güvenli bir tercih olabilir.</t>
         </is>
@@ -15045,7 +15217,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="209.5" customHeight="1">
+    <row r="35" ht="371.5" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>TAG Nedir?</t>
@@ -15088,9 +15260,11 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>H2: TAG Nedir?
+          <t>H2: TAG Nedir, TAG Açılımı Nedir?
+H2: Martı TAG Nedir, Nasıl Kullanılır?
+H2: AirTag ve Smart Tag Nedir?
+H2: NFC Tag Nedir?
 H2: Sosyal Medyada Etiketleme Ne Anlama Gelir?
-H2: NFC Etiketi (Tag) Nedir?
 H2: Web ve Ölçümlemede Tag Ne Demek?
 H2: Hangi Bağlamda Hangi Anlam Kullanılır?
 H2: TAG Hakkında Sıkça Sorulan Sorular</t>
@@ -15098,8 +15272,11 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>TON: Çok anlamlı terim açıklaması. Açılış paragrafı kelimenin birden çok anlamı olduğunu duyurur ve yazıda hangi üç anlamın ele alındığını sayar; okuyucu doğru bölüme hemen gidebilmeli.
-H2 · TAG Nedir: Genel anlamıyla etiket; içeriği sınıflandıran işaret.
+          <t>TON: Çok anlamlı terim açıklaması. Açılış paragrafı kelimenin birden çok anlamı olduğunu duyurur ve yazıda hangi anlamların ele alındığını sayar; okuyucu doğru bölüme hemen gidebilmeli.
+NİYET NOTU: Soru kelimesi taramasında bu terimin baskın anlamı ulaşım uygulaması (martı tag 6.600, tag taksi 450, tag sürücü 450, tag premium 250) ve takip cihazı (air tag 2.600, smart tag 200) olarak çıkmaktadır. Sosyal medya etiketi ve ölçümleme etiketi anlamları arama tarafında çok daha küçük paya sahiptir. Bu nedenle bölüm sırası arama hacmine göre kurulmuş, jenerik "tag nedir" hacminin tamamının bu yazıyla karşılanamayacağı not edilmiştir.
+H2 · TAG Nedir: Genel anlamıyla etiket; içeriği sınıflandıran işaret. Açılımı ve kelimenin hangi alanlarda karşımıza çıktığı tek paragrafta.
+H2 · Martı TAG: Ulaşım uygulamasındaki kullanım nötr biçimde, bilgilendirme düzeyinde anlatılır; yönlendirme ya da karşılaştırma yapılmaz.
+H2 · AirTag ve Smart Tag: İki takip cihazının ne olduğu ve hangi ekosistemde çalıştığı; ayrıntı için AirTag yazısına iç bağlantı verilir.
 H2 · Sosyal Medyada Etiketleme: Kişi etiketleme ve konu etiketi (hashtag) ayrımı; ikisi karıştırılıyor.
 H2 · NFC Etiketi: Küçük bir çipin okutulmasıyla işlem başlatılması; ev otomasyonu ve kartvizit iki örnekle.
 H2 · Web ve Ölçümlemede Tag: Sayfaya eklenen ölçümleme kodu anlamı ve HTML etiketi anlamı iki cümlede ayrı ayrı.
@@ -15109,14 +15286,44 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>H3: TAG Nedir?
-TAG, Türkçede etiket anlamına gelir ve bağlama göre sosyal medyada kişi etiketlemeyi, NFC çipini ya da web sayfasına eklenen ölçümleme kodunu ifade eder.
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">H3: TAG Nedir?
+TAG, Türkçede etiket anlamına gelir; bağlama göre bir ulaşım uygulamasını, takip cihazını, sosyal medyada kişi etiketlemeyi, NFC çipini ya da web sayfasına eklenen ölçümleme kodunu ifade eder.
+H3: TAG Açılımı Nedir?
+İngilizce etiket anlamındaki tag kelimesinden gelir; kısaltma değil, doğrudan bir sözcüktür.
+H3: Martı TAG Nedir?
+Martı TAG, uygulama üzerinden sürücü ile yolcuyu eşleştiren bir ulaşım hizmetidir.
+H3: AirTag ile Smart Tag Arasındaki Fark Nedir?
+İkisi de eşya takip cihazıdır; AirTag Apple ekosisteminde, Smart Tag ise </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Samsung</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve"> ekosisteminde çalışır.
 H3: Sosyal Medyada Tag Ne Demek?
 Bir gönderide kişinin hesabının bağlanmasıdır; konu etiketi anlamındaki hashtag ise içeriğin konusunu sınıflandırır.
 H3: NFC Tag Ne İşe Yarar?
 Telefonun yaklaştırılmasıyla önceden tanımlanmış bir işlemi başlatan küçük bir çiptir; ev otomasyonu ve dijital kartvizit gibi kullanımları vardır.
 H3: HTML'de Tag Ne Anlama Gelir?
 Sayfanın yapısını tanımlayan işaretleme öğesidir; başlık, paragraf ve bağlantı gibi öğeler tag'lerle belirtilir.</t>
+          </r>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -15142,7 +15349,8 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>Kelimenin birden çok anlamı bulunmaktadır; açılışta hangi anlamların ele alındığı belirtilmelidir.</t>
+          <t>Kelimenin birden çok anlamı bulunmaktadır; açılışta hangi anlamların ele alındığı belirtilmelidir.
+NİYET NOTU: Jenerik 'tag' hacminin büyük bölümü ulaşım uygulaması (martı tag 6.600, tag taksi 450, tag sürücü 450, tag premium 250) ve takip cihazı (air tag 2.600) aramalarından gelmektedir; skin tag ve Google Tag Manager gibi alan dışı anlamlar da bu hacme dahildir. Yazı, arama hacmine göre sıralanmış anlam bölümleriyle kurgulanmıştır; kümeye atanan hacmin tamamının karşılanması beklenmemelidir.</t>
         </is>
       </c>
       <c r="R35" s="8" t="n">
@@ -15169,7 +15377,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="250" customHeight="1">
+    <row r="36" ht="358" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Karekod Nasıl Okutulur?</t>
@@ -15214,10 +15422,14 @@
         <is>
           <t>H2: Karekod Nedir?
 H2: Karekod Nasıl Okutulur?
+H2: Telefondan Karekod Nasıl Okutulur?
 H3: iPhone ile Karekod Okutma
 H3: Android ile Karekod Okutma
 H2: Kamera Karekodu Okutmuyorsa Ne Yapmalı?
 H2: Ekrandaki Karekod Nasıl Okutulur?
+H2: Ders Kitabındaki Karekod Nasıl Okutulur?
+H2: Wifi Karekodu ile Ağa Nasıl Bağlanılır?
+H2: Wi-Fi Karekodu Nasıl Okutulur ve Oluşturulur?
 H2: Sahte Karekodlar Nasıl Ayırt Edilir?
 H2: Karekod Hakkında Sıkça Sorulan Sorular</t>
         </is>
@@ -15244,7 +15456,11 @@
 H3: Karekod Güvenli mi?
 Kodun kendisi bir bağlantıdan ibarettir; açılan adres kontrol edilmeden kişisel bilgi veya ödeme bilgisi girilmemelidir.
 H3: Karekod ile QR Kod Aynı Şey mi?
-Evet. Karekod, QR kodun Türkçe karşılığıdır.</t>
+Evet. Karekod, QR kodun Türkçe karşılığıdır.
+H3: Ders Kitabındaki Karekod Nasıl Okutulur?
+Kitabın sayfasındaki kod telefon kamerasına tutulur; bazı yayınlar kendi uygulamaları üzerinden okutmayı gerektirir.
+H3: Wi-Fi Karekodu Nasıl Okutulur?
+Kamera koda tutulduğunda ağa bağlan seçeneği çıkar ve şifre girilmeden bağlantı kurulur; telefonlarda kayıtlı ağın karekodu da paylaşılabilir.</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -15443,7 +15659,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="209.5" customHeight="1">
+    <row r="38" ht="263.5" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t>URL Nedir?</t>
@@ -15511,6 +15727,8 @@
         <is>
           <t>H3: URL Nedir?
 URL, internetteki bir sayfanın veya dosyanın tam adresidir ve tarayıcının hangi kaynağa ulaşacağını belirtir.
+H3: URL Adresi Nedir, Nerede Görülür?
+URL adresi tarayıcının en üstündeki adres çubuğunda görünen tam adrestir; bağlantıya uzun basılarak da kopyalanabilir.
 H3: URL Hangi Bölümlerden Oluşur?
 Protokol, alan adı, yol ve gerektiğinde sorgu parametrelerinden oluşur.
 H3: Güvenli URL Nasıl Anlaşılır?
@@ -15695,7 +15913,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="209.5" customHeight="1">
+    <row r="40" ht="263.5" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>FreeDOS Nedir? İşletim Sistemi Yüklü Olmayan Bilgisayar</t>
@@ -15766,6 +15984,8 @@
 Cihazın Windows veya macOS gibi bir işletim sistemiyle değil, temel bir sistemle geldiğini gösterir; günlük kullanım için ayrıca işletim sistemi kurulması gerekir.
 H3: FreeDOS Bilgisayara Windows Kurulabilir mi?
 Kurulabilir. Lisans satın alındıktan sonra kurulum medyası hazırlanarak sistem yüklenebilir.
+H3: FreeDOS İşletim Sistemi Nedir?
+MS-DOS ile uyumlu, komut satırı tabanlı ve ücretsiz bir işletim sistemidir; günlük masaüstü kullanım için tasarlanmamıştır.
 H3: FreeDOS Bilgisayar Neden Daha Ucuz?
 Fiyat farkı büyük ölçüde işletim sistemi lisans bedelinin cihaza dahil olmamasından kaynaklanır.</t>
         </is>
@@ -16377,7 +16597,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="291" customHeight="1">
+    <row r="4" ht="358" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/isletim-sistemi-nedir-ve-cesitleri-nelerdir</t>
@@ -16485,6 +16705,8 @@
 H3: Linux Nedir, Neden Tercih Edilir?
 H2: İşletim Sistemi Yalnız Bilgisayarlarda mı Bulunur?
 H2: Android ve iOS Arasındaki Farklar Nelerdir?
+H2: Televizyon İşletim Sistemleri: Tizen, webOS ve Vidaa
+H2: Pardus Nedir, Yerli İşletim Sistemi Ne Anlama Gelir?
 H2: İşletim Sistemleri Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: İşletim Sistemi Özellikleri Nelerdir?</t>
         </is>
@@ -16510,7 +16732,11 @@
 H3: İşletim Sistemi Yalnızca Bilgisayarlarda mı Bulunur?
 Hayır. Telefonlar, akıllı televizyonlar, akıllı saatler ve araç bilgi sistemleri de kendi işletim sistemleriyle çalışır.
 H3: Android ile iOS Arasındaki Fark Nedir?
-Android çok sayıda üreticinin cihazında çalışır ve daha geniş özelleştirme sunar; iOS yalnızca Apple cihazlarında çalışır ve güncellemeleri tüm cihazlara aynı anda ulaşır.</t>
+Android çok sayıda üreticinin cihazında çalışır ve daha geniş özelleştirme sunar; iOS yalnızca Apple cihazlarında çalışır ve güncellemeleri tüm cihazlara aynı anda ulaşır.
+H3: Tizen İşletim Sistemi Nedir?
+Tizen, akıllı televizyonlarda ve giyilebilir cihazlarda kullanılan, Linux tabanlı bir işletim sistemidir.
+H3: Pardus İşletim Sistemi Nedir?
+Pardus, Türkiye'de geliştirilen ve kamu kurumlarında da kullanılan Linux tabanlı açık kaynaklı bir işletim sistemidir.</t>
         </is>
       </c>
       <c r="X4" s="4" t="inlineStr">
@@ -16818,7 +17044,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="317.5" customHeight="1">
+    <row r="6" ht="409" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/nfc-nedir-nfc-ile-neler-yapilabilir</t>
@@ -16965,6 +17191,7 @@
 H3: Xiaomi ve Redmi Cihazlarda NFC Nasıl Açılır?
 H2: NFC Özelliği Olan Telefonlar Hangileri?
 H2: Telefonda NFC Alanı Neresi?
+H2: Bu NFC Etiketi İçin Desteklenen Uygulama Yok Hatası Ne Anlama Gelir?
 H2: NFC Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: NFC Nedir, NFC ile Neler Yapılabilir?</t>
           </r>
@@ -16994,7 +17221,11 @@
 H3: Telefonumda NFC Var mı, Nasıl Anlarım?
 Cihaz ayarlarında bağlantılar bölümünde NFC seçeneğinin bulunması desteklendiğini gösterir; seçenek yoksa cihaz NFC desteklemiyor demektir.
 H3: Telefonda NFC Alanı Nerede?
-NFC anteni çoğu modelde cihazın arka yüzünün üst bölümünde yer alır; okutma sırasında bu bölgenin okuyucuya temas etmesi gerekir.</t>
+NFC anteni çoğu modelde cihazın arka yüzünün üst bölümünde yer alır; okutma sırasında bu bölgenin okuyucuya temas etmesi gerekir.
+H3: NFC Desteği Ne Demek?
+Cihazın NFC donanımına sahip olduğunu ve temassız veri alışverişi ile ödeme yapabildiğini ifade eder.
+H3: Bu NFC Etiketi İçin Desteklenen Uygulama Yok Hatası Neden Alınır?
+Okutulan etiketin içeriğini açabilecek bir uygulama telefonda kurulu değildir; etiketin yönlendirdiği uygulamanın kurulması ya da etiketin yeniden yazılması gerekir.</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
@@ -17115,7 +17346,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="276" customHeight="1">
+    <row r="7" ht="371.5" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/gemini-nedir-googlein-yapay-zeka-uygulamasina-genel-bakis</t>
@@ -17210,6 +17441,7 @@
       <c r="U7" s="4" t="inlineStr">
         <is>
           <t>H2: Gemini Yapay Zeka Ne İşe Yarar?
+H2: Google Gemini Uygulaması Nasıl Kullanılır?
 H2: Gemini Türkçe Destekliyor mu?
 H2: Gemini ile ChatGPT Arasındaki Fark Nedir?
 H2: Gemini Ücretsiz mi?
@@ -17239,7 +17471,11 @@
 H3: Gemini Ücretsiz mi?
 Temel sürüm ücretsiz kullanılabilir; gelişmiş modeller ve ek özellikler ücretli abonelikle sunulur.
 H3: Gemini ile ChatGPT Arasındaki Fark Nedir?
-İki servis de yapay zeka sohbet asistanıdır; farklar güncel bilgiye erişim biçimi, entegre oldukları uygulama ekosistemi ve ücretsiz sürüm sınırlarında ortaya çıkar.</t>
+İki servis de yapay zeka sohbet asistanıdır; farklar güncel bilgiye erişim biçimi, entegre oldukları uygulama ekosistemi ve ücretsiz sürüm sınırlarında ortaya çıkar.
+H3: Google Gemini Uygulaması Nedir?
+Gemini'nin telefon ve tablet için sunulan uygulamasıdır; sesli soru sorma, görsel yükleme ve diğer Google uygulamalarıyla birlikte çalışma özelliklerini taşır.
+H3: Gemini Nedir, Ne İşe Yarar?
+Metin yazma ve özetleme, görsel yorumlama, kod yardımı ve Google uygulamalarıyla birlikte çalışma gibi işlerde kullanılan yapay zeka asistanıdır.</t>
         </is>
       </c>
       <c r="X7" s="4" t="inlineStr">
@@ -17290,7 +17526,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="263.5" customHeight="1">
+    <row r="8" ht="358" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni</t>
@@ -17390,6 +17626,7 @@
 H3: Komut Satırından Ping Testi
 H3: Hız Testi Siteleriyle Ping Ölçümü
 H2: İdeal Ping Değerleri Tablosu
+H2: Ping Atmak Ne Demek?
 H2: Ping Nasıl Düşürülür? Dört Adım
 H2: Ping Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Ping Testi Nedir? Nasıl Yapılır?</t>
@@ -17438,6 +17675,10 @@
 Komut satırından ping komutu çalıştırılarak ya da bir hız testi sitesi üzerinden ölçüm yapılarak test edilir.
 H3: Ping Nasıl Düşürülür?
 Kablolu bağlantıya geçilmesi, 5 GHz bandın kullanılması, arka plan indirmelerinin durdurulması ve yakın sunucu bölgesinin seçilmesi gecikmeyi azaltır.
+H3: Ping Atmak Ne Demek?
+Bir adrese küçük bir veri paketi gönderip yanıt süresini ölçmeyi ifade eder; bağlantının çalışıp çalışmadığını ve gecikmesini gösterir.
+H3: Ping ve Jitter Nedir, Farkı Nedir?
+Ping gecikmenin süresini, jitter ise bu sürenin ne kadar dalgalandığını ölçer.
 H3: Yüksek Ping Neden Olur?
 Ağ yoğunluğu, kablosuz bağlantı kalitesi, uzak sunucu konumu ve arka planda çalışan indirmeler yüksek pingin başlıca nedenleridir.</t>
         </is>
@@ -17542,7 +17783,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="236.5" customHeight="1">
+    <row r="9" ht="290.5" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/type-c-teknolojisi-ne-ise-yarar-neden-bu-kadar-yaygin</t>
@@ -17654,6 +17895,7 @@
             <t xml:space="preserve">H2: Type-C Nedir, Ne Demek?
 H2: USB 3.2, USB4 ve Thunderbolt Arasındaki Fark Nedir?
 H2: Type-C ile Hızlı Şarj Nasıl Çalışır?
+H2: Type-C Şarj Aleti Nedir, Nasıl Seçilir?
 H2: Kablo Kalitesi Aktarım Hızını Nasıl Etkiler?
 H2: Type-C Hakkında Sıkça Sorulan Sorular
 Rakip yazıda bulunup bu yazıda karşılığı olmayan ara başlıklar: Type C Nedir? · Type C Girişe Sahip Olan Cihazlar Hangileridir? · USB Type-C’nin diğer USB türlerinden Farkı · USB Type-C’nin Avantajları ve USB Type-C’nin Dezavantajları · Type-C Girişli Telefonlara </t>
@@ -17697,6 +17939,8 @@
 Değildir. Konnektör aynı olsa da desteklenen USB standardı ve kablo sertifikasyonu aktarım hızını belirler.
 H3: Type-C ile Hızlı Şarj Nasıl Çalışır?
 Power Delivery protokolü sayesinde şarj cihazı ile telefon anlaşır ve cihazın desteklediği en yüksek güç kademesinde şarj yapılır.
+H3: Type-C Şarj Aleti Nedir?
+Type-C çıkışlı, Power Delivery destekleyen şarj adaptörünü tanımlar; cihazın desteklediği güç kademesine kadar hızlı şarj sağlar.
 H3: Type-C Girişten Görüntü Aktarılır mı?
 Cihaz ve kablo destekliyorsa aktarılır; her Type-C girişte görüntü çıkışı bulunmaz.</t>
         </is>

--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -12810,7 +12810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12828,13 +12828,12 @@
     <col width="110" customWidth="1" min="13" max="13"/>
     <col width="62" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="44" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="52" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="52" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -12863,9 +12862,8 @@
       <c r="S1" s="2" t="n"/>
       <c r="T1" s="2" t="n"/>
       <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="81" customHeight="1">
+    </row>
+    <row r="2" ht="96" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <r>
@@ -12947,6 +12945,24 @@
               <sz val="10.5"/>
             </rPr>
             <t xml:space="preserve">
+Kurgu sütunu: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>İçerik yönergesi ayrı bir sütun değildir: hangi bölümün yazılacağı ve o bölümün nasıl yazılacağı "İçerik Kurgusu ve Yönergesi" sütununda birlikte verilmektedir. Sütun bölüm bölüm ilerler: ton, giriş, her H2 ve H3 için biçim (tablo, adım listesi, madde listesi), derinlik, rakip yazının aynı bölümü nasıl işlediği ve hangi PAA sorusunun nerede karşılandığı.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00FF7B52"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">
 Uzun hücreler: </t>
           </r>
           <r>
@@ -12979,7 +12995,6 @@
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -13003,7 +13018,6 @@
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -13063,7 +13077,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>İçerik Kurgusu</t>
+          <t>İçerik Kurgusu ve Yönergesi</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -13083,35 +13097,30 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>İçerik Yönergesi</t>
+          <t>Dikkat Edilecek</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>Dikkat Edilecek</t>
+          <t>Puan</t>
         </is>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Puan</t>
+          <t>Öncelik</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Öncelik</t>
+          <t>Peak Ayı</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>Peak Ayı</t>
+          <t>Önerilen Yayın Ayı</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>Önerilen Yayın Ayı</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>Ne Anlama Geliyor</t>
         </is>
@@ -13260,37 +13269,28 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>1. 192.168.1.1 ve 192.168.0.1 farkı açıklanır
-2. Marka bazında varsayılan kullanıcı adı ve şifre tablosu verilir
-3. Arayüze girilemediğinde kontrol listesi verilir
-4. WiFi adı ve şifresi değiştirme adım adım anlatılır
-5. Modem sıfırlama adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
           <t>Turkcell modem modelleri için varsayılan bilgiler ürün ekibiyle doğrulanmalıdır.</t>
         </is>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="Q5" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="R5" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Ocak</t>
+        </is>
+      </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>Ocak</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V5" s="6" t="inlineStr">
+      <c r="U5" s="6" t="inlineStr">
         <is>
           <t>Modem şifresini değiştirmek isteyen kişi önce arayüze girmeye çalışıyor. Bu adım rakipte en çok trafik getiren sayfa.</t>
         </is>
@@ -13519,37 +13519,28 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>1. Numara gizleme kodu ve operatör ayarı açıklanır
-2. Gizli numaradan gelen aramayı engelleme adım adım anlatılır
-3. IPhone ve Android ayrı adımlar adım adım anlatılır
-4. Operatör servisiyle kalıcı engelleme adım adım anlatılır
-5. Yasal sınırlar açıklanır</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
           <t>Numarayı gizleme ve gizli numarayı engelleme zıt niyetlerdir; başlık ve ara başlıklar ikisini de karşılamalıdır.</t>
         </is>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="Q6" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="R6" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Ağustos</t>
+        </is>
+      </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>Ağustos</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="V6" s="6" t="inlineStr">
+      <c r="U6" s="6" t="inlineStr">
         <is>
           <t>Kullanıcı ya numarasını gizlemek ya da gizli aramadan kurtulmak istiyor. İki ihtiyaç aynı sayfada karşılanırsa iki arama da aynı yere geliyor.</t>
         </is>
@@ -13771,37 +13762,28 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>1. Kayıt ücreti ve geçerli yılın harç tutarı tablo hâlinde açıklanır
-2. E-Devlet ve BTK üzerinden sorgulama adımları adım adım anlatılır
-3. Kayıtsız telefonun kaç gün kullanılabildiği açıklanır
-4. IMEI numarasının telefondan öğrenilmesi adım adım anlatılır
-5. Kayıt sonrası bekleme süresi açıklanır</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
           <t>Ücret ve süre bilgileri yıl içinde değişmektedir; sayfanın güncellenme tarihi görünür tutulabilir.</t>
         </is>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="Q7" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="R7" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Eylül</t>
+        </is>
+      </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>Eylül</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="V7" s="6" t="inlineStr">
+      <c r="U7" s="6" t="inlineStr">
         <is>
           <t>Yurt dışından telefon getiren kişi ücreti ve süreyi arıyor. Bu bilgiyi tek sayfada toplayan taraf aramanın tamamını karşılıyor.</t>
         </is>
@@ -14032,36 +14014,28 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>1. Google güvenli aramanın ne yaptığı açıklanır
-2. Açma ve kapatma adımları adım adım anlatılır
-3. Kilitli olduğunda yapılabilecekler açıklanır
-4. Çocuk hesaplarında aile bağlantısı ayarı açıklanır</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
           <t>Operatör tarafındaki güvenli internet hizmetiyle karıştırılmaması için ikisi ayrı ara başlıkta ele alınabilir.</t>
         </is>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="Q8" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="R8" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>Nisan</t>
+        </is>
+      </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
-          <t>Nisan</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
           <t>Şubat</t>
         </is>
       </c>
-      <c r="V8" s="6" t="inlineStr">
+      <c r="U8" s="6" t="inlineStr">
         <is>
           <t>Arama sonuçlarındaki filtreyi açmak veya kapatmak isteyen kullanıcı adım arıyor. Basit ama sürekli aranan bir konu.</t>
         </is>
@@ -14200,36 +14174,28 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>1. PUK kodunun nereden öğrenileceği açıklanır
-2. PIN değiştirme ve kaldırma adım adım anlatılır
-3. Üç kez yanlış PIN girildiğinde izlenecek yol açıklanır
-4. SIM blokesinin kaldırılması adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
           <t>Abone doğrulaması gerektiren adımlarda self servis kanallara yönlendirme yapılabilir.</t>
         </is>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="Q9" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="R9" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>Ağustos</t>
+        </is>
+      </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>Ağustos</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="V9" s="6" t="inlineStr">
+      <c r="U9" s="6" t="inlineStr">
         <is>
           <t>SIM kartı kilitlenen kişi acil çözüm arıyor. Bu anda doğru adımı veren sayfa ziyaret alıyor.</t>
         </is>
@@ -14438,36 +14404,28 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>1. Kablosuz yansıtma için gereken koşullar açıklanır
-2. IPhone ve Android adımları adım adım anlatılır
-3. Kablo ile yansıtma adım adım anlatılır
-4. Televizyon bulunamadığında kontrol listesi verilir</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
           <t>Yansıtma kalitesi ev ağına bağlıdır; bağlantı bölümüne kısa bir not eklenebilir.</t>
         </is>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="Q10" s="9" t="n">
         <v>88</v>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="R10" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>Aralık</t>
+        </is>
+      </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>Aralık</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
-        <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="V10" s="6" t="inlineStr">
+      <c r="U10" s="6" t="inlineStr">
         <is>
           <t>Telefondaki görüntüyü televizyona aktarmak isteyen kişi adım arıyor. Cihaz farkları netleşince arama karşılanıyor.</t>
         </is>
@@ -14624,36 +14582,28 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>1. IP adresinin tanımı açıklanır
-2. Kendi IP adresinin öğrenilmesi adım adım anlatılır
-3. Statik ve dinamik IP farkı açıklanır
-4. IP adresinin gizlenmesi ve değiştirilmesi adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
           <t>Sonuç sayfasında IP gösteren araçlar öndedir; yazının bir sorgulama aracına bağlanması değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="Q11" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="R11" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>Ocak</t>
+        </is>
+      </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>Ocak</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="U11" s="6" t="inlineStr">
         <is>
           <t>Kendi IP adresini öğrenmek isteyen kişi hızlı yanıt arıyor. Sonuç sayfasında araçlar önde, açıklama katmanı boş.</t>
         </is>
@@ -14818,36 +14768,28 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>1. Android ve iPhone'da indirilenler klasörünün yeri açıklanır
-2. Tarayıcıya göre değişen konumlar açıklanır
-3. Indirilen dosyanın bulunamaması durumu açıklanır
-4. Depolama temizliği açıklanır</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
           <t>Cihaz ve sürüm farkları ekran görüntüsüyle desteklenebilir.</t>
         </is>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="Q12" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="R12" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>Ekim</t>
+        </is>
+      </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>Ekim</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="V12" s="6" t="inlineStr">
+      <c r="U12" s="6" t="inlineStr">
         <is>
           <t>İndirdiği dosyayı bulamayan kişi klasörün yerini arıyor. Cihaza göre değişen bir bilgi, tek sayfada toplanabilir.</t>
         </is>
@@ -14997,37 +14939,28 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>1. Hesabı geçici dondurma adımları ve kalıcı silmeden farkı açıklanır
-2. Dondurulan hesabın geri açılması adım adım anlatılır
-3. Uygulama açılmadığında kontrol listesi verilir
-4. Giriş yapılamadığında doğrulama adımları adım adım anlatılır
-5. Gönderilen takip isteklerinin görülmesi adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
           <t>Uygulama arayüzü sık değiştiğinden adımların ekran görüntüsüyle desteklenmesi ve güncellenme tarihinin görünür tutulması önerilir.</t>
         </is>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="Q13" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="R13" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>Eylül</t>
+        </is>
+      </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>Eylül</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="V13" s="6" t="inlineStr">
+      <c r="U13" s="6" t="inlineStr">
         <is>
           <t>Hesabını donduran ya da uygulamaya giremeyen kişi hızlı yanıt arıyor. Rakiplerde konu ayrı yazılara bölünmüş durumda.</t>
         </is>
@@ -15186,35 +15119,28 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>1. Spam tanımı açıklanır
-2. Spam mesaj ve arama engelleme adımları adım adım anlatılır
-3. Operatör tarafındaki engelleme servisleri açıklanır</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
           <t>Kısa ve doğrudan yanıt veren bir yapı önerilmektedir; sorgu tanım niyetlidir.</t>
         </is>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="Q14" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="R14" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>Aralık</t>
+        </is>
+      </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>Aralık</t>
-        </is>
-      </c>
-      <c r="U14" s="7" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V14" s="6" t="inlineStr">
+      <c r="U14" s="6" t="inlineStr">
         <is>
           <t>Spam kelimesinin anlamını ve engelleme yolunu arayan kişi kısa yanıt istiyor.</t>
         </is>
@@ -15366,38 +15292,29 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>1. SSD ile HDD farkı açıklanır
-2. RAM'in görevi ve yeterli kapasite açıklanır
-3. Ekran kartının ne işe yaradığı açıklanır
-4. Anakartın rolü açıklanır
-5. Bilgisayar yavaşladığında hangi bileşene bakılacağı açıklanır</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
           <t>Ürün önerisi verilmemeli; bilgi katmanında kalınmalıdır.
 NİYET NOTU: 'ram krizi' (500) bellek fiyatlarına ilişkin haber niyetlidir ve bu yazının kapsamı dışındadır.</t>
         </is>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="Q15" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="R15" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>Aralık</t>
+        </is>
+      </c>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>Aralık</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="V15" s="6" t="inlineStr">
+      <c r="U15" s="6" t="inlineStr">
         <is>
           <t>Bilgisayar alacak veya yükseltecek kişi bileşenlerin ne işe yaradığını soruyor. Tek rehber birden çok aramayı karşılıyor.</t>
         </is>
@@ -15548,35 +15465,28 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>1. E-imza tanımı açıklanır
-2. Başvuru adımları adım adım anlatılır
-3. Mobil imza ile farkı açıklanır</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
           <t>Turkcell Mobil İmza hizmetiyle bağ kurulabilir; karşılaştırma bölümü ayırt edici olmaktadır.</t>
         </is>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="Q16" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="R16" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>Ağustos</t>
+        </is>
+      </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>Ağustos</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="V16" s="6" t="inlineStr">
+      <c r="U16" s="6" t="inlineStr">
         <is>
           <t>E-imza almak isteyen kişi başvuru adımını arıyor. Mobil imza karşılaştırması markaya bağlanıyor.</t>
         </is>
@@ -15727,36 +15637,28 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>1. Taahhüdün tanımı açıklanır
-2. Taahhütlü ve taahhütsüz farkı açıklanır
-3. Taahhüt süresi dolmadan çıkışta ne olduğu açıklanır
-4. Taahhüt süresinin öğrenilmesi adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
           <t>Tanım sorgusudur; ilk paragrafta tek cümlelik karşılık verilmesi önerilir. Kampanya koşulları ürün ekibiyle doğrulanmalıdır.</t>
         </is>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="Q17" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="R17" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>Aralık</t>
+        </is>
+      </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>Aralık</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="V17" s="6" t="inlineStr">
+      <c r="U17" s="6" t="inlineStr">
         <is>
           <t>Taahhüt kelimesinin ne anlama geldiğini soran kişi tek cümlelik karşılık bekliyor.</t>
         </is>
@@ -15838,7 +15740,7 @@
             </rPr>
             <t>TON: Uygulamalı ve dürüst. Kritik bölüm numaradan konum bulma; rakip yazılar net yanıt vermiyor, ayırt edici yan burada.
 H2 · Konum Paylaşma Nedir: Kısaca; anlık ve canlı konum farkı.
-H2 · Konum Nasıl Atılır: Detaylı; üç H3 (WhatsApp, Google Haritalar, iPhone), her biri kısa adım listesi. Rakip yazılar (</t>
+H2 · Konum Nasıl Atılır: Detaylı; üç H3 (WhatsApp, Google Haritalar, iPhone'da Mesajlar/iMessage), her biri kısa adım listesi. Rakip yazılar (</t>
           </r>
           <r>
             <rPr>
@@ -15935,36 +15837,28 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>1. WhatsApp, Google Haritalar ve iMessage üzerinden konum paylaşma adım adım anlatılır
-2. Canlı konum paylaşımı süresi açıklanır
-3. Numaradan konum bulmanın gerçekte mümkün olup olmadığı açıklanır
-4. Konum servislerinin pil etkisi açıklanır</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
           <t>Numaradan konum bulma başlığı yanıltıcı vaatlere açıktır; yasal çerçeve ve gerçek sınırlar açıkça yazılmalıdır.</t>
         </is>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="Q18" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="R18" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>Ağustos</t>
+        </is>
+      </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Ağustos</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="V18" s="6" t="inlineStr">
+      <c r="U18" s="6" t="inlineStr">
         <is>
           <t>Konum paylaşmak isteyen çok kişi var; numaradan konum bulma ise beklentisi yanlış kurulmuş bir arama. İkisini dürüstçe ayıran sayfa güven kazanıyor.</t>
         </is>
@@ -16116,37 +16010,28 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>1. Android'den iPhone'a aktarma adım adım anlatılır
-2. IPhone'dan iPhone'a hızlı başlangıç açıklanır
-3. Android'den Android'e aktarma adım adım anlatılır
-4. WhatsApp geçmişinin taşınması adım adım anlatılır
-5. Aktarma sırasında sık karşılaşılan durumlar açıklanır</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
           <t>Numara taşıma ile veri aktarma farklı işlemlerdir; ikisinin karıştırılmaması için kısa bir ayrım notu eklenebilir.</t>
         </is>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="Q19" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="R19" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>Ocak</t>
+        </is>
+      </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>Ocak</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="V19" s="6" t="inlineStr">
+      <c r="U19" s="6" t="inlineStr">
         <is>
           <t>Telefon değiştiren kişi verisini kaybetmeden taşımak istiyor. Android ve iPhone ayrımını tek sayfada veren içerik bulunmuyor.</t>
         </is>
@@ -16222,7 +16107,7 @@
             </rPr>
             <t>TON: Seçki formatı. Sonuç sayfası liste bekliyor; kurulum adımları listenin sonuna alınır.
 H2 · Chrome Eklentileri Nedir: Kısaca; uzantı ve eklenti kelimelerinin aynı şeyi anlattığı belirtilir.
-H2-H4 · Üç kategori: Her kategoride dört-beş eklenti, her eklenti aynı şablonla: ad, ne işe yaradığı, kime uygun olduğu. Puanlama yapılmaz. Rakip yazılar (</t>
+H2-H4 · Üç kategori (üretkenlik, güvenlik, alışveriş): Her kategoride dört-beş eklenti, her eklenti aynı şablonla: ad, ne işe yaradığı, kime uygun olduğu. Puanlama yapılmaz. Rakip yazılar (</t>
           </r>
           <r>
             <rPr>
@@ -16304,36 +16189,28 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>1. Kullanım alanına göre eklenti seçkisi: üretkenlik, güvenlik, alışveriş açıklanır
-2. Her eklenti için tek cümlelik ne işe yaradığı açıklanır
-3. Eklentinin eklenmesi ve kaldırılması adım adım anlatılır
-4. Eklenti izinlerinin görülmesi ve güvenilir eklentinin ayırt edilmesi adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
           <t>Seçki formatı sonuç sayfasıyla uyumludur; kurulum adımları listenin sonunda kısa bir bölüm olarak verilebilir.</t>
         </is>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="Q20" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="S20" s="11" t="inlineStr">
+      <c r="R20" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Kasım</t>
-        </is>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V20" s="6" t="inlineStr">
+      <c r="U20" s="6" t="inlineStr">
         <is>
           <t>Eklenti arayan kişi tek bir kurulum adımı değil, hangi eklentinin ne işe yaradığını gösteren bir seçki bekliyor.</t>
         </is>
@@ -16481,36 +16358,28 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>1. E-posta adresi oluşturma adımları adım adım anlatılır
-2. Telefonda hesap kurulumu adım adım anlatılır
-3. E-posta yazarken dikkat edilecekler açıklanır
-4. Iki adımlı doğrulama adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
           <t>Sağlayıcı adımları değişmektedir; adımlar sağlayıcı bazında ayrılabilir.</t>
         </is>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="Q21" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="S21" s="11" t="inlineStr">
+      <c r="R21" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>Eylül</t>
+        </is>
+      </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>Eylül</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="V21" s="6" t="inlineStr">
+      <c r="U21" s="6" t="inlineStr">
         <is>
           <t>E-posta hesabı açmak veya telefona kurmak isteyen kişi adım arıyor.</t>
         </is>
@@ -16632,36 +16501,28 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>1. Android ve iOS için güncelleme adımları adım adım anlatılır
-2. Güncelleme görünmüyorsa yapılabilecekler açıklanır
-3. Güncelleme öncesi yedekleme adım adım anlatılır
-4. Depolama alanı yetmediğinde izlenecek yol açıklanır</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
           <t>Tek soruya odaklı içeriktir; yanıt açılış paragrafında verilip adımlar numaralı listeye alınabilir.</t>
         </is>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="Q22" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="S22" s="11" t="inlineStr">
+      <c r="R22" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
       <c r="T22" s="7" t="inlineStr">
         <is>
-          <t>Kasım</t>
-        </is>
-      </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="V22" s="6" t="inlineStr">
+      <c r="U22" s="6" t="inlineStr">
         <is>
           <t>Telefonunu güncellemek isteyen kişi adım arıyor; tek soruya odaklı kısa içerik yeterli oluyor.</t>
         </is>
@@ -16735,7 +16596,7 @@
         <is>
           <t>TON: Kısayol rehberi. Kısayol tablosu yazının merkezinde, sayfanın üst yarısında.
 H2 · Nedir: Kısaca; ekran görüntüsü ve ekran kaydı farkı tek ayrımla. PAA'daki "ekran kaydı hangi tuş" sorusu bu ayrımda karşılanır.
-H2 · Windows: Üç H3, her yöntem için ne zaman tercih edileceği tek satırla.
+H2 · Windows: Üç H3 (PrtScn tuşu, Windows+Shift+S, Ekran Alıntısı Aracı), her yöntem için ne zaman tercih edileceği tek satırla.
 H2 · Mac: Kısayollar madde listesi.
 H2 · Kısayollar Tablosu: İşletim sistemi / iş / kısayol / kaydedilen yer sütunları; alıntılanabilir blok.
 H2 · Nereye Kaydedilir: Pano ve dosya ayrımı; varsayılan klasörler.
@@ -16809,37 +16670,28 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>1. Windows'ta üç yöntem: PrtScn, Windows+Shift+S, Ekran Alıntısı Aracı açıklanır
-2. Mac kısayolları adım adım anlatılır
-3. Kısayol tablosu verilir
-4. Görüntünün kaydedildiği klasör açıklanır
-5. Ekran görüntüsünün düzenlenmesi ve paylaşılması adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
           <t>Kısayol tablosu alıntılanabilir bir blok olarak kurgulanabilir.</t>
         </is>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="Q23" s="9" t="n">
         <v>83</v>
       </c>
-      <c r="S23" s="11" t="inlineStr">
+      <c r="R23" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>Aralık</t>
+        </is>
+      </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>Aralık</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="V23" s="6" t="inlineStr">
+      <c r="U23" s="6" t="inlineStr">
         <is>
           <t>Bilgisayarda ekran görüntüsü almak isteyen kişi kısayol arıyor; Windows ve Mac karşılığını tek sayfada veren içerik sonuç sayfasında sınırlı.</t>
         </is>
@@ -16969,36 +16821,28 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>1. ESIM ile fiziksel SIM farkı açıklanır
-2. ESIM destekleyen telefon listesi verilir
-3. Mevcut hattı eSIM'e taşıma adımları adım adım anlatılır
-4. Yurt dışında eSIM kullanımı açıklanır</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
           <t>Destekleyen cihaz listesi hızla değişmektedir; güncellenebilir tablo olarak kurgulanabilir.</t>
         </is>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="Q24" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="R24" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>Eylül</t>
+        </is>
+      </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>Eylül</t>
-        </is>
-      </c>
-      <c r="U24" s="7" t="inlineStr">
-        <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="V24" s="6" t="inlineStr">
+      <c r="U24" s="6" t="inlineStr">
         <is>
           <t>eSIM'e geçmek isteyen kişi önce telefonunun desteklediğini doğrulamak istiyor. Cihaz listesi sayfayı vazgeçilmez kılıyor. Telco AI Overview takip listesi: bu başlık Telco AI Overview takibindeki eSIM kümesiyle örtüşmektedir ve Öncelik 2 bandından yükseltilmiştir; ayrıntısı 06B sekmesindedir.</t>
         </is>
@@ -17179,36 +17023,28 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>1. Sıfırlama öncesi yedekleme adım adım anlatılır
-2. Android'de fabrika ayarlarına dönüş adımları adım adım anlatılır
-3. IPhone'da sıfırlama adımları adım adım anlatılır
-4. Sıfırlama sonrası hesap doğrulama adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
           <t>Veri kaybı uyarısının açılışta verilmesi önerilir; adımlar cihaz sürümüne göre değiştiğinden güncellenme tarihi görünür tutulabilir.</t>
         </is>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="Q25" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="S25" s="11" t="inlineStr">
+      <c r="R25" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>Ağustos</t>
+        </is>
+      </c>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>Ağustos</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="V25" s="6" t="inlineStr">
+      <c r="U25" s="6" t="inlineStr">
         <is>
           <t>Telefonunu satmadan ya da sorun gidermek için sıfırlamak isteyen kişi adım arıyor.</t>
         </is>
@@ -17352,35 +17188,28 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>1. Deepfake tanımı açıklanır
-2. Sahte içeriğin anlaşılma yolları adım adım anlatılır
-3. Dolandırıcılık senaryoları açıklanır</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
           <t>Blogun mevcut yapay zeka içerikleriyle iç bağlantı kurulabilir.</t>
         </is>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="Q26" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="S26" s="11" t="inlineStr">
+      <c r="R26" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>Ocak</t>
+        </is>
+      </c>
       <c r="T26" s="7" t="inlineStr">
         <is>
-          <t>Ocak</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="V26" s="6" t="inlineStr">
+      <c r="U26" s="6" t="inlineStr">
         <is>
           <t>Sahte video ve ses içeriklerinin nasıl anlaşıldığını merak eden kişi tanım arıyor.</t>
         </is>
@@ -17448,7 +17277,7 @@
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>TON: Karar yardımı; satış yapmaz.
-H2 · Ne Demek: Kısaca.
+H2 · Ne Demek: Kısaca; yenileme yetkisinin yönetmelikle tanımlı olduğu ve yetkili yenileme merkezi kavramı tek cümleyle verilir.
 H2 · İkinci El Farkı: Dört satırlık tablo. PAA'da "2. el mi yenilenmiş mi" doğrudan soruluyor; tablo bu soruyu karşılar.
 H2 · Kalite Sınıfları: Tablo; A/B/C ve G1/G2 adlandırmaları açıklanır, satıcıya göre değişebildiği notu. Soru kelimesi taramasında sınıf bazlı aramalar ayrı hacim taşıyor.
 H2 · Garanti Süresi: Kısaca; kapsam ve dışında kalanlar.
@@ -17511,36 +17340,28 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>1. Yenilenmiş telefon tanımı ve yasal çerçeve açıklanır
-2. Kalite sınıfları açıklanır
-3. Garanti süresi ve kapsamı açıklanır
-4. Satın almadan önce kontrol listesi verilir</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
           <t>Yenilenmiş cihaz satışıyla ilgili güncel mevzuat doğrulanmalıdır.</t>
         </is>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="Q27" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="S27" s="11" t="inlineStr">
+      <c r="R27" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>Ağustos</t>
+        </is>
+      </c>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>Ağustos</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
           <t>Haziran</t>
         </is>
       </c>
-      <c r="V27" s="6" t="inlineStr">
+      <c r="U27" s="6" t="inlineStr">
         <is>
           <t>Yenilenmiş telefon almayı düşünen kişi garanti ve kalite soruyor. Satın alma kararına yakın bir arama.</t>
         </is>
@@ -17691,35 +17512,28 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>1. AirTag tanımı ve çalışma mantığı açıklanır
-2. Kurulum adımları adım adım anlatılır
-3. Takip edilme uyarısı ve gizlilik açıklanır</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
           <t>Gizlilik uyarısı bölümü rakip sayfalarda eksiktir.</t>
         </is>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="Q28" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="S28" s="11" t="inlineStr">
+      <c r="R28" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>Haziran</t>
+        </is>
+      </c>
       <c r="T28" s="7" t="inlineStr">
         <is>
-          <t>Haziran</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
           <t>Nisan</t>
         </is>
       </c>
-      <c r="V28" s="6" t="inlineStr">
+      <c r="U28" s="6" t="inlineStr">
         <is>
           <t>Eşya takip cihazı alan veya takip edildiğinden şüphelenen kişi bilgi arıyor.</t>
         </is>
@@ -17835,35 +17649,28 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>1. OEM tanımı açıklanır
-2. OEM ürün ile orijinal ürün farkı açıklanır
-3. Telefon ve donanımda OEM kullanımı açıklanır</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
           <t>Tanım sorgusudur; kısa ve alıntılanabilir bir açılış paragrafı önerilmektedir.</t>
         </is>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="Q29" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="S29" s="11" t="inlineStr">
+      <c r="R29" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>Kasım</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="V29" s="6" t="inlineStr">
+      <c r="U29" s="6" t="inlineStr">
         <is>
           <t>Ürün açıklamalarında gördüğü OEM ifadesinin anlamını arayan kişi tek cümlelik yanıt istiyor.</t>
         </is>
@@ -17994,35 +17801,28 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>1. KVKK tanımı açıklanır
-2. Kişisel veri türleri açıklanır
-3. Veri sahibinin hakları açıklanır</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
           <t>Hukuki metin niteliği taşımamalıdır; bilgilendirme sınırında kalınmalıdır.</t>
         </is>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="Q30" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="S30" s="11" t="inlineStr">
+      <c r="R30" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>Aralık</t>
+        </is>
+      </c>
       <c r="T30" s="7" t="inlineStr">
         <is>
-          <t>Aralık</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
-        <is>
           <t>Ekim</t>
         </is>
       </c>
-      <c r="V30" s="6" t="inlineStr">
+      <c r="U30" s="6" t="inlineStr">
         <is>
           <t>Kişisel verilerle ilgili hakkını merak eden kişi kısa açıklama arıyor.</t>
         </is>
@@ -18193,36 +17993,28 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>1. Isınmanın yaygın nedenleri açıklanır
-2. Şarj sırasında ısınma adım adım anlatılır
-3. Isınmayı azaltan ayarlar açıklanır
-4. Servise götürmeyi gerektiren durumlar açıklanır</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
           <t>Tek soruya odaklı içeriktir; yanıt açılış paragrafında üç nedenle özetlenebilir.</t>
         </is>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="Q31" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="S31" s="11" t="inlineStr">
+      <c r="R31" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>Temmuz</t>
+        </is>
+      </c>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>Temmuz</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
           <t>Mayıs</t>
         </is>
       </c>
-      <c r="V31" s="6" t="inlineStr">
+      <c r="U31" s="6" t="inlineStr">
         <is>
           <t>Telefonu ısınan kişi nedenini ve ne yapacağını soruyor; yanıt kısa ve doğrudan verilebilir.</t>
         </is>
@@ -18354,36 +18146,29 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>1. Müşteri numarasının tanımı açıklanır
-2. Faturada ve uygulamada nereden görüldüğü açıklanır
-3. Abone numarası ile farkı açıklanır</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
           <t>Tanım sorgusudur; hesap ekranına yönlendirme ürün ekibiyle doğrulanmalıdır.
 NİYET NOTU: Jenerik 'müşteri numarası' hacminin büyük bölümü bankacılık aramalarından gelmektedir (yapı kredi 2.400, banka 600, firma 500, halkbank 450, ziraat ve akbank 250'şer). Banka markası içeren aramalar bu yazıyla karşılanamaz. Yazı bankacılık ve telekom kullanımını ayrı bölümlerde ele almakta, aynı ayrımı rakip blog da yapmaktadır.</t>
         </is>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="Q32" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="S32" s="11" t="inlineStr">
+      <c r="R32" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>Mart</t>
+        </is>
+      </c>
       <c r="T32" s="7" t="inlineStr">
         <is>
-          <t>Mart</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V32" s="6" t="inlineStr">
+      <c r="U32" s="6" t="inlineStr">
         <is>
           <t>Müşteri numarasını nereden bulacağını arayan abone kısa ve net yanıt bekliyor.</t>
         </is>
@@ -18531,36 +18316,28 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>1. OTP tanımı açıklanır
-2. SMS ile gelen tek kullanımlık şifrenin nasıl çalıştığı açıklanır
-3. OTP paylaşımının riskleri açıklanır
-4. OTP gelmediğinde yapılabilecekler açıklanır</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
           <t>Dolandırıcılık uyarısı bölümü marka güvenliği açısından değerli olabilir.</t>
         </is>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="Q33" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="S33" s="12" t="inlineStr">
+      <c r="R33" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>Mart</t>
+        </is>
+      </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>Mart</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V33" s="6" t="inlineStr">
+      <c r="U33" s="6" t="inlineStr">
         <is>
           <t>Bankadan ya da uygulamadan gelen OTP ifadesinin ne olduğunu soran kişi kısa yanıt bekliyor.</t>
         </is>
@@ -18669,36 +18446,28 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>1. QLED tanımı açıklanır
-2. QLED ve OLED farkı tablo hâlinde açıklanır
-3. Hangi kullanım için hangisi açıklanır
-4. Parlaklık ve ömür karşılaştırması verilir</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
           <t>Ürün önerisi verilmemesi, bilgi katmanında kalınması önerilir.</t>
         </is>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="Q34" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="S34" s="12" t="inlineStr">
+      <c r="R34" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
       <c r="T34" s="7" t="inlineStr">
         <is>
-          <t>Kasım</t>
-        </is>
-      </c>
-      <c r="U34" s="7" t="inlineStr">
-        <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="V34" s="6" t="inlineStr">
+      <c r="U34" s="6" t="inlineStr">
         <is>
           <t>Televizyon alacak kişi QLED ile OLED arasındaki farkı soruyor.</t>
         </is>
@@ -18803,36 +18572,28 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>1. Medya okuryazarlığının tanımı açıklanır
-2. Yanlış bilgiyi ayırt etme adımları adım adım anlatılır
-3. Kaynak doğrulama yöntemleri açıklanır
-4. Çocuklar için ipuçları açıklanır</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
           <t>Blogun dijital güvenlik yazılarıyla bağlantılandırılması konuyu markanın çizgisine oturtabilir.</t>
         </is>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="Q35" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="S35" s="12" t="inlineStr">
+      <c r="R35" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>Eylül</t>
+        </is>
+      </c>
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>Eylül</t>
-        </is>
-      </c>
-      <c r="U35" s="7" t="inlineStr">
-        <is>
           <t>Temmuz</t>
         </is>
       </c>
-      <c r="V35" s="6" t="inlineStr">
+      <c r="U35" s="6" t="inlineStr">
         <is>
           <t>Doğru bilgiyi ayırt etmeyi öğrenmek isteyen kişi tanım ve yöntem arıyor.</t>
         </is>
@@ -18962,37 +18723,29 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>1. TAG teriminin anlamı açıklanır
-2. Sosyal medyada etiketleme adım adım anlatılır
-3. NFC etiketi anlamı açıklanır
-4. Hangi bağlamda hangi anlamın kullanıldığı açıklanır</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
           <t>Kelimenin birden çok anlamı bulunmaktadır; açılışta hangi anlamların ele alındığı belirtilmelidir.
 NİYET NOTU: Jenerik 'tag' hacminin büyük bölümü ulaşım uygulaması (martı tag 6.600, tag taksi 450, tag sürücü 450, tag premium 250) ve takip cihazı (air tag 2.600) aramalarından gelmektedir; skin tag ve Google Tag Manager gibi alan dışı anlamlar da bu hacme dahildir. Yazı, arama hacmine göre sıralanmış anlam bölümleriyle kurgulanmıştır; kümeye atanan hacmin tamamının karşılanması beklenmemelidir.</t>
         </is>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="Q36" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="S36" s="12" t="inlineStr">
+      <c r="R36" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>Ekim</t>
+        </is>
+      </c>
       <c r="T36" s="7" t="inlineStr">
         <is>
-          <t>Ekim</t>
-        </is>
-      </c>
-      <c r="U36" s="7" t="inlineStr">
-        <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="V36" s="6" t="inlineStr">
+      <c r="U36" s="6" t="inlineStr">
         <is>
           <t>TAG kelimesinin karşılığını arayan kişi kısa tanım bekliyor.</t>
         </is>
@@ -19161,35 +18914,28 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>1. Kamerayla karekod okutma adımları adım adım anlatılır
-2. Kamera okutmadığında yapılabilecekler açıklanır
-3. Sahte karekodların ayırt edilmesi adım adım anlatılır</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
           <t>Tek soruya odaklı içeriktir; adımlar numaralı listeye alınabilir.</t>
         </is>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="Q37" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="S37" s="12" t="inlineStr">
+      <c r="R37" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>Ekim</t>
+        </is>
+      </c>
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>Ekim</t>
-        </is>
-      </c>
-      <c r="U37" s="7" t="inlineStr">
-        <is>
           <t>Ağustos</t>
         </is>
       </c>
-      <c r="V37" s="6" t="inlineStr">
+      <c r="U37" s="6" t="inlineStr">
         <is>
           <t>Karekod okutmayı bilmeyen kişi adım arıyor; soru tek ve nettir.</t>
         </is>
@@ -19319,36 +19065,28 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>1. Hat devrinin tanımı açıklanır
-2. Devir için gereken belgeler açıklanır
-3. Devir ücreti açıklanır
-4. Devir sonrası fatura ve taahhüt durumu açıklanır</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
           <t>Ücret ve belge bilgileri değişkendir; ürün ekibiyle doğrulanmalı ve güncellenme tarihi görünür tutulmalıdır.</t>
         </is>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="Q38" s="9" t="n">
         <v>77</v>
       </c>
-      <c r="S38" s="12" t="inlineStr">
+      <c r="R38" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
       <c r="T38" s="7" t="inlineStr">
         <is>
-          <t>Kasım</t>
-        </is>
-      </c>
-      <c r="U38" s="7" t="inlineStr">
-        <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="V38" s="6" t="inlineStr">
+      <c r="U38" s="6" t="inlineStr">
         <is>
           <t>Hattını başkasına devretmek isteyen abone ücreti ve gereken belgeleri arıyor.</t>
         </is>
@@ -19417,7 +19155,7 @@
             </rPr>
             <t>TON: Tanım sorgusu. İlk paragraf tanım, hemen ardından örnek adresin parçalanmış şeması.
 H2 · URL Nedir: Kısaca; açılım parantez içinde. PAA'daki "URL ne demek Türkçe" burada.
-H2 · Bölümleri: Üç H3, örnek adres üzerinden; şema sade metin, görsel yok. Rakip yazı (</t>
+H2 · Bölümleri: Üç H3 (protokol, alan adı, yol), örnek adres üzerinden; şema sade metin, görsel yok. Rakip yazı (</t>
           </r>
           <r>
             <rPr>
@@ -19472,35 +19210,28 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>1. URL tanımı açıklanır
-2. URL bölümleri: protokol, alan adı, yol açıklanır
-3. Güvenli URL'nin nasıl anlaşıldığı açıklanır</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
           <t>Tanım sorgusudur; ilk paragrafta tek cümlelik karşılık ve ardından bölüm şeması önerilir.</t>
         </is>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="Q39" s="9" t="n">
         <v>77</v>
       </c>
-      <c r="S39" s="12" t="inlineStr">
+      <c r="R39" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>Mart</t>
+        </is>
+      </c>
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>Mart</t>
-        </is>
-      </c>
-      <c r="U39" s="7" t="inlineStr">
-        <is>
           <t>Ocak</t>
         </is>
       </c>
-      <c r="V39" s="6" t="inlineStr">
+      <c r="U39" s="6" t="inlineStr">
         <is>
           <t>URL kelimesinin karşılığını arayan kişi kısa tanım bekliyor.</t>
         </is>
@@ -19625,36 +19356,28 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>1. Apple Arcade tanımı açıklanır
-2. Abonelik ücreti ve deneme süresi açıklanır
-3. Hangi cihazlarda çalıştığı açıklanır
-4. Oyunların çevrimdışı oynanabilirliği açıklanır</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
           <t>Ücret bilgisi değişkendir; güncellenme tarihi görünür tutulabilir.</t>
         </is>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="Q40" s="9" t="n">
         <v>76</v>
       </c>
-      <c r="S40" s="12" t="inlineStr">
+      <c r="R40" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>Ocak</t>
+        </is>
+      </c>
       <c r="T40" s="7" t="inlineStr">
         <is>
-          <t>Ocak</t>
-        </is>
-      </c>
-      <c r="U40" s="7" t="inlineStr">
-        <is>
           <t>Kasım</t>
         </is>
       </c>
-      <c r="V40" s="6" t="inlineStr">
+      <c r="U40" s="6" t="inlineStr">
         <is>
           <t>Apple Arcade aboneliğini merak eden kişi kapsamı ve ücreti soruyor.</t>
         </is>
@@ -19770,35 +19493,28 @@
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>1. FreeDOS tanımı açıklanır
-2. Işletim sistemi yüklü olmayan bilgisayarın anlamı açıklanır
-3. Sonrasında yapılabilecekler açıklanır</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
           <t>Blogun işletim sistemi yazısıyla iç bağlantı kurulabilir.</t>
         </is>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="Q41" s="9" t="n">
         <v>73</v>
       </c>
-      <c r="S41" s="12" t="inlineStr">
+      <c r="R41" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>Kasım</t>
+        </is>
+      </c>
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>Kasım</t>
-        </is>
-      </c>
-      <c r="U41" s="7" t="inlineStr">
-        <is>
           <t>Eylül</t>
         </is>
       </c>
-      <c r="V41" s="6" t="inlineStr">
+      <c r="U41" s="6" t="inlineStr">
         <is>
           <t>İşletim sistemi yüklü olmayan bilgisayar alan kişi ne yapacağını arıyor.</t>
         </is>
@@ -19806,8 +19522,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30994,7 +30710,7 @@
         </is>
       </c>
     </row>
-    <row r="425" ht="51" customHeight="1">
+    <row r="425" ht="66" customHeight="1">
       <c r="A425" s="6" t="inlineStr">
         <is>
           <t>Konum Paylaşma ve Numaradan Konum Bulma</t>
@@ -31023,7 +30739,7 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t>Detaylı; üç H3 (WhatsApp, Google Haritalar, iPhone), her biri kısa adım listesi. Rakip yazılar (</t>
+            <t>Detaylı; üç H3 (WhatsApp, Google Haritalar, iPhone'da Mesajlar/iMessage), her biri kısa adım listesi. Rakip yazılar (</t>
           </r>
           <r>
             <rPr>
@@ -32397,7 +32113,7 @@
       </c>
       <c r="D476" s="6" t="inlineStr">
         <is>
-          <t>H2-H4 · Üç kategori</t>
+          <t>H2-H4 · Üç kategori (üretkenlik, güvenlik, alışveriş)</t>
         </is>
       </c>
       <c r="E476" s="6" t="inlineStr">
@@ -34182,7 +33898,7 @@
       </c>
       <c r="E544" s="6" t="inlineStr">
         <is>
-          <t>Üç H3, her yöntem için ne zaman tercih edileceği tek satırla.</t>
+          <t>Üç H3 (PrtScn tuşu, Windows+Shift+S, Ekran Alıntısı Aracı), her yöntem için ne zaman tercih edileceği tek satırla.</t>
         </is>
       </c>
     </row>
@@ -36819,7 +36535,7 @@
       </c>
       <c r="E643" s="6" t="inlineStr">
         <is>
-          <t>Kısaca.</t>
+          <t>Kısaca; yenileme yetkisinin yönetmelikle tanımlı olduğu ve yetkili yenileme merkezi kavramı tek cümleyle verilir.</t>
         </is>
       </c>
     </row>
@@ -44443,7 +44159,7 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t>Üç H3, örnek adres üzerinden; şema sade metin, görsel yok. Rakip yazı (</t>
+            <t>Üç H3 (protokol, alan adı, yol), örnek adres üzerinden; şema sade metin, görsel yok. Rakip yazı (</t>
           </r>
           <r>
             <rPr>
@@ -46630,7 +46346,7 @@
         </is>
       </c>
     </row>
-    <row r="1015" ht="36" customHeight="1">
+    <row r="1015" ht="66" customHeight="1">
       <c r="A1015" s="6" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/web-sitelerinin-altyapisi-hosting-nedir-ne-ise-yarar</t>
@@ -46653,7 +46369,31 @@
       </c>
       <c r="E1015" s="6" t="inlineStr">
         <is>
-          <t>Ziyaretçi bandına göre üç senaryo madde listesi; her senaryoda önerilen tür ve gerekçe. PAA'daki "hosting ücreti nedir" sorusu tutar verilmeden, neye göre değiştiği anlatılarak karşılanır.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Ziyaretçi bandına göre üç senaryo madde listesi; her senaryoda önerilen tür ve gerekçe. Rakip yazı (</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Türk Telekom</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>, 3. sıra) konuyu tek uzun bölümde veriyor ve bizim yazımız 12 ara başlıkla zaten daha ayrıntılı; eksik olan derinlik değil seçim kriteri, bu yüzden bölüm karar yardımı olarak yazılır. PAA'daki "hosting ücreti nedir" sorusu tutar verilmeden, neye göre değiştiği anlatılarak karşılanır.</t>
+          </r>
         </is>
       </c>
     </row>
@@ -48358,7 +48098,7 @@
         </is>
       </c>
     </row>
-    <row r="1080" ht="36" customHeight="1">
+    <row r="1080" ht="51" customHeight="1">
       <c r="A1080" s="6" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/ping-internette-gecikmenin-gercek-nedeni</t>
@@ -48387,7 +48127,7 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t xml:space="preserve">İki H3 (komut satırı, hız testi siteleri), kısa adımlar; oyun içi gösterge tek paragraf. </t>
+            <t xml:space="preserve">İki H3 (komut satırı, hız testi siteleri), kısa adımlar; oyun içi gösterge tek paragraf. Mevcut yazıda ölçüm bölümü var, test adımı yok. Rakip yazının başlığı doğrudan "Ping Testi Nedir? Nasıl Yapılır?"; </t>
           </r>
           <r>
             <rPr>
@@ -48404,7 +48144,7 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t xml:space="preserve"> sıralamayı test aracıyla alıyor; yazı kendi hız testi aracına iç bağlantı verir.</t>
+            <t xml:space="preserve"> sıralamayı test aracıyla alıyor, yazı kendi hız testi aracına iç bağlantı verir.</t>
           </r>
         </is>
       </c>
@@ -51320,7 +51060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -51348,12 +51088,11 @@
     <col width="110" customWidth="1" min="23" max="23"/>
     <col width="58" customWidth="1" min="24" max="24"/>
     <col width="52" customWidth="1" min="25" max="25"/>
-    <col width="58" customWidth="1" min="26" max="26"/>
-    <col width="44" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="50" customWidth="1" min="31" max="31"/>
+    <col width="44" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="50" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -51391,9 +51130,8 @@
       <c r="AB1" s="2" t="n"/>
       <c r="AC1" s="2" t="n"/>
       <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="81" customHeight="1">
+    </row>
+    <row r="2" ht="96" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <r>
@@ -51475,6 +51213,24 @@
               <sz val="10.5"/>
             </rPr>
             <t xml:space="preserve">
+Kurgu sütunu: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Güncelleme yönergesi ayrı bir sütun değildir: eklenecek bölümler, bölümlerin yazıdaki yeri ve gövde düzenlemesi "İçerik Kurgusu ve Yönergesi" sütununda birleştirilmiştir. Kelime yoğunluğu yönergesi ayrı sütunda kalmaktadır.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00FF7B52"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">
 Durum: </t>
           </r>
           <r>
@@ -51516,7 +51272,6 @@
       <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -51549,7 +51304,6 @@
       <c r="AB3" s="2" t="n"/>
       <c r="AC3" s="2" t="n"/>
       <c r="AD3" s="2" t="n"/>
-      <c r="AE3" s="2" t="n"/>
     </row>
     <row r="4" ht="51" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -51727,7 +51481,7 @@
       </c>
       <c r="V4" s="5" t="inlineStr">
         <is>
-          <t>İçerik Kurgusu</t>
+          <t>İçerik Kurgusu ve Yönergesi</t>
         </is>
       </c>
       <c r="W4" s="5" t="inlineStr">
@@ -51747,30 +51501,25 @@
       </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
-          <t>Güncelleme Yönergesi</t>
+          <t>Dikkat Edilecek</t>
         </is>
       </c>
       <c r="AA4" s="5" t="inlineStr">
         <is>
-          <t>Dikkat Edilecek</t>
+          <t>Toplam Aylık Arama</t>
         </is>
       </c>
       <c r="AB4" s="5" t="inlineStr">
         <is>
-          <t>Toplam Aylık Arama</t>
+          <t>Puan</t>
         </is>
       </c>
       <c r="AC4" s="5" t="inlineStr">
         <is>
-          <t>Puan</t>
+          <t>Öncelik</t>
         </is>
       </c>
       <c r="AD4" s="5" t="inlineStr">
-        <is>
-          <t>Öncelik</t>
-        </is>
-      </c>
-      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>Ne Anlama Geliyor</t>
         </is>
@@ -51953,30 +51702,21 @@
       </c>
       <c r="Z5" s="6" t="inlineStr">
         <is>
-          <t>1. 'Windows nedir' sorgusu 1.059 Impression alıyor ancak sayfa 9.7 ortalama sırada kalıyor; Windows, macOS ve Linux için üç ayrı H3 açılıp her birine sürüm adı, tipik kullanıcı profili ve donanım gereksinimi yazılabilir
-2. 'işletim sistemleri sadece bilgisayarlara özgü müdür' sorgusu 646 Impression ile 3.2 sırada geliyor, yani soru soruluyor ama yanıt bölümü yok: telefon, akıllı televizyon, akıllı saat ve araç sistemlerini kapsayan 'İşletim Sistemi Yalnız Bilgisayarlarda mı Bulunur?' başlığı eklenebilir
-3. Mobil tarafta Android ve iOS tek cümlede geçiyor; ikisi ayrı H3 olarak açılıp aralarındaki uygulama mağazası, güncelleme ve donanım farkı üç maddeyle verilebilir
-4. 'bilgisayar işletim sistemleri' ve 'işletim sistemleri nelerdir' kelimeleri gövdede hiç geçmiyor; mevcut 'İşletim Sistemi Çeşitleri Nelerdir?' başlığının açılış cümlesi bu iki kalıbı da karşılayacak biçimde yazılabilir
-5. 'işletim sistemleri hakkında aşağıdakilerden hangisi doğru değildir' sorgusu 4.221 Impression alıyor ve ödev kaynaklı; bu sorguya içerik yazılması önerilmez, ölçüm okunurken hesaba katılması yeterlidir açıklanır</t>
-        </is>
-      </c>
-      <c r="AA5" s="6" t="inlineStr">
-        <is>
           <t>Sürüm adları ve donanım gereksinimleri yıl içinde değişiyor; güncellenme tarihinin görünür tutulması bu yazıda değer taşıyor.</t>
         </is>
       </c>
-      <c r="AB5" s="8" t="n">
+      <c r="AA5" s="8" t="n">
         <v>11870</v>
       </c>
-      <c r="AC5" s="9" t="n">
+      <c r="AB5" s="9" t="n">
         <v>71</v>
       </c>
-      <c r="AD5" s="10" t="inlineStr">
+      <c r="AC5" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AE5" s="6" t="inlineStr">
+      <c r="AD5" s="6" t="inlineStr">
         <is>
           <t>Rakip aynı soruda üçüncü sırada ve yedi kat trafik alıyor. Mobil ve masaüstü ayrımı eksik.</t>
         </is>
@@ -52098,12 +51838,36 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>EKLENECEK BÖLÜMLERİN YERİ: Karşılaştırma tablosu mevcut "Hosting Türleri Nelerdir?" başlığının içine; domain bölümü mevcut fark bölümünün yerine; seçim bölümü sona.
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>EKLENECEK BÖLÜMLERİN YERİ: Karşılaştırma tablosu mevcut "Hosting Türleri Nelerdir?" başlığının içine; domain bölümü mevcut fark bölümünün yerine; seçim bölümü sona.
 H2 · Hosting Türleri Karşılaştırma Tablosu: Sayfa "hosting" sorgusunda 31.2 sırada. Mevcut türler bölümü metin; paylaşımlı, VPS, bulut, adanmış satırlarında kaynak paylaşımı, trafik kapasitesi ve kimin için uygun olduğu sütunlu tabloya çevrilir. Rakip yazı (GoDaddy) her tür için avantaj-dezavantaj çifti veriyor; tabloya iki sütun daha eklenir.
 H2 · Domain ve Hosting Ayrı Ayrı mı Alınır: "domain ve hosting nedir" 4.6 sırada 409 Impression. Tek örnek üzerinden ilişki, ardından doğrudan yanıt: ayrı da birlikte de alınabilir.
-H2 · Küçük İşletme İçin Hangi Hosting: Ziyaretçi bandına göre üç senaryo madde listesi; her senaryoda önerilen tür ve gerekçe. PAA'daki "hosting ücreti nedir" sorusu tutar verilmeden, neye göre değiştiği anlatılarak karşılanır.
+H2 · Küçük İşletme İçin Hangi Hosting: Ziyaretçi bandına göre üç senaryo madde listesi; her senaryoda önerilen tür ve gerekçe. Rakip yazı (</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Türk Telekom</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>, 3. sıra) konuyu tek uzun bölümde veriyor ve bizim yazımız 12 ara başlıkla zaten daha ayrıntılı; eksik olan derinlik değil seçim kriteri, bu yüzden bölüm karar yardımı olarak yazılır. PAA'daki "hosting ücreti nedir" sorusu tutar verilmeden, neye göre değiştiği anlatılarak karşılanır.
 GÖVDE DÜZENLEMESİ: "turkcell host" sorgusu 399 Impression ile 5.1 sırada; markanın barındırma hizmetine tek iç bağlantı.
 DİKKAT: Fiyat verilmez; kapasite ve senaryo üzerinden anlatılır.</t>
+          </r>
         </is>
       </c>
       <c r="W6" s="6" t="inlineStr">
@@ -52155,53 +51919,21 @@
       </c>
       <c r="Z6" s="6" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve">1. Sayfa 'hosting' sorgusunda 31.2 ortalama sırada; bu sorguda ilk sayfaya girebilmek için mevcut 'Hosting Türleri Nelerdir?' başlığı tabloya çevrilebilir: paylaşımlı, VPS, bulut ve adanmış sunucu satırlarında kaynak paylaşımı, tipik trafik kapasitesi ve kimin için uygun olduğu üç sütunda verilir
-2. 'domain ve hosting nedir' sorgusu 4.6 sırada 409 Impression alıyor; mevcut fark bölümü iki cümlede kalıyor, alan adı ile barındırmanın ilişkisi bir örnek üzerinden anlatılıp 'ikisi ayrı ayrı mı alınır' sorusu yanıtlanabilir
-3. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>Türk Telekom</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>'un aynı sorguda 3. sıradaki yazısı 1.239 kelime ve konuyu tek uzun bölümde veriyor; bizim yazımız 12 ara başlıkla daha ayrıntılı, eksik olan derinlik değil seçim kriteri: 'Küçük İşletme İçin Hangi Hosting Seçilir?' başlığı altında aylık ziyaretçi bandına göre üç senaryo eklenebilir
-4. 'turkcell host' sorgusu 399 Impression ile 5.1 sırada geliyor; markanın barındırma hizmetine tek cümlelik bir bağlantı, arama niyetini karşılar açıklanır</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA6" s="6" t="inlineStr">
-        <is>
           <t>Fiyat bilgisi verilmemesi, kapasite ve kullanım senaryosu üzerinden anlatılması önerilir.</t>
         </is>
       </c>
-      <c r="AB6" s="8" t="n">
+      <c r="AA6" s="8" t="n">
         <v>8640</v>
       </c>
-      <c r="AC6" s="9" t="n">
+      <c r="AB6" s="9" t="n">
         <v>71</v>
       </c>
-      <c r="AD6" s="10" t="inlineStr">
+      <c r="AC6" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AE6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t>Bu soruda hosting satan siteler önde. Yazının ilk sıraya çıkması zor; beklenti buna göre kurulmalı.</t>
         </is>
@@ -52498,54 +52230,21 @@
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve">1. 'nfc etiketi nedir' sorgusu 3.835 Impression alıyor ancak sayfa 8.7 sırada ve tek click getiriyor; yazıda NFC etiketi hiç geçmiyor. 'NFC Etiketi Nedir, Ne İşe Yarar?' başlığı altında etiketin ne olduğu, telefona nasıl okutulduğu ve ev otomasyonu gibi kullanım örnekleri verilebilir
-2. 'nfc kart nedir' 832 Impression alıyor; temassız kartın NFC ile ilişkisi ayrı bir H3 olarak açılabilir
-3. 'nfc açma', 'iphone nfc açma', 'apple nfc açma' ve 'nfc özelliği nasıl açılır redmi' kelimelerinin hiçbiri gövdede geçmiyor; mevcut 'NFC Nasıl Açılır ve Kullanılır?' başlığı cihaz bazında üçe ayrılabilir: iPhone, </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>Samsung</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve"> ve Xiaomi/Redmi. Her biri iki-üç adımla anlatılır
-4. 'nfc özelliği olan telefonlar' kelimesi gövdede yok; NFC destekleyen model ailelerini marka bazında listeleyen kısa bir tablo, bu aramayı karşılar açıklanır
-5. 'nfc alanı neresi' aramasının karşılığı da bulunmuyor; NFC anteninin telefonun neresinde olduğu ve nasıl bulunacağı tek paragrafla eklenebilir</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA7" s="6" t="inlineStr">
-        <is>
           <t>Cihaz arayüzleri sürümle değişiyor; adımların model ailesi düzeyinde verilmesi ve güncellenme tarihinin görünür tutulması önerilir.</t>
         </is>
       </c>
-      <c r="AB7" s="8" t="n">
+      <c r="AA7" s="8" t="n">
         <v>145620</v>
       </c>
-      <c r="AC7" s="9" t="n">
+      <c r="AB7" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="AD7" s="10" t="inlineStr">
+      <c r="AC7" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AE7" s="6" t="inlineStr">
+      <c r="AD7" s="6" t="inlineStr">
         <is>
           <t>Sayfa tanımı veriyor ama kullanıcı NFC'yi telefonunda açmaya çalışıyor. Açma adımları eklenirse arama karşılanmış oluyor.</t>
         </is>
@@ -52703,30 +52402,21 @@
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
-          <t>1. 'gemini yapay zeka' sorgusu 92.496 Impression ile 79 click getiriyor ve kelime gövdede hiç geçmiyor; giriş paragrafında ve bir ara başlıkta bu kalıbın kullanılması, sayfanın hâlihazırda göründüğü aramayı güçlendirir açıklanır
-2. 'gemini türkçe' kelimesi de gövdede yok; 'Gemini Türkçe Destekliyor mu?' başlığı altında dil desteği, Türkçe yanıt kalitesi ve arayüz dili üç maddeyle verilebilir
-3. Mevcut 'Gemini ile Bard Arasındaki Fark' bölümü artık geçerliliğini yitiriyor, Bard adı kullanımdan kalktı; bu bölüm 'Gemini ile ChatGPT Arasındaki Fark' karşılaştırmasına çevrilip yanıt kaynağı, görsel üretimi, dosya yükleme ve ücretsiz sürüm sınırları dört satırlık tabloya alınabilir
-4. Ücretsiz ve ücretli sürüm ayrımı yazıda geçmiyor; 'Gemini Ücretsiz mi?' başlığı, sonuç sayfasındaki soru bloğunda da görünen bir arama adım adım anlatılır
-5. Sayfanın Impression'ı jenerik marka aramasından geliyor ve o aramada sonuç sayfasının ilk beş sırası Google'ın kendi adresleri; kazanım kullanım ve karşılaştırma sorularında olduğu için yeni bölümler bu iki eksende kurgulanmalıdır</t>
-        </is>
-      </c>
-      <c r="AA8" s="6" t="inlineStr">
-        <is>
           <t>Yapay zeka ürünlerinde sürüm ve fiyatlandırma sık değişiyor; tablo değerlerinin tarihiyle birlikte verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="AB8" s="8" t="n">
+      <c r="AA8" s="8" t="n">
         <v>77400</v>
       </c>
-      <c r="AC8" s="9" t="n">
+      <c r="AB8" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="AD8" s="10" t="inlineStr">
+      <c r="AC8" s="10" t="inlineStr">
         <is>
           <t>Öncelik 1</t>
         </is>
       </c>
-      <c r="AE8" s="6" t="inlineStr">
+      <c r="AD8" s="6" t="inlineStr">
         <is>
           <t>Yazı altı ayda 16.3 milyon impression alıp 2.125 click getirmiştir. Sorun içerikte değil, jenerik marka aramasının sonuç sayfasında: üst sıralar Google'ın kendi adreslerinde. Kazanım, kullanım ve karşılaştırma sorularında.</t>
         </is>
@@ -52847,7 +52537,7 @@
               <sz val="10.5"/>
             </rPr>
             <t xml:space="preserve">EKLENECEK BÖLÜMLERİN YERİ: Test bölümü mevcut ölçüm bölümünün yerine; değer tablosu tanımın hemen ardına; ping atmak bölümü onun ardına; düşürme bölümü mevcut "Ping Nasıl Düşürülür?" başlığının yerine.
-H2 · Ping Testi Nasıl Yapılır: İki H3 (komut satırı, hız testi siteleri), kısa adımlar; oyun içi gösterge tek paragraf. </t>
+H2 · Ping Testi Nasıl Yapılır: İki H3 (komut satırı, hız testi siteleri), kısa adımlar; oyun içi gösterge tek paragraf. Mevcut yazıda ölçüm bölümü var, test adımı yok. Rakip yazının başlığı doğrudan "Ping Testi Nedir? Nasıl Yapılır?"; </t>
           </r>
           <r>
             <rPr>
@@ -52864,7 +52554,7 @@
               <color rgb="0010332F"/>
               <sz val="10.5"/>
             </rPr>
-            <t xml:space="preserve"> sıralamayı test aracıyla alıyor; yazı kendi hız testi aracına iç bağlantı verir.
+            <t xml:space="preserve"> sıralamayı test aracıyla alıyor, yazı kendi hız testi aracına iç bağlantı verir.
 H2 · İdeal Ping Değerleri Tablosu: "ping nedir" sorgusunda 3.918 Impression'dan 1 click; yanıt sonuç sayfasında veriliyor. Giriş tanımı kısaltılır ve hemen altına değer tablosu (rekabetçi oyun, genel oyun, video görüşme, üzeri) konur; her satırda bağlantı türü. PAA'daki "ping kaç olursa iyi" ve "50 ping iyi mi" soruları tabloyla karşılanır.
 H2 · Ping Atmak Ne Demek: Kısaca.
 H2 · Nasıl Düşürülür: Dört somut adım madde listesi; her adımda beklenen etki. PAA'daki "neden yüksek olur" sorusu bölüm girişinde.
@@ -52940,53 +52630,21 @@
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve">1. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>Türk Telekom</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>'un aynı konudaki yazısının başlığı 'Ping Testi Nedir? Nasıl Yapılır?'; bizim yazımızda ölçüm bölümü var ancak test adımı yok. Komut satırından ping testi, hız testi siteleri ve oyun içi gecikme göstergesi üç adımda anlatılabilir
-2. 'ping nedir' sorgusunda sayfa 3.7 ortalama sırada ancak 3.918 Impression'dan yalnız 1 click geliyor; bu tablo sonuç sayfasının üstünde yanıtın verildiğine işaret ediyor. Giriş paragrafındaki tanımın tek cümleye indirilmesi ve ideal ping aralığının hemen altına tablo olarak konması, alıntılanma ihtimalini artırır açıklanır
-3. Ideal değer aralığı yazıda cümle içinde geçiyor; 'Rekabetçi oyun 0-30 ms, genel oyun 30-60 ms, video görüşme 60-100 ms, üzeri sorunlu' satırlarından oluşan bir tablo hem okuyucuya hem AI yanıtına daha kullanışlı geliyor açıklanır
-4. Mevcut 'Ping Nasıl Düşürülür?' bölümü genel öneriler içeriyor; kablo bağlantısı, 5 GHz bant, arka plan indirmeleri ve sunucu bölgesi seçimi gibi dört somut adıma çevrilebilir</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA9" s="6" t="inlineStr">
-        <is>
           <t>Ping değerleri bağlantı türüne göre değişiyor; verilen aralıkların hangi bağlantı için geçerli olduğu belirtilmelidir.</t>
         </is>
       </c>
-      <c r="AB9" s="8" t="n">
+      <c r="AA9" s="8" t="n">
         <v>4400</v>
       </c>
-      <c r="AC9" s="9" t="n">
+      <c r="AB9" s="9" t="n">
         <v>66</v>
       </c>
-      <c r="AD9" s="11" t="inlineStr">
+      <c r="AC9" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AE9" s="6" t="inlineStr">
+      <c r="AD9" s="6" t="inlineStr">
         <is>
           <t>Rakip bir test aracıyla sıralanıyor. Yazıya araç bağlantısı eklenmesi aradaki farkı açıklıyor.</t>
         </is>
@@ -53212,29 +52870,21 @@
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
-          <t>1. Sayfa 'type c' sorgusunda 91.693 Impression alıyor ancak 7.8 sırada ve 23 click getiriyor; bu aramada sonuç sayfasının üst sıraları ürün listeleyen mağazalarda olduğu için bilgi tarafında kazanım 'type c nedir' ve 'type c ne demek' kalıplarında. İkisi de gövdede birer kez geçiyor, ara başlığa taşınabilir
-2. USB-C sürümleri yazıda ayrışmıyor; USB 3.2, USB4 ve Thunderbolt 4 için veri hızı, güç aktarımı ve görüntü desteği sütunlarından oluşan bir tablo, konunun en çok karıştırılan yanını karşılar açıklanır
-3. 'Type-C ile hızlı şarj nasıl çalışır' sorusu yazıda yanıtlanmıyor; Power Delivery kademelerinin watt değerleriyle verildiği bir bölüm eklenebilir
-4. Yazıda kablo kalitesinin aktarım hızını nasıl sınırladığı geçmiyor; aynı görünen iki kablonun farklı hız vermesi somut bir okuyucu sorusu ve tek paragrafla karşılanabilir</t>
-        </is>
-      </c>
-      <c r="AA10" s="6" t="inlineStr">
-        <is>
           <t>Ürün önerisi verilmemesi, teknik ayrım katmanında kalınması önerilir; şarj aleti ve kablo aramaları mağaza sayfalarına aittir.</t>
         </is>
       </c>
-      <c r="AB10" s="8" t="n">
+      <c r="AA10" s="8" t="n">
         <v>3400</v>
       </c>
-      <c r="AC10" s="9" t="n">
+      <c r="AB10" s="9" t="n">
         <v>65</v>
       </c>
-      <c r="AD10" s="11" t="inlineStr">
+      <c r="AC10" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AE10" s="6" t="inlineStr">
+      <c r="AD10" s="6" t="inlineStr">
         <is>
           <t>Arayan kişi çoğunlukla kablo satın alıyor. Yazı bunu karşılamıyor; ürün sayfasına köprü kurmak daha gerçekçi.</t>
         </is>
@@ -53499,59 +53149,27 @@
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve">1. 'adsl vdsl farkı' sorgusu 3.3 ortalama sırada 3.014 Impression alıyor; bu sayfanın en güçlü olduğu alan ve mevcut karşılaştırma metin hâlinde. Hız, mesafe hassasiyeti, upload oranı ve tipik kullanım satırlarından oluşan bir tabloya çevrilmesi ilk üçe girme ihtimalini artırır açıklanır
-2. 'vdsl modem nedir' sorgusu 1.878 Impression ile 4.5 sırada; modem tarafı yazıda tek cümlede geçiyor. 'VDSL Modem Nedir, ADSL Modemden Farkı Ne?' başlığı altında uyumluluk ve değişim gerekliliği anlatılabilir
-3. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>Vodafone</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>'un aynı sorguda 1. sıradaki yazısı 485 kelime; bizim yazımız 1.092 kelimeyle iki katı ve daha kapsamlı. Eksik olan uzunluk değil, tablo ve karar yardımı: 'Hangi Bağlantı Kimin İçin Uygun?' bölümü, ev tipi ve kullanıcı sayısına göre üç senaryo verebilir
-4. Fiber bağlantı yazıda karşılaştırmaya girmiyor; ADSL, VDSL ve fiber üçlüsünün aynı tabloda görülmesi, okuyucunun asıl sorusunu karşılar açıklanır</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA11" s="6" t="inlineStr">
-        <is>
           <t>Altyapı ve hız değerleri bölgeye göre değişiyor; sorgulama işleminin ilgili hizmet sayfasından yapılabileceği belirtilebilir.</t>
         </is>
       </c>
-      <c r="AB11" s="8" t="n">
+      <c r="AA11" s="8" t="n">
         <v>7160</v>
       </c>
-      <c r="AC11" s="9" t="n">
+      <c r="AB11" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="AD11" s="11" t="inlineStr">
+      <c r="AC11" s="11" t="inlineStr">
         <is>
           <t>Öncelik 2</t>
         </is>
       </c>
-      <c r="AE11" s="6" t="inlineStr">
+      <c r="AD11" s="6" t="inlineStr">
         <is>
           <t>Rakipler aynı konuyu daha ayrıntılı işliyor ve dört kat trafik alıyor. Karşılaştırma tablosu farkı kapatabilir.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="263.5" customHeight="1">
+    <row r="12" ht="209.5" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/blog/internette-dalgalanma-neden-olur-jitter-degeri-nedir</t>
@@ -53748,54 +53366,21 @@
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve">1. 'jitter kaç olmalı' sorgusu 866 Impression ile 7.8 sırada geliyor ve yazıda ideal aralık tablo hâlinde verilmiyor; 'Video görüşme için 30 ms altı, oyun için 20 ms altı, akış için 50 ms altı' satırlarından oluşan bir tablo bu aramayı karşılar açıklanır
-2. 'net jitter ne demek' ve 'net jitter' sorguları birlikte 1.869 Impression alıyor; terim gövdede geçmiyor. Ağ tarafındaki kullanımın ayrı bir cümleyle açıklanması yeterli açıklanır
-3. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>Vodafone</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>'un 1. sıradaki yazısında ana terim 55 kez geçiyor, bizim yazımızda 23; sayının artırılması değil, jitter kelimesinin ara başlıklarda ve tablo satırlarında da kullanılması öneriliyor açıklanır
-4. Jitter ile ping ve paket kaybı arasındaki fark yazıda net ayrılmıyor; üç kavramı yan yana koyan kısa bir bölüm, konunun en sık karıştırılan yanını kapatıyor açıklanır
-5. Jitter düşürme adımları yazıda genel kalıyor; kablolu bağlantı, QoS ayarı, arka plan trafiği ve modem konumu dört somut maddeye çevrilebilir</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
           <t>Değerler bağlantı türüne ve uygulamaya göre değişiyor; aralıkların hangi senaryo için geçerli olduğu yazılmalıdır.</t>
         </is>
       </c>
-      <c r="AB12" s="8" t="n">
+      <c r="AA12" s="8" t="n">
         <v>5350</v>
       </c>
-      <c r="AC12" s="9" t="n">
+      <c r="AB12" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="AD12" s="12" t="inlineStr">
+      <c r="AC12" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AE12" s="6" t="inlineStr">
+      <c r="AD12" s="6" t="inlineStr">
         <is>
           <t>Rakip aynı formatta ama birinci sırada. Fark, ideal değer tablosu gibi somut bilgide.</t>
         </is>
@@ -54041,53 +53626,21 @@
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve">1. 'wifi 6 modem' ve 'wifi 6 modem nedir' sorguları birlikte 4.132 Impression alıyor, sayfa 7.8 ve 4.1 sıralarda; modem tarafı yazıda tek cümlede geçiyor. 'Wi-Fi 6 Modem Nedir, Hangi Modemler Destekler?' başlığı altında uyumluluk, cihaz tarafı gereksinimi ve mevcut modemin yeterli olup olmadığı anlatılabilir
-2. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>Vodafone</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>'un aynı sorguda 1. sıradaki yazısı 1.639 kelime ve 14 ara başlık taşıyor; bizim yazımız 1.146 kelime ve 11 başlık. Fark, kapsam derinliğinde: OFDMA, MU-MIMO ve Target Wake Time gibi teknik kavramların her biri iki cümlelik alt bölüme çevrilebilir
-3. Wi-Fi 6E ve Wi-Fi 7 yazıda geçmiyor; okuyucu Wi-Fi 6 ile Wi-Fi 6E ayrımını sık soruyor, kısa bir bölüm bu boşluğu kapatır açıklanır
-4. 'wifi 6 nedir' sorgusunda sayfa 3.4 sırada ve 48 click alıyor; giriş paragrafındaki tanımın tek cümleye indirilmesi, ilk üçe yaklaşmak için en düşük maliyetli adım açıklanır</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
           <t>Cihaz uyumluluğu marka ve model ailesine göre değişiyor; genel ifadeler yerine standart adları kullanılmalıdır.</t>
         </is>
       </c>
-      <c r="AB13" s="8" t="n">
+      <c r="AA13" s="8" t="n">
         <v>3370</v>
       </c>
-      <c r="AC13" s="9" t="n">
+      <c r="AB13" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="AD13" s="12" t="inlineStr">
+      <c r="AC13" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AE13" s="6" t="inlineStr">
+      <c r="AD13" s="6" t="inlineStr">
         <is>
           <t>Birinci sırada olmasına rağmen tıklama gelmiyor, çünkü arayan kişi modem arıyor. Cihaz bağlantısı eklenmeli.</t>
         </is>
@@ -54267,53 +53820,21 @@
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t xml:space="preserve">1. 'mac adresi sorgulama' ve 'mac adresi nasıl bulunur' sorguları birlikte 1.800 Impression alıyor, sayfa 6.7 ve 9.2 sıralarda; adım anlatımı yazıda cihaz bazında ayrışmıyor. Windows, macOS, Android, iPhone ve modem arayüzü için beş kısa adım listesi eklenebilir
-2. 'mac adresinden cihaz bulma' sorgusu 237 Impression alıyor ve yazıda karşılığı yok; MAC adresinin ilk üç baytının üretici kodunu taşıdığı ve bu bilgiyle cihaz markasının bulunabildiği tek paragrafla açıklanabilir
-3. 'telefon mac adresi nedir' sorgusu 4.3 sırada 283 Impression alıyor; telefonlarda rastgele MAC kullanımının (privacy MAC) neden devreye girdiği, okuyucunun gördüğü değerin neden değiştiğini açıklar açıklanır
-4. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>Vodafone</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="0010332F"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>'un 3. sıradaki yazısında ana terim 46 kez geçiyor, bizim yazımızda 43; kelime sıklığı yeterli, eksik olan cihaz bazında adım anlatımı açıklanır</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
           <t>Rastgele MAC kullanımı işletim sistemi sürümüne göre değişiyor; adımların sürüm bilgisiyle verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="AB14" s="8" t="n">
+      <c r="AA14" s="8" t="n">
         <v>2510</v>
       </c>
-      <c r="AC14" s="9" t="n">
+      <c r="AB14" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="AD14" s="12" t="inlineStr">
+      <c r="AC14" s="12" t="inlineStr">
         <is>
           <t>Öncelik 3</t>
         </is>
       </c>
-      <c r="AE14" s="6" t="inlineStr">
+      <c r="AD14" s="6" t="inlineStr">
         <is>
           <t>Kullanıcı MAC adresini bulmaya çalışıyor. Cihaz bazında adım eklenirse sayfa aramayı karşılıyor.</t>
         </is>
@@ -54321,8 +53842,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:AE1"/>
-    <mergeCell ref="A2:AE2"/>
+    <mergeCell ref="A2:AD2"/>
+    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>

--- a/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
+++ b/Turkcell_Blog_Yeni_Trafik_Kaynaklari_Fikir_Hacim.xlsx
@@ -64286,7 +64286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -64295,7 +64295,8 @@
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -64310,8 +64311,9 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="51" customHeight="1">
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="81" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <r>
@@ -64339,6 +64341,24 @@
               <sz val="10.5"/>
             </rPr>
             <t xml:space="preserve">
+Brief: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="0010332F"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t>Bu sekme kelime listesidir, öneri listesi değildir. Karşılık gelen önerinin ayrıntılı brief'i (alt başlıklar, içerik kurgusu ve yönergesi, cevaplanması gereken sorular, iç link önerileri) 02 Blog Önerileri sekmesindedir; Brief sütunu ilgili satırı göstermektedir. Bölüm bölüm okunabilir dökümü 02B Kurgu ve FAQ Detayı sekmesinde bulunmaktadır. Karşılığı çizgiyle işaretli kelimeler öneri kapsamına alınmamıştır: bir bölümü ürün ya da mağaza aramasıdır, bir bölümü blogun kapsamı dışındadır.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00FF7B52"/>
+              <sz val="10.5"/>
+            </rPr>
+            <t xml:space="preserve">
 Yöntem: </t>
           </r>
           <r>
@@ -64357,6 +64377,7 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -64366,6 +64387,7 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4" ht="21" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -64400,6 +64422,11 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
+          <t>Brief</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
           <t>Not</t>
         </is>
       </c>
@@ -64433,7 +64460,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64468,7 +64500,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64503,7 +64540,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 5</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -64538,7 +64580,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64573,7 +64620,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64608,7 +64660,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 12</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -64643,7 +64700,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64678,7 +64740,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64713,7 +64780,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64748,7 +64820,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64783,7 +64860,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 11</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -64818,7 +64900,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64853,7 +64940,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -64888,7 +64980,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 8</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -64923,7 +65020,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 8</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -64958,7 +65060,12 @@
           <t>eSIM nedir, nasıl aktive edilir?</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 24</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -64993,7 +65100,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65028,7 +65140,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 6</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65063,7 +65180,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65098,7 +65220,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65133,7 +65260,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 8</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65168,7 +65300,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65203,7 +65340,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 6</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65238,7 +65380,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65273,7 +65420,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 6</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65308,7 +65460,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 5</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65343,7 +65500,12 @@
           <t>Taahhüt ne demek?</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 17</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65378,7 +65540,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65413,7 +65580,12 @@
           <t>Spam ne demek?</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 14</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65448,7 +65620,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 10</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65483,7 +65660,12 @@
           <t>AirTag nedir ve nasıl çalışır?</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 28</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65518,7 +65700,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65553,7 +65740,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 23</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65588,7 +65780,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65623,7 +65820,12 @@
           <t>Yenilenmiş telefon ne demek?</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 27</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65658,7 +65860,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 18</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65693,7 +65900,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65728,7 +65940,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 7</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65763,7 +65980,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 15</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65798,7 +66020,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 6</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65833,7 +66060,12 @@
           <t>E-imza nasıl alınır?</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 16</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65868,7 +66100,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -65903,7 +66140,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 6</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65938,7 +66180,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 13</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -65973,7 +66220,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 7</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66008,7 +66260,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66043,7 +66300,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66078,7 +66340,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66113,7 +66380,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66148,7 +66420,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66183,7 +66460,12 @@
           <t>KVKK nedir?</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 30</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66218,7 +66500,12 @@
           <t>Deepfake nedir ve nasıl anlaşılır?</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 26</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66253,7 +66540,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66288,7 +66580,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66323,7 +66620,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66358,7 +66660,12 @@
           <t>Telefon neden ısınır?</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 31</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66393,7 +66700,12 @@
           <t>eSIM nedir, nasıl aktive edilir?</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 24</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66428,7 +66740,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66463,7 +66780,12 @@
           <t>Deepfake nedir ve nasıl anlaşılır?</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 26</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66498,7 +66820,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 10</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66533,7 +66860,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 9</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66568,7 +66900,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 6</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66603,7 +66940,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66638,7 +66980,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 6</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66673,7 +67020,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66708,7 +67060,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 5</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66743,7 +67100,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 10</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66778,7 +67140,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -66813,7 +67180,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 7</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66848,7 +67220,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 8</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66883,7 +67260,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 5</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66918,7 +67300,12 @@
           <t>Apple Arcade nedir?</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 40</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66953,7 +67340,12 @@
           <t>Medya okuryazarlığı nedir?</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 35</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -66988,7 +67380,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 11</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67023,7 +67420,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67058,7 +67460,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 11</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67093,7 +67500,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67128,7 +67540,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67163,7 +67580,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67198,7 +67620,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 19</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67233,7 +67660,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67268,7 +67700,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 9</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67303,7 +67740,12 @@
           <t>OEM ne demek?</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 29</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67338,7 +67780,12 @@
           <t>FreeDOS nedir?</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 41</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67373,7 +67820,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 15</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67408,7 +67860,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67443,7 +67900,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67478,7 +67940,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67513,7 +67980,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67548,7 +68020,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67583,7 +68060,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 13</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67618,7 +68100,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67653,7 +68140,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67688,7 +68180,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67723,7 +68220,12 @@
           <t>TAG nedir?</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 36</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67758,7 +68260,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 7</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67793,7 +68300,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" s="6" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 5</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67828,7 +68340,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G102" s="6" t="inlineStr">
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67863,7 +68380,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G103" s="6" t="inlineStr">
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -67898,7 +68420,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G104" s="6" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 12</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67933,7 +68460,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G105" s="6" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 7</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -67968,7 +68500,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 18</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -68003,7 +68540,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G107" s="6" t="inlineStr">
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68038,7 +68580,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68073,7 +68620,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G109" s="6" t="inlineStr">
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68108,7 +68660,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G110" s="6" t="inlineStr">
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68143,7 +68700,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G111" s="6" t="inlineStr">
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68178,7 +68740,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G112" s="6" t="inlineStr">
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68213,7 +68780,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G113" s="6" t="inlineStr">
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68248,7 +68820,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G114" s="6" t="inlineStr">
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 6</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -68283,7 +68860,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" s="6" t="inlineStr">
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 7</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -68318,7 +68900,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G116" s="6" t="inlineStr">
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 11</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -68353,7 +68940,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G117" s="6" t="inlineStr">
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68388,7 +68980,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="6" t="inlineStr">
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68423,7 +69020,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G119" s="6" t="inlineStr">
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 23</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -68458,7 +69060,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G120" s="6" t="inlineStr">
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68493,7 +69100,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" s="6" t="inlineStr">
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68528,7 +69140,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="6" t="inlineStr">
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
         <is>
           <t>AI Overview yanıtına kaynak olabilecek kısa bölüm değerlendirilebilir</t>
         </is>
@@ -68563,7 +69180,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 5</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -68598,7 +69220,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G124" s="6" t="inlineStr">
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>02 Blog Önerileri · satır 7</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
         <is>
           <t>Öneri kapsamındadır</t>
         </is>
@@ -68606,8 +69233,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
